--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:50</t>
+          <t>2026-05-31 17:52:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:50</t>
+          <t>2026-05-31 17:52:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.509469</v>
+        <v>4.5098476</v>
       </c>
       <c r="G3" t="n">
-        <v>30249</v>
+        <v>30253</v>
       </c>
       <c r="H3" t="n">
-        <v>8927</v>
+        <v>8936</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3222</v>
+        <v>3226</v>
       </c>
       <c r="O3" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P3" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="Q3" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="R3" t="n">
-        <v>25912</v>
+        <v>25923</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:50</t>
+          <t>2026-05-31 17:52:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.6241043</v>
       </c>
       <c r="G4" t="n">
-        <v>24843</v>
+        <v>24844</v>
       </c>
       <c r="H4" t="n">
         <v>5570</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2550034</v>
+        <v>2550442</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7184</v>
+        <v>7185</v>
       </c>
       <c r="O4" t="n">
         <v>841</v>
@@ -739,7 +739,7 @@
         <v>1164</v>
       </c>
       <c r="R4" t="n">
-        <v>14775</v>
+        <v>14776</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:50</t>
+          <t>2026-05-31 17:52:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5310044</v>
+        <v>4.529258</v>
       </c>
       <c r="G5" t="n">
-        <v>25690</v>
+        <v>25696</v>
       </c>
       <c r="H5" t="n">
-        <v>9570</v>
+        <v>9576</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>647517</v>
+        <v>647574</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -807,13 +807,13 @@
         <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>761</v>
+        <v>784</v>
       </c>
       <c r="Q5" t="n">
         <v>1693</v>
       </c>
       <c r="R5" t="n">
-        <v>20955</v>
+        <v>20937</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:50</t>
+          <t>2026-05-31 17:52:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -849,7 +849,7 @@
         <v>445</v>
       </c>
       <c r="H6" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:50</t>
+          <t>2026-05-31 17:52:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.8111587</v>
+        <v>4.795745</v>
       </c>
       <c r="G7" t="n">
-        <v>3077</v>
+        <v>3079</v>
       </c>
       <c r="H7" t="n">
         <v>1150</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>417681</v>
+        <v>417917</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -954,10 +954,10 @@
         <v>12</v>
       </c>
       <c r="Q7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R7" t="n">
-        <v>2892</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:51</t>
+          <t>2026-05-31 17:52:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1700935</v>
+        <v>4.17603</v>
       </c>
       <c r="G8" t="n">
-        <v>5999</v>
+        <v>6000</v>
       </c>
       <c r="H8" t="n">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>428316</v>
+        <v>428344</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>986</v>
+        <v>976</v>
       </c>
       <c r="O8" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P8" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R8" t="n">
-        <v>4450</v>
+        <v>4459</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:51</t>
+          <t>2026-05-31 17:52:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.0186915</v>
+        <v>3.9906542</v>
       </c>
       <c r="G9" t="n">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H9" t="n">
         <v>490</v>
@@ -1089,14 +1089,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
         <v>237</v>
       </c>
       <c r="O9" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="P9" t="n">
         <v>79</v>
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>859</v>
+        <v>848</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:51</t>
+          <t>2026-05-31 17:52:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>85366</v>
+        <v>85410</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:51</t>
+          <t>2026-05-31 17:52:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6876945</v>
+        <v>4.6879377</v>
       </c>
       <c r="G11" t="n">
-        <v>14498</v>
+        <v>14502</v>
       </c>
       <c r="H11" t="n">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>248807</v>
+        <v>248834</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="O11" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P11" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="Q11" t="n">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="R11" t="n">
-        <v>12668</v>
+        <v>12673</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:51</t>
+          <t>2026-05-31 17:52:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>4634</v>
       </c>
       <c r="H12" t="n">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>347136</v>
+        <v>347156</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:51</t>
+          <t>2026-05-31 17:52:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21659</v>
+        <v>21664</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:52</t>
+          <t>2026-05-31 17:52:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1430,10 +1430,10 @@
         <v>3.4195933</v>
       </c>
       <c r="G14" t="n">
-        <v>11939</v>
+        <v>11942</v>
       </c>
       <c r="H14" t="n">
-        <v>4656</v>
+        <v>4657</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1211174</v>
+        <v>1211419</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4159</v>
+        <v>4160</v>
       </c>
       <c r="O14" t="n">
         <v>308</v>
@@ -1471,7 +1471,7 @@
         <v>419</v>
       </c>
       <c r="R14" t="n">
-        <v>6608</v>
+        <v>6610</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:52</t>
+          <t>2026-05-31 17:53:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.3284457</v>
       </c>
       <c r="G15" t="n">
-        <v>3857</v>
+        <v>3859</v>
       </c>
       <c r="H15" t="n">
         <v>1557</v>
@@ -1529,11 +1529,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1545,7 +1545,7 @@
         <v>101</v>
       </c>
       <c r="R15" t="n">
-        <v>2091</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-30 17:54:52</t>
+          <t>2026-05-31 17:53:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.727402</v>
+        <v>4.7277684</v>
       </c>
       <c r="G16" t="n">
-        <v>46621</v>
+        <v>46622</v>
       </c>
       <c r="H16" t="n">
         <v>2923</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="O16" t="n">
         <v>320</v>
@@ -1616,10 +1616,10 @@
         <v>718</v>
       </c>
       <c r="Q16" t="n">
-        <v>2300</v>
+        <v>2287</v>
       </c>
       <c r="R16" t="n">
-        <v>41278</v>
+        <v>41292</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-31 17:52:27</t>
+          <t>2026-06-01 17:42:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="G2" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H2" t="n">
         <v>154</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36337</v>
+        <v>36427</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -588,10 +588,10 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R2" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-31 17:52:28</t>
+          <t>2026-06-01 17:42:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5098476</v>
+        <v>4.51003</v>
       </c>
       <c r="G3" t="n">
-        <v>30253</v>
+        <v>30267</v>
       </c>
       <c r="H3" t="n">
-        <v>8936</v>
+        <v>8938</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2344161</v>
+        <v>2345813</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>550</v>
       </c>
       <c r="R3" t="n">
-        <v>25923</v>
+        <v>25937</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-31 17:52:28</t>
+          <t>2026-06-01 17:42:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6241043</v>
+        <v>3.6239371</v>
       </c>
       <c r="G4" t="n">
         <v>24844</v>
       </c>
       <c r="H4" t="n">
-        <v>5570</v>
+        <v>5571</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7185</v>
+        <v>7197</v>
       </c>
       <c r="O4" t="n">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="P4" t="n">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="Q4" t="n">
-        <v>1164</v>
+        <v>1152</v>
       </c>
       <c r="R4" t="n">
-        <v>14776</v>
+        <v>14785</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-31 17:52:28</t>
+          <t>2026-06-01 17:42:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.529258</v>
+        <v>4.5284657</v>
       </c>
       <c r="G5" t="n">
-        <v>25696</v>
+        <v>25705</v>
       </c>
       <c r="H5" t="n">
-        <v>9576</v>
+        <v>9583</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>647574</v>
+        <v>647777</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="O5" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P5" t="n">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="Q5" t="n">
-        <v>1693</v>
+        <v>1697</v>
       </c>
       <c r="R5" t="n">
-        <v>20937</v>
+        <v>20933</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-31 17:52:28</t>
+          <t>2026-06-01 17:42:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="G6" t="n">
         <v>445</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>93410</v>
+        <v>94027</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
         <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-31 17:52:28</t>
+          <t>2026-06-01 17:42:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.795745</v>
+        <v>4.7923727</v>
       </c>
       <c r="G7" t="n">
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="H7" t="n">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>417917</v>
+        <v>418206</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         <v>12</v>
       </c>
       <c r="Q7" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="R7" t="n">
-        <v>2881</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-31 17:52:28</t>
+          <t>2026-06-01 17:42:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.17603</v>
+        <v>4.17757</v>
       </c>
       <c r="G8" t="n">
-        <v>6000</v>
+        <v>6001</v>
       </c>
       <c r="H8" t="n">
         <v>2229</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>428344</v>
+        <v>428470</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="O8" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P8" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R8" t="n">
-        <v>4459</v>
+        <v>4464</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-31 17:52:29</t>
+          <t>2026-06-01 17:42:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,7 +1064,7 @@
         <v>3.9906542</v>
       </c>
       <c r="G9" t="n">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H9" t="n">
         <v>490</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>174428</v>
+        <v>174510</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-31 17:52:29</t>
+          <t>2026-06-01 17:42:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87</v>
+        <v>3.8811882</v>
       </c>
       <c r="G10" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H10" t="n">
         <v>224</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>85410</v>
+        <v>85488</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="R10" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-31 17:52:29</t>
+          <t>2026-06-01 17:42:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1212,7 +1212,7 @@
         <v>4.6879377</v>
       </c>
       <c r="G11" t="n">
-        <v>14502</v>
+        <v>14512</v>
       </c>
       <c r="H11" t="n">
         <v>688</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>248834</v>
+        <v>248956</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="O11" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P11" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q11" t="n">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="R11" t="n">
-        <v>12673</v>
+        <v>12681</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-31 17:52:29</t>
+          <t>2026-06-01 17:42:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.5853019</v>
+        <v>2.5811517</v>
       </c>
       <c r="G12" t="n">
-        <v>4634</v>
+        <v>4635</v>
       </c>
       <c r="H12" t="n">
         <v>1915</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>347156</v>
+        <v>347253</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2566</v>
+        <v>2571</v>
       </c>
       <c r="O12" t="n">
         <v>133</v>
@@ -1323,7 +1323,7 @@
         <v>205</v>
       </c>
       <c r="R12" t="n">
-        <v>1568</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-31 17:52:30</t>
+          <t>2026-06-01 17:42:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21664</v>
+        <v>21672</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-31 17:52:30</t>
+          <t>2026-06-01 17:42:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4195933</v>
+        <v>3.4326568</v>
       </c>
       <c r="G14" t="n">
-        <v>11942</v>
+        <v>11950</v>
       </c>
       <c r="H14" t="n">
-        <v>4657</v>
+        <v>4658</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1211419</v>
+        <v>1212317</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4160</v>
+        <v>4132</v>
       </c>
       <c r="O14" t="n">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="P14" t="n">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q14" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="R14" t="n">
-        <v>6610</v>
+        <v>6657</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:02</t>
+          <t>2026-06-01 17:42:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.3284457</v>
       </c>
       <c r="G15" t="n">
-        <v>3859</v>
+        <v>3860</v>
       </c>
       <c r="H15" t="n">
         <v>1557</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>385618</v>
+        <v>385825</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1545,7 +1545,7 @@
         <v>101</v>
       </c>
       <c r="R15" t="n">
-        <v>2092</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-31 17:53:02</t>
+          <t>2026-06-01 17:42:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1578,10 +1578,10 @@
         <v>4.7277684</v>
       </c>
       <c r="G16" t="n">
-        <v>46622</v>
+        <v>46618</v>
       </c>
       <c r="H16" t="n">
-        <v>2923</v>
+        <v>2925</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>547440</v>
+        <v>548092</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>2287</v>
       </c>
       <c r="R16" t="n">
-        <v>41292</v>
+        <v>41288</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:54</t>
+          <t>2026-06-01 20:49:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:55</t>
+          <t>2026-06-01 20:49:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.51003</v>
+        <v>4.508726</v>
       </c>
       <c r="G3" t="n">
-        <v>30267</v>
+        <v>30268</v>
       </c>
       <c r="H3" t="n">
-        <v>8938</v>
+        <v>8939</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3226</v>
+        <v>3236</v>
       </c>
       <c r="O3" t="n">
         <v>269</v>
@@ -665,7 +665,7 @@
         <v>550</v>
       </c>
       <c r="R3" t="n">
-        <v>25937</v>
+        <v>25928</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:55</t>
+          <t>2026-06-01 20:49:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2550442</v>
+        <v>2551646</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:55</t>
+          <t>2026-06-01 20:49:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5284657</v>
+        <v>4.527511</v>
       </c>
       <c r="G5" t="n">
-        <v>25705</v>
+        <v>25706</v>
       </c>
       <c r="H5" t="n">
-        <v>9583</v>
+        <v>9584</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1999</v>
+        <v>2008</v>
       </c>
       <c r="O5" t="n">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="P5" t="n">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="Q5" t="n">
-        <v>1697</v>
+        <v>1705</v>
       </c>
       <c r="R5" t="n">
-        <v>20933</v>
+        <v>20923</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:55</t>
+          <t>2026-06-01 20:49:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:56</t>
+          <t>2026-06-01 20:49:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:56</t>
+          <t>2026-06-01 20:49:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:56</t>
+          <t>2026-06-01 20:49:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1067,7 +1067,7 @@
         <v>1212</v>
       </c>
       <c r="H9" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:56</t>
+          <t>2026-06-01 20:49:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:57</t>
+          <t>2026-06-01 20:49:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:57</t>
+          <t>2026-06-01 20:49:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:57</t>
+          <t>2026-06-01 20:49:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:58</t>
+          <t>2026-06-01 20:49:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4326568</v>
+        <v>3.4312096</v>
       </c>
       <c r="G14" t="n">
-        <v>11950</v>
+        <v>11951</v>
       </c>
       <c r="H14" t="n">
         <v>4658</v>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4132</v>
+        <v>4137</v>
       </c>
       <c r="O14" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P14" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q14" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="R14" t="n">
-        <v>6657</v>
+        <v>6653</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:58</t>
+          <t>2026-06-01 20:49:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-01 17:42:58</t>
+          <t>2026-06-01 20:49:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7277684</v>
+        <v>4.7278333</v>
       </c>
       <c r="G16" t="n">
-        <v>46618</v>
+        <v>46620</v>
       </c>
       <c r="H16" t="n">
         <v>2925</v>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="O16" t="n">
         <v>320</v>
       </c>
       <c r="P16" t="n">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="Q16" t="n">
         <v>2287</v>
       </c>
       <c r="R16" t="n">
-        <v>41288</v>
+        <v>41291</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:42</t>
+          <t>2026-06-02 19:59:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>3.96</v>
       </c>
       <c r="G2" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H2" t="n">
         <v>154</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36427</v>
+        <v>36429</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
       <c r="R2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:42</t>
+          <t>2026-06-02 19:59:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.508726</v>
+        <v>4.506292</v>
       </c>
       <c r="G3" t="n">
-        <v>30268</v>
+        <v>30278</v>
       </c>
       <c r="H3" t="n">
-        <v>8939</v>
+        <v>8942</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2345813</v>
+        <v>2346390</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3236</v>
+        <v>3248</v>
       </c>
       <c r="O3" t="n">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="P3" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="R3" t="n">
-        <v>25928</v>
+        <v>25918</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:42</t>
+          <t>2026-06-02 19:59:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6239371</v>
+        <v>3.6267974</v>
       </c>
       <c r="G4" t="n">
-        <v>24844</v>
+        <v>24848</v>
       </c>
       <c r="H4" t="n">
         <v>5571</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2551646</v>
+        <v>2551652</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7197</v>
+        <v>7177</v>
       </c>
       <c r="O4" t="n">
         <v>828</v>
@@ -736,10 +736,10 @@
         <v>876</v>
       </c>
       <c r="Q4" t="n">
-        <v>1152</v>
+        <v>1169</v>
       </c>
       <c r="R4" t="n">
-        <v>14785</v>
+        <v>14794</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:42</t>
+          <t>2026-06-02 19:59:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.527511</v>
+        <v>4.5288506</v>
       </c>
       <c r="G5" t="n">
-        <v>25706</v>
+        <v>25722</v>
       </c>
       <c r="H5" t="n">
-        <v>9584</v>
+        <v>9591</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>647777</v>
+        <v>647952</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -804,16 +804,16 @@
         <v>2008</v>
       </c>
       <c r="O5" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P5" t="n">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="Q5" t="n">
-        <v>1705</v>
+        <v>1695</v>
       </c>
       <c r="R5" t="n">
-        <v>20923</v>
+        <v>20956</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:43</t>
+          <t>2026-06-02 19:59:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>94027</v>
+        <v>94313</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:43</t>
+          <t>2026-06-02 19:59:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7923727</v>
+        <v>4.7941175</v>
       </c>
       <c r="G7" t="n">
-        <v>3080</v>
+        <v>3082</v>
       </c>
       <c r="H7" t="n">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>418206</v>
+        <v>418502</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -957,7 +957,7 @@
         <v>51</v>
       </c>
       <c r="R7" t="n">
-        <v>2870</v>
+        <v>2874</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:43</t>
+          <t>2026-06-02 19:59:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -990,7 +990,7 @@
         <v>4.17757</v>
       </c>
       <c r="G8" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="H8" t="n">
         <v>2229</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>428470</v>
+        <v>428543</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>234</v>
       </c>
       <c r="R8" t="n">
-        <v>4464</v>
+        <v>4465</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:43</t>
+          <t>2026-06-02 19:59:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.9906542</v>
+        <v>3.953271</v>
       </c>
       <c r="G9" t="n">
         <v>1212</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>174510</v>
+        <v>174569</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="O9" t="n">
         <v>33</v>
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>849</v>
+        <v>837</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:44</t>
+          <t>2026-06-02 19:59:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8811882</v>
+        <v>3.8921568</v>
       </c>
       <c r="G10" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="H10" t="n">
         <v>224</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>85488</v>
+        <v>85576</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="R10" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:44</t>
+          <t>2026-06-02 19:59:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6879377</v>
+        <v>4.68629</v>
       </c>
       <c r="G11" t="n">
-        <v>14512</v>
+        <v>14525</v>
       </c>
       <c r="H11" t="n">
         <v>688</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="O11" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P11" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="Q11" t="n">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="R11" t="n">
-        <v>12681</v>
+        <v>12690</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:44</t>
+          <t>2026-06-02 19:59:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>347253</v>
+        <v>347396</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:44</t>
+          <t>2026-06-02 19:59:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:45</t>
+          <t>2026-06-02 19:59:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4312096</v>
+        <v>3.4370983</v>
       </c>
       <c r="G14" t="n">
-        <v>11951</v>
+        <v>11955</v>
       </c>
       <c r="H14" t="n">
-        <v>4658</v>
+        <v>4660</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4137</v>
+        <v>4116</v>
       </c>
       <c r="O14" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="P14" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="Q14" t="n">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="R14" t="n">
-        <v>6653</v>
+        <v>6673</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:45</t>
+          <t>2026-06-02 19:59:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.3284457</v>
       </c>
       <c r="G15" t="n">
-        <v>3860</v>
+        <v>3861</v>
       </c>
       <c r="H15" t="n">
         <v>1557</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>385825</v>
+        <v>386009</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-01 20:49:45</t>
+          <t>2026-06-02 19:59:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7278333</v>
+        <v>4.72652</v>
       </c>
       <c r="G16" t="n">
-        <v>46620</v>
+        <v>46631</v>
       </c>
       <c r="H16" t="n">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>548092</v>
+        <v>548095</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,16 +1607,16 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1999</v>
+        <v>2018</v>
       </c>
       <c r="O16" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P16" t="n">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="Q16" t="n">
-        <v>2287</v>
+        <v>2283</v>
       </c>
       <c r="R16" t="n">
         <v>41291</v>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:54</t>
+          <t>2026-06-03 20:13:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36429</v>
+        <v>36465</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:55</t>
+          <t>2026-06-03 20:13:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.506292</v>
+        <v>4.501299</v>
       </c>
       <c r="G3" t="n">
-        <v>30278</v>
+        <v>30286</v>
       </c>
       <c r="H3" t="n">
-        <v>8942</v>
+        <v>8945</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3248</v>
+        <v>3292</v>
       </c>
       <c r="O3" t="n">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="P3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q3" t="n">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="R3" t="n">
-        <v>25918</v>
+        <v>25880</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:55</t>
+          <t>2026-06-03 20:13:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6267974</v>
+        <v>3.6276944</v>
       </c>
       <c r="G4" t="n">
-        <v>24848</v>
+        <v>24851</v>
       </c>
       <c r="H4" t="n">
         <v>5571</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7177</v>
+        <v>7174</v>
       </c>
       <c r="O4" t="n">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="P4" t="n">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="Q4" t="n">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="R4" t="n">
-        <v>14794</v>
+        <v>14802</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:55</t>
+          <t>2026-06-03 20:13:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5288506</v>
+        <v>4.52464</v>
       </c>
       <c r="G5" t="n">
-        <v>25722</v>
+        <v>25737</v>
       </c>
       <c r="H5" t="n">
-        <v>9591</v>
+        <v>9593</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>647952</v>
+        <v>648210</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2008</v>
+        <v>2042</v>
       </c>
       <c r="O5" t="n">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="P5" t="n">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="Q5" t="n">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="R5" t="n">
-        <v>20956</v>
+        <v>20943</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:55</t>
+          <t>2026-06-03 20:13:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>94313</v>
+        <v>94556</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:55</t>
+          <t>2026-06-03 20:13:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7941175</v>
+        <v>4.7875</v>
       </c>
       <c r="G7" t="n">
-        <v>3082</v>
+        <v>3084</v>
       </c>
       <c r="H7" t="n">
         <v>1152</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>418502</v>
+        <v>418833</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R7" t="n">
-        <v>2874</v>
+        <v>2865</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:56</t>
+          <t>2026-06-03 20:13:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -993,7 +993,7 @@
         <v>6002</v>
       </c>
       <c r="H8" t="n">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>428543</v>
+        <v>428625</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:56</t>
+          <t>2026-06-03 20:13:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>174569</v>
+        <v>174639</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:56</t>
+          <t>2026-06-03 20:13:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,11 +1149,11 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>85576</v>
+        <v>85681</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.8.7</t>
+          <t>0.8.9</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>May 9, 2026</t>
+          <t>May 22, 2026</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:56</t>
+          <t>2026-06-03 20:13:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.68629</v>
+        <v>4.685803</v>
       </c>
       <c r="G11" t="n">
-        <v>14525</v>
+        <v>14531</v>
       </c>
       <c r="H11" t="n">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>248956</v>
+        <v>249006</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="O11" t="n">
         <v>145</v>
@@ -1250,10 +1250,10 @@
         <v>235</v>
       </c>
       <c r="Q11" t="n">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="R11" t="n">
-        <v>12690</v>
+        <v>12693</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:56</t>
+          <t>2026-06-03 20:13:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1286,7 +1286,7 @@
         <v>2.5811517</v>
       </c>
       <c r="G12" t="n">
-        <v>4635</v>
+        <v>4634</v>
       </c>
       <c r="H12" t="n">
         <v>1915</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>347396</v>
+        <v>347397</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="O12" t="n">
         <v>133</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:56</t>
+          <t>2026-06-03 20:13:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21672</v>
+        <v>21680</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:57</t>
+          <t>2026-06-03 20:13:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4370983</v>
+        <v>3.4393382</v>
       </c>
       <c r="G14" t="n">
-        <v>11955</v>
+        <v>11961</v>
       </c>
       <c r="H14" t="n">
-        <v>4660</v>
+        <v>4662</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4116</v>
+        <v>4111</v>
       </c>
       <c r="O14" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P14" t="n">
         <v>439</v>
@@ -1471,7 +1471,7 @@
         <v>416</v>
       </c>
       <c r="R14" t="n">
-        <v>6673</v>
+        <v>6683</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:57</t>
+          <t>2026-06-03 20:13:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>386009</v>
+        <v>386202</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-02 19:59:57</t>
+          <t>2026-06-03 20:13:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.72652</v>
+        <v>4.7257266</v>
       </c>
       <c r="G16" t="n">
-        <v>46631</v>
+        <v>46637</v>
       </c>
       <c r="H16" t="n">
-        <v>2926</v>
+        <v>2928</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>548095</v>
+        <v>548450</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="O16" t="n">
         <v>319</v>
       </c>
       <c r="P16" t="n">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="Q16" t="n">
-        <v>2283</v>
+        <v>2291</v>
       </c>
       <c r="R16" t="n">
-        <v>41291</v>
+        <v>41281</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:04</t>
+          <t>2026-06-04 19:10:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36465</v>
+        <v>36509</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:04</t>
+          <t>2026-06-04 19:10:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.501299</v>
+        <v>4.4990726</v>
       </c>
       <c r="G3" t="n">
-        <v>30286</v>
+        <v>30291</v>
       </c>
       <c r="H3" t="n">
-        <v>8945</v>
+        <v>8947</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2346390</v>
+        <v>2348402</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3292</v>
+        <v>3304</v>
       </c>
       <c r="O3" t="n">
         <v>269</v>
       </c>
       <c r="P3" t="n">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="Q3" t="n">
         <v>561</v>
       </c>
       <c r="R3" t="n">
-        <v>25880</v>
+        <v>25862</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:05</t>
+          <t>2026-06-04 19:10:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6276944</v>
+        <v>3.6267974</v>
       </c>
       <c r="G4" t="n">
-        <v>24851</v>
+        <v>24853</v>
       </c>
       <c r="H4" t="n">
-        <v>5571</v>
+        <v>5570</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2551652</v>
+        <v>2554474</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7174</v>
+        <v>7179</v>
       </c>
       <c r="O4" t="n">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="P4" t="n">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="Q4" t="n">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="R4" t="n">
-        <v>14802</v>
+        <v>14797</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:05</t>
+          <t>2026-06-04 19:10:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.52464</v>
+        <v>4.526087</v>
       </c>
       <c r="G5" t="n">
-        <v>25737</v>
+        <v>25744</v>
       </c>
       <c r="H5" t="n">
-        <v>9593</v>
+        <v>9597</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>648210</v>
+        <v>648604</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2042</v>
+        <v>2036</v>
       </c>
       <c r="O5" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P5" t="n">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="Q5" t="n">
-        <v>1694</v>
+        <v>1689</v>
       </c>
       <c r="R5" t="n">
-        <v>20943</v>
+        <v>20963</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:06</t>
+          <t>2026-06-04 19:10:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>94556</v>
+        <v>95360</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:06</t>
+          <t>2026-06-04 19:10:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -919,7 +919,7 @@
         <v>3084</v>
       </c>
       <c r="H7" t="n">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>418833</v>
+        <v>419307</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:06</t>
+          <t>2026-06-04 19:10:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.17757</v>
+        <v>4.1791043</v>
       </c>
       <c r="G8" t="n">
         <v>6002</v>
       </c>
       <c r="H8" t="n">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>428625</v>
+        <v>429049</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="O8" t="n">
         <v>144</v>
@@ -1031,7 +1031,7 @@
         <v>234</v>
       </c>
       <c r="R8" t="n">
-        <v>4465</v>
+        <v>4467</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:06</t>
+          <t>2026-06-04 19:10:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.953271</v>
+        <v>3.9906542</v>
       </c>
       <c r="G9" t="n">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H9" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>174639</v>
+        <v>174753</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="O9" t="n">
         <v>33</v>
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>837</v>
+        <v>848</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:07</t>
+          <t>2026-06-04 19:10:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>3.8921568</v>
       </c>
       <c r="G10" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H10" t="n">
         <v>224</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>85681</v>
+        <v>86025</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="R10" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:07</t>
+          <t>2026-06-04 19:10:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.685803</v>
+        <v>4.6831913</v>
       </c>
       <c r="G11" t="n">
-        <v>14531</v>
+        <v>14538</v>
       </c>
       <c r="H11" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>249006</v>
+        <v>249196</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O11" t="n">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="Q11" t="n">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="R11" t="n">
-        <v>12693</v>
+        <v>12690</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:08</t>
+          <t>2026-06-04 19:10:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.5811517</v>
+        <v>2.6057441</v>
       </c>
       <c r="G12" t="n">
-        <v>4634</v>
+        <v>4640</v>
       </c>
       <c r="H12" t="n">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>347397</v>
+        <v>347646</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2570</v>
+        <v>2543</v>
       </c>
       <c r="O12" t="n">
         <v>133</v>
       </c>
       <c r="P12" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="Q12" t="n">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="R12" t="n">
-        <v>1564</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:08</t>
+          <t>2026-06-04 19:10:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21680</v>
+        <v>21695</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:08</t>
+          <t>2026-06-04 19:10:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4393382</v>
+        <v>3.4379025</v>
       </c>
       <c r="G14" t="n">
-        <v>11961</v>
+        <v>11972</v>
       </c>
       <c r="H14" t="n">
         <v>4662</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1212317</v>
+        <v>1214683</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4111</v>
+        <v>4118</v>
       </c>
       <c r="O14" t="n">
         <v>307</v>
       </c>
       <c r="P14" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q14" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="R14" t="n">
-        <v>6683</v>
+        <v>6684</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:08</t>
+          <t>2026-06-04 19:10:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3284457</v>
+        <v>3.3401759</v>
       </c>
       <c r="G15" t="n">
-        <v>3861</v>
+        <v>3865</v>
       </c>
       <c r="H15" t="n">
         <v>1557</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>386202</v>
+        <v>386516</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1449</v>
+        <v>1438</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1545,7 +1545,7 @@
         <v>101</v>
       </c>
       <c r="R15" t="n">
-        <v>2093</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-03 20:13:09</t>
+          <t>2026-06-04 19:10:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7257266</v>
+        <v>4.7252126</v>
       </c>
       <c r="G16" t="n">
-        <v>46637</v>
+        <v>46638</v>
       </c>
       <c r="H16" t="n">
         <v>2928</v>
@@ -1589,11 +1589,11 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>548450</v>
+        <v>549411</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.1</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1603,11 +1603,11 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>May 25, 2026</t>
+          <t>Jun 4, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2026</v>
+        <v>2036</v>
       </c>
       <c r="O16" t="n">
         <v>319</v>
@@ -1616,10 +1616,10 @@
         <v>715</v>
       </c>
       <c r="Q16" t="n">
-        <v>2291</v>
+        <v>2278</v>
       </c>
       <c r="R16" t="n">
-        <v>41281</v>
+        <v>41286</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:54</t>
+          <t>2026-06-05 18:53:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.96</v>
+        <v>3.97</v>
       </c>
       <c r="G2" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H2" t="n">
         <v>154</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36509</v>
+        <v>36569</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -588,10 +588,10 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R2" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:54</t>
+          <t>2026-06-05 18:53:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4990726</v>
+        <v>4.4994445</v>
       </c>
       <c r="G3" t="n">
-        <v>30291</v>
+        <v>30306</v>
       </c>
       <c r="H3" t="n">
-        <v>8947</v>
+        <v>8949</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3304</v>
+        <v>3298</v>
       </c>
       <c r="O3" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P3" t="n">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="R3" t="n">
-        <v>25862</v>
+        <v>25873</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:54</t>
+          <t>2026-06-05 18:53:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6267974</v>
+        <v>3.6281047</v>
       </c>
       <c r="G4" t="n">
-        <v>24853</v>
+        <v>24856</v>
       </c>
       <c r="H4" t="n">
         <v>5570</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7179</v>
+        <v>7163</v>
       </c>
       <c r="O4" t="n">
         <v>828</v>
       </c>
       <c r="P4" t="n">
-        <v>876</v>
+        <v>893</v>
       </c>
       <c r="Q4" t="n">
         <v>1169</v>
       </c>
       <c r="R4" t="n">
-        <v>14797</v>
+        <v>14798</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:54</t>
+          <t>2026-06-05 18:53:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.526087</v>
+        <v>4.5245333</v>
       </c>
       <c r="G5" t="n">
-        <v>25744</v>
+        <v>25758</v>
       </c>
       <c r="H5" t="n">
-        <v>9597</v>
+        <v>9605</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>648604</v>
+        <v>649026</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="O5" t="n">
         <v>256</v>
       </c>
       <c r="P5" t="n">
-        <v>794</v>
+        <v>815</v>
       </c>
       <c r="Q5" t="n">
-        <v>1689</v>
+        <v>1699</v>
       </c>
       <c r="R5" t="n">
-        <v>20963</v>
+        <v>20947</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:55</t>
+          <t>2026-06-05 18:53:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.59</v>
       </c>
       <c r="G6" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H6" t="n">
         <v>160</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O6" t="n">
         <v>7</v>
@@ -883,7 +883,7 @@
         <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:55</t>
+          <t>2026-06-05 18:53:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>419307</v>
+        <v>419727</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:55</t>
+          <t>2026-06-05 18:53:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1791043</v>
+        <v>4.180633</v>
       </c>
       <c r="G8" t="n">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="H8" t="n">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="O8" t="n">
         <v>144</v>
@@ -1031,7 +1031,7 @@
         <v>234</v>
       </c>
       <c r="R8" t="n">
-        <v>4467</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:55</t>
+          <t>2026-06-05 18:53:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.9906542</v>
+        <v>4.0280375</v>
       </c>
       <c r="G9" t="n">
         <v>1211</v>
       </c>
       <c r="H9" t="n">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="O9" t="n">
         <v>33</v>
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>848</v>
+        <v>860</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:55</t>
+          <t>2026-06-05 18:53:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:55</t>
+          <t>2026-06-05 18:53:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6831913</v>
+        <v>4.6818886</v>
       </c>
       <c r="G11" t="n">
-        <v>14538</v>
+        <v>14544</v>
       </c>
       <c r="H11" t="n">
         <v>690</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="Q11" t="n">
         <v>709</v>
       </c>
       <c r="R11" t="n">
-        <v>12690</v>
+        <v>12696</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:56</t>
+          <t>2026-06-05 18:53:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6057441</v>
+        <v>2.6535432</v>
       </c>
       <c r="G12" t="n">
-        <v>4640</v>
+        <v>4646</v>
       </c>
       <c r="H12" t="n">
         <v>1917</v>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2543</v>
+        <v>2487</v>
       </c>
       <c r="O12" t="n">
         <v>133</v>
       </c>
       <c r="P12" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q12" t="n">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1598</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:56</t>
+          <t>2026-06-05 18:53:52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21695</v>
+        <v>21700</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:56</t>
+          <t>2026-06-05 18:53:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4379025</v>
+        <v>3.4442396</v>
       </c>
       <c r="G14" t="n">
-        <v>11972</v>
+        <v>11978</v>
       </c>
       <c r="H14" t="n">
-        <v>4662</v>
+        <v>4664</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4118</v>
+        <v>4095</v>
       </c>
       <c r="O14" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P14" t="n">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="Q14" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="R14" t="n">
-        <v>6684</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:56</t>
+          <t>2026-06-05 18:53:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.3401759</v>
       </c>
       <c r="G15" t="n">
-        <v>3865</v>
+        <v>3866</v>
       </c>
       <c r="H15" t="n">
         <v>1557</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1545,7 +1545,7 @@
         <v>101</v>
       </c>
       <c r="R15" t="n">
-        <v>2107</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-04 19:10:56</t>
+          <t>2026-06-05 18:53:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7252126</v>
+        <v>4.7254715</v>
       </c>
       <c r="G16" t="n">
-        <v>46638</v>
+        <v>46643</v>
       </c>
       <c r="H16" t="n">
         <v>2928</v>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="O16" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P16" t="n">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Q16" t="n">
-        <v>2278</v>
+        <v>2276</v>
       </c>
       <c r="R16" t="n">
-        <v>41286</v>
+        <v>41295</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:51</t>
+          <t>2026-06-06 17:58:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:51</t>
+          <t>2026-06-06 17:58:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4994445</v>
+        <v>4.5007405</v>
       </c>
       <c r="G3" t="n">
-        <v>30306</v>
+        <v>30312</v>
       </c>
       <c r="H3" t="n">
-        <v>8949</v>
+        <v>8952</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2348402</v>
+        <v>2349070</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -649,11 +649,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>May 20, 2026</t>
+          <t>Jun 4, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3298</v>
+        <v>3288</v>
       </c>
       <c r="O3" t="n">
         <v>268</v>
@@ -665,7 +665,7 @@
         <v>560</v>
       </c>
       <c r="R3" t="n">
-        <v>25873</v>
+        <v>25888</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:51</t>
+          <t>2026-06-06 17:58:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6281047</v>
+        <v>3.6257348</v>
       </c>
       <c r="G4" t="n">
-        <v>24856</v>
+        <v>24860</v>
       </c>
       <c r="H4" t="n">
         <v>5570</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7163</v>
+        <v>7175</v>
       </c>
       <c r="O4" t="n">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="P4" t="n">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="Q4" t="n">
-        <v>1169</v>
+        <v>1183</v>
       </c>
       <c r="R4" t="n">
-        <v>14798</v>
+        <v>14775</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:51</t>
+          <t>2026-06-06 17:58:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5245333</v>
+        <v>4.529105</v>
       </c>
       <c r="G5" t="n">
-        <v>25758</v>
+        <v>25771</v>
       </c>
       <c r="H5" t="n">
-        <v>9605</v>
+        <v>9607</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>649026</v>
+        <v>649440</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2035</v>
+        <v>2003</v>
       </c>
       <c r="O5" t="n">
         <v>256</v>
       </c>
       <c r="P5" t="n">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="Q5" t="n">
-        <v>1699</v>
+        <v>1712</v>
       </c>
       <c r="R5" t="n">
-        <v>20947</v>
+        <v>20978</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:51</t>
+          <t>2026-06-06 17:58:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="G6" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H6" t="n">
         <v>160</v>
@@ -871,10 +871,10 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
         <v>12</v>
@@ -883,7 +883,7 @@
         <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:52</t>
+          <t>2026-06-06 17:58:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7875</v>
+        <v>4.7717843</v>
       </c>
       <c r="G7" t="n">
-        <v>3084</v>
+        <v>3085</v>
       </c>
       <c r="H7" t="n">
         <v>1151</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -957,7 +957,7 @@
         <v>50</v>
       </c>
       <c r="R7" t="n">
-        <v>2865</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:52</t>
+          <t>2026-06-06 17:58:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.180633</v>
+        <v>4.1747212</v>
       </c>
       <c r="G8" t="n">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="H8" t="n">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>972</v>
+        <v>981</v>
       </c>
       <c r="O8" t="n">
         <v>144</v>
@@ -1028,10 +1028,10 @@
         <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R8" t="n">
-        <v>4470</v>
+        <v>4462</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:52</t>
+          <t>2026-06-06 17:58:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>174753</v>
+        <v>174922</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:52</t>
+          <t>2026-06-06 17:58:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>86025</v>
+        <v>86121</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:52</t>
+          <t>2026-06-06 17:58:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6818886</v>
+        <v>4.6826253</v>
       </c>
       <c r="G11" t="n">
-        <v>14544</v>
+        <v>14548</v>
       </c>
       <c r="H11" t="n">
         <v>690</v>
@@ -1223,11 +1223,11 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>249196</v>
+        <v>249248</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.0.44</t>
+          <t>1.0.45</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1237,23 +1237,23 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>May 4, 2026</t>
+          <t>May 21, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q11" t="n">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="R11" t="n">
-        <v>12696</v>
+        <v>12705</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:52</t>
+          <t>2026-06-06 17:58:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6535432</v>
+        <v>2.668421</v>
       </c>
       <c r="G12" t="n">
         <v>4646</v>
       </c>
       <c r="H12" t="n">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2487</v>
+        <v>2468</v>
       </c>
       <c r="O12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P12" t="n">
         <v>170</v>
@@ -1323,7 +1323,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1645</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:52</t>
+          <t>2026-06-06 17:58:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21700</v>
+        <v>21704</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:53</t>
+          <t>2026-06-06 17:58:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4442396</v>
+        <v>3.4470046</v>
       </c>
       <c r="G14" t="n">
-        <v>11978</v>
+        <v>11980</v>
       </c>
       <c r="H14" t="n">
-        <v>4664</v>
+        <v>4666</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4095</v>
+        <v>4074</v>
       </c>
       <c r="O14" t="n">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="P14" t="n">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="Q14" t="n">
         <v>419</v>
       </c>
       <c r="R14" t="n">
-        <v>6700</v>
+        <v>6702</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:53</t>
+          <t>2026-06-06 17:58:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1507,7 +1507,7 @@
         <v>3866</v>
       </c>
       <c r="H15" t="n">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>386516</v>
+        <v>386802</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-05 18:53:53</t>
+          <t>2026-06-06 17:58:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1578,10 +1578,10 @@
         <v>4.7254715</v>
       </c>
       <c r="G16" t="n">
-        <v>46643</v>
+        <v>46644</v>
       </c>
       <c r="H16" t="n">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>2276</v>
       </c>
       <c r="R16" t="n">
-        <v>41295</v>
+        <v>41296</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:42</t>
+          <t>2026-06-07 17:57:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36569</v>
+        <v>36668</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:43</t>
+          <t>2026-06-07 17:57:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5007405</v>
+        <v>4.498147</v>
       </c>
       <c r="G3" t="n">
-        <v>30312</v>
+        <v>30322</v>
       </c>
       <c r="H3" t="n">
-        <v>8952</v>
+        <v>8959</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2349070</v>
+        <v>2350031</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Jun 4, 2026</t>
+          <t>Jun 6, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3288</v>
+        <v>3303</v>
       </c>
       <c r="O3" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P3" t="n">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="Q3" t="n">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="R3" t="n">
-        <v>25888</v>
+        <v>25871</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:43</t>
+          <t>2026-06-07 17:57:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,10 +698,10 @@
         <v>3.6257348</v>
       </c>
       <c r="G4" t="n">
-        <v>24860</v>
+        <v>24859</v>
       </c>
       <c r="H4" t="n">
-        <v>5570</v>
+        <v>5572</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2554474</v>
+        <v>2556262</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:43</t>
+          <t>2026-06-07 17:57:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.529105</v>
+        <v>4.5272093</v>
       </c>
       <c r="G5" t="n">
-        <v>25771</v>
+        <v>25776</v>
       </c>
       <c r="H5" t="n">
-        <v>9607</v>
+        <v>9616</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>649440</v>
+        <v>649801</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="O5" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="P5" t="n">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="Q5" t="n">
-        <v>1712</v>
+        <v>1705</v>
       </c>
       <c r="R5" t="n">
-        <v>20978</v>
+        <v>20972</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:43</t>
+          <t>2026-06-07 17:57:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -849,7 +849,7 @@
         <v>447</v>
       </c>
       <c r="H6" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>95360</v>
+        <v>96680</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:43</t>
+          <t>2026-06-07 17:57:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -919,7 +919,7 @@
         <v>3085</v>
       </c>
       <c r="H7" t="n">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>419727</v>
+        <v>420457</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:43</t>
+          <t>2026-06-07 17:57:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1747212</v>
+        <v>4.1700935</v>
       </c>
       <c r="G8" t="n">
-        <v>6004</v>
+        <v>6006</v>
       </c>
       <c r="H8" t="n">
         <v>2234</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>429049</v>
+        <v>429323</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="O8" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P8" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R8" t="n">
-        <v>4462</v>
+        <v>4455</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:44</t>
+          <t>2026-06-07 17:57:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>174922</v>
+        <v>175012</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:44</t>
+          <t>2026-06-07 17:57:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>86121</v>
+        <v>86222</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:44</t>
+          <t>2026-06-07 17:57:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6826253</v>
+        <v>4.6821704</v>
       </c>
       <c r="G11" t="n">
-        <v>14548</v>
+        <v>14551</v>
       </c>
       <c r="H11" t="n">
         <v>690</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>249248</v>
+        <v>249339</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q11" t="n">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="R11" t="n">
-        <v>12705</v>
+        <v>12711</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:44</t>
+          <t>2026-06-07 17:57:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.668421</v>
+        <v>2.6666667</v>
       </c>
       <c r="G12" t="n">
-        <v>4646</v>
+        <v>4650</v>
       </c>
       <c r="H12" t="n">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>347646</v>
+        <v>347931</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2468</v>
+        <v>2476</v>
       </c>
       <c r="O12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P12" t="n">
         <v>170</v>
       </c>
       <c r="Q12" t="n">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="R12" t="n">
-        <v>1662</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:44</t>
+          <t>2026-06-07 17:57:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21704</v>
+        <v>21714</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:45</t>
+          <t>2026-06-07 17:57:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4470046</v>
+        <v>3.4439337</v>
       </c>
       <c r="G14" t="n">
-        <v>11980</v>
+        <v>11983</v>
       </c>
       <c r="H14" t="n">
-        <v>4666</v>
+        <v>4668</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1214683</v>
+        <v>1216075</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4074</v>
+        <v>4085</v>
       </c>
       <c r="O14" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P14" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q14" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="R14" t="n">
-        <v>6702</v>
+        <v>6695</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:45</t>
+          <t>2026-06-07 17:57:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3401759</v>
+        <v>3.3333333</v>
       </c>
       <c r="G15" t="n">
-        <v>3866</v>
+        <v>3867</v>
       </c>
       <c r="H15" t="n">
         <v>1558</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>386802</v>
+        <v>387316</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1439</v>
+        <v>1446</v>
       </c>
       <c r="O15" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P15" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R15" t="n">
-        <v>2108</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-06 17:58:45</t>
+          <t>2026-06-07 17:57:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7254715</v>
+        <v>4.725088</v>
       </c>
       <c r="G16" t="n">
-        <v>46644</v>
+        <v>46649</v>
       </c>
       <c r="H16" t="n">
         <v>2929</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>549411</v>
+        <v>550200</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2034</v>
+        <v>2031</v>
       </c>
       <c r="O16" t="n">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="P16" t="n">
         <v>714</v>
       </c>
       <c r="Q16" t="n">
-        <v>2276</v>
+        <v>2274</v>
       </c>
       <c r="R16" t="n">
-        <v>41296</v>
+        <v>41297</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:49</t>
+          <t>2026-06-08 19:12:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="G2" t="n">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="H2" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36668</v>
+        <v>36707</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -588,10 +588,10 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R2" t="n">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:49</t>
+          <t>2026-06-08 19:12:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.498147</v>
+        <v>4.4981494</v>
       </c>
       <c r="G3" t="n">
-        <v>30322</v>
+        <v>30342</v>
       </c>
       <c r="H3" t="n">
-        <v>8959</v>
+        <v>8966</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2350031</v>
+        <v>2351223</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3303</v>
+        <v>3300</v>
       </c>
       <c r="O3" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="P3" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="Q3" t="n">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="R3" t="n">
-        <v>25871</v>
+        <v>25894</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:50</t>
+          <t>2026-06-08 19:12:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6257348</v>
+        <v>3.6237752</v>
       </c>
       <c r="G4" t="n">
-        <v>24859</v>
+        <v>24865</v>
       </c>
       <c r="H4" t="n">
         <v>5572</v>
@@ -709,11 +709,11 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2556262</v>
+        <v>2557372</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.21.5</t>
+          <t>2.22.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>May 9, 2026</t>
+          <t>May 21, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7175</v>
+        <v>7194</v>
       </c>
       <c r="O4" t="n">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="P4" t="n">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="Q4" t="n">
-        <v>1183</v>
+        <v>1169</v>
       </c>
       <c r="R4" t="n">
-        <v>14775</v>
+        <v>14778</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:50</t>
+          <t>2026-06-08 19:12:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5272093</v>
+        <v>4.528671</v>
       </c>
       <c r="G5" t="n">
-        <v>25776</v>
+        <v>25793</v>
       </c>
       <c r="H5" t="n">
-        <v>9616</v>
+        <v>9620</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>649801</v>
+        <v>650109</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="O5" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P5" t="n">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="Q5" t="n">
-        <v>1705</v>
+        <v>1690</v>
       </c>
       <c r="R5" t="n">
-        <v>20972</v>
+        <v>21007</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:50</t>
+          <t>2026-06-08 19:12:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H6" t="n">
         <v>161</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>96680</v>
+        <v>97444</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="O6" t="n">
         <v>12</v>
@@ -883,7 +883,7 @@
         <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:50</t>
+          <t>2026-06-08 19:12:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7717843</v>
+        <v>4.7551866</v>
       </c>
       <c r="G7" t="n">
         <v>3085</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>420457</v>
+        <v>420713</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -957,7 +957,7 @@
         <v>50</v>
       </c>
       <c r="R7" t="n">
-        <v>2854</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:50</t>
+          <t>2026-06-08 19:12:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -993,7 +993,7 @@
         <v>6006</v>
       </c>
       <c r="H8" t="n">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>429323</v>
+        <v>429452</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:51</t>
+          <t>2026-06-08 19:12:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,7 +1064,7 @@
         <v>4.0280375</v>
       </c>
       <c r="G9" t="n">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H9" t="n">
         <v>489</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>175012</v>
+        <v>175111</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:51</t>
+          <t>2026-06-08 19:12:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>3.8921568</v>
       </c>
       <c r="G10" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H10" t="n">
         <v>224</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>86222</v>
+        <v>86299</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="R10" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:51</t>
+          <t>2026-06-08 19:12:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6821704</v>
+        <v>4.6831913</v>
       </c>
       <c r="G11" t="n">
-        <v>14551</v>
+        <v>14562</v>
       </c>
       <c r="H11" t="n">
         <v>690</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>249339</v>
+        <v>249403</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         <v>235</v>
       </c>
       <c r="Q11" t="n">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="R11" t="n">
-        <v>12711</v>
+        <v>12733</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:51</t>
+          <t>2026-06-08 19:12:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6666667</v>
+        <v>2.6684072</v>
       </c>
       <c r="G12" t="n">
-        <v>4650</v>
+        <v>4651</v>
       </c>
       <c r="H12" t="n">
         <v>1919</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>347931</v>
+        <v>348024</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="O12" t="n">
         <v>133</v>
       </c>
       <c r="P12" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q12" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R12" t="n">
-        <v>1671</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:51</t>
+          <t>2026-06-08 19:12:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21714</v>
+        <v>21716</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:51</t>
+          <t>2026-06-08 19:12:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4439337</v>
+        <v>3.4431193</v>
       </c>
       <c r="G14" t="n">
-        <v>11983</v>
+        <v>11988</v>
       </c>
       <c r="H14" t="n">
-        <v>4668</v>
+        <v>4669</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1216075</v>
+        <v>1216538</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4085</v>
+        <v>4090</v>
       </c>
       <c r="O14" t="n">
         <v>318</v>
       </c>
       <c r="P14" t="n">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q14" t="n">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="R14" t="n">
-        <v>6695</v>
+        <v>6697</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:51</t>
+          <t>2026-06-08 19:12:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3333333</v>
+        <v>3.3284457</v>
       </c>
       <c r="G15" t="n">
-        <v>3867</v>
+        <v>3868</v>
       </c>
       <c r="H15" t="n">
         <v>1558</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>387316</v>
+        <v>387606</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,23 +1529,23 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1446</v>
+        <v>1451</v>
       </c>
       <c r="O15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P15" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R15" t="n">
-        <v>2102</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-07 17:57:52</t>
+          <t>2026-06-08 19:12:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.725088</v>
+        <v>4.724406</v>
       </c>
       <c r="G16" t="n">
-        <v>46649</v>
+        <v>46652</v>
       </c>
       <c r="H16" t="n">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>550200</v>
+        <v>550425</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2031</v>
+        <v>2041</v>
       </c>
       <c r="O16" t="n">
         <v>329</v>
       </c>
       <c r="P16" t="n">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="Q16" t="n">
-        <v>2274</v>
+        <v>2272</v>
       </c>
       <c r="R16" t="n">
-        <v>41297</v>
+        <v>41293</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:44</t>
+          <t>2026-06-09 19:06:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.96</v>
+        <v>4.059406</v>
       </c>
       <c r="G2" t="n">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="H2" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36707</v>
+        <v>36759</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -588,10 +588,10 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R2" t="n">
-        <v>251</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:45</t>
+          <t>2026-06-09 19:06:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4981494</v>
+        <v>4.4931507</v>
       </c>
       <c r="G3" t="n">
-        <v>30342</v>
+        <v>30355</v>
       </c>
       <c r="H3" t="n">
-        <v>8966</v>
+        <v>8969</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2351223</v>
+        <v>2352211</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3300</v>
+        <v>3336</v>
       </c>
       <c r="O3" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P3" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q3" t="n">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="R3" t="n">
-        <v>25894</v>
+        <v>25858</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:45</t>
+          <t>2026-06-09 19:06:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6237752</v>
+        <v>3.6240208</v>
       </c>
       <c r="G4" t="n">
-        <v>24865</v>
+        <v>24867</v>
       </c>
       <c r="H4" t="n">
         <v>5572</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7194</v>
+        <v>7189</v>
       </c>
       <c r="O4" t="n">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="P4" t="n">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="Q4" t="n">
-        <v>1169</v>
+        <v>1183</v>
       </c>
       <c r="R4" t="n">
-        <v>14778</v>
+        <v>14770</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:45</t>
+          <t>2026-06-09 19:06:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.528671</v>
+        <v>4.529488</v>
       </c>
       <c r="G5" t="n">
-        <v>25793</v>
+        <v>25797</v>
       </c>
       <c r="H5" t="n">
-        <v>9620</v>
+        <v>9624</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>650109</v>
+        <v>650471</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="O5" t="n">
         <v>268</v>
       </c>
       <c r="P5" t="n">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="Q5" t="n">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="R5" t="n">
-        <v>21007</v>
+        <v>21019</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:45</t>
+          <t>2026-06-09 19:06:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H6" t="n">
         <v>161</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>97444</v>
+        <v>98895</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O6" t="n">
         <v>12</v>
@@ -883,7 +883,7 @@
         <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:45</t>
+          <t>2026-06-09 19:06:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7551866</v>
+        <v>4.7561984</v>
       </c>
       <c r="G7" t="n">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="H7" t="n">
         <v>1152</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>420713</v>
+        <v>420889</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -957,7 +957,7 @@
         <v>50</v>
       </c>
       <c r="R7" t="n">
-        <v>2840</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:46</t>
+          <t>2026-06-09 19:06:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1700935</v>
+        <v>4.1641793</v>
       </c>
       <c r="G8" t="n">
         <v>6006</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>429452</v>
+        <v>429633</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>987</v>
+        <v>996</v>
       </c>
       <c r="O8" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P8" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R8" t="n">
-        <v>4455</v>
+        <v>4448</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:46</t>
+          <t>2026-06-09 19:06:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:46</t>
+          <t>2026-06-09 19:06:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>86299</v>
+        <v>86344</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:46</t>
+          <t>2026-06-09 19:06:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6831913</v>
+        <v>4.682552</v>
       </c>
       <c r="G11" t="n">
-        <v>14562</v>
+        <v>14578</v>
       </c>
       <c r="H11" t="n">
         <v>690</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>249403</v>
+        <v>249543</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="O11" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P11" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q11" t="n">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="R11" t="n">
-        <v>12733</v>
+        <v>12751</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:46</t>
+          <t>2026-06-09 19:06:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6684072</v>
+        <v>2.671916</v>
       </c>
       <c r="G12" t="n">
-        <v>4651</v>
+        <v>4653</v>
       </c>
       <c r="H12" t="n">
         <v>1919</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>348024</v>
+        <v>348196</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="O12" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="P12" t="n">
         <v>169</v>
       </c>
       <c r="Q12" t="n">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1674</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:47</t>
+          <t>2026-06-09 19:06:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21716</v>
+        <v>21730</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:47</t>
+          <t>2026-06-09 19:06:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4431193</v>
+        <v>3.4471993</v>
       </c>
       <c r="G14" t="n">
-        <v>11988</v>
+        <v>11993</v>
       </c>
       <c r="H14" t="n">
-        <v>4669</v>
+        <v>4671</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1216538</v>
+        <v>1217718</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4090</v>
+        <v>4085</v>
       </c>
       <c r="O14" t="n">
         <v>318</v>
       </c>
       <c r="P14" t="n">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="Q14" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R14" t="n">
-        <v>6697</v>
+        <v>6716</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:47</t>
+          <t>2026-06-09 19:06:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>387606</v>
+        <v>387905</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-08 19:12:47</t>
+          <t>2026-06-09 19:06:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.724406</v>
+        <v>4.7230587</v>
       </c>
       <c r="G16" t="n">
-        <v>46652</v>
+        <v>46651</v>
       </c>
       <c r="H16" t="n">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>550425</v>
+        <v>551085</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2041</v>
+        <v>2063</v>
       </c>
       <c r="O16" t="n">
         <v>329</v>
       </c>
       <c r="P16" t="n">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="Q16" t="n">
         <v>2272</v>
       </c>
       <c r="R16" t="n">
-        <v>41293</v>
+        <v>41282</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:14</t>
+          <t>2026-06-10 19:28:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.059406</v>
+        <v>4.13</v>
       </c>
       <c r="G2" t="n">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="H2" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -588,10 +588,10 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>267</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:14</t>
+          <t>2026-06-10 19:28:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4931507</v>
+        <v>4.487037</v>
       </c>
       <c r="G3" t="n">
-        <v>30355</v>
+        <v>30365</v>
       </c>
       <c r="H3" t="n">
-        <v>8969</v>
+        <v>8972</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2352211</v>
+        <v>2353113</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3336</v>
+        <v>3385</v>
       </c>
       <c r="O3" t="n">
         <v>292</v>
@@ -665,7 +665,7 @@
         <v>572</v>
       </c>
       <c r="R3" t="n">
-        <v>25858</v>
+        <v>25820</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:15</t>
+          <t>2026-06-10 19:28:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -701,7 +701,7 @@
         <v>24867</v>
       </c>
       <c r="H4" t="n">
-        <v>5572</v>
+        <v>5574</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2557372</v>
+        <v>2558373</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7189</v>
+        <v>7190</v>
       </c>
       <c r="O4" t="n">
         <v>826</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:15</t>
+          <t>2026-06-10 19:28:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.529488</v>
+        <v>4.5296154</v>
       </c>
       <c r="G5" t="n">
-        <v>25797</v>
+        <v>25805</v>
       </c>
       <c r="H5" t="n">
-        <v>9624</v>
+        <v>9625</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>650471</v>
+        <v>650474</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2001</v>
+        <v>1996</v>
       </c>
       <c r="O5" t="n">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="P5" t="n">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="Q5" t="n">
-        <v>1688</v>
+        <v>1684</v>
       </c>
       <c r="R5" t="n">
-        <v>21019</v>
+        <v>21029</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:15</t>
+          <t>2026-06-10 19:28:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="G6" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="H6" t="n">
         <v>161</v>
@@ -871,19 +871,19 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="O6" t="n">
         <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q6" t="n">
         <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:15</t>
+          <t>2026-06-10 19:28:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -919,7 +919,7 @@
         <v>3086</v>
       </c>
       <c r="H7" t="n">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>420889</v>
+        <v>421249</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:16</t>
+          <t>2026-06-10 19:28:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1641793</v>
+        <v>4.1626167</v>
       </c>
       <c r="G8" t="n">
-        <v>6006</v>
+        <v>6007</v>
       </c>
       <c r="H8" t="n">
         <v>2235</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>429633</v>
+        <v>429637</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="O8" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P8" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R8" t="n">
-        <v>4448</v>
+        <v>4445</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:16</t>
+          <t>2026-06-10 19:28:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>175111</v>
+        <v>175191</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:16</t>
+          <t>2026-06-10 19:28:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>3.8921568</v>
       </c>
       <c r="G10" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H10" t="n">
         <v>224</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>86344</v>
+        <v>86446</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:16</t>
+          <t>2026-06-10 19:28:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.682552</v>
+        <v>4.6872587</v>
       </c>
       <c r="G11" t="n">
-        <v>14578</v>
+        <v>14592</v>
       </c>
       <c r="H11" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="O11" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q11" t="n">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="R11" t="n">
-        <v>12751</v>
+        <v>12777</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:16</t>
+          <t>2026-06-10 19:28:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.671916</v>
+        <v>2.6780105</v>
       </c>
       <c r="G12" t="n">
-        <v>4653</v>
+        <v>4654</v>
       </c>
       <c r="H12" t="n">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2478</v>
+        <v>2472</v>
       </c>
       <c r="O12" t="n">
         <v>121</v>
@@ -1323,7 +1323,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1672</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:17</t>
+          <t>2026-06-10 19:28:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:17</t>
+          <t>2026-06-10 19:28:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4471993</v>
+        <v>3.4544618</v>
       </c>
       <c r="G14" t="n">
-        <v>11993</v>
+        <v>12002</v>
       </c>
       <c r="H14" t="n">
-        <v>4671</v>
+        <v>4672</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4085</v>
+        <v>4062</v>
       </c>
       <c r="O14" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P14" t="n">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="Q14" t="n">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="R14" t="n">
-        <v>6716</v>
+        <v>6745</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:17</t>
+          <t>2026-06-10 19:28:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3284457</v>
+        <v>3.3216374</v>
       </c>
       <c r="G15" t="n">
-        <v>3868</v>
+        <v>3869</v>
       </c>
       <c r="H15" t="n">
         <v>1558</v>
@@ -1529,23 +1529,23 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1451</v>
+        <v>1458</v>
       </c>
       <c r="O15" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P15" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R15" t="n">
-        <v>2098</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-09 19:06:18</t>
+          <t>2026-06-10 19:28:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7230587</v>
+        <v>4.7214775</v>
       </c>
       <c r="G16" t="n">
-        <v>46651</v>
+        <v>46652</v>
       </c>
       <c r="H16" t="n">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2063</v>
+        <v>2073</v>
       </c>
       <c r="O16" t="n">
         <v>329</v>
       </c>
       <c r="P16" t="n">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="Q16" t="n">
-        <v>2272</v>
+        <v>2282</v>
       </c>
       <c r="R16" t="n">
-        <v>41282</v>
+        <v>41252</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:47</t>
+          <t>2026-06-11 19:28:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.13</v>
       </c>
       <c r="G2" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H2" t="n">
         <v>165</v>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -591,7 +591,7 @@
         <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:47</t>
+          <t>2026-06-11 19:28:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.487037</v>
+        <v>4.484647</v>
       </c>
       <c r="G3" t="n">
-        <v>30365</v>
+        <v>30372</v>
       </c>
       <c r="H3" t="n">
-        <v>8972</v>
+        <v>8977</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2353113</v>
+        <v>2353773</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3385</v>
+        <v>3404</v>
       </c>
       <c r="O3" t="n">
         <v>292</v>
@@ -665,7 +665,7 @@
         <v>572</v>
       </c>
       <c r="R3" t="n">
-        <v>25820</v>
+        <v>25809</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:47</t>
+          <t>2026-06-11 19:28:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6240208</v>
+        <v>3.631682</v>
       </c>
       <c r="G4" t="n">
-        <v>24867</v>
+        <v>24878</v>
       </c>
       <c r="H4" t="n">
-        <v>5574</v>
+        <v>5575</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7190</v>
+        <v>7167</v>
       </c>
       <c r="O4" t="n">
-        <v>826</v>
+        <v>810</v>
       </c>
       <c r="P4" t="n">
-        <v>891</v>
+        <v>875</v>
       </c>
       <c r="Q4" t="n">
         <v>1183</v>
       </c>
       <c r="R4" t="n">
-        <v>14770</v>
+        <v>14838</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:47</t>
+          <t>2026-06-11 19:28:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5296154</v>
+        <v>4.5313044</v>
       </c>
       <c r="G5" t="n">
-        <v>25805</v>
+        <v>25814</v>
       </c>
       <c r="H5" t="n">
-        <v>9625</v>
+        <v>9630</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>650474</v>
+        <v>651015</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1996</v>
+        <v>1974</v>
       </c>
       <c r="O5" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P5" t="n">
-        <v>813</v>
+        <v>841</v>
       </c>
       <c r="Q5" t="n">
-        <v>1684</v>
+        <v>1671</v>
       </c>
       <c r="R5" t="n">
-        <v>21029</v>
+        <v>21043</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:47</t>
+          <t>2026-06-11 19:28:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,18 +846,18 @@
         <v>3.62</v>
       </c>
       <c r="G6" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H6" t="n">
         <v>161</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50,000+</t>
+          <t>100,000+</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>98895</v>
+        <v>100468</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:47</t>
+          <t>2026-06-11 19:28:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7561984</v>
+        <v>4.7530866</v>
       </c>
       <c r="G7" t="n">
-        <v>3086</v>
+        <v>3087</v>
       </c>
       <c r="H7" t="n">
         <v>1153</v>
@@ -954,10 +954,10 @@
         <v>24</v>
       </c>
       <c r="Q7" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="R7" t="n">
-        <v>2842</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:48</t>
+          <t>2026-06-11 19:28:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:48</t>
+          <t>2026-06-11 19:28:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,7 +1064,7 @@
         <v>4.0280375</v>
       </c>
       <c r="G9" t="n">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H9" t="n">
         <v>489</v>
@@ -1096,7 +1096,7 @@
         <v>226</v>
       </c>
       <c r="O9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P9" t="n">
         <v>79</v>
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:48</t>
+          <t>2026-06-11 19:28:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>3.8921568</v>
       </c>
       <c r="G10" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H10" t="n">
         <v>224</v>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:48</t>
+          <t>2026-06-11 19:28:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6872587</v>
+        <v>4.6846156</v>
       </c>
       <c r="G11" t="n">
-        <v>14592</v>
+        <v>14607</v>
       </c>
       <c r="H11" t="n">
         <v>691</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="Q11" t="n">
-        <v>686</v>
+        <v>718</v>
       </c>
       <c r="R11" t="n">
-        <v>12777</v>
+        <v>12751</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:48</t>
+          <t>2026-06-11 19:28:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6780105</v>
+        <v>2.7154047</v>
       </c>
       <c r="G12" t="n">
-        <v>4654</v>
+        <v>4660</v>
       </c>
       <c r="H12" t="n">
         <v>1921</v>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2472</v>
+        <v>2432</v>
       </c>
       <c r="O12" t="n">
         <v>121</v>
       </c>
       <c r="P12" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q12" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R12" t="n">
-        <v>1680</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:48</t>
+          <t>2026-06-11 19:28:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:48</t>
+          <t>2026-06-11 19:28:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4544618</v>
+        <v>3.459633</v>
       </c>
       <c r="G14" t="n">
-        <v>12002</v>
+        <v>12010</v>
       </c>
       <c r="H14" t="n">
-        <v>4672</v>
+        <v>4676</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4062</v>
+        <v>4054</v>
       </c>
       <c r="O14" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P14" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q14" t="n">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="R14" t="n">
-        <v>6745</v>
+        <v>6775</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:49</t>
+          <t>2026-06-11 19:28:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-10 19:28:49</t>
+          <t>2026-06-11 19:28:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7214775</v>
+        <v>4.721543</v>
       </c>
       <c r="G16" t="n">
-        <v>46652</v>
+        <v>46653</v>
       </c>
       <c r="H16" t="n">
         <v>2932</v>
@@ -1589,11 +1589,11 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>551085</v>
+        <v>551812</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.2</t>
+          <t>3.1.3</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1603,14 +1603,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Jun 4, 2026</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
         <v>2073</v>
       </c>
       <c r="O16" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P16" t="n">
         <v>712</v>
@@ -1619,7 +1619,7 @@
         <v>2282</v>
       </c>
       <c r="R16" t="n">
-        <v>41252</v>
+        <v>41254</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:47</t>
+          <t>2026-06-12 18:56:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="G2" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H2" t="n">
         <v>165</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36759</v>
+        <v>36842</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -591,7 +591,7 @@
         <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:47</t>
+          <t>2026-06-12 18:56:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.484647</v>
+        <v>4.481139</v>
       </c>
       <c r="G3" t="n">
-        <v>30372</v>
+        <v>30385</v>
       </c>
       <c r="H3" t="n">
-        <v>8977</v>
+        <v>8978</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2353773</v>
+        <v>2354706</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3404</v>
+        <v>3426</v>
       </c>
       <c r="O3" t="n">
         <v>292</v>
       </c>
       <c r="P3" t="n">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="Q3" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="R3" t="n">
-        <v>25809</v>
+        <v>25788</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:48</t>
+          <t>2026-06-12 18:56:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.631682</v>
+        <v>3.6374838</v>
       </c>
       <c r="G4" t="n">
-        <v>24878</v>
+        <v>24895</v>
       </c>
       <c r="H4" t="n">
-        <v>5575</v>
+        <v>5577</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2558373</v>
+        <v>2560076</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7167</v>
+        <v>7134</v>
       </c>
       <c r="O4" t="n">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="P4" t="n">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="Q4" t="n">
-        <v>1183</v>
+        <v>1209</v>
       </c>
       <c r="R4" t="n">
-        <v>14838</v>
+        <v>14869</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:48</t>
+          <t>2026-06-12 18:56:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5313044</v>
+        <v>4.5348635</v>
       </c>
       <c r="G5" t="n">
-        <v>25814</v>
+        <v>25824</v>
       </c>
       <c r="H5" t="n">
-        <v>9630</v>
+        <v>9631</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1974</v>
+        <v>1956</v>
       </c>
       <c r="O5" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="Q5" t="n">
-        <v>1671</v>
+        <v>1666</v>
       </c>
       <c r="R5" t="n">
-        <v>21043</v>
+        <v>21081</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:48</t>
+          <t>2026-06-12 18:56:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:48</t>
+          <t>2026-06-12 18:56:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>421249</v>
+        <v>421614</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:48</t>
+          <t>2026-06-12 18:56:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1626167</v>
+        <v>4.1641793</v>
       </c>
       <c r="G8" t="n">
-        <v>6007</v>
+        <v>6008</v>
       </c>
       <c r="H8" t="n">
         <v>2235</v>
@@ -1001,11 +1001,11 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>429637</v>
+        <v>429865</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.1.25</t>
+          <t>2.1.26</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1015,23 +1015,23 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>May 20, 2026</t>
+          <t>Jun 10, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="O8" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P8" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R8" t="n">
-        <v>4445</v>
+        <v>4449</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:49</t>
+          <t>2026-06-12 18:56:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,10 +1064,10 @@
         <v>4.0280375</v>
       </c>
       <c r="G9" t="n">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H9" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>175191</v>
+        <v>175325</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:49</t>
+          <t>2026-06-12 18:56:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>86446</v>
+        <v>86566</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:49</t>
+          <t>2026-06-12 18:56:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6846156</v>
+        <v>4.6865444</v>
       </c>
       <c r="G11" t="n">
-        <v>14607</v>
+        <v>14616</v>
       </c>
       <c r="H11" t="n">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>249543</v>
+        <v>249647</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="O11" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P11" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q11" t="n">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="R11" t="n">
-        <v>12751</v>
+        <v>12772</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:49</t>
+          <t>2026-06-12 18:56:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1286,7 +1286,7 @@
         <v>2.7154047</v>
       </c>
       <c r="G12" t="n">
-        <v>4660</v>
+        <v>4661</v>
       </c>
       <c r="H12" t="n">
         <v>1921</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>348196</v>
+        <v>348332</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="O12" t="n">
         <v>121</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:49</t>
+          <t>2026-06-12 18:56:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21730</v>
+        <v>21735</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:49</t>
+          <t>2026-06-12 18:56:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.459633</v>
+        <v>3.4783</v>
       </c>
       <c r="G14" t="n">
-        <v>12010</v>
+        <v>12026</v>
       </c>
       <c r="H14" t="n">
-        <v>4676</v>
+        <v>4677</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1217718</v>
+        <v>1218448</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4054</v>
+        <v>4011</v>
       </c>
       <c r="O14" t="n">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="P14" t="n">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="Q14" t="n">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="R14" t="n">
-        <v>6775</v>
+        <v>6849</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:49</t>
+          <t>2026-06-12 18:56:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>387905</v>
+        <v>388188</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-11 19:28:50</t>
+          <t>2026-06-12 18:56:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.721543</v>
+        <v>4.721608</v>
       </c>
       <c r="G16" t="n">
         <v>46653</v>
       </c>
       <c r="H16" t="n">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
         <v>712</v>
       </c>
       <c r="Q16" t="n">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="R16" t="n">
-        <v>41254</v>
+        <v>41255</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:14</t>
+          <t>2026-06-13 18:02:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:14</t>
+          <t>2026-06-13 18:02:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.481139</v>
+        <v>4.4822354</v>
       </c>
       <c r="G3" t="n">
-        <v>30385</v>
+        <v>30390</v>
       </c>
       <c r="H3" t="n">
-        <v>8978</v>
+        <v>8982</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2354706</v>
+        <v>2354710</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3426</v>
+        <v>3418</v>
       </c>
       <c r="O3" t="n">
         <v>292</v>
@@ -662,10 +662,10 @@
         <v>303</v>
       </c>
       <c r="Q3" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="R3" t="n">
-        <v>25788</v>
+        <v>25800</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:14</t>
+          <t>2026-06-13 18:02:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6374838</v>
+        <v>3.64235</v>
       </c>
       <c r="G4" t="n">
-        <v>24895</v>
+        <v>24902</v>
       </c>
       <c r="H4" t="n">
-        <v>5577</v>
+        <v>5579</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7134</v>
+        <v>7104</v>
       </c>
       <c r="O4" t="n">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="P4" t="n">
-        <v>870</v>
+        <v>883</v>
       </c>
       <c r="Q4" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="R4" t="n">
-        <v>14869</v>
+        <v>14902</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:15</t>
+          <t>2026-06-13 18:02:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5348635</v>
+        <v>4.534542</v>
       </c>
       <c r="G5" t="n">
-        <v>25824</v>
+        <v>25830</v>
       </c>
       <c r="H5" t="n">
-        <v>9631</v>
+        <v>9634</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1956</v>
+        <v>1962</v>
       </c>
       <c r="O5" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P5" t="n">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="Q5" t="n">
-        <v>1666</v>
+        <v>1661</v>
       </c>
       <c r="R5" t="n">
-        <v>21081</v>
+        <v>21089</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:15</t>
+          <t>2026-06-13 18:02:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="G6" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H6" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="O6" t="n">
         <v>12</v>
@@ -883,7 +883,7 @@
         <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:15</t>
+          <t>2026-06-13 18:02:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7530866</v>
+        <v>4.768595</v>
       </c>
       <c r="G7" t="n">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="H7" t="n">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>421614</v>
+        <v>422375</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -957,7 +957,7 @@
         <v>62</v>
       </c>
       <c r="R7" t="n">
-        <v>2831</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:15</t>
+          <t>2026-06-13 18:02:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1641793</v>
+        <v>4.1623135</v>
       </c>
       <c r="G8" t="n">
-        <v>6008</v>
+        <v>6006</v>
       </c>
       <c r="H8" t="n">
-        <v>2235</v>
+        <v>2240</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>429865</v>
+        <v>430059</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>996</v>
+        <v>1007</v>
       </c>
       <c r="O8" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="P8" t="n">
         <v>178</v>
@@ -1031,7 +1031,7 @@
         <v>234</v>
       </c>
       <c r="R8" t="n">
-        <v>4449</v>
+        <v>4448</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:15</t>
+          <t>2026-06-13 18:02:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.0280375</v>
+        <v>3.9906542</v>
       </c>
       <c r="G9" t="n">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="H9" t="n">
         <v>490</v>
@@ -1089,11 +1089,11 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="O9" t="n">
         <v>34</v>
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>862</v>
+        <v>851</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:16</t>
+          <t>2026-06-13 18:02:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:16</t>
+          <t>2026-06-13 18:02:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6865444</v>
+        <v>4.6872144</v>
       </c>
       <c r="G11" t="n">
-        <v>14616</v>
+        <v>14619</v>
       </c>
       <c r="H11" t="n">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="O11" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P11" t="n">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q11" t="n">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="R11" t="n">
-        <v>12772</v>
+        <v>12771</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:16</t>
+          <t>2026-06-13 18:02:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>348332</v>
+        <v>348553</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:16</t>
+          <t>2026-06-13 18:02:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:16</t>
+          <t>2026-06-13 18:02:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4783</v>
+        <v>3.4755435</v>
       </c>
       <c r="G14" t="n">
-        <v>12026</v>
+        <v>12024</v>
       </c>
       <c r="H14" t="n">
         <v>4677</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1218448</v>
+        <v>1219751</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4011</v>
+        <v>4018</v>
       </c>
       <c r="O14" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P14" t="n">
         <v>456</v>
       </c>
       <c r="Q14" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="R14" t="n">
-        <v>6849</v>
+        <v>6838</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:17</t>
+          <t>2026-06-13 18:02:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1507,7 +1507,7 @@
         <v>3869</v>
       </c>
       <c r="H15" t="n">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-12 18:56:17</t>
+          <t>2026-06-13 18:02:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.721608</v>
+        <v>4.720668</v>
       </c>
       <c r="G16" t="n">
         <v>46653</v>
       </c>
       <c r="H16" t="n">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>551812</v>
+        <v>552259</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2073</v>
+        <v>2083</v>
       </c>
       <c r="O16" t="n">
         <v>328</v>
@@ -1619,7 +1619,7 @@
         <v>2281</v>
       </c>
       <c r="R16" t="n">
-        <v>41255</v>
+        <v>41244</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:23</t>
+          <t>2026-06-14 18:06:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="G2" t="n">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H2" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36842</v>
+        <v>36906</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -591,7 +591,7 @@
         <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:23</t>
+          <t>2026-06-14 18:06:35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4822354</v>
+        <v>4.4824786</v>
       </c>
       <c r="G3" t="n">
-        <v>30390</v>
+        <v>30398</v>
       </c>
       <c r="H3" t="n">
-        <v>8982</v>
+        <v>8983</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="O3" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="R3" t="n">
-        <v>25800</v>
+        <v>25810</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:23</t>
+          <t>2026-06-14 18:06:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.64235</v>
+        <v>3.630378</v>
       </c>
       <c r="G4" t="n">
-        <v>24902</v>
+        <v>24910</v>
       </c>
       <c r="H4" t="n">
-        <v>5579</v>
+        <v>5580</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2560076</v>
+        <v>2561287</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7104</v>
+        <v>7176</v>
       </c>
       <c r="O4" t="n">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="P4" t="n">
-        <v>883</v>
+        <v>893</v>
       </c>
       <c r="Q4" t="n">
-        <v>1204</v>
+        <v>1185</v>
       </c>
       <c r="R4" t="n">
-        <v>14902</v>
+        <v>14841</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:24</t>
+          <t>2026-06-14 18:06:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.534542</v>
+        <v>4.5335917</v>
       </c>
       <c r="G5" t="n">
-        <v>25830</v>
+        <v>25837</v>
       </c>
       <c r="H5" t="n">
-        <v>9634</v>
+        <v>9637</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>651015</v>
+        <v>651390</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1962</v>
+        <v>1969</v>
       </c>
       <c r="O5" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P5" t="n">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="Q5" t="n">
-        <v>1661</v>
+        <v>1668</v>
       </c>
       <c r="R5" t="n">
-        <v>21089</v>
+        <v>21085</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:24</t>
+          <t>2026-06-14 18:06:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="G6" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H6" t="n">
         <v>162</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>100468</v>
+        <v>101240</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -871,19 +871,19 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:24</t>
+          <t>2026-06-14 18:06:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.768595</v>
+        <v>4.7663937</v>
       </c>
       <c r="G7" t="n">
-        <v>3086</v>
+        <v>3088</v>
       </c>
       <c r="H7" t="n">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -954,10 +954,10 @@
         <v>24</v>
       </c>
       <c r="Q7" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="R7" t="n">
-        <v>2842</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:25</t>
+          <t>2026-06-14 18:06:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1623135</v>
+        <v>4.18097</v>
       </c>
       <c r="G8" t="n">
-        <v>6006</v>
+        <v>6023</v>
       </c>
       <c r="H8" t="n">
-        <v>2240</v>
+        <v>2245</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1007</v>
+        <v>977</v>
       </c>
       <c r="O8" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P8" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="R8" t="n">
-        <v>4448</v>
+        <v>4472</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:25</t>
+          <t>2026-06-14 18:06:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>175325</v>
+        <v>175435</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:25</t>
+          <t>2026-06-14 18:06:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>86566</v>
+        <v>86753</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:26</t>
+          <t>2026-06-14 18:06:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6872144</v>
+        <v>4.687211</v>
       </c>
       <c r="G11" t="n">
-        <v>14619</v>
+        <v>14624</v>
       </c>
       <c r="H11" t="n">
         <v>693</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>249647</v>
+        <v>249814</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="O11" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q11" t="n">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="R11" t="n">
-        <v>12771</v>
+        <v>12775</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:26</t>
+          <t>2026-06-14 18:06:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7154047</v>
+        <v>2.7213542</v>
       </c>
       <c r="G12" t="n">
-        <v>4661</v>
+        <v>4662</v>
       </c>
       <c r="H12" t="n">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2433</v>
+        <v>2427</v>
       </c>
       <c r="O12" t="n">
         <v>121</v>
       </c>
       <c r="P12" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q12" t="n">
         <v>205</v>
       </c>
       <c r="R12" t="n">
-        <v>1726</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:26</t>
+          <t>2026-06-14 18:06:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21735</v>
+        <v>21750</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:27</t>
+          <t>2026-06-14 18:06:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4755435</v>
+        <v>3.477355</v>
       </c>
       <c r="G14" t="n">
-        <v>12024</v>
+        <v>12020</v>
       </c>
       <c r="H14" t="n">
-        <v>4677</v>
+        <v>4709</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="O14" t="n">
         <v>315</v>
       </c>
       <c r="P14" t="n">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="Q14" t="n">
         <v>391</v>
       </c>
       <c r="R14" t="n">
-        <v>6838</v>
+        <v>6847</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:27</t>
+          <t>2026-06-14 18:06:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3216374</v>
+        <v>3.3148687</v>
       </c>
       <c r="G15" t="n">
-        <v>3869</v>
+        <v>3870</v>
       </c>
       <c r="H15" t="n">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>388188</v>
+        <v>388606</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="O15" t="n">
         <v>123</v>
@@ -1545,7 +1545,7 @@
         <v>100</v>
       </c>
       <c r="R15" t="n">
-        <v>2092</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-13 18:02:27</t>
+          <t>2026-06-14 18:06:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.720668</v>
+        <v>4.719455</v>
       </c>
       <c r="G16" t="n">
-        <v>46653</v>
+        <v>46655</v>
       </c>
       <c r="H16" t="n">
         <v>2932</v>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2083</v>
+        <v>2093</v>
       </c>
       <c r="O16" t="n">
         <v>328</v>
       </c>
       <c r="P16" t="n">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="Q16" t="n">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="R16" t="n">
-        <v>41244</v>
+        <v>41228</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:35</t>
+          <t>2026-06-15 20:19:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="G2" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H2" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -591,7 +591,7 @@
         <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:35</t>
+          <t>2026-06-15 20:19:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4824786</v>
+        <v>4.481139</v>
       </c>
       <c r="G3" t="n">
-        <v>30398</v>
+        <v>30400</v>
       </c>
       <c r="H3" t="n">
         <v>8983</v>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2354710</v>
+        <v>2356630</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.42.1</t>
+          <t>4.43.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3419</v>
+        <v>3428</v>
       </c>
       <c r="O3" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q3" t="n">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="R3" t="n">
-        <v>25810</v>
+        <v>25801</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:35</t>
+          <t>2026-06-15 20:19:33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.630378</v>
       </c>
       <c r="G4" t="n">
-        <v>24910</v>
+        <v>24915</v>
       </c>
       <c r="H4" t="n">
         <v>5580</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2561287</v>
+        <v>2562223</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7176</v>
+        <v>7178</v>
       </c>
       <c r="O4" t="n">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="P4" t="n">
         <v>893</v>
@@ -739,7 +739,7 @@
         <v>1185</v>
       </c>
       <c r="R4" t="n">
-        <v>14841</v>
+        <v>14844</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:35</t>
+          <t>2026-06-15 20:19:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5335917</v>
+        <v>4.5373263</v>
       </c>
       <c r="G5" t="n">
-        <v>25837</v>
+        <v>25851</v>
       </c>
       <c r="H5" t="n">
-        <v>9637</v>
+        <v>9640</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1969</v>
+        <v>1952</v>
       </c>
       <c r="O5" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="P5" t="n">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="Q5" t="n">
-        <v>1668</v>
+        <v>1649</v>
       </c>
       <c r="R5" t="n">
-        <v>21085</v>
+        <v>21138</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:36</t>
+          <t>2026-06-15 20:19:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:36</t>
+          <t>2026-06-15 20:19:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7663937</v>
+        <v>4.7695475</v>
       </c>
       <c r="G7" t="n">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="H7" t="n">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         <v>24</v>
       </c>
       <c r="Q7" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="R7" t="n">
-        <v>2834</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:36</t>
+          <t>2026-06-15 20:19:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.18097</v>
+        <v>4.1862197</v>
       </c>
       <c r="G8" t="n">
-        <v>6023</v>
+        <v>6031</v>
       </c>
       <c r="H8" t="n">
-        <v>2245</v>
+        <v>2248</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>430059</v>
+        <v>430388</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="O8" t="n">
         <v>134</v>
       </c>
       <c r="P8" t="n">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="Q8" t="n">
         <v>258</v>
       </c>
       <c r="R8" t="n">
-        <v>4472</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:36</t>
+          <t>2026-06-15 20:19:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1067,7 +1067,7 @@
         <v>1216</v>
       </c>
       <c r="H9" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:36</t>
+          <t>2026-06-15 20:19:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>3.8921568</v>
       </c>
       <c r="G10" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H10" t="n">
         <v>224</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>86753</v>
+        <v>86754</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>26</v>
       </c>
       <c r="R10" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:37</t>
+          <t>2026-06-15 20:19:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.687211</v>
+        <v>4.690769</v>
       </c>
       <c r="G11" t="n">
-        <v>14624</v>
+        <v>14635</v>
       </c>
       <c r="H11" t="n">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1253,7 +1253,7 @@
         <v>720</v>
       </c>
       <c r="R11" t="n">
-        <v>12775</v>
+        <v>12799</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:37</t>
+          <t>2026-06-15 20:19:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7213542</v>
+        <v>2.7303665</v>
       </c>
       <c r="G12" t="n">
-        <v>4662</v>
+        <v>4663</v>
       </c>
       <c r="H12" t="n">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>348553</v>
+        <v>348768</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2427</v>
+        <v>2416</v>
       </c>
       <c r="O12" t="n">
         <v>121</v>
       </c>
       <c r="P12" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q12" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1735</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:37</t>
+          <t>2026-06-15 20:19:35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:37</t>
+          <t>2026-06-15 20:19:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.477355</v>
+        <v>3.6624203</v>
       </c>
       <c r="G14" t="n">
-        <v>12020</v>
+        <v>12111</v>
       </c>
       <c r="H14" t="n">
-        <v>4709</v>
+        <v>4749</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1219751</v>
+        <v>1219753</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4017</v>
+        <v>3547</v>
       </c>
       <c r="O14" t="n">
-        <v>315</v>
+        <v>252</v>
       </c>
       <c r="P14" t="n">
-        <v>445</v>
+        <v>417</v>
       </c>
       <c r="Q14" t="n">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="R14" t="n">
-        <v>6847</v>
+        <v>7481</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:38</t>
+          <t>2026-06-15 20:19:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3148687</v>
+        <v>3.3216374</v>
       </c>
       <c r="G15" t="n">
         <v>3870</v>
       </c>
       <c r="H15" t="n">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1466</v>
+        <v>1459</v>
       </c>
       <c r="O15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P15" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R15" t="n">
-        <v>2086</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-14 18:06:38</t>
+          <t>2026-06-15 20:19:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.719455</v>
+        <v>4.71784</v>
       </c>
       <c r="G16" t="n">
-        <v>46655</v>
+        <v>46659</v>
       </c>
       <c r="H16" t="n">
         <v>2932</v>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2093</v>
+        <v>2113</v>
       </c>
       <c r="O16" t="n">
         <v>328</v>
       </c>
       <c r="P16" t="n">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="Q16" t="n">
-        <v>2279</v>
+        <v>2277</v>
       </c>
       <c r="R16" t="n">
-        <v>41228</v>
+        <v>41214</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:33</t>
+          <t>2026-06-17 20:05:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.17</v>
       </c>
       <c r="G2" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H2" t="n">
         <v>164</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36906</v>
+        <v>37011</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -591,7 +591,7 @@
         <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:33</t>
+          <t>2026-06-17 20:05:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.481139</v>
+        <v>4.4783735</v>
       </c>
       <c r="G3" t="n">
-        <v>30400</v>
+        <v>30407</v>
       </c>
       <c r="H3" t="n">
-        <v>8983</v>
+        <v>8987</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2356630</v>
+        <v>2357374</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -649,11 +649,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Jun 6, 2026</t>
+          <t>Jun 15, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3428</v>
+        <v>3450</v>
       </c>
       <c r="O3" t="n">
         <v>292</v>
@@ -665,7 +665,7 @@
         <v>572</v>
       </c>
       <c r="R3" t="n">
-        <v>25801</v>
+        <v>25785</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:33</t>
+          <t>2026-06-17 20:05:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.630378</v>
+        <v>3.6269531</v>
       </c>
       <c r="G4" t="n">
-        <v>24915</v>
+        <v>24911</v>
       </c>
       <c r="H4" t="n">
         <v>5580</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2562223</v>
+        <v>2563482</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7178</v>
+        <v>7200</v>
       </c>
       <c r="O4" t="n">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="P4" t="n">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="Q4" t="n">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="R4" t="n">
-        <v>14844</v>
+        <v>14822</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:34</t>
+          <t>2026-06-17 20:05:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5373263</v>
+        <v>4.543799</v>
       </c>
       <c r="G5" t="n">
-        <v>25851</v>
+        <v>25863</v>
       </c>
       <c r="H5" t="n">
-        <v>9640</v>
+        <v>9646</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,11 +783,11 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>651390</v>
+        <v>652301</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -797,23 +797,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Jun 10, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1952</v>
+        <v>1906</v>
       </c>
       <c r="O5" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="Q5" t="n">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="R5" t="n">
-        <v>21138</v>
+        <v>21185</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:34</t>
+          <t>2026-06-17 20:05:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="G6" t="n">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H6" t="n">
         <v>162</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>101240</v>
+        <v>103561</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -871,19 +871,19 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:34</t>
+          <t>2026-06-17 20:05:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -916,7 +916,7 @@
         <v>4.7695475</v>
       </c>
       <c r="G7" t="n">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="H7" t="n">
         <v>1151</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>422375</v>
+        <v>423213</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>62</v>
       </c>
       <c r="R7" t="n">
-        <v>2845</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:34</t>
+          <t>2026-06-17 20:05:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1862197</v>
+        <v>4.17658</v>
       </c>
       <c r="G8" t="n">
-        <v>6031</v>
+        <v>6040</v>
       </c>
       <c r="H8" t="n">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>430388</v>
+        <v>430580</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>976</v>
+        <v>987</v>
       </c>
       <c r="O8" t="n">
         <v>134</v>
@@ -1028,10 +1028,10 @@
         <v>168</v>
       </c>
       <c r="Q8" t="n">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="R8" t="n">
-        <v>4491</v>
+        <v>4467</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:34</t>
+          <t>2026-06-17 20:05:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,7 +1064,7 @@
         <v>3.9906542</v>
       </c>
       <c r="G9" t="n">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="H9" t="n">
         <v>492</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>175435</v>
+        <v>175598</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:34</t>
+          <t>2026-06-17 20:05:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8921568</v>
+        <v>3.84</v>
       </c>
       <c r="G10" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H10" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>86754</v>
+        <v>87042</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:35</t>
+          <t>2026-06-17 20:05:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.690769</v>
+        <v>4.68894</v>
       </c>
       <c r="G11" t="n">
-        <v>14635</v>
+        <v>14642</v>
       </c>
       <c r="H11" t="n">
         <v>691</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>249814</v>
+        <v>249993</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1250,10 +1250,10 @@
         <v>247</v>
       </c>
       <c r="Q11" t="n">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="R11" t="n">
-        <v>12799</v>
+        <v>12808</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:35</t>
+          <t>2026-06-17 20:05:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7303665</v>
+        <v>2.7408378</v>
       </c>
       <c r="G12" t="n">
-        <v>4663</v>
+        <v>4665</v>
       </c>
       <c r="H12" t="n">
         <v>1923</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>348768</v>
+        <v>348889</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2416</v>
+        <v>2405</v>
       </c>
       <c r="O12" t="n">
         <v>121</v>
@@ -1323,7 +1323,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1744</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:35</t>
+          <t>2026-06-17 20:05:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21750</v>
+        <v>21767</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:35</t>
+          <t>2026-06-17 20:05:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.6624203</v>
+        <v>3.7836626</v>
       </c>
       <c r="G14" t="n">
-        <v>12111</v>
+        <v>12226</v>
       </c>
       <c r="H14" t="n">
-        <v>4749</v>
+        <v>4774</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,11 +1441,11 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1219753</v>
+        <v>1221839</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10.6.4</t>
+          <t>10.6.5</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1455,23 +1455,23 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Mar 27, 2026</t>
+          <t>May 20, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3547</v>
+        <v>3269</v>
       </c>
       <c r="O14" t="n">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="P14" t="n">
-        <v>417</v>
+        <v>383</v>
       </c>
       <c r="Q14" t="n">
-        <v>406</v>
+        <v>361</v>
       </c>
       <c r="R14" t="n">
-        <v>7481</v>
+        <v>7988</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:35</t>
+          <t>2026-06-17 20:05:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>388606</v>
+        <v>389094</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-15 20:19:35</t>
+          <t>2026-06-17 20:05:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.71784</v>
+        <v>4.717774</v>
       </c>
       <c r="G16" t="n">
-        <v>46659</v>
+        <v>46654</v>
       </c>
       <c r="H16" t="n">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>552259</v>
+        <v>553141</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1613,13 +1613,13 @@
         <v>328</v>
       </c>
       <c r="P16" t="n">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="Q16" t="n">
         <v>2277</v>
       </c>
       <c r="R16" t="n">
-        <v>41214</v>
+        <v>41209</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:06</t>
+          <t>2026-06-18 19:17:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,10 +550,10 @@
         <v>4.17</v>
       </c>
       <c r="G2" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H2" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>37011</v>
+        <v>37069</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:06</t>
+          <t>2026-06-18 19:17:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4783735</v>
+        <v>4.474539</v>
       </c>
       <c r="G3" t="n">
-        <v>30407</v>
+        <v>30418</v>
       </c>
       <c r="H3" t="n">
-        <v>8987</v>
+        <v>8991</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2357374</v>
+        <v>2358008</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3450</v>
+        <v>3479</v>
       </c>
       <c r="O3" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="R3" t="n">
-        <v>25785</v>
+        <v>25758</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:06</t>
+          <t>2026-06-18 19:17:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6269531</v>
+        <v>3.62833</v>
       </c>
       <c r="G4" t="n">
-        <v>24911</v>
+        <v>24917</v>
       </c>
       <c r="H4" t="n">
         <v>5580</v>
@@ -709,11 +709,11 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2563482</v>
+        <v>2565216</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.22.0</t>
+          <t>2.22.1.1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>May 21, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7200</v>
+        <v>7187</v>
       </c>
       <c r="O4" t="n">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="P4" t="n">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="Q4" t="n">
-        <v>1182</v>
+        <v>1213</v>
       </c>
       <c r="R4" t="n">
-        <v>14822</v>
+        <v>14813</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:06</t>
+          <t>2026-06-18 19:17:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.543799</v>
+        <v>4.544944</v>
       </c>
       <c r="G5" t="n">
-        <v>25863</v>
+        <v>25870</v>
       </c>
       <c r="H5" t="n">
-        <v>9646</v>
+        <v>9648</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>652301</v>
+        <v>652534</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -797,23 +797,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1906</v>
+        <v>1900</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="Q5" t="n">
-        <v>1648</v>
+        <v>1653</v>
       </c>
       <c r="R5" t="n">
-        <v>21185</v>
+        <v>21196</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:07</t>
+          <t>2026-06-18 19:17:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="G6" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H6" t="n">
         <v>162</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>103561</v>
+        <v>104297</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -871,19 +871,19 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:07</t>
+          <t>2026-06-18 19:17:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -916,7 +916,7 @@
         <v>4.7695475</v>
       </c>
       <c r="G7" t="n">
-        <v>3086</v>
+        <v>3087</v>
       </c>
       <c r="H7" t="n">
         <v>1151</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>423213</v>
+        <v>423542</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>62</v>
       </c>
       <c r="R7" t="n">
-        <v>2844</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:07</t>
+          <t>2026-06-18 19:17:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.17658</v>
+        <v>4.17963</v>
       </c>
       <c r="G8" t="n">
-        <v>6040</v>
+        <v>6044</v>
       </c>
       <c r="H8" t="n">
         <v>2250</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="O8" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P8" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q8" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R8" t="n">
-        <v>4467</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:07</t>
+          <t>2026-06-18 19:17:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,7 +1064,7 @@
         <v>3.9906542</v>
       </c>
       <c r="G9" t="n">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H9" t="n">
         <v>492</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>175598</v>
+        <v>175650</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:08</t>
+          <t>2026-06-18 19:17:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1141,7 +1141,7 @@
         <v>539</v>
       </c>
       <c r="H10" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>87042</v>
+        <v>87139</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:08</t>
+          <t>2026-06-18 19:17:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.68894</v>
+        <v>4.69468</v>
       </c>
       <c r="G11" t="n">
-        <v>14642</v>
+        <v>14649</v>
       </c>
       <c r="H11" t="n">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>249993</v>
+        <v>250071</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>719</v>
+        <v>700</v>
       </c>
       <c r="O11" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P11" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q11" t="n">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="R11" t="n">
-        <v>12808</v>
+        <v>12841</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:08</t>
+          <t>2026-06-18 19:17:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1286,10 +1286,10 @@
         <v>2.7408378</v>
       </c>
       <c r="G12" t="n">
-        <v>4665</v>
+        <v>4667</v>
       </c>
       <c r="H12" t="n">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="O12" t="n">
         <v>121</v>
@@ -1323,7 +1323,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:08</t>
+          <t>2026-06-18 19:17:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21767</v>
+        <v>21775</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:08</t>
+          <t>2026-06-18 19:17:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.7836626</v>
+        <v>3.832287</v>
       </c>
       <c r="G14" t="n">
-        <v>12226</v>
+        <v>12279</v>
       </c>
       <c r="H14" t="n">
-        <v>4774</v>
+        <v>4799</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1221839</v>
+        <v>1222429</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3269</v>
+        <v>3149</v>
       </c>
       <c r="O14" t="n">
         <v>219</v>
       </c>
       <c r="P14" t="n">
-        <v>383</v>
+        <v>362</v>
       </c>
       <c r="Q14" t="n">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="R14" t="n">
-        <v>7988</v>
+        <v>8192</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:09</t>
+          <t>2026-06-18 19:17:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.3216374</v>
       </c>
       <c r="G15" t="n">
-        <v>3870</v>
+        <v>3871</v>
       </c>
       <c r="H15" t="n">
         <v>1559</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>389094</v>
+        <v>389320</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,11 +1529,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-17 20:05:09</t>
+          <t>2026-06-18 19:17:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.717774</v>
+        <v>4.71784</v>
       </c>
       <c r="G16" t="n">
         <v>46654</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>553141</v>
+        <v>553507</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1613,13 +1613,13 @@
         <v>328</v>
       </c>
       <c r="P16" t="n">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="Q16" t="n">
         <v>2277</v>
       </c>
       <c r="R16" t="n">
-        <v>41209</v>
+        <v>41210</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:46</t>
+          <t>2026-06-19 18:27:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="G2" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H2" t="n">
         <v>165</v>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -591,7 +591,7 @@
         <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:47</t>
+          <t>2026-06-19 18:27:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.474539</v>
+        <v>4.4783893</v>
       </c>
       <c r="G3" t="n">
-        <v>30418</v>
+        <v>30424</v>
       </c>
       <c r="H3" t="n">
-        <v>8991</v>
+        <v>8993</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3479</v>
+        <v>3450</v>
       </c>
       <c r="O3" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q3" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="R3" t="n">
-        <v>25758</v>
+        <v>25792</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:47</t>
+          <t>2026-06-19 18:27:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.62833</v>
       </c>
       <c r="G4" t="n">
-        <v>24917</v>
+        <v>24915</v>
       </c>
       <c r="H4" t="n">
         <v>5580</v>
@@ -739,7 +739,7 @@
         <v>1213</v>
       </c>
       <c r="R4" t="n">
-        <v>14813</v>
+        <v>14812</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:47</t>
+          <t>2026-06-19 18:27:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.544944</v>
+        <v>4.541991</v>
       </c>
       <c r="G5" t="n">
-        <v>25870</v>
+        <v>25880</v>
       </c>
       <c r="H5" t="n">
-        <v>9648</v>
+        <v>9649</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1900</v>
+        <v>1915</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="Q5" t="n">
-        <v>1653</v>
+        <v>1645</v>
       </c>
       <c r="R5" t="n">
-        <v>21196</v>
+        <v>21184</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:47</t>
+          <t>2026-06-19 18:27:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -849,7 +849,7 @@
         <v>456</v>
       </c>
       <c r="H6" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:47</t>
+          <t>2026-06-19 18:27:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:47</t>
+          <t>2026-06-19 18:27:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.17963</v>
+        <v>4.1767955</v>
       </c>
       <c r="G8" t="n">
-        <v>6044</v>
+        <v>6048</v>
       </c>
       <c r="H8" t="n">
         <v>2250</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="O8" t="n">
         <v>133</v>
       </c>
       <c r="P8" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q8" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R8" t="n">
-        <v>4476</v>
+        <v>4477</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:48</t>
+          <t>2026-06-19 18:27:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:48</t>
+          <t>2026-06-19 18:27:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>3.84</v>
       </c>
       <c r="G10" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H10" t="n">
         <v>226</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:48</t>
+          <t>2026-06-19 18:27:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.69468</v>
+        <v>4.692071</v>
       </c>
       <c r="G11" t="n">
-        <v>14649</v>
+        <v>14656</v>
       </c>
       <c r="H11" t="n">
         <v>693</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="O11" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q11" t="n">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="R11" t="n">
-        <v>12841</v>
+        <v>12839</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:48</t>
+          <t>2026-06-19 18:27:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7408378</v>
+        <v>2.7362924</v>
       </c>
       <c r="G12" t="n">
-        <v>4667</v>
+        <v>4671</v>
       </c>
       <c r="H12" t="n">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2406</v>
+        <v>2425</v>
       </c>
       <c r="O12" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="P12" t="n">
         <v>170</v>
       </c>
       <c r="Q12" t="n">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="R12" t="n">
-        <v>1758</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:49</t>
+          <t>2026-06-19 18:27:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:49</t>
+          <t>2026-06-19 18:27:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.832287</v>
+        <v>3.9065003</v>
       </c>
       <c r="G14" t="n">
-        <v>12279</v>
+        <v>12361</v>
       </c>
       <c r="H14" t="n">
         <v>4799</v>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3149</v>
+        <v>2960</v>
       </c>
       <c r="O14" t="n">
         <v>219</v>
       </c>
       <c r="P14" t="n">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="Q14" t="n">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="R14" t="n">
-        <v>8192</v>
+        <v>8507</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:49</t>
+          <t>2026-06-19 18:27:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.3216374</v>
       </c>
       <c r="G15" t="n">
-        <v>3871</v>
+        <v>3872</v>
       </c>
       <c r="H15" t="n">
         <v>1559</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-18 19:17:50</t>
+          <t>2026-06-19 18:27:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.71784</v>
+        <v>4.717738</v>
       </c>
       <c r="G16" t="n">
-        <v>46654</v>
+        <v>46657</v>
       </c>
       <c r="H16" t="n">
         <v>2933</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="O16" t="n">
         <v>328</v>
@@ -1616,10 +1616,10 @@
         <v>721</v>
       </c>
       <c r="Q16" t="n">
-        <v>2277</v>
+        <v>2286</v>
       </c>
       <c r="R16" t="n">
-        <v>41210</v>
+        <v>41204</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:36</t>
+          <t>2026-06-20 18:04:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.13</v>
       </c>
       <c r="G2" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H2" t="n">
         <v>165</v>
@@ -588,10 +588,10 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R2" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:36</t>
+          <t>2026-06-20 18:04:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4783893</v>
+        <v>4.4820967</v>
       </c>
       <c r="G3" t="n">
-        <v>30424</v>
+        <v>30434</v>
       </c>
       <c r="H3" t="n">
-        <v>8993</v>
+        <v>8994</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2358008</v>
+        <v>2358831</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Jun 15, 2026</t>
+          <t>Jun 19, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3450</v>
+        <v>3414</v>
       </c>
       <c r="O3" t="n">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="P3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="R3" t="n">
-        <v>25792</v>
+        <v>25827</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:36</t>
+          <t>2026-06-20 18:04:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.62833</v>
       </c>
       <c r="G4" t="n">
-        <v>24915</v>
+        <v>24918</v>
       </c>
       <c r="H4" t="n">
         <v>5580</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Jun 17, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -739,7 +739,7 @@
         <v>1213</v>
       </c>
       <c r="R4" t="n">
-        <v>14812</v>
+        <v>14814</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:37</t>
+          <t>2026-06-20 18:04:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.541991</v>
+        <v>4.54109</v>
       </c>
       <c r="G5" t="n">
-        <v>25880</v>
+        <v>25892</v>
       </c>
       <c r="H5" t="n">
-        <v>9649</v>
+        <v>9652</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -797,11 +797,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jun 10, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
@@ -810,10 +810,10 @@
         <v>850</v>
       </c>
       <c r="Q5" t="n">
-        <v>1645</v>
+        <v>1679</v>
       </c>
       <c r="R5" t="n">
-        <v>21184</v>
+        <v>21165</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:37</t>
+          <t>2026-06-20 18:04:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>104297</v>
+        <v>105101</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:37</t>
+          <t>2026-06-20 18:04:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>423542</v>
+        <v>423839</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:37</t>
+          <t>2026-06-20 18:04:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -993,7 +993,7 @@
         <v>6048</v>
       </c>
       <c r="H8" t="n">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>430580</v>
+        <v>430647</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:37</t>
+          <t>2026-06-20 18:04:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>175650</v>
+        <v>175711</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:38</t>
+          <t>2026-06-20 18:04:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>87139</v>
+        <v>87204</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:38</t>
+          <t>2026-06-20 18:04:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.692071</v>
+        <v>4.692544</v>
       </c>
       <c r="G11" t="n">
-        <v>14656</v>
+        <v>14658</v>
       </c>
       <c r="H11" t="n">
         <v>693</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>250071</v>
+        <v>250138</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1250,10 +1250,10 @@
         <v>247</v>
       </c>
       <c r="Q11" t="n">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="R11" t="n">
-        <v>12839</v>
+        <v>12843</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:38</t>
+          <t>2026-06-20 18:04:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7362924</v>
+        <v>2.7454545</v>
       </c>
       <c r="G12" t="n">
-        <v>4671</v>
+        <v>4673</v>
       </c>
       <c r="H12" t="n">
         <v>1926</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>348889</v>
+        <v>348960</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2425</v>
+        <v>2414</v>
       </c>
       <c r="O12" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P12" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q12" t="n">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="R12" t="n">
-        <v>1768</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:38</t>
+          <t>2026-06-20 18:04:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:38</t>
+          <t>2026-06-20 18:04:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.9065003</v>
+        <v>3.9109528</v>
       </c>
       <c r="G14" t="n">
-        <v>12361</v>
+        <v>12367</v>
       </c>
       <c r="H14" t="n">
-        <v>4799</v>
+        <v>4803</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2960</v>
+        <v>2939</v>
       </c>
       <c r="O14" t="n">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="P14" t="n">
         <v>340</v>
@@ -1471,7 +1471,7 @@
         <v>329</v>
       </c>
       <c r="R14" t="n">
-        <v>8507</v>
+        <v>8523</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:38</t>
+          <t>2026-06-20 18:04:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1507,7 +1507,7 @@
         <v>3872</v>
       </c>
       <c r="H15" t="n">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>389320</v>
+        <v>389536</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-19 18:27:39</t>
+          <t>2026-06-20 18:04:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.717738</v>
+        <v>4.7178707</v>
       </c>
       <c r="G16" t="n">
-        <v>46657</v>
+        <v>46655</v>
       </c>
       <c r="H16" t="n">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>553507</v>
+        <v>553843</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="O16" t="n">
         <v>328</v>
@@ -1616,10 +1616,10 @@
         <v>721</v>
       </c>
       <c r="Q16" t="n">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="R16" t="n">
-        <v>41204</v>
+        <v>41205</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:12</t>
+          <t>2026-06-21 18:14:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:12</t>
+          <t>2026-06-21 18:14:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4820967</v>
+        <v>4.4813857</v>
       </c>
       <c r="G3" t="n">
-        <v>30434</v>
+        <v>30437</v>
       </c>
       <c r="H3" t="n">
-        <v>8994</v>
+        <v>8999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2358831</v>
+        <v>2359641</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3414</v>
+        <v>3421</v>
       </c>
       <c r="O3" t="n">
         <v>302</v>
@@ -665,7 +665,7 @@
         <v>583</v>
       </c>
       <c r="R3" t="n">
-        <v>25827</v>
+        <v>25825</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:13</t>
+          <t>2026-06-21 18:14:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.62833</v>
+        <v>3.627922</v>
       </c>
       <c r="G4" t="n">
         <v>24918</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2565216</v>
+        <v>2567019</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7187</v>
+        <v>7182</v>
       </c>
       <c r="O4" t="n">
         <v>808</v>
       </c>
       <c r="P4" t="n">
-        <v>890</v>
+        <v>904</v>
       </c>
       <c r="Q4" t="n">
         <v>1213</v>
       </c>
       <c r="R4" t="n">
-        <v>14814</v>
+        <v>14803</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:13</t>
+          <t>2026-06-21 18:14:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.54109</v>
+        <v>4.5431404</v>
       </c>
       <c r="G5" t="n">
-        <v>25892</v>
+        <v>25899</v>
       </c>
       <c r="H5" t="n">
-        <v>9652</v>
+        <v>9655</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>652534</v>
+        <v>653005</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -797,23 +797,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1914</v>
+        <v>1910</v>
       </c>
       <c r="O5" t="n">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="P5" t="n">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="Q5" t="n">
-        <v>1679</v>
+        <v>1686</v>
       </c>
       <c r="R5" t="n">
-        <v>21165</v>
+        <v>21183</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:13</t>
+          <t>2026-06-21 18:14:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>105101</v>
+        <v>106909</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:13</t>
+          <t>2026-06-21 18:14:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>423839</v>
+        <v>424420</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:13</t>
+          <t>2026-06-21 18:14:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -993,7 +993,7 @@
         <v>6048</v>
       </c>
       <c r="H8" t="n">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>430647</v>
+        <v>430949</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:14</t>
+          <t>2026-06-21 18:14:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:14</t>
+          <t>2026-06-21 18:14:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:14</t>
+          <t>2026-06-21 18:14:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.692544</v>
+        <v>4.6889915</v>
       </c>
       <c r="G11" t="n">
-        <v>14658</v>
+        <v>14662</v>
       </c>
       <c r="H11" t="n">
         <v>693</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>250138</v>
+        <v>250284</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1250,10 +1250,10 @@
         <v>247</v>
       </c>
       <c r="Q11" t="n">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="R11" t="n">
-        <v>12843</v>
+        <v>12833</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:14</t>
+          <t>2026-06-21 18:14:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7454545</v>
+        <v>2.7395833</v>
       </c>
       <c r="G12" t="n">
-        <v>4673</v>
+        <v>4671</v>
       </c>
       <c r="H12" t="n">
         <v>1926</v>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="O12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P12" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q12" t="n">
         <v>205</v>
       </c>
       <c r="R12" t="n">
-        <v>1771</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:14</t>
+          <t>2026-06-21 18:14:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:15</t>
+          <t>2026-06-21 18:14:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.9109528</v>
+        <v>3.9174068</v>
       </c>
       <c r="G14" t="n">
-        <v>12367</v>
+        <v>12380</v>
       </c>
       <c r="H14" t="n">
-        <v>4803</v>
+        <v>4820</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2939</v>
+        <v>2924</v>
       </c>
       <c r="O14" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="P14" t="n">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="Q14" t="n">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="R14" t="n">
-        <v>8523</v>
+        <v>8564</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:15</t>
+          <t>2026-06-21 18:14:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1507,7 +1507,7 @@
         <v>3872</v>
       </c>
       <c r="H15" t="n">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>389536</v>
+        <v>389952</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,11 +1529,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1545,7 +1545,7 @@
         <v>101</v>
       </c>
       <c r="R15" t="n">
-        <v>2093</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-20 18:04:15</t>
+          <t>2026-06-21 18:14:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1581,7 +1581,7 @@
         <v>46655</v>
       </c>
       <c r="H16" t="n">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:25</t>
+          <t>2026-06-22 19:59:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.13</v>
       </c>
       <c r="G2" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2" t="n">
         <v>165</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>37069</v>
+        <v>37160</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:25</t>
+          <t>2026-06-22 19:59:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4813857</v>
+        <v>4.478245</v>
       </c>
       <c r="G3" t="n">
-        <v>30437</v>
+        <v>30449</v>
       </c>
       <c r="H3" t="n">
-        <v>8999</v>
+        <v>9006</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2359641</v>
+        <v>2359642</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3421</v>
+        <v>3445</v>
       </c>
       <c r="O3" t="n">
         <v>302</v>
@@ -665,7 +665,7 @@
         <v>583</v>
       </c>
       <c r="R3" t="n">
-        <v>25825</v>
+        <v>25811</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:25</t>
+          <t>2026-06-22 19:59:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.627922</v>
+        <v>3.6262167</v>
       </c>
       <c r="G4" t="n">
-        <v>24918</v>
+        <v>24921</v>
       </c>
       <c r="H4" t="n">
         <v>5580</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2567019</v>
+        <v>2567020</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 17, 2026</t>
+          <t>Jun 21, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7182</v>
+        <v>7195</v>
       </c>
       <c r="O4" t="n">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="P4" t="n">
         <v>904</v>
       </c>
       <c r="Q4" t="n">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="R4" t="n">
-        <v>14803</v>
+        <v>14796</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:25</t>
+          <t>2026-06-22 19:59:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5431404</v>
+        <v>4.542351</v>
       </c>
       <c r="G5" t="n">
-        <v>25899</v>
+        <v>25913</v>
       </c>
       <c r="H5" t="n">
-        <v>9655</v>
+        <v>9661</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1910</v>
+        <v>1914</v>
       </c>
       <c r="O5" t="n">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>848</v>
+        <v>839</v>
       </c>
       <c r="Q5" t="n">
-        <v>1686</v>
+        <v>1679</v>
       </c>
       <c r="R5" t="n">
-        <v>21183</v>
+        <v>21198</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:25</t>
+          <t>2026-06-22 19:59:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="G6" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H6" t="n">
         <v>163</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>106909</v>
+        <v>106969</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -883,7 +883,7 @@
         <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:25</t>
+          <t>2026-06-22 19:59:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:26</t>
+          <t>2026-06-22 19:59:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1767955</v>
+        <v>4.178309</v>
       </c>
       <c r="G8" t="n">
-        <v>6048</v>
+        <v>6049</v>
       </c>
       <c r="H8" t="n">
         <v>2250</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>430949</v>
+        <v>430967</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="O8" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P8" t="n">
         <v>166</v>
       </c>
       <c r="Q8" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="R8" t="n">
-        <v>4477</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:26</t>
+          <t>2026-06-22 19:59:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>175711</v>
+        <v>175856</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:26</t>
+          <t>2026-06-22 19:59:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,10 +1138,10 @@
         <v>3.84</v>
       </c>
       <c r="G10" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H10" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>87204</v>
+        <v>87432</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:26</t>
+          <t>2026-06-22 19:59:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6889915</v>
+        <v>4.6906586</v>
       </c>
       <c r="G11" t="n">
-        <v>14662</v>
+        <v>14672</v>
       </c>
       <c r="H11" t="n">
         <v>693</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>250284</v>
+        <v>250288</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q11" t="n">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="R11" t="n">
-        <v>12833</v>
+        <v>12851</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:26</t>
+          <t>2026-06-22 19:59:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7395833</v>
+        <v>2.7512953</v>
       </c>
       <c r="G12" t="n">
-        <v>4671</v>
+        <v>4672</v>
       </c>
       <c r="H12" t="n">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>348960</v>
+        <v>349174</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2420</v>
+        <v>2408</v>
       </c>
       <c r="O12" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P12" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q12" t="n">
         <v>205</v>
       </c>
       <c r="R12" t="n">
-        <v>1763</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:26</t>
+          <t>2026-06-22 19:59:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21775</v>
+        <v>21782</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:26</t>
+          <t>2026-06-22 19:59:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.9174068</v>
+        <v>4.038053</v>
       </c>
       <c r="G14" t="n">
-        <v>12380</v>
+        <v>12453</v>
       </c>
       <c r="H14" t="n">
-        <v>4820</v>
+        <v>4842</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1222429</v>
+        <v>1223643</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2924</v>
+        <v>2599</v>
       </c>
       <c r="O14" t="n">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="P14" t="n">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="Q14" t="n">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="R14" t="n">
-        <v>8564</v>
+        <v>9024</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:27</t>
+          <t>2026-06-22 19:59:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3216374</v>
+        <v>3.3099415</v>
       </c>
       <c r="G15" t="n">
-        <v>3872</v>
+        <v>3873</v>
       </c>
       <c r="H15" t="n">
         <v>1562</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1459</v>
+        <v>1472</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1545,7 +1545,7 @@
         <v>101</v>
       </c>
       <c r="R15" t="n">
-        <v>2094</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-21 18:14:27</t>
+          <t>2026-06-22 19:59:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7178707</v>
+        <v>4.716194</v>
       </c>
       <c r="G16" t="n">
-        <v>46655</v>
+        <v>46658</v>
       </c>
       <c r="H16" t="n">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>553843</v>
+        <v>554537</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2111</v>
+        <v>2132</v>
       </c>
       <c r="O16" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P16" t="n">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="Q16" t="n">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="R16" t="n">
-        <v>41205</v>
+        <v>41190</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:34</t>
+          <t>2026-06-23 18:59:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:34</t>
+          <t>2026-06-23 18:59:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.478245</v>
+        <v>4.486716</v>
       </c>
       <c r="G3" t="n">
-        <v>30449</v>
+        <v>30457</v>
       </c>
       <c r="H3" t="n">
-        <v>9006</v>
+        <v>9003</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3445</v>
+        <v>3381</v>
       </c>
       <c r="O3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q3" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="R3" t="n">
-        <v>25811</v>
+        <v>25882</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:34</t>
+          <t>2026-06-23 18:59:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:35</t>
+          <t>2026-06-23 18:59:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.542351</v>
+        <v>4.542512</v>
       </c>
       <c r="G5" t="n">
-        <v>25913</v>
+        <v>25928</v>
       </c>
       <c r="H5" t="n">
-        <v>9661</v>
+        <v>9666</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>653005</v>
+        <v>653028</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>839</v>
+        <v>850</v>
       </c>
       <c r="Q5" t="n">
-        <v>1679</v>
+        <v>1667</v>
       </c>
       <c r="R5" t="n">
-        <v>21198</v>
+        <v>21216</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:35</t>
+          <t>2026-06-23 18:59:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:35</t>
+          <t>2026-06-23 18:59:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7695475</v>
+        <v>4.7540984</v>
       </c>
       <c r="G7" t="n">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="H7" t="n">
         <v>1151</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>424420</v>
+        <v>424427</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -957,7 +957,7 @@
         <v>62</v>
       </c>
       <c r="R7" t="n">
-        <v>2845</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:35</t>
+          <t>2026-06-23 18:59:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.178309</v>
+        <v>4.1798167</v>
       </c>
       <c r="G8" t="n">
-        <v>6049</v>
+        <v>6050</v>
       </c>
       <c r="H8" t="n">
         <v>2250</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="O8" t="n">
         <v>132</v>
@@ -1031,7 +1031,7 @@
         <v>277</v>
       </c>
       <c r="R8" t="n">
-        <v>4480</v>
+        <v>4483</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:35</t>
+          <t>2026-06-23 18:59:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:35</t>
+          <t>2026-06-23 18:59:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.84</v>
+        <v>3.862745</v>
       </c>
       <c r="G10" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H10" t="n">
         <v>227</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:35</t>
+          <t>2026-06-23 18:59:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6906586</v>
+        <v>4.6915383</v>
       </c>
       <c r="G11" t="n">
-        <v>14672</v>
+        <v>14679</v>
       </c>
       <c r="H11" t="n">
         <v>693</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q11" t="n">
-        <v>695</v>
+        <v>710</v>
       </c>
       <c r="R11" t="n">
-        <v>12851</v>
+        <v>12849</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:36</t>
+          <t>2026-06-23 18:59:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7512953</v>
+        <v>2.765013</v>
       </c>
       <c r="G12" t="n">
-        <v>4672</v>
+        <v>4676</v>
       </c>
       <c r="H12" t="n">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2408</v>
+        <v>2392</v>
       </c>
       <c r="O12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P12" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q12" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1778</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:36</t>
+          <t>2026-06-23 18:59:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:36</t>
+          <t>2026-06-23 18:59:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.038053</v>
+        <v>4.1491227</v>
       </c>
       <c r="G14" t="n">
-        <v>12453</v>
+        <v>12534</v>
       </c>
       <c r="H14" t="n">
-        <v>4842</v>
+        <v>4857</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2599</v>
+        <v>2296</v>
       </c>
       <c r="O14" t="n">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="P14" t="n">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="Q14" t="n">
-        <v>308</v>
+        <v>263</v>
       </c>
       <c r="R14" t="n">
-        <v>9024</v>
+        <v>9477</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:36</t>
+          <t>2026-06-23 18:59:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.3099415</v>
       </c>
       <c r="G15" t="n">
-        <v>3873</v>
+        <v>3874</v>
       </c>
       <c r="H15" t="n">
         <v>1562</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>389952</v>
+        <v>389983</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1545,7 +1545,7 @@
         <v>101</v>
       </c>
       <c r="R15" t="n">
-        <v>2083</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-22 19:59:36</t>
+          <t>2026-06-23 18:59:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.716194</v>
+        <v>4.71559</v>
       </c>
       <c r="G16" t="n">
-        <v>46658</v>
+        <v>46664</v>
       </c>
       <c r="H16" t="n">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2132</v>
+        <v>2140</v>
       </c>
       <c r="O16" t="n">
         <v>327</v>
@@ -1616,7 +1616,7 @@
         <v>720</v>
       </c>
       <c r="Q16" t="n">
-        <v>2284</v>
+        <v>2282</v>
       </c>
       <c r="R16" t="n">
         <v>41190</v>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:19</t>
+          <t>2026-06-24 18:26:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:19</t>
+          <t>2026-06-24 18:26:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.486716</v>
+        <v>4.486188</v>
       </c>
       <c r="G3" t="n">
-        <v>30457</v>
+        <v>30459</v>
       </c>
       <c r="H3" t="n">
-        <v>9003</v>
+        <v>9006</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.43.0</t>
+          <t>4.44.1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3381</v>
+        <v>3387</v>
       </c>
       <c r="O3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="R3" t="n">
-        <v>25882</v>
+        <v>25881</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:19</t>
+          <t>2026-06-24 18:26:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6262167</v>
+        <v>3.625405</v>
       </c>
       <c r="G4" t="n">
-        <v>24921</v>
+        <v>24928</v>
       </c>
       <c r="H4" t="n">
-        <v>5580</v>
+        <v>5581</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7195</v>
+        <v>7205</v>
       </c>
       <c r="O4" t="n">
         <v>807</v>
       </c>
       <c r="P4" t="n">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="Q4" t="n">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="R4" t="n">
         <v>14796</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:19</t>
+          <t>2026-06-24 18:26:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.542512</v>
+        <v>4.544315</v>
       </c>
       <c r="G5" t="n">
-        <v>25928</v>
+        <v>25943</v>
       </c>
       <c r="H5" t="n">
-        <v>9666</v>
+        <v>9674</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1912</v>
+        <v>1917</v>
       </c>
       <c r="O5" t="n">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="P5" t="n">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="Q5" t="n">
-        <v>1667</v>
+        <v>1659</v>
       </c>
       <c r="R5" t="n">
-        <v>21216</v>
+        <v>21254</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:20</t>
+          <t>2026-06-24 18:26:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:20</t>
+          <t>2026-06-24 18:26:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:20</t>
+          <t>2026-06-24 18:26:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:20</t>
+          <t>2026-06-24 18:26:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:21</t>
+          <t>2026-06-24 18:26:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:21</t>
+          <t>2026-06-24 18:26:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6915383</v>
+        <v>4.692249</v>
       </c>
       <c r="G11" t="n">
-        <v>14679</v>
+        <v>14682</v>
       </c>
       <c r="H11" t="n">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1250,10 +1250,10 @@
         <v>247</v>
       </c>
       <c r="Q11" t="n">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="R11" t="n">
-        <v>12849</v>
+        <v>12856</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:21</t>
+          <t>2026-06-24 18:26:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>4676</v>
       </c>
       <c r="H12" t="n">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:21</t>
+          <t>2026-06-24 18:26:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:21</t>
+          <t>2026-06-24 18:26:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.1491227</v>
+        <v>4.2246504</v>
       </c>
       <c r="G14" t="n">
-        <v>12534</v>
+        <v>12608</v>
       </c>
       <c r="H14" t="n">
-        <v>4857</v>
+        <v>4890</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2296</v>
+        <v>2093</v>
       </c>
       <c r="O14" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P14" t="n">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="Q14" t="n">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="R14" t="n">
-        <v>9477</v>
+        <v>9808</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:21</t>
+          <t>2026-06-24 18:26:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1507,7 +1507,7 @@
         <v>3874</v>
       </c>
       <c r="H15" t="n">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-23 18:59:22</t>
+          <t>2026-06-24 18:26:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.71559</v>
+        <v>4.714787</v>
       </c>
       <c r="G16" t="n">
-        <v>46664</v>
+        <v>46666</v>
       </c>
       <c r="H16" t="n">
         <v>2935</v>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2140</v>
+        <v>2150</v>
       </c>
       <c r="O16" t="n">
         <v>327</v>
       </c>
       <c r="P16" t="n">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="Q16" t="n">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="R16" t="n">
-        <v>41190</v>
+        <v>41184</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:12</t>
+          <t>2026-06-25 19:00:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:12</t>
+          <t>2026-06-25 19:00:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.486188</v>
+        <v>4.484323</v>
       </c>
       <c r="G3" t="n">
-        <v>30459</v>
+        <v>30465</v>
       </c>
       <c r="H3" t="n">
-        <v>9006</v>
+        <v>9007</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3387</v>
+        <v>3403</v>
       </c>
       <c r="O3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q3" t="n">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="R3" t="n">
-        <v>25881</v>
+        <v>25879</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:12</t>
+          <t>2026-06-25 19:00:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.625405</v>
+        <v>3.6263735</v>
       </c>
       <c r="G4" t="n">
-        <v>24928</v>
+        <v>24931</v>
       </c>
       <c r="H4" t="n">
-        <v>5581</v>
+        <v>5583</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 21, 2026</t>
+          <t>Jun 20, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7205</v>
+        <v>7202</v>
       </c>
       <c r="O4" t="n">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="P4" t="n">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="Q4" t="n">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="R4" t="n">
-        <v>14796</v>
+        <v>14809</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:13</t>
+          <t>2026-06-25 19:00:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.544315</v>
+        <v>4.5423145</v>
       </c>
       <c r="G5" t="n">
-        <v>25943</v>
+        <v>25962</v>
       </c>
       <c r="H5" t="n">
-        <v>9674</v>
+        <v>9679</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -797,23 +797,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jun 10, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1917</v>
+        <v>1938</v>
       </c>
       <c r="O5" t="n">
         <v>268</v>
       </c>
       <c r="P5" t="n">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="Q5" t="n">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="R5" t="n">
-        <v>21254</v>
+        <v>21264</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:13</t>
+          <t>2026-06-25 19:00:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:16</t>
+          <t>2026-06-25 19:00:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7540984</v>
+        <v>4.755102</v>
       </c>
       <c r="G7" t="n">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="H7" t="n">
         <v>1151</v>
@@ -957,7 +957,7 @@
         <v>62</v>
       </c>
       <c r="R7" t="n">
-        <v>2833</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:16</t>
+          <t>2026-06-25 19:00:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:17</t>
+          <t>2026-06-25 19:00:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:17</t>
+          <t>2026-06-25 19:00:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.862745</v>
+        <v>3.8349514</v>
       </c>
       <c r="G10" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H10" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:17</t>
+          <t>2026-06-25 19:00:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.692249</v>
+        <v>4.6920123</v>
       </c>
       <c r="G11" t="n">
-        <v>14682</v>
+        <v>14697</v>
       </c>
       <c r="H11" t="n">
         <v>694</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1250,10 +1250,10 @@
         <v>247</v>
       </c>
       <c r="Q11" t="n">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="R11" t="n">
-        <v>12856</v>
+        <v>12867</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:18</t>
+          <t>2026-06-25 19:00:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:18</t>
+          <t>2026-06-25 19:00:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:18</t>
+          <t>2026-06-25 19:00:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.2246504</v>
+        <v>4.3316064</v>
       </c>
       <c r="G14" t="n">
-        <v>12608</v>
+        <v>12706</v>
       </c>
       <c r="H14" t="n">
-        <v>4890</v>
+        <v>4910</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2093</v>
+        <v>1798</v>
       </c>
       <c r="O14" t="n">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="P14" t="n">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="Q14" t="n">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="R14" t="n">
-        <v>9808</v>
+        <v>10258</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:19</t>
+          <t>2026-06-25 19:00:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3099415</v>
+        <v>3.2982457</v>
       </c>
       <c r="G15" t="n">
         <v>3874</v>
@@ -1529,11 +1529,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1471</v>
+        <v>1482</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1545,7 +1545,7 @@
         <v>101</v>
       </c>
       <c r="R15" t="n">
-        <v>2084</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-24 18:26:19</t>
+          <t>2026-06-25 19:00:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1578,7 +1578,7 @@
         <v>4.714787</v>
       </c>
       <c r="G16" t="n">
-        <v>46666</v>
+        <v>46665</v>
       </c>
       <c r="H16" t="n">
         <v>2935</v>
@@ -1619,7 +1619,7 @@
         <v>2281</v>
       </c>
       <c r="R16" t="n">
-        <v>41184</v>
+        <v>41183</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:09</t>
+          <t>2026-06-26 18:20:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:09</t>
+          <t>2026-06-26 18:20:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.484323</v>
+        <v>4.483026</v>
       </c>
       <c r="G3" t="n">
-        <v>30465</v>
+        <v>30471</v>
       </c>
       <c r="H3" t="n">
-        <v>9007</v>
+        <v>9010</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3403</v>
+        <v>3406</v>
       </c>
       <c r="O3" t="n">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="P3" t="n">
         <v>303</v>
@@ -665,7 +665,7 @@
         <v>572</v>
       </c>
       <c r="R3" t="n">
-        <v>25879</v>
+        <v>25871</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:09</t>
+          <t>2026-06-26 18:20:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6263735</v>
+        <v>3.6281471</v>
       </c>
       <c r="G4" t="n">
-        <v>24931</v>
+        <v>24935</v>
       </c>
       <c r="H4" t="n">
         <v>5583</v>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 20, 2026</t>
+          <t>Jun 21, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7202</v>
+        <v>7194</v>
       </c>
       <c r="O4" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="P4" t="n">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="Q4" t="n">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="R4" t="n">
-        <v>14809</v>
+        <v>14824</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:09</t>
+          <t>2026-06-26 18:20:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5423145</v>
+        <v>4.5446315</v>
       </c>
       <c r="G5" t="n">
-        <v>25962</v>
+        <v>25975</v>
       </c>
       <c r="H5" t="n">
         <v>9679</v>
@@ -797,23 +797,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1938</v>
+        <v>1915</v>
       </c>
       <c r="O5" t="n">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="Q5" t="n">
-        <v>1658</v>
+        <v>1668</v>
       </c>
       <c r="R5" t="n">
-        <v>21264</v>
+        <v>21281</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:10</t>
+          <t>2026-06-26 18:20:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="G6" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H6" t="n">
         <v>163</v>
@@ -877,13 +877,13 @@
         <v>13</v>
       </c>
       <c r="P6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q6" t="n">
         <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:10</t>
+          <t>2026-06-26 18:20:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -916,7 +916,7 @@
         <v>4.755102</v>
       </c>
       <c r="G7" t="n">
-        <v>3089</v>
+        <v>3090</v>
       </c>
       <c r="H7" t="n">
         <v>1151</v>
@@ -957,7 +957,7 @@
         <v>62</v>
       </c>
       <c r="R7" t="n">
-        <v>2836</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:10</t>
+          <t>2026-06-26 18:20:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1798167</v>
+        <v>4.175503</v>
       </c>
       <c r="G8" t="n">
-        <v>6050</v>
+        <v>6052</v>
       </c>
       <c r="H8" t="n">
         <v>2250</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="O8" t="n">
         <v>132</v>
       </c>
       <c r="P8" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Q8" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="R8" t="n">
-        <v>4483</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:10</t>
+          <t>2026-06-26 18:20:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:11</t>
+          <t>2026-06-26 18:20:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8349514</v>
+        <v>3.92</v>
       </c>
       <c r="G10" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H10" t="n">
         <v>228</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:11</t>
+          <t>2026-06-26 18:20:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6920123</v>
+        <v>4.693548</v>
       </c>
       <c r="G11" t="n">
-        <v>14697</v>
+        <v>14703</v>
       </c>
       <c r="H11" t="n">
         <v>694</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="O11" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P11" t="n">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="Q11" t="n">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="R11" t="n">
-        <v>12867</v>
+        <v>12872</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:11</t>
+          <t>2026-06-26 18:20:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:11</t>
+          <t>2026-06-26 18:20:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:12</t>
+          <t>2026-06-26 18:20:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.3316064</v>
+        <v>4.4306507</v>
       </c>
       <c r="G14" t="n">
-        <v>12706</v>
+        <v>12834</v>
       </c>
       <c r="H14" t="n">
-        <v>4910</v>
+        <v>4904</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1798</v>
+        <v>1537</v>
       </c>
       <c r="O14" t="n">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="P14" t="n">
-        <v>230</v>
+        <v>196</v>
       </c>
       <c r="Q14" t="n">
-        <v>208</v>
+        <v>163</v>
       </c>
       <c r="R14" t="n">
-        <v>10258</v>
+        <v>10734</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:12</t>
+          <t>2026-06-26 18:20:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.2982457</v>
+        <v>3.2915452</v>
       </c>
       <c r="G15" t="n">
-        <v>3874</v>
+        <v>3876</v>
       </c>
       <c r="H15" t="n">
         <v>1563</v>
@@ -1529,23 +1529,23 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1482</v>
+        <v>1491</v>
       </c>
       <c r="O15" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P15" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R15" t="n">
-        <v>2072</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-25 19:00:12</t>
+          <t>2026-06-26 18:20:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.714787</v>
+        <v>4.713918</v>
       </c>
       <c r="G16" t="n">
-        <v>46665</v>
+        <v>46667</v>
       </c>
       <c r="H16" t="n">
         <v>2935</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2150</v>
+        <v>2161</v>
       </c>
       <c r="O16" t="n">
         <v>327</v>
@@ -1619,7 +1619,7 @@
         <v>2281</v>
       </c>
       <c r="R16" t="n">
-        <v>41183</v>
+        <v>41175</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:08</t>
+          <t>2026-06-27 17:53:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>37160</v>
+        <v>37199</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:08</t>
+          <t>2026-06-27 17:53:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.483026</v>
+        <v>4.483217</v>
       </c>
       <c r="G3" t="n">
-        <v>30471</v>
+        <v>30479</v>
       </c>
       <c r="H3" t="n">
-        <v>9010</v>
+        <v>9012</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>572</v>
       </c>
       <c r="R3" t="n">
-        <v>25871</v>
+        <v>25879</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:08</t>
+          <t>2026-06-27 17:53:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6281471</v>
+        <v>3.628866</v>
       </c>
       <c r="G4" t="n">
-        <v>24935</v>
+        <v>24942</v>
       </c>
       <c r="H4" t="n">
         <v>5583</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7194</v>
+        <v>7182</v>
       </c>
       <c r="O4" t="n">
-        <v>804</v>
+        <v>818</v>
       </c>
       <c r="P4" t="n">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="Q4" t="n">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="R4" t="n">
-        <v>14824</v>
+        <v>14833</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:09</t>
+          <t>2026-06-27 17:53:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5446315</v>
+        <v>4.5455723</v>
       </c>
       <c r="G5" t="n">
-        <v>25975</v>
+        <v>25984</v>
       </c>
       <c r="H5" t="n">
-        <v>9679</v>
+        <v>9682</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>653028</v>
+        <v>653342</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1915</v>
+        <v>1907</v>
       </c>
       <c r="O5" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P5" t="n">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="Q5" t="n">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="R5" t="n">
-        <v>21281</v>
+        <v>21291</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:09</t>
+          <t>2026-06-27 17:53:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>106969</v>
+        <v>107045</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:09</t>
+          <t>2026-06-27 17:53:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -916,7 +916,7 @@
         <v>4.755102</v>
       </c>
       <c r="G7" t="n">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="H7" t="n">
         <v>1151</v>
@@ -957,7 +957,7 @@
         <v>62</v>
       </c>
       <c r="R7" t="n">
-        <v>2837</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:09</t>
+          <t>2026-06-27 17:53:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.175503</v>
+        <v>4.177007</v>
       </c>
       <c r="G8" t="n">
-        <v>6052</v>
+        <v>6053</v>
       </c>
       <c r="H8" t="n">
         <v>2250</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>430967</v>
+        <v>431356</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="O8" t="n">
         <v>132</v>
@@ -1031,7 +1031,7 @@
         <v>275</v>
       </c>
       <c r="R8" t="n">
-        <v>4480</v>
+        <v>4483</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:09</t>
+          <t>2026-06-27 17:53:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>175856</v>
+        <v>175915</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:09</t>
+          <t>2026-06-27 17:53:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1141,7 +1141,7 @@
         <v>545</v>
       </c>
       <c r="H10" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>87432</v>
+        <v>87559</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:10</t>
+          <t>2026-06-27 17:53:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1212,7 +1212,7 @@
         <v>4.693548</v>
       </c>
       <c r="G11" t="n">
-        <v>14703</v>
+        <v>14704</v>
       </c>
       <c r="H11" t="n">
         <v>694</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>250288</v>
+        <v>250350</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>711</v>
       </c>
       <c r="R11" t="n">
-        <v>12872</v>
+        <v>12873</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:10</t>
+          <t>2026-06-27 17:53:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:10</t>
+          <t>2026-06-27 17:53:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21782</v>
+        <v>21784</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:10</t>
+          <t>2026-06-27 17:53:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.4306507</v>
+        <v>4.4301534</v>
       </c>
       <c r="G14" t="n">
-        <v>12834</v>
+        <v>12843</v>
       </c>
       <c r="H14" t="n">
-        <v>4904</v>
+        <v>4909</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1223643</v>
+        <v>1224283</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="O14" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P14" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q14" t="n">
         <v>163</v>
       </c>
       <c r="R14" t="n">
-        <v>10734</v>
+        <v>10741</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:10</t>
+          <t>2026-06-27 17:53:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>389983</v>
+        <v>390161</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-26 18:20:10</t>
+          <t>2026-06-27 17:53:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:25</t>
+          <t>2026-06-28 17:56:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>37199</v>
+        <v>37220</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:25</t>
+          <t>2026-06-28 17:56:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.483217</v>
+        <v>4.482314</v>
       </c>
       <c r="G3" t="n">
-        <v>30479</v>
+        <v>30482</v>
       </c>
       <c r="H3" t="n">
-        <v>9012</v>
+        <v>9013</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2359642</v>
+        <v>2361713</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3406</v>
+        <v>3414</v>
       </c>
       <c r="O3" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="R3" t="n">
-        <v>25879</v>
+        <v>25876</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:25</t>
+          <t>2026-06-28 17:56:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.628866</v>
+        <v>3.6156352</v>
       </c>
       <c r="G4" t="n">
-        <v>24942</v>
+        <v>24946</v>
       </c>
       <c r="H4" t="n">
-        <v>5583</v>
+        <v>5584</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2567020</v>
+        <v>2568355</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7182</v>
+        <v>7263</v>
       </c>
       <c r="O4" t="n">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="P4" t="n">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="Q4" t="n">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="R4" t="n">
-        <v>14833</v>
+        <v>14754</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:25</t>
+          <t>2026-06-28 17:56:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5455723</v>
+        <v>4.546356</v>
       </c>
       <c r="G5" t="n">
-        <v>25984</v>
+        <v>25988</v>
       </c>
       <c r="H5" t="n">
-        <v>9682</v>
+        <v>9686</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>653342</v>
+        <v>653493</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="O5" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="Q5" t="n">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="R5" t="n">
-        <v>21291</v>
+        <v>21302</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:25</t>
+          <t>2026-06-28 17:56:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>107045</v>
+        <v>107765</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:26</t>
+          <t>2026-06-28 17:56:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -916,10 +916,10 @@
         <v>4.755102</v>
       </c>
       <c r="G7" t="n">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="H7" t="n">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>424427</v>
+        <v>425019</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>62</v>
       </c>
       <c r="R7" t="n">
-        <v>2836</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:26</t>
+          <t>2026-06-28 17:56:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -993,7 +993,7 @@
         <v>6053</v>
       </c>
       <c r="H8" t="n">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>431356</v>
+        <v>431908</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:26</t>
+          <t>2026-06-28 17:56:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,7 +1064,7 @@
         <v>3.9906542</v>
       </c>
       <c r="G9" t="n">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H9" t="n">
         <v>492</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>175915</v>
+        <v>175955</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:26</t>
+          <t>2026-06-28 17:56:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="G10" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H10" t="n">
         <v>229</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>87559</v>
+        <v>87652</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:26</t>
+          <t>2026-06-28 17:56:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.693548</v>
+        <v>4.690184</v>
       </c>
       <c r="G11" t="n">
-        <v>14704</v>
+        <v>14706</v>
       </c>
       <c r="H11" t="n">
         <v>694</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>250350</v>
+        <v>250399</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="O11" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="R11" t="n">
-        <v>12873</v>
+        <v>12856</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:27</t>
+          <t>2026-06-28 17:56:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1286,7 +1286,7 @@
         <v>2.765013</v>
       </c>
       <c r="G12" t="n">
-        <v>4676</v>
+        <v>4677</v>
       </c>
       <c r="H12" t="n">
         <v>1928</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>349174</v>
+        <v>349320</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1323,7 +1323,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:27</t>
+          <t>2026-06-28 17:56:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:27</t>
+          <t>2026-06-28 17:56:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.4301534</v>
+        <v>4.443211</v>
       </c>
       <c r="G14" t="n">
-        <v>12843</v>
+        <v>12856</v>
       </c>
       <c r="H14" t="n">
-        <v>4909</v>
+        <v>4921</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1224283</v>
+        <v>1224733</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1541</v>
+        <v>1514</v>
       </c>
       <c r="O14" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="P14" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="Q14" t="n">
         <v>163</v>
       </c>
       <c r="R14" t="n">
-        <v>10741</v>
+        <v>10802</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:27</t>
+          <t>2026-06-28 17:56:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>390161</v>
+        <v>390313</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-27 17:53:27</t>
+          <t>2026-06-28 17:56:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.713918</v>
+        <v>4.713818</v>
       </c>
       <c r="G16" t="n">
         <v>46667</v>
       </c>
       <c r="H16" t="n">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>554537</v>
+        <v>555680</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="O16" t="n">
         <v>327</v>
@@ -1616,10 +1616,10 @@
         <v>719</v>
       </c>
       <c r="Q16" t="n">
-        <v>2281</v>
+        <v>2291</v>
       </c>
       <c r="R16" t="n">
-        <v>41175</v>
+        <v>41166</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:43</t>
+          <t>2026-06-29 18:56:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,7 +553,7 @@
         <v>383</v>
       </c>
       <c r="H2" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:43</t>
+          <t>2026-06-29 18:56:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -624,10 +624,10 @@
         <v>4.482314</v>
       </c>
       <c r="G3" t="n">
-        <v>30482</v>
+        <v>30488</v>
       </c>
       <c r="H3" t="n">
-        <v>9013</v>
+        <v>9017</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2361713</v>
+        <v>2363867</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Jun 19, 2026</t>
+          <t>Jun 28, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -665,7 +665,7 @@
         <v>571</v>
       </c>
       <c r="R3" t="n">
-        <v>25876</v>
+        <v>25881</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:43</t>
+          <t>2026-06-29 18:56:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6156352</v>
+        <v>3.6174366</v>
       </c>
       <c r="G4" t="n">
-        <v>24946</v>
+        <v>24951</v>
       </c>
       <c r="H4" t="n">
-        <v>5584</v>
+        <v>5586</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 21, 2026</t>
+          <t>Jun 20, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7263</v>
+        <v>7256</v>
       </c>
       <c r="O4" t="n">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="P4" t="n">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="Q4" t="n">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="R4" t="n">
-        <v>14754</v>
+        <v>14772</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:43</t>
+          <t>2026-06-29 18:56:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.546356</v>
+        <v>4.5458856</v>
       </c>
       <c r="G5" t="n">
-        <v>25988</v>
+        <v>26000</v>
       </c>
       <c r="H5" t="n">
         <v>9686</v>
@@ -797,23 +797,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jun 10, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="Q5" t="n">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="R5" t="n">
-        <v>21302</v>
+        <v>21305</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:43</t>
+          <t>2026-06-29 18:56:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:44</t>
+          <t>2026-06-29 18:56:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:44</t>
+          <t>2026-06-29 18:56:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.177007</v>
+        <v>4.1760435</v>
       </c>
       <c r="G8" t="n">
-        <v>6053</v>
+        <v>6056</v>
       </c>
       <c r="H8" t="n">
         <v>2252</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="O8" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P8" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="Q8" t="n">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="R8" t="n">
-        <v>4483</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:44</t>
+          <t>2026-06-29 18:56:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:44</t>
+          <t>2026-06-29 18:56:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1141,7 +1141,7 @@
         <v>546</v>
       </c>
       <c r="H10" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:44</t>
+          <t>2026-06-29 18:56:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.690184</v>
+        <v>4.689127</v>
       </c>
       <c r="G11" t="n">
-        <v>14706</v>
+        <v>14714</v>
       </c>
       <c r="H11" t="n">
         <v>694</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1250,10 +1250,10 @@
         <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>721</v>
+        <v>697</v>
       </c>
       <c r="R11" t="n">
-        <v>12856</v>
+        <v>12876</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:44</t>
+          <t>2026-06-29 18:56:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>4677</v>
       </c>
       <c r="H12" t="n">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>349320</v>
+        <v>349870</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:45</t>
+          <t>2026-06-29 18:56:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:45</t>
+          <t>2026-06-29 18:56:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.443211</v>
+        <v>4.497021</v>
       </c>
       <c r="G14" t="n">
-        <v>12856</v>
+        <v>12922</v>
       </c>
       <c r="H14" t="n">
-        <v>4921</v>
+        <v>4931</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1514</v>
+        <v>1352</v>
       </c>
       <c r="O14" t="n">
         <v>185</v>
       </c>
       <c r="P14" t="n">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="Q14" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="R14" t="n">
-        <v>10802</v>
+        <v>11029</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:45</t>
+          <t>2026-06-29 18:56:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-28 17:56:45</t>
+          <t>2026-06-29 18:56:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.713818</v>
+        <v>4.713885</v>
       </c>
       <c r="G16" t="n">
         <v>46667</v>
       </c>
       <c r="H16" t="n">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="O16" t="n">
         <v>327</v>
@@ -1616,10 +1616,10 @@
         <v>719</v>
       </c>
       <c r="Q16" t="n">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="R16" t="n">
-        <v>41166</v>
+        <v>41168</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:12</t>
+          <t>2026-06-30 18:27:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.13</v>
+        <v>4.1485147</v>
       </c>
       <c r="G2" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="H2" t="n">
         <v>167</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>37220</v>
+        <v>37494</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -588,10 +588,10 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:12</t>
+          <t>2026-06-30 18:27:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.482314</v>
+        <v>4.4801326</v>
       </c>
       <c r="G3" t="n">
-        <v>30488</v>
+        <v>30493</v>
       </c>
       <c r="H3" t="n">
-        <v>9017</v>
+        <v>9023</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2363867</v>
+        <v>2364583</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3414</v>
+        <v>3432</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
@@ -665,7 +665,7 @@
         <v>571</v>
       </c>
       <c r="R3" t="n">
-        <v>25881</v>
+        <v>25869</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:13</t>
+          <t>2026-06-30 18:27:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6174366</v>
+        <v>3.6201298</v>
       </c>
       <c r="G4" t="n">
-        <v>24951</v>
+        <v>24955</v>
       </c>
       <c r="H4" t="n">
-        <v>5586</v>
+        <v>5585</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2568355</v>
+        <v>2571737</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7256</v>
+        <v>7243</v>
       </c>
       <c r="O4" t="n">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="P4" t="n">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="Q4" t="n">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="R4" t="n">
-        <v>14772</v>
+        <v>14793</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:13</t>
+          <t>2026-06-30 18:27:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5458856</v>
+        <v>4.5472593</v>
       </c>
       <c r="G5" t="n">
-        <v>26000</v>
+        <v>26005</v>
       </c>
       <c r="H5" t="n">
-        <v>9686</v>
+        <v>9691</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>653493</v>
+        <v>655193</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1903</v>
+        <v>1896</v>
       </c>
       <c r="O5" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P5" t="n">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="Q5" t="n">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="R5" t="n">
-        <v>21305</v>
+        <v>21324</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:13</t>
+          <t>2026-06-30 18:27:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>107765</v>
+        <v>109499</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:13</t>
+          <t>2026-06-30 18:27:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>425019</v>
+        <v>426508</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:13</t>
+          <t>2026-06-30 18:27:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1760435</v>
+        <v>4.177536</v>
       </c>
       <c r="G8" t="n">
-        <v>6056</v>
+        <v>6057</v>
       </c>
       <c r="H8" t="n">
         <v>2252</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>431908</v>
+        <v>433965</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="O8" t="n">
         <v>131</v>
@@ -1031,7 +1031,7 @@
         <v>284</v>
       </c>
       <c r="R8" t="n">
-        <v>4473</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:14</t>
+          <t>2026-06-30 18:27:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>175955</v>
+        <v>176311</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:14</t>
+          <t>2026-06-30 18:27:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="G10" t="n">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H10" t="n">
         <v>230</v>
@@ -1149,11 +1149,11 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>87652</v>
+        <v>88227</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.8.9</t>
+          <t>0.9.0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1163,11 +1163,11 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>May 22, 2026</t>
+          <t>Jun 26, 2026</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>381</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:14</t>
+          <t>2026-06-30 18:27:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.689127</v>
+        <v>4.6878347</v>
       </c>
       <c r="G11" t="n">
-        <v>14714</v>
+        <v>14725</v>
       </c>
       <c r="H11" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>250399</v>
+        <v>250795</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1250,10 +1250,10 @@
         <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>697</v>
+        <v>675</v>
       </c>
       <c r="R11" t="n">
-        <v>12876</v>
+        <v>12899</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:14</t>
+          <t>2026-06-30 18:27:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.765013</v>
+        <v>2.7708333</v>
       </c>
       <c r="G12" t="n">
-        <v>4677</v>
+        <v>4678</v>
       </c>
       <c r="H12" t="n">
         <v>1929</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2393</v>
+        <v>2387</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1323,7 +1323,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1794</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:14</t>
+          <t>2026-06-30 18:27:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21784</v>
+        <v>21811</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:15</t>
+          <t>2026-06-30 18:27:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.497021</v>
+        <v>4.532203</v>
       </c>
       <c r="G14" t="n">
-        <v>12922</v>
+        <v>12964</v>
       </c>
       <c r="H14" t="n">
-        <v>4931</v>
+        <v>4938</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1224733</v>
+        <v>1228519</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1352</v>
+        <v>1251</v>
       </c>
       <c r="O14" t="n">
         <v>185</v>
       </c>
       <c r="P14" t="n">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="Q14" t="n">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="R14" t="n">
-        <v>11029</v>
+        <v>11194</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:15</t>
+          <t>2026-06-30 18:27:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>390313</v>
+        <v>391240</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56:15</t>
+          <t>2026-06-30 18:27:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.713885</v>
+        <v>4.713818</v>
       </c>
       <c r="G16" t="n">
-        <v>46667</v>
+        <v>46666</v>
       </c>
       <c r="H16" t="n">
         <v>2935</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>555680</v>
+        <v>556779</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="O16" t="n">
         <v>327</v>
@@ -1619,7 +1619,7 @@
         <v>2290</v>
       </c>
       <c r="R16" t="n">
-        <v>41168</v>
+        <v>41166</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:08</t>
+          <t>2026-07-01 18:53:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.1485147</v>
+        <v>4.14</v>
       </c>
       <c r="G2" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2" t="n">
         <v>167</v>
@@ -582,13 +582,13 @@
         <v>72</v>
       </c>
       <c r="O2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R2" t="n">
         <v>294</v>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:08</t>
+          <t>2026-07-01 18:53:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4801326</v>
+        <v>4.478261</v>
       </c>
       <c r="G3" t="n">
-        <v>30493</v>
+        <v>30495</v>
       </c>
       <c r="H3" t="n">
-        <v>9023</v>
+        <v>9025</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3432</v>
+        <v>3449</v>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q3" t="n">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="R3" t="n">
-        <v>25869</v>
+        <v>25865</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:09</t>
+          <t>2026-07-01 18:53:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6201298</v>
+        <v>3.6210253</v>
       </c>
       <c r="G4" t="n">
-        <v>24955</v>
+        <v>24958</v>
       </c>
       <c r="H4" t="n">
-        <v>5585</v>
+        <v>5586</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2571737</v>
+        <v>2572713</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7243</v>
+        <v>7238</v>
       </c>
       <c r="O4" t="n">
         <v>825</v>
@@ -736,10 +736,10 @@
         <v>890</v>
       </c>
       <c r="Q4" t="n">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="R4" t="n">
-        <v>14793</v>
+        <v>14802</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:09</t>
+          <t>2026-07-01 18:53:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5472593</v>
+        <v>4.5436935</v>
       </c>
       <c r="G5" t="n">
-        <v>26005</v>
+        <v>26021</v>
       </c>
       <c r="H5" t="n">
-        <v>9691</v>
+        <v>9698</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1896</v>
+        <v>1915</v>
       </c>
       <c r="O5" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="P5" t="n">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="Q5" t="n">
-        <v>1660</v>
+        <v>1657</v>
       </c>
       <c r="R5" t="n">
-        <v>21324</v>
+        <v>21315</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:09</t>
+          <t>2026-07-01 18:53:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:09</t>
+          <t>2026-07-01 18:53:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.755102</v>
+        <v>4.756098</v>
       </c>
       <c r="G7" t="n">
-        <v>3088</v>
+        <v>3090</v>
       </c>
       <c r="H7" t="n">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>426508</v>
+        <v>426849</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -957,7 +957,7 @@
         <v>62</v>
       </c>
       <c r="R7" t="n">
-        <v>2835</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:09</t>
+          <t>2026-07-01 18:53:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -993,7 +993,7 @@
         <v>6057</v>
       </c>
       <c r="H8" t="n">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:10</t>
+          <t>2026-07-01 18:53:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>176311</v>
+        <v>176400</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:10</t>
+          <t>2026-07-01 18:53:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>4.04</v>
       </c>
       <c r="G10" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H10" t="n">
         <v>230</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:10</t>
+          <t>2026-07-01 18:53:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6878347</v>
+        <v>4.684009</v>
       </c>
       <c r="G11" t="n">
-        <v>14725</v>
+        <v>14734</v>
       </c>
       <c r="H11" t="n">
         <v>695</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1250,10 +1250,10 @@
         <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="R11" t="n">
-        <v>12899</v>
+        <v>12884</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:10</t>
+          <t>2026-07-01 18:53:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7708333</v>
+        <v>2.775457</v>
       </c>
       <c r="G12" t="n">
-        <v>4678</v>
+        <v>4677</v>
       </c>
       <c r="H12" t="n">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>349870</v>
+        <v>350011</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2387</v>
+        <v>2380</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1323,7 +1323,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1802</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:10</t>
+          <t>2026-07-01 18:53:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21811</v>
+        <v>21826</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:11</t>
+          <t>2026-07-01 18:53:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.532203</v>
+        <v>4.5922165</v>
       </c>
       <c r="G14" t="n">
-        <v>12964</v>
+        <v>13006</v>
       </c>
       <c r="H14" t="n">
-        <v>4938</v>
+        <v>4942</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1251</v>
+        <v>1088</v>
       </c>
       <c r="O14" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="P14" t="n">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="Q14" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="R14" t="n">
-        <v>11194</v>
+        <v>11442</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:11</t>
+          <t>2026-07-01 18:53:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.2915452</v>
       </c>
       <c r="G15" t="n">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="H15" t="n">
         <v>1563</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>391240</v>
+        <v>391471</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>100</v>
       </c>
       <c r="R15" t="n">
-        <v>2066</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-30 18:27:11</t>
+          <t>2026-07-01 18:53:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.713818</v>
+        <v>4.7145863</v>
       </c>
       <c r="G16" t="n">
         <v>46666</v>
       </c>
       <c r="H16" t="n">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>556779</v>
+        <v>557237</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="O16" t="n">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="P16" t="n">
         <v>719</v>
@@ -1619,7 +1619,7 @@
         <v>2290</v>
       </c>
       <c r="R16" t="n">
-        <v>41166</v>
+        <v>41178</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:33</t>
+          <t>2026-07-02 18:22:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,7 +553,7 @@
         <v>388</v>
       </c>
       <c r="H2" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.4.7</t>
+          <t>0.5.4</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>May 3, 2026</t>
+          <t>Jul 2, 2026</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:33</t>
+          <t>2026-07-02 18:22:01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.478261</v>
+        <v>4.4790287</v>
       </c>
       <c r="G3" t="n">
-        <v>30495</v>
+        <v>30506</v>
       </c>
       <c r="H3" t="n">
-        <v>9025</v>
+        <v>9028</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3449</v>
+        <v>3445</v>
       </c>
       <c r="O3" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="R3" t="n">
-        <v>25865</v>
+        <v>25880</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:34</t>
+          <t>2026-07-02 18:22:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6210253</v>
+        <v>3.6165364</v>
       </c>
       <c r="G4" t="n">
-        <v>24958</v>
+        <v>24962</v>
       </c>
       <c r="H4" t="n">
         <v>5586</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7238</v>
+        <v>7280</v>
       </c>
       <c r="O4" t="n">
-        <v>825</v>
+        <v>812</v>
       </c>
       <c r="P4" t="n">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="Q4" t="n">
-        <v>1197</v>
+        <v>1186</v>
       </c>
       <c r="R4" t="n">
-        <v>14802</v>
+        <v>14787</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:34</t>
+          <t>2026-07-02 18:22:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5436935</v>
+        <v>4.5483456</v>
       </c>
       <c r="G5" t="n">
-        <v>26021</v>
+        <v>26038</v>
       </c>
       <c r="H5" t="n">
-        <v>9698</v>
+        <v>9703</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -797,11 +797,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026</t>
+          <t>Jun 11, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1915</v>
+        <v>1890</v>
       </c>
       <c r="O5" t="n">
         <v>290</v>
@@ -810,10 +810,10 @@
         <v>839</v>
       </c>
       <c r="Q5" t="n">
-        <v>1657</v>
+        <v>1644</v>
       </c>
       <c r="R5" t="n">
-        <v>21315</v>
+        <v>21371</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:34</t>
+          <t>2026-07-02 18:22:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:35</t>
+          <t>2026-07-02 18:22:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.756098</v>
+        <v>4.7489877</v>
       </c>
       <c r="G7" t="n">
-        <v>3090</v>
+        <v>3091</v>
       </c>
       <c r="H7" t="n">
         <v>1151</v>
@@ -951,13 +951,13 @@
         <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Q7" t="n">
         <v>62</v>
       </c>
       <c r="R7" t="n">
-        <v>2838</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:35</t>
+          <t>2026-07-02 18:22:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.177536</v>
+        <v>4.186257</v>
       </c>
       <c r="G8" t="n">
-        <v>6057</v>
+        <v>6058</v>
       </c>
       <c r="H8" t="n">
         <v>2253</v>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.1.26</t>
+          <t>2.1.27</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1015,11 +1015,11 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Jun 10, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>987</v>
+        <v>974</v>
       </c>
       <c r="O8" t="n">
         <v>131</v>
@@ -1028,10 +1028,10 @@
         <v>174</v>
       </c>
       <c r="Q8" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="R8" t="n">
-        <v>4476</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:35</t>
+          <t>2026-07-02 18:22:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.9906542</v>
+        <v>4.0280375</v>
       </c>
       <c r="G9" t="n">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H9" t="n">
         <v>492</v>
@@ -1089,11 +1089,11 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="O9" t="n">
         <v>34</v>
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>855</v>
+        <v>867</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:35</t>
+          <t>2026-07-02 18:22:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:36</t>
+          <t>2026-07-02 18:22:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.684009</v>
+        <v>4.6839695</v>
       </c>
       <c r="G11" t="n">
-        <v>14734</v>
+        <v>14744</v>
       </c>
       <c r="H11" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1250,10 +1250,10 @@
         <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="R11" t="n">
-        <v>12884</v>
+        <v>12886</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:36</t>
+          <t>2026-07-02 18:22:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.775457</v>
+        <v>2.765013</v>
       </c>
       <c r="G12" t="n">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="H12" t="n">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2380</v>
+        <v>2393</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1323,7 +1323,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1806</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:36</t>
+          <t>2026-07-02 18:22:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:36</t>
+          <t>2026-07-02 18:22:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.5922165</v>
+        <v>4.63644</v>
       </c>
       <c r="G14" t="n">
-        <v>13006</v>
+        <v>13040</v>
       </c>
       <c r="H14" t="n">
-        <v>4942</v>
+        <v>4947</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1088</v>
+        <v>963</v>
       </c>
       <c r="O14" t="n">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="P14" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="Q14" t="n">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="R14" t="n">
-        <v>11442</v>
+        <v>11627</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:36</t>
+          <t>2026-07-02 18:22:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,10 +1504,10 @@
         <v>3.2915452</v>
       </c>
       <c r="G15" t="n">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="H15" t="n">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1529,11 +1529,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="O15" t="n">
         <v>123</v>
@@ -1545,7 +1545,7 @@
         <v>100</v>
       </c>
       <c r="R15" t="n">
-        <v>2067</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-01 18:53:37</t>
+          <t>2026-07-02 18:22:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7145863</v>
+        <v>4.713318</v>
       </c>
       <c r="G16" t="n">
-        <v>46666</v>
+        <v>46668</v>
       </c>
       <c r="H16" t="n">
         <v>2936</v>
@@ -1610,16 +1610,16 @@
         <v>2158</v>
       </c>
       <c r="O16" t="n">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="P16" t="n">
         <v>719</v>
       </c>
       <c r="Q16" t="n">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="R16" t="n">
-        <v>41178</v>
+        <v>41161</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:01</t>
+          <t>2026-07-03 18:06:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.14</v>
+        <v>4.06</v>
       </c>
       <c r="G2" t="n">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="H2" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="O2" t="n">
         <v>7</v>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:01</t>
+          <t>2026-07-03 18:06:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4790287</v>
+        <v>4.477798</v>
       </c>
       <c r="G3" t="n">
-        <v>30506</v>
+        <v>30517</v>
       </c>
       <c r="H3" t="n">
-        <v>9028</v>
+        <v>9029</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2364583</v>
+        <v>2364584</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3445</v>
+        <v>3448</v>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="P3" t="n">
         <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="R3" t="n">
         <v>25880</v>
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:02</t>
+          <t>2026-07-03 18:06:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 20, 2026</t>
+          <t>Jun 21, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:02</t>
+          <t>2026-07-03 18:06:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5483456</v>
+        <v>4.5467067</v>
       </c>
       <c r="G5" t="n">
-        <v>26038</v>
+        <v>26050</v>
       </c>
       <c r="H5" t="n">
-        <v>9703</v>
+        <v>9705</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1890</v>
+        <v>1894</v>
       </c>
       <c r="O5" t="n">
         <v>290</v>
       </c>
       <c r="P5" t="n">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="Q5" t="n">
-        <v>1644</v>
+        <v>1670</v>
       </c>
       <c r="R5" t="n">
-        <v>21371</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:02</t>
+          <t>2026-07-03 18:06:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:02</t>
+          <t>2026-07-03 18:06:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>426849</v>
+        <v>426851</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:03</t>
+          <t>2026-07-03 18:06:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.186257</v>
+        <v>4.181982</v>
       </c>
       <c r="G8" t="n">
-        <v>6058</v>
+        <v>6060</v>
       </c>
       <c r="H8" t="n">
         <v>2253</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="O8" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P8" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q8" t="n">
         <v>283</v>
       </c>
       <c r="R8" t="n">
-        <v>4491</v>
+        <v>4487</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:03</t>
+          <t>2026-07-03 18:06:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,7 +1064,7 @@
         <v>4.0280375</v>
       </c>
       <c r="G9" t="n">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H9" t="n">
         <v>492</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>176400</v>
+        <v>176401</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:03</t>
+          <t>2026-07-03 18:06:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.04</v>
+        <v>3.970297</v>
       </c>
       <c r="G10" t="n">
         <v>549</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>394</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:03</t>
+          <t>2026-07-03 18:06:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6839695</v>
+        <v>4.684492</v>
       </c>
       <c r="G11" t="n">
-        <v>14744</v>
+        <v>14755</v>
       </c>
       <c r="H11" t="n">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1250,10 +1250,10 @@
         <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="R11" t="n">
-        <v>12886</v>
+        <v>12905</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:04</t>
+          <t>2026-07-03 18:06:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.765013</v>
+        <v>2.7708333</v>
       </c>
       <c r="G12" t="n">
-        <v>4679</v>
+        <v>4680</v>
       </c>
       <c r="H12" t="n">
         <v>1932</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2393</v>
+        <v>2388</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1323,7 +1323,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1795</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:04</t>
+          <t>2026-07-03 18:06:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:04</t>
+          <t>2026-07-03 18:06:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.63644</v>
+        <v>4.632155</v>
       </c>
       <c r="G14" t="n">
-        <v>13040</v>
+        <v>13042</v>
       </c>
       <c r="H14" t="n">
-        <v>4947</v>
+        <v>4944</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>963</v>
+        <v>976</v>
       </c>
       <c r="O14" t="n">
         <v>141</v>
@@ -1471,7 +1471,7 @@
         <v>152</v>
       </c>
       <c r="R14" t="n">
-        <v>11627</v>
+        <v>11613</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:04</t>
+          <t>2026-07-03 18:06:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.2915452</v>
+        <v>3.3119533</v>
       </c>
       <c r="G15" t="n">
-        <v>3874</v>
+        <v>3878</v>
       </c>
       <c r="H15" t="n">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1490</v>
+        <v>1469</v>
       </c>
       <c r="O15" t="n">
         <v>123</v>
@@ -1542,10 +1542,10 @@
         <v>89</v>
       </c>
       <c r="Q15" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="R15" t="n">
-        <v>2066</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-02 18:22:05</t>
+          <t>2026-07-03 18:06:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.713318</v>
+        <v>4.7133846</v>
       </c>
       <c r="G16" t="n">
         <v>46668</v>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="O16" t="n">
         <v>337</v>
       </c>
       <c r="P16" t="n">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="Q16" t="n">
         <v>2289</v>
       </c>
       <c r="R16" t="n">
-        <v>41161</v>
+        <v>41162</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:29</t>
+          <t>2026-07-04 17:53:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:29</t>
+          <t>2026-07-04 17:53:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.477798</v>
+        <v>4.4760675</v>
       </c>
       <c r="G3" t="n">
-        <v>30517</v>
+        <v>30519</v>
       </c>
       <c r="H3" t="n">
-        <v>9029</v>
+        <v>9030</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3448</v>
+        <v>3460</v>
       </c>
       <c r="O3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q3" t="n">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="R3" t="n">
-        <v>25880</v>
+        <v>25866</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:30</t>
+          <t>2026-07-04 17:53:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6165364</v>
+        <v>3.6161354</v>
       </c>
       <c r="G4" t="n">
-        <v>24962</v>
+        <v>24963</v>
       </c>
       <c r="H4" t="n">
         <v>5586</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7280</v>
+        <v>7275</v>
       </c>
       <c r="O4" t="n">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="P4" t="n">
-        <v>893</v>
+        <v>908</v>
       </c>
       <c r="Q4" t="n">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="R4" t="n">
-        <v>14787</v>
+        <v>14779</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:30</t>
+          <t>2026-07-04 17:53:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5467067</v>
+        <v>4.5478745</v>
       </c>
       <c r="G5" t="n">
-        <v>26050</v>
+        <v>26055</v>
       </c>
       <c r="H5" t="n">
-        <v>9705</v>
+        <v>9707</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1894</v>
+        <v>1890</v>
       </c>
       <c r="O5" t="n">
         <v>290</v>
       </c>
       <c r="P5" t="n">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="Q5" t="n">
-        <v>1670</v>
+        <v>1665</v>
       </c>
       <c r="R5" t="n">
-        <v>21350</v>
+        <v>21366</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:30</t>
+          <t>2026-07-04 17:53:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:30</t>
+          <t>2026-07-04 17:53:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:30</t>
+          <t>2026-07-04 17:53:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.181982</v>
+        <v>4.183453</v>
       </c>
       <c r="G8" t="n">
-        <v>6060</v>
+        <v>6061</v>
       </c>
       <c r="H8" t="n">
         <v>2253</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="O8" t="n">
         <v>130</v>
@@ -1028,10 +1028,10 @@
         <v>173</v>
       </c>
       <c r="Q8" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="R8" t="n">
-        <v>4487</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:30</t>
+          <t>2026-07-04 17:53:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:31</t>
+          <t>2026-07-04 17:53:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.970297</v>
+        <v>4.04</v>
       </c>
       <c r="G10" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="H10" t="n">
         <v>230</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>385</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:31</t>
+          <t>2026-07-04 17:53:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.684492</v>
+        <v>4.684009</v>
       </c>
       <c r="G11" t="n">
-        <v>14755</v>
+        <v>14763</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="O11" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P11" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q11" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="R11" t="n">
-        <v>12905</v>
+        <v>12909</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:31</t>
+          <t>2026-07-04 17:53:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:31</t>
+          <t>2026-07-04 17:53:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:31</t>
+          <t>2026-07-04 17:53:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.632155</v>
+        <v>4.6330814</v>
       </c>
       <c r="G14" t="n">
-        <v>13042</v>
+        <v>13046</v>
       </c>
       <c r="H14" t="n">
         <v>4944</v>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="O14" t="n">
         <v>141</v>
@@ -1471,7 +1471,7 @@
         <v>152</v>
       </c>
       <c r="R14" t="n">
-        <v>11613</v>
+        <v>11621</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:32</t>
+          <t>2026-07-04 17:53:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3119533</v>
+        <v>3.3411078</v>
       </c>
       <c r="G15" t="n">
-        <v>3878</v>
+        <v>3882</v>
       </c>
       <c r="H15" t="n">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1469</v>
+        <v>1436</v>
       </c>
       <c r="O15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P15" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="Q15" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="R15" t="n">
-        <v>2079</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-03 18:06:32</t>
+          <t>2026-07-04 17:53:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:14</t>
+          <t>2026-07-05 17:53:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:15</t>
+          <t>2026-07-05 17:53:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4760675</v>
+        <v>4.473878</v>
       </c>
       <c r="G3" t="n">
-        <v>30519</v>
+        <v>30521</v>
       </c>
       <c r="H3" t="n">
-        <v>9030</v>
+        <v>9033</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3460</v>
+        <v>3469</v>
       </c>
       <c r="O3" t="n">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="P3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="R3" t="n">
-        <v>25866</v>
+        <v>25849</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:15</t>
+          <t>2026-07-05 17:53:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -701,7 +701,7 @@
         <v>24963</v>
       </c>
       <c r="H4" t="n">
-        <v>5586</v>
+        <v>5589</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1184</v>
       </c>
       <c r="R4" t="n">
-        <v>14779</v>
+        <v>14778</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:15</t>
+          <t>2026-07-05 17:53:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5478745</v>
+        <v>4.5484977</v>
       </c>
       <c r="G5" t="n">
-        <v>26055</v>
+        <v>26059</v>
       </c>
       <c r="H5" t="n">
-        <v>9707</v>
+        <v>9715</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="O5" t="n">
         <v>290</v>
       </c>
       <c r="P5" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="Q5" t="n">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="R5" t="n">
-        <v>21366</v>
+        <v>21383</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:15</t>
+          <t>2026-07-05 17:53:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:15</t>
+          <t>2026-07-05 17:53:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7489877</v>
+        <v>4.75</v>
       </c>
       <c r="G7" t="n">
-        <v>3091</v>
+        <v>3092</v>
       </c>
       <c r="H7" t="n">
         <v>1151</v>
@@ -954,10 +954,10 @@
         <v>36</v>
       </c>
       <c r="Q7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R7" t="n">
-        <v>2827</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:15</t>
+          <t>2026-07-05 17:53:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -993,7 +993,7 @@
         <v>6061</v>
       </c>
       <c r="H8" t="n">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:16</t>
+          <t>2026-07-05 17:53:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:16</t>
+          <t>2026-07-05 17:53:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:16</t>
+          <t>2026-07-05 17:53:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.684009</v>
+        <v>4.6821647</v>
       </c>
       <c r="G11" t="n">
-        <v>14763</v>
+        <v>14769</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="O11" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="R11" t="n">
-        <v>12909</v>
+        <v>12910</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:16</t>
+          <t>2026-07-05 17:53:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:16</t>
+          <t>2026-07-05 17:53:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:16</t>
+          <t>2026-07-05 17:53:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6330814</v>
+        <v>4.633779</v>
       </c>
       <c r="G14" t="n">
-        <v>13046</v>
+        <v>13052</v>
       </c>
       <c r="H14" t="n">
-        <v>4944</v>
+        <v>4945</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,16 +1459,16 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="O14" t="n">
         <v>141</v>
       </c>
       <c r="P14" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q14" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="R14" t="n">
         <v>11621</v>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:16</t>
+          <t>2026-07-05 17:53:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3411078</v>
+        <v>3.3498542</v>
       </c>
       <c r="G15" t="n">
-        <v>3882</v>
+        <v>3884</v>
       </c>
       <c r="H15" t="n">
         <v>1567</v>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="O15" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="P15" t="n">
         <v>101</v>
@@ -1545,7 +1545,7 @@
         <v>113</v>
       </c>
       <c r="R15" t="n">
-        <v>2105</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-04 17:53:17</t>
+          <t>2026-07-05 17:53:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7133846</v>
+        <v>4.7135515</v>
       </c>
       <c r="G16" t="n">
-        <v>46668</v>
+        <v>46667</v>
       </c>
       <c r="H16" t="n">
         <v>2936</v>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="O16" t="n">
         <v>337</v>
       </c>
       <c r="P16" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="Q16" t="n">
-        <v>2289</v>
+        <v>2277</v>
       </c>
       <c r="R16" t="n">
-        <v>41162</v>
+        <v>41171</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:54</t>
+          <t>2026-07-06 18:50:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:54</t>
+          <t>2026-07-06 18:50:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.473878</v>
+        <v>4.4711714</v>
       </c>
       <c r="G3" t="n">
-        <v>30521</v>
+        <v>30528</v>
       </c>
       <c r="H3" t="n">
-        <v>9033</v>
+        <v>9039</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3469</v>
+        <v>3486</v>
       </c>
       <c r="O3" t="n">
         <v>335</v>
       </c>
       <c r="P3" t="n">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="Q3" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="R3" t="n">
-        <v>25849</v>
+        <v>25830</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:54</t>
+          <t>2026-07-06 18:50:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6161354</v>
+        <v>3.6162338</v>
       </c>
       <c r="G4" t="n">
-        <v>24963</v>
+        <v>24966</v>
       </c>
       <c r="H4" t="n">
-        <v>5589</v>
+        <v>5590</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 21, 2026</t>
+          <t>Jun 20, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7275</v>
+        <v>7278</v>
       </c>
       <c r="O4" t="n">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="P4" t="n">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="Q4" t="n">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="R4" t="n">
-        <v>14778</v>
+        <v>14783</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:54</t>
+          <t>2026-07-06 18:50:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5484977</v>
+        <v>4.5443635</v>
       </c>
       <c r="G5" t="n">
-        <v>26059</v>
+        <v>26075</v>
       </c>
       <c r="H5" t="n">
-        <v>9715</v>
+        <v>9717</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -797,23 +797,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jun 10, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1889</v>
+        <v>1910</v>
       </c>
       <c r="O5" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="P5" t="n">
         <v>838</v>
       </c>
       <c r="Q5" t="n">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="R5" t="n">
-        <v>21383</v>
+        <v>21368</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:55</t>
+          <t>2026-07-06 18:50:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:55</t>
+          <t>2026-07-06 18:50:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:55</t>
+          <t>2026-07-06 18:50:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.183453</v>
+        <v>4.18638</v>
       </c>
       <c r="G8" t="n">
-        <v>6061</v>
+        <v>6062</v>
       </c>
       <c r="H8" t="n">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="O8" t="n">
         <v>130</v>
       </c>
       <c r="P8" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q8" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R8" t="n">
-        <v>4490</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:55</t>
+          <t>2026-07-06 18:50:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:55</t>
+          <t>2026-07-06 18:50:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:55</t>
+          <t>2026-07-06 18:50:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6821647</v>
+        <v>4.6822</v>
       </c>
       <c r="G11" t="n">
-        <v>14769</v>
+        <v>14776</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1250,10 +1250,10 @@
         <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="R11" t="n">
-        <v>12910</v>
+        <v>12924</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:55</t>
+          <t>2026-07-06 18:50:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:56</t>
+          <t>2026-07-06 18:50:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:56</t>
+          <t>2026-07-06 18:50:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.633779</v>
+        <v>4.646167</v>
       </c>
       <c r="G14" t="n">
-        <v>13052</v>
+        <v>13058</v>
       </c>
       <c r="H14" t="n">
-        <v>4945</v>
+        <v>4946</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>970</v>
+        <v>934</v>
       </c>
       <c r="O14" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P14" t="n">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="Q14" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="R14" t="n">
-        <v>11621</v>
+        <v>11671</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:56</t>
+          <t>2026-07-06 18:50:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3498542</v>
+        <v>3.3430233</v>
       </c>
       <c r="G15" t="n">
         <v>3884</v>
       </c>
       <c r="H15" t="n">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1529,23 +1529,23 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1437</v>
+        <v>1444</v>
       </c>
       <c r="O15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="R15" t="n">
-        <v>2117</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-05 17:53:56</t>
+          <t>2026-07-06 18:50:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7135515</v>
+        <v>4.713685</v>
       </c>
       <c r="G16" t="n">
-        <v>46667</v>
+        <v>46665</v>
       </c>
       <c r="H16" t="n">
         <v>2936</v>
@@ -1607,16 +1607,16 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="O16" t="n">
         <v>337</v>
       </c>
       <c r="P16" t="n">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="Q16" t="n">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="R16" t="n">
         <v>41171</v>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:24</t>
+          <t>2026-07-07 18:53:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:24</t>
+          <t>2026-07-07 18:53:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4711714</v>
+        <v>4.46875</v>
       </c>
       <c r="G3" t="n">
-        <v>30528</v>
+        <v>30539</v>
       </c>
       <c r="H3" t="n">
-        <v>9039</v>
+        <v>9044</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2364584</v>
+        <v>2369193</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3486</v>
+        <v>3502</v>
       </c>
       <c r="O3" t="n">
         <v>335</v>
@@ -662,10 +662,10 @@
         <v>313</v>
       </c>
       <c r="Q3" t="n">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="R3" t="n">
-        <v>25830</v>
+        <v>25811</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:24</t>
+          <t>2026-07-07 18:53:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6162338</v>
+        <v>3.6145833</v>
       </c>
       <c r="G4" t="n">
-        <v>24966</v>
+        <v>24967</v>
       </c>
       <c r="H4" t="n">
-        <v>5590</v>
+        <v>5591</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 20, 2026</t>
+          <t>Jun 21, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7278</v>
+        <v>7281</v>
       </c>
       <c r="O4" t="n">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="P4" t="n">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="Q4" t="n">
-        <v>1182</v>
+        <v>1202</v>
       </c>
       <c r="R4" t="n">
-        <v>14783</v>
+        <v>14758</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:24</t>
+          <t>2026-07-07 18:53:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5443635</v>
+        <v>4.5453377</v>
       </c>
       <c r="G5" t="n">
-        <v>26075</v>
+        <v>26083</v>
       </c>
       <c r="H5" t="n">
-        <v>9717</v>
+        <v>9721</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,11 +783,11 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>655193</v>
+        <v>657491</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>391.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -797,23 +797,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026</t>
+          <t>Jul 1, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1910</v>
+        <v>1907</v>
       </c>
       <c r="O5" t="n">
         <v>300</v>
       </c>
       <c r="P5" t="n">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="Q5" t="n">
-        <v>1653</v>
+        <v>1650</v>
       </c>
       <c r="R5" t="n">
-        <v>21368</v>
+        <v>21385</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:24</t>
+          <t>2026-07-07 18:53:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:25</t>
+          <t>2026-07-07 18:53:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.75</v>
+        <v>4.7349396</v>
       </c>
       <c r="G7" t="n">
-        <v>3092</v>
+        <v>3093</v>
       </c>
       <c r="H7" t="n">
         <v>1151</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -957,7 +957,7 @@
         <v>61</v>
       </c>
       <c r="R7" t="n">
-        <v>2829</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:25</t>
+          <t>2026-07-07 18:53:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.18638</v>
+        <v>4.18068</v>
       </c>
       <c r="G8" t="n">
-        <v>6062</v>
+        <v>6064</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>976</v>
+        <v>987</v>
       </c>
       <c r="O8" t="n">
         <v>130</v>
@@ -1031,7 +1031,7 @@
         <v>281</v>
       </c>
       <c r="R8" t="n">
-        <v>4497</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:25</t>
+          <t>2026-07-07 18:53:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:25</t>
+          <t>2026-07-07 18:53:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:25</t>
+          <t>2026-07-07 18:53:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6822</v>
+        <v>4.684492</v>
       </c>
       <c r="G11" t="n">
-        <v>14776</v>
+        <v>14783</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="O11" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="P11" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q11" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="R11" t="n">
-        <v>12924</v>
+        <v>12941</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:26</t>
+          <t>2026-07-07 18:53:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:26</t>
+          <t>2026-07-07 18:53:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:26</t>
+          <t>2026-07-07 18:53:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.646167</v>
+        <v>4.6515913</v>
       </c>
       <c r="G14" t="n">
-        <v>13058</v>
+        <v>13078</v>
       </c>
       <c r="H14" t="n">
-        <v>4946</v>
+        <v>4948</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>934</v>
+        <v>919</v>
       </c>
       <c r="O14" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P14" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q14" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R14" t="n">
-        <v>11671</v>
+        <v>11707</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:26</t>
+          <t>2026-07-07 18:53:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3430233</v>
+        <v>3.3381925</v>
       </c>
       <c r="G15" t="n">
-        <v>3884</v>
+        <v>3886</v>
       </c>
       <c r="H15" t="n">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1529,23 +1529,23 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1444</v>
+        <v>1449</v>
       </c>
       <c r="O15" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q15" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="R15" t="n">
-        <v>2110</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-06 18:50:27</t>
+          <t>2026-07-07 18:53:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.713685</v>
+        <v>4.713819</v>
       </c>
       <c r="G16" t="n">
-        <v>46665</v>
+        <v>46667</v>
       </c>
       <c r="H16" t="n">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="O16" t="n">
         <v>337</v>
@@ -1616,10 +1616,10 @@
         <v>718</v>
       </c>
       <c r="Q16" t="n">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="R16" t="n">
-        <v>41171</v>
+        <v>41175</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:15</t>
+          <t>2026-07-08 18:12:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:15</t>
+          <t>2026-07-08 18:12:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.46875</v>
+        <v>4.4686007</v>
       </c>
       <c r="G3" t="n">
-        <v>30539</v>
+        <v>30552</v>
       </c>
       <c r="H3" t="n">
-        <v>9044</v>
+        <v>9045</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2369193</v>
+        <v>2370120</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.44.1</t>
+          <t>4.44.2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3502</v>
+        <v>3511</v>
       </c>
       <c r="O3" t="n">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="P3" t="n">
         <v>313</v>
       </c>
       <c r="Q3" t="n">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="R3" t="n">
-        <v>25811</v>
+        <v>25816</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:16</t>
+          <t>2026-07-08 18:12:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6145833</v>
+        <v>3.6154847</v>
       </c>
       <c r="G4" t="n">
-        <v>24967</v>
+        <v>24970</v>
       </c>
       <c r="H4" t="n">
         <v>5591</v>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 21, 2026</t>
+          <t>Jun 20, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7281</v>
+        <v>7277</v>
       </c>
       <c r="O4" t="n">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="P4" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="Q4" t="n">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="R4" t="n">
-        <v>14758</v>
+        <v>14767</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:16</t>
+          <t>2026-07-08 18:12:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5453377</v>
+        <v>4.546352</v>
       </c>
       <c r="G5" t="n">
-        <v>26083</v>
+        <v>26091</v>
       </c>
       <c r="H5" t="n">
-        <v>9721</v>
+        <v>9725</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1907</v>
+        <v>1914</v>
       </c>
       <c r="O5" t="n">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="Q5" t="n">
-        <v>1650</v>
+        <v>1657</v>
       </c>
       <c r="R5" t="n">
-        <v>21385</v>
+        <v>21398</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:16</t>
+          <t>2026-07-08 18:12:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:16</t>
+          <t>2026-07-08 18:12:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:16</t>
+          <t>2026-07-08 18:12:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:16</t>
+          <t>2026-07-08 18:12:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,7 +1064,7 @@
         <v>4.0280375</v>
       </c>
       <c r="G9" t="n">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H9" t="n">
         <v>492</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:16</t>
+          <t>2026-07-08 18:12:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:17</t>
+          <t>2026-07-08 18:12:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.684492</v>
+        <v>4.6849732</v>
       </c>
       <c r="G11" t="n">
-        <v>14783</v>
+        <v>14787</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="O11" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P11" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="R11" t="n">
-        <v>12941</v>
+        <v>12948</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:17</t>
+          <t>2026-07-08 18:12:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7708333</v>
+        <v>2.765013</v>
       </c>
       <c r="G12" t="n">
-        <v>4680</v>
+        <v>4679</v>
       </c>
       <c r="H12" t="n">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>350011</v>
+        <v>350732</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2388</v>
+        <v>2393</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1323,7 +1323,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1802</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:17</t>
+          <t>2026-07-08 18:12:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:17</t>
+          <t>2026-07-08 18:12:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6515913</v>
+        <v>4.6850457</v>
       </c>
       <c r="G14" t="n">
-        <v>13078</v>
+        <v>13097</v>
       </c>
       <c r="H14" t="n">
-        <v>4948</v>
+        <v>4949</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>919</v>
+        <v>842</v>
       </c>
       <c r="O14" t="n">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="P14" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="Q14" t="n">
         <v>163</v>
       </c>
       <c r="R14" t="n">
-        <v>11707</v>
+        <v>11849</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:17</t>
+          <t>2026-07-08 18:12:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.3381925</v>
       </c>
       <c r="G15" t="n">
-        <v>3886</v>
+        <v>3888</v>
       </c>
       <c r="H15" t="n">
         <v>1567</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>391471</v>
+        <v>391472</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1545,7 +1545,7 @@
         <v>113</v>
       </c>
       <c r="R15" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-07 18:53:18</t>
+          <t>2026-07-08 18:12:14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.713819</v>
+        <v>4.712952</v>
       </c>
       <c r="G16" t="n">
-        <v>46667</v>
+        <v>46670</v>
       </c>
       <c r="H16" t="n">
         <v>2937</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2156</v>
+        <v>2166</v>
       </c>
       <c r="O16" t="n">
         <v>337</v>
@@ -1619,7 +1619,7 @@
         <v>2275</v>
       </c>
       <c r="R16" t="n">
-        <v>41175</v>
+        <v>41169</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:11</t>
+          <t>2026-07-09 18:44:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>37494</v>
+        <v>37942</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:11</t>
+          <t>2026-07-09 18:44:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4686007</v>
+        <v>4.4688997</v>
       </c>
       <c r="G3" t="n">
-        <v>30552</v>
+        <v>30554</v>
       </c>
       <c r="H3" t="n">
-        <v>9045</v>
+        <v>9046</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Jun 28, 2026</t>
+          <t>Jul 8, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3511</v>
+        <v>3508</v>
       </c>
       <c r="O3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q3" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="R3" t="n">
-        <v>25816</v>
+        <v>25818</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:11</t>
+          <t>2026-07-09 18:44:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6154847</v>
+        <v>3.6180873</v>
       </c>
       <c r="G4" t="n">
         <v>24970</v>
       </c>
       <c r="H4" t="n">
-        <v>5591</v>
+        <v>5593</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2572713</v>
+        <v>2578789</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -723,11 +723,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 20, 2026</t>
+          <t>Jun 21, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7277</v>
+        <v>7261</v>
       </c>
       <c r="O4" t="n">
         <v>810</v>
@@ -739,7 +739,7 @@
         <v>1200</v>
       </c>
       <c r="R4" t="n">
-        <v>14767</v>
+        <v>14783</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:12</t>
+          <t>2026-07-09 18:44:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.546352</v>
+        <v>4.5476394</v>
       </c>
       <c r="G5" t="n">
-        <v>26091</v>
+        <v>26101</v>
       </c>
       <c r="H5" t="n">
-        <v>9725</v>
+        <v>9734</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>657491</v>
+        <v>657998</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>839</v>
+        <v>827</v>
       </c>
       <c r="Q5" t="n">
-        <v>1657</v>
+        <v>1645</v>
       </c>
       <c r="R5" t="n">
-        <v>21398</v>
+        <v>21429</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:12</t>
+          <t>2026-07-09 18:44:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>109499</v>
+        <v>109792</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:12</t>
+          <t>2026-07-09 18:44:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>426851</v>
+        <v>429891</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:12</t>
+          <t>2026-07-09 18:44:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -990,7 +990,7 @@
         <v>4.18068</v>
       </c>
       <c r="G8" t="n">
-        <v>6064</v>
+        <v>6065</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>433965</v>
+        <v>437132</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:12</t>
+          <t>2026-07-09 18:44:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>176401</v>
+        <v>177137</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:13</t>
+          <t>2026-07-09 18:44:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>4.04</v>
       </c>
       <c r="G10" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H10" t="n">
         <v>230</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>88227</v>
+        <v>89065</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:13</t>
+          <t>2026-07-09 18:44:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6849732</v>
+        <v>4.6885495</v>
       </c>
       <c r="G11" t="n">
-        <v>14787</v>
+        <v>14797</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>250795</v>
+        <v>251560</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="O11" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P11" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q11" t="n">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="R11" t="n">
-        <v>12948</v>
+        <v>12977</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:13</t>
+          <t>2026-07-09 18:44:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.765013</v>
+        <v>2.7708333</v>
       </c>
       <c r="G12" t="n">
-        <v>4679</v>
+        <v>4682</v>
       </c>
       <c r="H12" t="n">
         <v>1933</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>350732</v>
+        <v>350895</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2393</v>
+        <v>2389</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1323,7 +1323,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1795</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:13</t>
+          <t>2026-07-09 18:44:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21826</v>
+        <v>21885</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:14</t>
+          <t>2026-07-09 18:44:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6850457</v>
+        <v>4.7035174</v>
       </c>
       <c r="G14" t="n">
-        <v>13097</v>
+        <v>13107</v>
       </c>
       <c r="H14" t="n">
-        <v>4949</v>
+        <v>4952</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1228519</v>
+        <v>1234956</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>842</v>
+        <v>790</v>
       </c>
       <c r="O14" t="n">
         <v>108</v>
       </c>
       <c r="P14" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="Q14" t="n">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="R14" t="n">
-        <v>11849</v>
+        <v>11931</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:14</t>
+          <t>2026-07-09 18:44:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.3381925</v>
       </c>
       <c r="G15" t="n">
-        <v>3888</v>
+        <v>3889</v>
       </c>
       <c r="H15" t="n">
         <v>1567</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>391472</v>
+        <v>393594</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,11 +1529,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="O15" t="n">
         <v>113</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-08 18:12:14</t>
+          <t>2026-07-09 18:44:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>557237</v>
+        <v>560298</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:39</t>
+          <t>2026-07-10 18:15:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:40</t>
+          <t>2026-07-10 18:15:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4688997</v>
+        <v>4.469875</v>
       </c>
       <c r="G3" t="n">
-        <v>30554</v>
+        <v>30559</v>
       </c>
       <c r="H3" t="n">
-        <v>9046</v>
+        <v>9047</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3508</v>
+        <v>3502</v>
       </c>
       <c r="O3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P3" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q3" t="n">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="R3" t="n">
-        <v>25818</v>
+        <v>25831</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:40</t>
+          <t>2026-07-10 18:15:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6180873</v>
+        <v>3.6204662</v>
       </c>
       <c r="G4" t="n">
-        <v>24970</v>
+        <v>24982</v>
       </c>
       <c r="H4" t="n">
         <v>5593</v>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 21, 2026</t>
+          <t>Jun 20, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7261</v>
+        <v>7247</v>
       </c>
       <c r="O4" t="n">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="P4" t="n">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="Q4" t="n">
-        <v>1200</v>
+        <v>1228</v>
       </c>
       <c r="R4" t="n">
-        <v>14783</v>
+        <v>14788</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:40</t>
+          <t>2026-07-10 18:15:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5476394</v>
+        <v>4.5480685</v>
       </c>
       <c r="G5" t="n">
-        <v>26101</v>
+        <v>26121</v>
       </c>
       <c r="H5" t="n">
-        <v>9734</v>
+        <v>9735</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="O5" t="n">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="P5" t="n">
-        <v>827</v>
+        <v>806</v>
       </c>
       <c r="Q5" t="n">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="R5" t="n">
-        <v>21429</v>
+        <v>21457</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:40</t>
+          <t>2026-07-10 18:15:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.64</v>
       </c>
       <c r="G6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H6" t="n">
         <v>163</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:40</t>
+          <t>2026-07-10 18:15:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:41</t>
+          <t>2026-07-10 18:15:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:41</t>
+          <t>2026-07-10 18:15:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1067,7 +1067,7 @@
         <v>1224</v>
       </c>
       <c r="H9" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>177137</v>
+        <v>177140</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:41</t>
+          <t>2026-07-10 18:15:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>4.04</v>
       </c>
       <c r="G10" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H10" t="n">
         <v>230</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>89065</v>
+        <v>89066</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:41</t>
+          <t>2026-07-10 18:15:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6885495</v>
+        <v>4.68845</v>
       </c>
       <c r="G11" t="n">
-        <v>14797</v>
+        <v>14804</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="O11" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P11" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="R11" t="n">
-        <v>12977</v>
+        <v>12969</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:41</t>
+          <t>2026-07-10 18:15:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7708333</v>
+        <v>2.765013</v>
       </c>
       <c r="G12" t="n">
         <v>4682</v>
       </c>
       <c r="H12" t="n">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2389</v>
+        <v>2395</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
       </c>
       <c r="P12" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q12" t="n">
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1803</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:41</t>
+          <t>2026-07-10 18:15:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:42</t>
+          <t>2026-07-10 18:15:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7035174</v>
+        <v>4.74728</v>
       </c>
       <c r="G14" t="n">
-        <v>13107</v>
+        <v>13133</v>
       </c>
       <c r="H14" t="n">
-        <v>4952</v>
+        <v>4953</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>790</v>
+        <v>658</v>
       </c>
       <c r="O14" t="n">
+        <v>97</v>
+      </c>
+      <c r="P14" t="n">
         <v>108</v>
       </c>
-      <c r="P14" t="n">
-        <v>119</v>
-      </c>
       <c r="Q14" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="R14" t="n">
-        <v>11931</v>
+        <v>12099</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:42</t>
+          <t>2026-07-10 18:15:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1507,7 +1507,7 @@
         <v>3889</v>
       </c>
       <c r="H15" t="n">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>393594</v>
+        <v>393595</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-09 18:44:42</t>
+          <t>2026-07-10 18:15:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.712952</v>
+        <v>4.7120857</v>
       </c>
       <c r="G16" t="n">
-        <v>46670</v>
+        <v>46668</v>
       </c>
       <c r="H16" t="n">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2166</v>
+        <v>2176</v>
       </c>
       <c r="O16" t="n">
         <v>337</v>
@@ -1616,10 +1616,10 @@
         <v>718</v>
       </c>
       <c r="Q16" t="n">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="R16" t="n">
-        <v>41169</v>
+        <v>41157</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:17</t>
+          <t>2026-07-11 17:44:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:17</t>
+          <t>2026-07-11 17:44:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.469875</v>
+        <v>4.4707613</v>
       </c>
       <c r="G3" t="n">
-        <v>30559</v>
+        <v>30567</v>
       </c>
       <c r="H3" t="n">
         <v>9047</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2370120</v>
+        <v>2370121</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3502</v>
+        <v>3495</v>
       </c>
       <c r="O3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q3" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="R3" t="n">
-        <v>25831</v>
+        <v>25844</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:17</t>
+          <t>2026-07-11 17:44:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6204662</v>
+        <v>3.6231415</v>
       </c>
       <c r="G4" t="n">
-        <v>24982</v>
+        <v>24987</v>
       </c>
       <c r="H4" t="n">
         <v>5593</v>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 20, 2026</t>
+          <t>Jun 21, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7247</v>
+        <v>7235</v>
       </c>
       <c r="O4" t="n">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="P4" t="n">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="Q4" t="n">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="R4" t="n">
-        <v>14788</v>
+        <v>14811</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:17</t>
+          <t>2026-07-11 17:44:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5480685</v>
+        <v>4.5426855</v>
       </c>
       <c r="G5" t="n">
-        <v>26121</v>
+        <v>26135</v>
       </c>
       <c r="H5" t="n">
-        <v>9735</v>
+        <v>9737</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>657998</v>
+        <v>657999</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1916</v>
+        <v>1949</v>
       </c>
       <c r="O5" t="n">
         <v>290</v>
       </c>
       <c r="P5" t="n">
-        <v>806</v>
+        <v>795</v>
       </c>
       <c r="Q5" t="n">
-        <v>1646</v>
+        <v>1681</v>
       </c>
       <c r="R5" t="n">
-        <v>21457</v>
+        <v>21414</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:18</t>
+          <t>2026-07-11 17:44:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.64</v>
       </c>
       <c r="G6" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H6" t="n">
         <v>163</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -883,7 +883,7 @@
         <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:18</t>
+          <t>2026-07-11 17:44:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:18</t>
+          <t>2026-07-11 17:44:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.18068</v>
+        <v>4.1821427</v>
       </c>
       <c r="G8" t="n">
-        <v>6065</v>
+        <v>6066</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="O8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P8" t="n">
         <v>172</v>
@@ -1031,7 +1031,7 @@
         <v>281</v>
       </c>
       <c r="R8" t="n">
-        <v>4490</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:18</t>
+          <t>2026-07-11 17:44:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,7 +1064,7 @@
         <v>4.0280375</v>
       </c>
       <c r="G9" t="n">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H9" t="n">
         <v>493</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:18</t>
+          <t>2026-07-11 17:44:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1141,7 +1141,7 @@
         <v>553</v>
       </c>
       <c r="H10" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:19</t>
+          <t>2026-07-11 17:44:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.68845</v>
+        <v>4.687976</v>
       </c>
       <c r="G11" t="n">
-        <v>14804</v>
+        <v>14808</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1223,11 +1223,11 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>251560</v>
+        <v>251561</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.0.45</t>
+          <t>1.1.0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1237,11 +1237,11 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>May 21, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="O11" t="n">
         <v>145</v>
@@ -1250,10 +1250,10 @@
         <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="R11" t="n">
-        <v>12969</v>
+        <v>12970</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:19</t>
+          <t>2026-07-11 17:44:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.765013</v>
+        <v>2.775457</v>
       </c>
       <c r="G12" t="n">
-        <v>4682</v>
+        <v>4683</v>
       </c>
       <c r="H12" t="n">
         <v>1934</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2395</v>
+        <v>2383</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1323,7 +1323,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1796</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:19</t>
+          <t>2026-07-11 17:44:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:19</t>
+          <t>2026-07-11 17:44:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.74728</v>
+        <v>4.7610693</v>
       </c>
       <c r="G14" t="n">
-        <v>13133</v>
+        <v>13149</v>
       </c>
       <c r="H14" t="n">
-        <v>4953</v>
+        <v>4956</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>658</v>
+        <v>614</v>
       </c>
       <c r="O14" t="n">
         <v>97</v>
@@ -1471,7 +1471,7 @@
         <v>163</v>
       </c>
       <c r="R14" t="n">
-        <v>12099</v>
+        <v>12159</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:19</t>
+          <t>2026-07-11 17:44:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3381925</v>
+        <v>3.3430233</v>
       </c>
       <c r="G15" t="n">
-        <v>3889</v>
+        <v>3891</v>
       </c>
       <c r="H15" t="n">
         <v>1569</v>
@@ -1529,11 +1529,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="O15" t="n">
         <v>113</v>
@@ -1545,7 +1545,7 @@
         <v>113</v>
       </c>
       <c r="R15" t="n">
-        <v>2107</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-10 18:15:20</t>
+          <t>2026-07-11 17:44:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7120857</v>
+        <v>4.71192</v>
       </c>
       <c r="G16" t="n">
         <v>46668</v>
@@ -1613,13 +1613,13 @@
         <v>337</v>
       </c>
       <c r="P16" t="n">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="Q16" t="n">
-        <v>2274</v>
+        <v>2285</v>
       </c>
       <c r="R16" t="n">
-        <v>41157</v>
+        <v>41147</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:18</t>
+          <t>2026-07-12 17:46:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:18</t>
+          <t>2026-07-12 17:46:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4707613</v>
+        <v>4.471691</v>
       </c>
       <c r="G3" t="n">
-        <v>30567</v>
+        <v>30569</v>
       </c>
       <c r="H3" t="n">
-        <v>9047</v>
+        <v>9048</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2370121</v>
+        <v>2375361</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Jul 8, 2026</t>
+          <t>Jul 12, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3495</v>
+        <v>3483</v>
       </c>
       <c r="O3" t="n">
         <v>325</v>
       </c>
       <c r="P3" t="n">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="Q3" t="n">
         <v>584</v>
       </c>
       <c r="R3" t="n">
-        <v>25844</v>
+        <v>25848</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:19</t>
+          <t>2026-07-12 17:46:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6231415</v>
+        <v>3.6258066</v>
       </c>
       <c r="G4" t="n">
-        <v>24987</v>
+        <v>24992</v>
       </c>
       <c r="H4" t="n">
         <v>5593</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7235</v>
+        <v>7222</v>
       </c>
       <c r="O4" t="n">
         <v>806</v>
       </c>
       <c r="P4" t="n">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="Q4" t="n">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="R4" t="n">
-        <v>14811</v>
+        <v>14832</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:19</t>
+          <t>2026-07-12 17:46:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5426855</v>
+        <v>4.542808</v>
       </c>
       <c r="G5" t="n">
-        <v>26135</v>
+        <v>26141</v>
       </c>
       <c r="H5" t="n">
         <v>9737</v>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1949</v>
+        <v>1946</v>
       </c>
       <c r="O5" t="n">
         <v>290</v>
       </c>
       <c r="P5" t="n">
-        <v>795</v>
+        <v>805</v>
       </c>
       <c r="Q5" t="n">
-        <v>1681</v>
+        <v>1678</v>
       </c>
       <c r="R5" t="n">
-        <v>21414</v>
+        <v>21417</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:19</t>
+          <t>2026-07-12 17:46:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:19</t>
+          <t>2026-07-12 17:46:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7349396</v>
+        <v>4.736</v>
       </c>
       <c r="G7" t="n">
-        <v>3093</v>
+        <v>3095</v>
       </c>
       <c r="H7" t="n">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>429891</v>
+        <v>432795</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>61</v>
       </c>
       <c r="R7" t="n">
-        <v>2818</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:20</t>
+          <t>2026-07-12 17:46:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1821427</v>
+        <v>4.183601</v>
       </c>
       <c r="G8" t="n">
         <v>6066</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>437132</v>
+        <v>437134</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="O8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P8" t="n">
         <v>172</v>
       </c>
       <c r="Q8" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R8" t="n">
-        <v>4494</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:20</t>
+          <t>2026-07-12 17:46:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:20</t>
+          <t>2026-07-12 17:46:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.04</v>
+        <v>4.0495048</v>
       </c>
       <c r="G10" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H10" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>89066</v>
+        <v>89628</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:21</t>
+          <t>2026-07-12 17:46:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.687976</v>
+        <v>4.686738</v>
       </c>
       <c r="G11" t="n">
-        <v>14808</v>
+        <v>14817</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="O11" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P11" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q11" t="n">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="R11" t="n">
-        <v>12970</v>
+        <v>12964</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:21</t>
+          <t>2026-07-12 17:46:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>350895</v>
+        <v>351596</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:21</t>
+          <t>2026-07-12 17:46:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21885</v>
+        <v>21928</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:22</t>
+          <t>2026-07-12 17:46:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7610693</v>
+        <v>4.758966</v>
       </c>
       <c r="G14" t="n">
         <v>13149</v>
       </c>
       <c r="H14" t="n">
-        <v>4956</v>
+        <v>4957</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="O14" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="P14" t="n">
         <v>108</v>
@@ -1471,7 +1471,7 @@
         <v>163</v>
       </c>
       <c r="R14" t="n">
-        <v>12159</v>
+        <v>12150</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:22</t>
+          <t>2026-07-12 17:46:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 17:44:22</t>
+          <t>2026-07-12 17:46:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1578,7 +1578,7 @@
         <v>4.71192</v>
       </c>
       <c r="G16" t="n">
-        <v>46668</v>
+        <v>46670</v>
       </c>
       <c r="H16" t="n">
         <v>2938</v>
@@ -1619,7 +1619,7 @@
         <v>2285</v>
       </c>
       <c r="R16" t="n">
-        <v>41147</v>
+        <v>41149</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:31</t>
+          <t>2026-07-13 18:24:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,7 +553,7 @@
         <v>392</v>
       </c>
       <c r="H2" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>37942</v>
+        <v>38309</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:31</t>
+          <t>2026-07-13 18:24:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.471691</v>
+        <v>4.4706316</v>
       </c>
       <c r="G3" t="n">
-        <v>30569</v>
+        <v>30577</v>
       </c>
       <c r="H3" t="n">
-        <v>9048</v>
+        <v>9051</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.44.2</t>
+          <t>4.44.4</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3483</v>
+        <v>3489</v>
       </c>
       <c r="O3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q3" t="n">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="R3" t="n">
-        <v>25848</v>
+        <v>25839</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:31</t>
+          <t>2026-07-13 18:24:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6258066</v>
+        <v>3.624031</v>
       </c>
       <c r="G4" t="n">
-        <v>24992</v>
+        <v>24990</v>
       </c>
       <c r="H4" t="n">
         <v>5593</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2578789</v>
+        <v>2584231</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7222</v>
+        <v>7231</v>
       </c>
       <c r="O4" t="n">
         <v>806</v>
       </c>
       <c r="P4" t="n">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="Q4" t="n">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="R4" t="n">
-        <v>14832</v>
+        <v>14818</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:31</t>
+          <t>2026-07-13 18:24:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.542808</v>
+        <v>4.543348</v>
       </c>
       <c r="G5" t="n">
-        <v>26141</v>
+        <v>26144</v>
       </c>
       <c r="H5" t="n">
-        <v>9737</v>
+        <v>9743</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>657999</v>
+        <v>660416</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1946</v>
+        <v>1940</v>
       </c>
       <c r="O5" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P5" t="n">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="Q5" t="n">
-        <v>1678</v>
+        <v>1682</v>
       </c>
       <c r="R5" t="n">
-        <v>21417</v>
+        <v>21419</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:31</t>
+          <t>2026-07-13 18:24:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.64</v>
       </c>
       <c r="G6" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H6" t="n">
         <v>163</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>109792</v>
+        <v>110013</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:32</t>
+          <t>2026-07-13 18:24:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.736</v>
+        <v>4.737052</v>
       </c>
       <c r="G7" t="n">
-        <v>3095</v>
+        <v>3096</v>
       </c>
       <c r="H7" t="n">
         <v>1152</v>
@@ -957,7 +957,7 @@
         <v>61</v>
       </c>
       <c r="R7" t="n">
-        <v>2821</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:32</t>
+          <t>2026-07-13 18:24:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>437134</v>
+        <v>440269</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:32</t>
+          <t>2026-07-13 18:24:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>177140</v>
+        <v>177753</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:32</t>
+          <t>2026-07-13 18:24:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.0495048</v>
+        <v>4.019608</v>
       </c>
       <c r="G10" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H10" t="n">
         <v>232</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:32</t>
+          <t>2026-07-13 18:24:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.686738</v>
+        <v>4.688115</v>
       </c>
       <c r="G11" t="n">
-        <v>14817</v>
+        <v>14825</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>251561</v>
+        <v>252116</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="O11" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P11" t="n">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Q11" t="n">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="R11" t="n">
-        <v>12964</v>
+        <v>12973</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:32</t>
+          <t>2026-07-13 18:24:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1286,7 +1286,7 @@
         <v>2.775457</v>
       </c>
       <c r="G12" t="n">
-        <v>4683</v>
+        <v>4682</v>
       </c>
       <c r="H12" t="n">
         <v>1934</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:33</t>
+          <t>2026-07-13 18:24:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:33</t>
+          <t>2026-07-13 18:24:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.758966</v>
+        <v>4.7789826</v>
       </c>
       <c r="G14" t="n">
-        <v>13149</v>
+        <v>13172</v>
       </c>
       <c r="H14" t="n">
-        <v>4957</v>
+        <v>4959</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1234956</v>
+        <v>1240278</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>613</v>
+        <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="P14" t="n">
         <v>108</v>
       </c>
       <c r="Q14" t="n">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="R14" t="n">
-        <v>12150</v>
+        <v>12248</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:33</t>
+          <t>2026-07-13 18:24:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.3430233</v>
       </c>
       <c r="G15" t="n">
-        <v>3891</v>
+        <v>3892</v>
       </c>
       <c r="H15" t="n">
         <v>1569</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>393595</v>
+        <v>395288</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>113</v>
       </c>
       <c r="R15" t="n">
-        <v>2114</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12 17:46:33</t>
+          <t>2026-07-13 18:24:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.71192</v>
+        <v>4.712121</v>
       </c>
       <c r="G16" t="n">
-        <v>46670</v>
+        <v>46673</v>
       </c>
       <c r="H16" t="n">
         <v>2938</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>560298</v>
+        <v>562778</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="O16" t="n">
         <v>337</v>
@@ -1616,10 +1616,10 @@
         <v>717</v>
       </c>
       <c r="Q16" t="n">
-        <v>2285</v>
+        <v>2283</v>
       </c>
       <c r="R16" t="n">
-        <v>41149</v>
+        <v>41156</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:37</t>
+          <t>2026-07-14 17:54:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.06</v>
       </c>
       <c r="G2" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2" t="n">
         <v>172</v>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:37</t>
+          <t>2026-07-14 17:54:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4706316</v>
+        <v>4.467108</v>
       </c>
       <c r="G3" t="n">
-        <v>30577</v>
+        <v>30586</v>
       </c>
       <c r="H3" t="n">
         <v>9051</v>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3489</v>
+        <v>3517</v>
       </c>
       <c r="O3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q3" t="n">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="R3" t="n">
-        <v>25839</v>
+        <v>25819</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:37</t>
+          <t>2026-07-14 17:54:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.624031</v>
+        <v>3.625323</v>
       </c>
       <c r="G4" t="n">
-        <v>24990</v>
+        <v>24988</v>
       </c>
       <c r="H4" t="n">
-        <v>5593</v>
+        <v>5591</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -733,13 +733,13 @@
         <v>806</v>
       </c>
       <c r="P4" t="n">
-        <v>903</v>
+        <v>887</v>
       </c>
       <c r="Q4" t="n">
         <v>1225</v>
       </c>
       <c r="R4" t="n">
-        <v>14818</v>
+        <v>14833</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:37</t>
+          <t>2026-07-14 17:54:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.543348</v>
+        <v>4.53922</v>
       </c>
       <c r="G5" t="n">
-        <v>26144</v>
+        <v>26161</v>
       </c>
       <c r="H5" t="n">
-        <v>9743</v>
+        <v>9751</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1940</v>
+        <v>1950</v>
       </c>
       <c r="O5" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P5" t="n">
-        <v>807</v>
+        <v>840</v>
       </c>
       <c r="Q5" t="n">
-        <v>1682</v>
+        <v>1692</v>
       </c>
       <c r="R5" t="n">
-        <v>21419</v>
+        <v>21384</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:38</t>
+          <t>2026-07-14 17:54:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.64</v>
       </c>
       <c r="G6" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H6" t="n">
         <v>163</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -883,7 +883,7 @@
         <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:38</t>
+          <t>2026-07-14 17:54:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.737052</v>
+        <v>4.7222223</v>
       </c>
       <c r="G7" t="n">
-        <v>3096</v>
+        <v>3097</v>
       </c>
       <c r="H7" t="n">
         <v>1152</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -957,7 +957,7 @@
         <v>61</v>
       </c>
       <c r="R7" t="n">
-        <v>2824</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:38</t>
+          <t>2026-07-14 17:54:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -990,7 +990,7 @@
         <v>4.183601</v>
       </c>
       <c r="G8" t="n">
-        <v>6066</v>
+        <v>6065</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1031,7 +1031,7 @@
         <v>280</v>
       </c>
       <c r="R8" t="n">
-        <v>4497</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:38</t>
+          <t>2026-07-14 17:54:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1067,7 +1067,7 @@
         <v>1225</v>
       </c>
       <c r="H9" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:39</t>
+          <t>2026-07-14 17:54:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.9.0</t>
+          <t>0.9.2</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Jun 26, 2026</t>
+          <t>Jul 2, 2026</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:39</t>
+          <t>2026-07-14 17:54:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.688115</v>
+        <v>4.690205</v>
       </c>
       <c r="G11" t="n">
-        <v>14825</v>
+        <v>14833</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="O11" t="n">
         <v>145</v>
       </c>
       <c r="P11" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="R11" t="n">
-        <v>12973</v>
+        <v>12985</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:39</t>
+          <t>2026-07-14 17:54:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.775457</v>
+        <v>2.7806787</v>
       </c>
       <c r="G12" t="n">
-        <v>4682</v>
+        <v>4683</v>
       </c>
       <c r="H12" t="n">
         <v>1934</v>
@@ -1311,13 +1311,13 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2383</v>
+        <v>2371</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
       </c>
       <c r="P12" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="Q12" t="n">
         <v>206</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:39</t>
+          <t>2026-07-14 17:54:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:39</t>
+          <t>2026-07-14 17:54:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7789826</v>
+        <v>4.7816668</v>
       </c>
       <c r="G14" t="n">
-        <v>13172</v>
+        <v>13183</v>
       </c>
       <c r="H14" t="n">
         <v>4959</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1240278</v>
+        <v>1240280</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="O14" t="n">
         <v>97</v>
@@ -1468,10 +1468,10 @@
         <v>108</v>
       </c>
       <c r="Q14" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="R14" t="n">
-        <v>12248</v>
+        <v>12259</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:39</t>
+          <t>2026-07-14 17:54:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3430233</v>
+        <v>3.3517442</v>
       </c>
       <c r="G15" t="n">
-        <v>3892</v>
+        <v>3893</v>
       </c>
       <c r="H15" t="n">
         <v>1569</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1447</v>
+        <v>1436</v>
       </c>
       <c r="O15" t="n">
         <v>113</v>
@@ -1542,10 +1542,10 @@
         <v>101</v>
       </c>
       <c r="Q15" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2115</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-13 18:24:40</t>
+          <t>2026-07-14 17:54:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1578,10 +1578,10 @@
         <v>4.712121</v>
       </c>
       <c r="G16" t="n">
-        <v>46673</v>
+        <v>46671</v>
       </c>
       <c r="H16" t="n">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>2283</v>
       </c>
       <c r="R16" t="n">
-        <v>41156</v>
+        <v>41154</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:47</t>
+          <t>2026-07-15 18:00:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>38309</v>
+        <v>38405</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:47</t>
+          <t>2026-07-15 18:00:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.467108</v>
+        <v>4.4651504</v>
       </c>
       <c r="G3" t="n">
-        <v>30586</v>
+        <v>30592</v>
       </c>
       <c r="H3" t="n">
-        <v>9051</v>
+        <v>9056</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2375361</v>
+        <v>2377410</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3517</v>
+        <v>3534</v>
       </c>
       <c r="O3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q3" t="n">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="R3" t="n">
-        <v>25819</v>
+        <v>25810</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:48</t>
+          <t>2026-07-15 18:00:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2584231</v>
+        <v>2586387</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -723,11 +723,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 21, 2026</t>
+          <t>Jun 20, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7231</v>
+        <v>7230</v>
       </c>
       <c r="O4" t="n">
         <v>806</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:48</t>
+          <t>2026-07-15 18:00:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.53922</v>
+        <v>4.539581</v>
       </c>
       <c r="G5" t="n">
-        <v>26161</v>
+        <v>26177</v>
       </c>
       <c r="H5" t="n">
-        <v>9751</v>
+        <v>9755</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>660416</v>
+        <v>661100</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1950</v>
+        <v>1959</v>
       </c>
       <c r="O5" t="n">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q5" t="n">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="R5" t="n">
-        <v>21384</v>
+        <v>21404</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:48</t>
+          <t>2026-07-15 18:00:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>110013</v>
+        <v>110080</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:48</t>
+          <t>2026-07-15 18:00:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>432795</v>
+        <v>433913</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:48</t>
+          <t>2026-07-15 18:00:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>440269</v>
+        <v>441435</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:48</t>
+          <t>2026-07-15 18:00:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.0280375</v>
+        <v>4.037037</v>
       </c>
       <c r="G9" t="n">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H9" t="n">
         <v>494</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>177753</v>
+        <v>177944</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="O9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>868</v>
+        <v>873</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:48</t>
+          <t>2026-07-15 18:00:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1141,7 +1141,7 @@
         <v>557</v>
       </c>
       <c r="H10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>89628</v>
+        <v>89828</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:49</t>
+          <t>2026-07-15 18:00:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.690205</v>
+        <v>4.689734</v>
       </c>
       <c r="G11" t="n">
-        <v>14833</v>
+        <v>14837</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>252116</v>
+        <v>252331</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O11" t="n">
         <v>145</v>
@@ -1250,10 +1250,10 @@
         <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="R11" t="n">
-        <v>12985</v>
+        <v>12986</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:49</t>
+          <t>2026-07-15 18:00:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>4683</v>
       </c>
       <c r="H12" t="n">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>351596</v>
+        <v>351852</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:49</t>
+          <t>2026-07-15 18:00:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21928</v>
+        <v>21943</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:49</t>
+          <t>2026-07-15 18:00:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7816668</v>
+        <v>4.7891665</v>
       </c>
       <c r="G14" t="n">
-        <v>13183</v>
+        <v>13200</v>
       </c>
       <c r="H14" t="n">
-        <v>4959</v>
+        <v>4960</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1240280</v>
+        <v>1242151</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="O14" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="P14" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="Q14" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="R14" t="n">
-        <v>12259</v>
+        <v>12308</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:49</t>
+          <t>2026-07-15 18:00:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>395288</v>
+        <v>395858</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-14 17:54:50</t>
+          <t>2026-07-15 18:00:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.712121</v>
+        <v>4.7121882</v>
       </c>
       <c r="G16" t="n">
         <v>46671</v>
       </c>
       <c r="H16" t="n">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>562778</v>
+        <v>563706</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="O16" t="n">
         <v>337</v>
@@ -1619,7 +1619,7 @@
         <v>2283</v>
       </c>
       <c r="R16" t="n">
-        <v>41154</v>
+        <v>41156</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:49</t>
+          <t>2026-07-16 17:58:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.06</v>
       </c>
       <c r="G2" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2" t="n">
         <v>172</v>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:49</t>
+          <t>2026-07-16 17:58:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -624,10 +624,10 @@
         <v>4.4651504</v>
       </c>
       <c r="G3" t="n">
-        <v>30592</v>
+        <v>30600</v>
       </c>
       <c r="H3" t="n">
-        <v>9056</v>
+        <v>9058</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2377410</v>
+        <v>2377411</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="O3" t="n">
         <v>324</v>
@@ -665,7 +665,7 @@
         <v>594</v>
       </c>
       <c r="R3" t="n">
-        <v>25810</v>
+        <v>25817</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:49</t>
+          <t>2026-07-16 17:58:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.625323</v>
       </c>
       <c r="G4" t="n">
-        <v>24988</v>
+        <v>24989</v>
       </c>
       <c r="H4" t="n">
         <v>5591</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 20, 2026</t>
+          <t>Jun 21, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:49</t>
+          <t>2026-07-16 17:58:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.539581</v>
+        <v>4.5397778</v>
       </c>
       <c r="G5" t="n">
-        <v>26177</v>
+        <v>26188</v>
       </c>
       <c r="H5" t="n">
-        <v>9755</v>
+        <v>9757</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>661100</v>
+        <v>661101</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
@@ -813,7 +813,7 @@
         <v>1690</v>
       </c>
       <c r="R5" t="n">
-        <v>21404</v>
+        <v>21416</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:50</t>
+          <t>2026-07-16 17:58:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:50</t>
+          <t>2026-07-16 17:58:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:50</t>
+          <t>2026-07-16 17:58:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -990,7 +990,7 @@
         <v>4.183601</v>
       </c>
       <c r="G8" t="n">
-        <v>6065</v>
+        <v>6066</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1022,7 +1022,7 @@
         <v>983</v>
       </c>
       <c r="O8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P8" t="n">
         <v>172</v>
@@ -1031,7 +1031,7 @@
         <v>280</v>
       </c>
       <c r="R8" t="n">
-        <v>4496</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:50</t>
+          <t>2026-07-16 17:58:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.037037</v>
+        <v>4.0280375</v>
       </c>
       <c r="G9" t="n">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H9" t="n">
         <v>494</v>
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:50</t>
+          <t>2026-07-16 17:58:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.019608</v>
+        <v>3.9902914</v>
       </c>
       <c r="G10" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H10" t="n">
         <v>233</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:51</t>
+          <t>2026-07-16 17:58:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.689734</v>
+        <v>4.6896815</v>
       </c>
       <c r="G11" t="n">
-        <v>14837</v>
+        <v>14845</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>732</v>
+        <v>742</v>
       </c>
       <c r="O11" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="P11" t="n">
         <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="R11" t="n">
-        <v>12986</v>
+        <v>12997</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:51</t>
+          <t>2026-07-16 17:58:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7806787</v>
+        <v>2.7760417</v>
       </c>
       <c r="G12" t="n">
-        <v>4683</v>
+        <v>4684</v>
       </c>
       <c r="H12" t="n">
         <v>1935</v>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2371</v>
+        <v>2377</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
       </c>
       <c r="P12" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q12" t="n">
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1808</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:51</t>
+          <t>2026-07-16 17:58:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:51</t>
+          <t>2026-07-16 17:58:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7891665</v>
+        <v>4.7966805</v>
       </c>
       <c r="G14" t="n">
-        <v>13200</v>
+        <v>13211</v>
       </c>
       <c r="H14" t="n">
-        <v>4960</v>
+        <v>4963</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>538</v>
+        <v>514</v>
       </c>
       <c r="O14" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q14" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R14" t="n">
-        <v>12308</v>
+        <v>12344</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:52</t>
+          <t>2026-07-16 17:58:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1545,7 +1545,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2116</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-15 18:00:52</t>
+          <t>2026-07-16 17:58:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7121882</v>
+        <v>4.7122555</v>
       </c>
       <c r="G16" t="n">
-        <v>46671</v>
+        <v>46670</v>
       </c>
       <c r="H16" t="n">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>563706</v>
+        <v>563707</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>717</v>
       </c>
       <c r="Q16" t="n">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="R16" t="n">
         <v>41156</v>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:40</t>
+          <t>2026-07-17 17:54:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:40</t>
+          <t>2026-07-17 17:54:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4651504</v>
+        <v>4.4656377</v>
       </c>
       <c r="G3" t="n">
-        <v>30600</v>
+        <v>30604</v>
       </c>
       <c r="H3" t="n">
-        <v>9058</v>
+        <v>9057</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2377411</v>
+        <v>2378162</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3535</v>
+        <v>3530</v>
       </c>
       <c r="O3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q3" t="n">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="R3" t="n">
-        <v>25817</v>
+        <v>25823</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:40</t>
+          <t>2026-07-17 17:54:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.625323</v>
+        <v>3.6242738</v>
       </c>
       <c r="G4" t="n">
         <v>24989</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7230</v>
+        <v>7227</v>
       </c>
       <c r="O4" t="n">
-        <v>806</v>
+        <v>822</v>
       </c>
       <c r="P4" t="n">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="Q4" t="n">
         <v>1225</v>
       </c>
       <c r="R4" t="n">
-        <v>14833</v>
+        <v>14824</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:41</t>
+          <t>2026-07-17 17:54:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5397778</v>
+        <v>4.5393834</v>
       </c>
       <c r="G5" t="n">
-        <v>26188</v>
+        <v>26195</v>
       </c>
       <c r="H5" t="n">
         <v>9757</v>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="Q5" t="n">
-        <v>1690</v>
+        <v>1693</v>
       </c>
       <c r="R5" t="n">
-        <v>21416</v>
+        <v>21417</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:41</t>
+          <t>2026-07-17 17:54:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:41</t>
+          <t>2026-07-17 17:54:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>433913</v>
+        <v>434279</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:41</t>
+          <t>2026-07-17 17:54:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.183601</v>
+        <v>4.1850533</v>
       </c>
       <c r="G8" t="n">
-        <v>6066</v>
+        <v>6068</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="O8" t="n">
         <v>129</v>
       </c>
       <c r="P8" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q8" t="n">
         <v>280</v>
       </c>
       <c r="R8" t="n">
-        <v>4497</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:41</t>
+          <t>2026-07-17 17:54:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:42</t>
+          <t>2026-07-17 17:54:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.9902914</v>
+        <v>4.01</v>
       </c>
       <c r="G10" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H10" t="n">
         <v>233</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>89828</v>
+        <v>89912</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="R10" t="n">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:42</t>
+          <t>2026-07-17 17:54:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6896815</v>
+        <v>4.687831</v>
       </c>
       <c r="G11" t="n">
-        <v>14845</v>
+        <v>14851</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>742</v>
+        <v>751</v>
       </c>
       <c r="O11" t="n">
         <v>134</v>
       </c>
       <c r="P11" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q11" t="n">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="R11" t="n">
         <v>12997</v>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:42</t>
+          <t>2026-07-17 17:54:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>4684</v>
       </c>
       <c r="H12" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:42</t>
+          <t>2026-07-17 17:54:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:42</t>
+          <t>2026-07-17 17:54:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7966805</v>
+        <v>4.804655</v>
       </c>
       <c r="G14" t="n">
-        <v>13211</v>
+        <v>13229</v>
       </c>
       <c r="H14" t="n">
-        <v>4963</v>
+        <v>4964</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="O14" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="P14" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="Q14" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="R14" t="n">
-        <v>12344</v>
+        <v>12392</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:43</t>
+          <t>2026-07-17 17:54:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3517442</v>
+        <v>3.3401163</v>
       </c>
       <c r="G15" t="n">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="H15" t="n">
         <v>1569</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>395858</v>
+        <v>396104</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1436</v>
+        <v>1448</v>
       </c>
       <c r="O15" t="n">
         <v>113</v>
@@ -1545,7 +1545,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2115</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-16 17:58:43</t>
+          <t>2026-07-17 17:54:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1578,7 +1578,7 @@
         <v>4.7122555</v>
       </c>
       <c r="G16" t="n">
-        <v>46670</v>
+        <v>46669</v>
       </c>
       <c r="H16" t="n">
         <v>2939</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>563707</v>
+        <v>564074</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>2282</v>
       </c>
       <c r="R16" t="n">
-        <v>41156</v>
+        <v>41155</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:37</t>
+          <t>2026-07-18 17:44:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>38405</v>
+        <v>38555</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:37</t>
+          <t>2026-07-18 17:44:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4656377</v>
+        <v>4.466226</v>
       </c>
       <c r="G3" t="n">
-        <v>30604</v>
+        <v>30606</v>
       </c>
       <c r="H3" t="n">
-        <v>9057</v>
+        <v>9056</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2378162</v>
+        <v>2379812</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3530</v>
+        <v>3527</v>
       </c>
       <c r="O3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q3" t="n">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="R3" t="n">
-        <v>25823</v>
+        <v>25830</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:37</t>
+          <t>2026-07-18 17:44:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,10 +698,10 @@
         <v>3.6242738</v>
       </c>
       <c r="G4" t="n">
-        <v>24989</v>
+        <v>24991</v>
       </c>
       <c r="H4" t="n">
-        <v>5591</v>
+        <v>5590</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2586387</v>
+        <v>2588906</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7227</v>
+        <v>7226</v>
       </c>
       <c r="O4" t="n">
         <v>822</v>
       </c>
       <c r="P4" t="n">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="Q4" t="n">
         <v>1225</v>
       </c>
       <c r="R4" t="n">
-        <v>14824</v>
+        <v>14825</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:37</t>
+          <t>2026-07-18 17:44:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5393834</v>
+        <v>4.5397778</v>
       </c>
       <c r="G5" t="n">
         <v>26195</v>
       </c>
       <c r="H5" t="n">
-        <v>9757</v>
+        <v>9758</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q5" t="n">
-        <v>1693</v>
+        <v>1690</v>
       </c>
       <c r="R5" t="n">
-        <v>21417</v>
+        <v>21422</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:38</t>
+          <t>2026-07-18 17:44:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>110080</v>
+        <v>110184</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:38</t>
+          <t>2026-07-18 17:44:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7222223</v>
+        <v>4.70751</v>
       </c>
       <c r="G7" t="n">
-        <v>3097</v>
+        <v>3098</v>
       </c>
       <c r="H7" t="n">
         <v>1152</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>434279</v>
+        <v>435255</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -957,7 +957,7 @@
         <v>61</v>
       </c>
       <c r="R7" t="n">
-        <v>2813</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:38</t>
+          <t>2026-07-18 17:44:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>441435</v>
+        <v>442752</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:38</t>
+          <t>2026-07-18 17:44:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>177944</v>
+        <v>178214</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:38</t>
+          <t>2026-07-18 17:44:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>4.01</v>
       </c>
       <c r="G10" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H10" t="n">
         <v>233</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>89912</v>
+        <v>90119</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
         <v>402</v>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:39</t>
+          <t>2026-07-18 17:44:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.687831</v>
+        <v>4.6854105</v>
       </c>
       <c r="G11" t="n">
-        <v>14851</v>
+        <v>14855</v>
       </c>
       <c r="H11" t="n">
         <v>697</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>252331</v>
+        <v>253379</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>751</v>
+        <v>767</v>
       </c>
       <c r="O11" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="P11" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q11" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="R11" t="n">
-        <v>12997</v>
+        <v>12991</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:39</t>
+          <t>2026-07-18 17:44:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7760417</v>
+        <v>2.770235</v>
       </c>
       <c r="G12" t="n">
-        <v>4684</v>
+        <v>4685</v>
       </c>
       <c r="H12" t="n">
         <v>1936</v>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2378</v>
+        <v>2385</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
       </c>
       <c r="P12" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q12" t="n">
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1804</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:39</t>
+          <t>2026-07-18 17:44:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:39</t>
+          <t>2026-07-18 17:44:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.804655</v>
+        <v>4.8106313</v>
       </c>
       <c r="G14" t="n">
-        <v>13229</v>
+        <v>13234</v>
       </c>
       <c r="H14" t="n">
-        <v>4964</v>
+        <v>4966</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1242151</v>
+        <v>1244534</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="O14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q14" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="R14" t="n">
-        <v>12392</v>
+        <v>12409</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:39</t>
+          <t>2026-07-18 17:44:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>396104</v>
+        <v>396615</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-17 17:54:39</t>
+          <t>2026-07-18 17:44:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7122555</v>
+        <v>4.712322</v>
       </c>
       <c r="G16" t="n">
-        <v>46669</v>
+        <v>46670</v>
       </c>
       <c r="H16" t="n">
         <v>2939</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>564074</v>
+        <v>564923</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="O16" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P16" t="n">
         <v>717</v>
@@ -1619,7 +1619,7 @@
         <v>2282</v>
       </c>
       <c r="R16" t="n">
-        <v>41155</v>
+        <v>41157</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:40</t>
+          <t>2026-07-19 17:46:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.06</v>
       </c>
       <c r="G2" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2" t="n">
         <v>172</v>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O2" t="n">
         <v>7</v>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:40</t>
+          <t>2026-07-19 17:46:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.466226</v>
+        <v>4.4651504</v>
       </c>
       <c r="G3" t="n">
-        <v>30606</v>
+        <v>30608</v>
       </c>
       <c r="H3" t="n">
-        <v>9056</v>
+        <v>9057</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3527</v>
+        <v>3536</v>
       </c>
       <c r="O3" t="n">
         <v>324</v>
@@ -665,7 +665,7 @@
         <v>594</v>
       </c>
       <c r="R3" t="n">
-        <v>25830</v>
+        <v>25824</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:41</t>
+          <t>2026-07-19 17:46:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.6242738</v>
       </c>
       <c r="G4" t="n">
-        <v>24991</v>
+        <v>24992</v>
       </c>
       <c r="H4" t="n">
         <v>5590</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:41</t>
+          <t>2026-07-19 17:46:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5397778</v>
+        <v>4.538758</v>
       </c>
       <c r="G5" t="n">
-        <v>26195</v>
+        <v>26201</v>
       </c>
       <c r="H5" t="n">
-        <v>9758</v>
+        <v>9759</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>661101</v>
+        <v>662029</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1960</v>
+        <v>1974</v>
       </c>
       <c r="O5" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P5" t="n">
-        <v>839</v>
+        <v>819</v>
       </c>
       <c r="Q5" t="n">
-        <v>1690</v>
+        <v>1705</v>
       </c>
       <c r="R5" t="n">
-        <v>21422</v>
+        <v>21420</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:41</t>
+          <t>2026-07-19 17:46:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:41</t>
+          <t>2026-07-19 17:46:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.70751</v>
+        <v>4.7086616</v>
       </c>
       <c r="G7" t="n">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="H7" t="n">
         <v>1152</v>
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="O7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q7" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="R7" t="n">
-        <v>2803</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:41</t>
+          <t>2026-07-19 17:46:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1850533</v>
+        <v>4.183601</v>
       </c>
       <c r="G8" t="n">
         <v>6068</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="O8" t="n">
         <v>129</v>
       </c>
       <c r="P8" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q8" t="n">
         <v>280</v>
       </c>
       <c r="R8" t="n">
-        <v>4501</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:42</t>
+          <t>2026-07-19 17:46:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:42</t>
+          <t>2026-07-19 17:46:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>90119</v>
+        <v>90120</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:42</t>
+          <t>2026-07-19 17:46:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6854105</v>
+        <v>4.686838</v>
       </c>
       <c r="G11" t="n">
-        <v>14855</v>
+        <v>14862</v>
       </c>
       <c r="H11" t="n">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="O11" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P11" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="R11" t="n">
-        <v>12991</v>
+        <v>13006</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:42</t>
+          <t>2026-07-19 17:46:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>351852</v>
+        <v>352163</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:42</t>
+          <t>2026-07-19 17:46:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21943</v>
+        <v>21957</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:43</t>
+          <t>2026-07-19 17:46:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.8106313</v>
+        <v>4.807309</v>
       </c>
       <c r="G14" t="n">
-        <v>13234</v>
+        <v>13236</v>
       </c>
       <c r="H14" t="n">
-        <v>4966</v>
+        <v>4970</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="O14" t="n">
         <v>75</v>
@@ -1471,7 +1471,7 @@
         <v>185</v>
       </c>
       <c r="R14" t="n">
-        <v>12409</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:43</t>
+          <t>2026-07-19 17:46:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-18 17:44:43</t>
+          <t>2026-07-19 17:46:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.712322</v>
+        <v>4.7122555</v>
       </c>
       <c r="G16" t="n">
-        <v>46670</v>
+        <v>46669</v>
       </c>
       <c r="H16" t="n">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="O16" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P16" t="n">
         <v>717</v>
@@ -1619,7 +1619,7 @@
         <v>2282</v>
       </c>
       <c r="R16" t="n">
-        <v>41157</v>
+        <v>41155</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:05</t>
+          <t>2026-07-20 18:47:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.06</v>
       </c>
       <c r="G2" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H2" t="n">
         <v>172</v>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O2" t="n">
         <v>7</v>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:05</t>
+          <t>2026-07-20 18:47:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4651504</v>
+        <v>4.464954</v>
       </c>
       <c r="G3" t="n">
-        <v>30608</v>
+        <v>30616</v>
       </c>
       <c r="H3" t="n">
-        <v>9057</v>
+        <v>9061</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3536</v>
+        <v>3538</v>
       </c>
       <c r="O3" t="n">
         <v>324</v>
@@ -665,7 +665,7 @@
         <v>594</v>
       </c>
       <c r="R3" t="n">
-        <v>25824</v>
+        <v>25829</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:06</t>
+          <t>2026-07-20 18:47:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.6242738</v>
       </c>
       <c r="G4" t="n">
-        <v>24992</v>
+        <v>24994</v>
       </c>
       <c r="H4" t="n">
         <v>5590</v>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7226</v>
+        <v>7227</v>
       </c>
       <c r="O4" t="n">
         <v>822</v>
@@ -739,7 +739,7 @@
         <v>1225</v>
       </c>
       <c r="R4" t="n">
-        <v>14825</v>
+        <v>14826</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:06</t>
+          <t>2026-07-20 18:47:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.538758</v>
+        <v>4.538396</v>
       </c>
       <c r="G5" t="n">
-        <v>26201</v>
+        <v>26211</v>
       </c>
       <c r="H5" t="n">
-        <v>9759</v>
+        <v>9762</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1974</v>
+        <v>1978</v>
       </c>
       <c r="O5" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="Q5" t="n">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="R5" t="n">
-        <v>21420</v>
+        <v>21424</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:06</t>
+          <t>2026-07-20 18:47:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.64</v>
       </c>
       <c r="G6" t="n">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H6" t="n">
         <v>163</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -883,7 +883,7 @@
         <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:07</t>
+          <t>2026-07-20 18:47:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7086616</v>
+        <v>4.709804</v>
       </c>
       <c r="G7" t="n">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="H7" t="n">
         <v>1152</v>
@@ -957,7 +957,7 @@
         <v>59</v>
       </c>
       <c r="R7" t="n">
-        <v>2805</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:07</t>
+          <t>2026-07-20 18:47:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:07</t>
+          <t>2026-07-20 18:47:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:07</t>
+          <t>2026-07-20 18:47:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>4.01</v>
       </c>
       <c r="G10" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H10" t="n">
         <v>233</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R10" t="n">
         <v>402</v>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:08</t>
+          <t>2026-07-20 18:47:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.686838</v>
+        <v>4.683371</v>
       </c>
       <c r="G11" t="n">
-        <v>14862</v>
+        <v>14872</v>
       </c>
       <c r="H11" t="n">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>764</v>
+        <v>778</v>
       </c>
       <c r="O11" t="n">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="P11" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q11" t="n">
-        <v>707</v>
+        <v>733</v>
       </c>
       <c r="R11" t="n">
-        <v>13006</v>
+        <v>12985</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:08</t>
+          <t>2026-07-20 18:47:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.770235</v>
+        <v>2.7818182</v>
       </c>
       <c r="G12" t="n">
-        <v>4685</v>
+        <v>4687</v>
       </c>
       <c r="H12" t="n">
         <v>1936</v>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2385</v>
+        <v>2373</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
       </c>
       <c r="P12" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Q12" t="n">
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1796</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:08</t>
+          <t>2026-07-20 18:47:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:09</t>
+          <t>2026-07-20 18:47:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.807309</v>
+        <v>4.805809</v>
       </c>
       <c r="G14" t="n">
-        <v>13236</v>
+        <v>13258</v>
       </c>
       <c r="H14" t="n">
-        <v>4970</v>
+        <v>4973</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="O14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="Q14" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="R14" t="n">
-        <v>12400</v>
+        <v>12420</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:09</t>
+          <t>2026-07-20 18:47:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,10 +1504,10 @@
         <v>3.3401163</v>
       </c>
       <c r="G15" t="n">
-        <v>3892</v>
+        <v>3891</v>
       </c>
       <c r="H15" t="n">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="O15" t="n">
         <v>113</v>
@@ -1545,7 +1545,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2104</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-19 17:46:09</t>
+          <t>2026-07-20 18:47:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7122555</v>
+        <v>4.712322</v>
       </c>
       <c r="G16" t="n">
-        <v>46669</v>
+        <v>46670</v>
       </c>
       <c r="H16" t="n">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="O16" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P16" t="n">
         <v>717</v>
@@ -1619,7 +1619,7 @@
         <v>2282</v>
       </c>
       <c r="R16" t="n">
-        <v>41155</v>
+        <v>41157</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:20</t>
+          <t>2026-07-21 18:05:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,7 +553,7 @@
         <v>397</v>
       </c>
       <c r="H2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:20</t>
+          <t>2026-07-21 18:05:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.464954</v>
+        <v>4.4655423</v>
       </c>
       <c r="G3" t="n">
-        <v>30616</v>
+        <v>30627</v>
       </c>
       <c r="H3" t="n">
-        <v>9061</v>
+        <v>9065</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2379812</v>
+        <v>2381896</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="O3" t="n">
         <v>324</v>
@@ -665,7 +665,7 @@
         <v>594</v>
       </c>
       <c r="R3" t="n">
-        <v>25829</v>
+        <v>25843</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:20</t>
+          <t>2026-07-21 18:05:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2588906</v>
+        <v>2591018</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         <v>886</v>
       </c>
       <c r="Q4" t="n">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="R4" t="n">
-        <v>14826</v>
+        <v>14827</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:20</t>
+          <t>2026-07-21 18:05:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.538396</v>
+        <v>4.5386915</v>
       </c>
       <c r="G5" t="n">
-        <v>26211</v>
+        <v>26219</v>
       </c>
       <c r="H5" t="n">
-        <v>9762</v>
+        <v>9767</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>662029</v>
+        <v>662842</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1978</v>
+        <v>1972</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>815</v>
+        <v>829</v>
       </c>
       <c r="Q5" t="n">
-        <v>1709</v>
+        <v>1703</v>
       </c>
       <c r="R5" t="n">
-        <v>21424</v>
+        <v>21432</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:20</t>
+          <t>2026-07-21 18:05:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.64</v>
       </c>
       <c r="G6" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H6" t="n">
         <v>163</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -883,7 +883,7 @@
         <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:21</t>
+          <t>2026-07-21 18:05:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>435255</v>
+        <v>436038</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:21</t>
+          <t>2026-07-21 18:05:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:21</t>
+          <t>2026-07-21 18:05:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,7 +1064,7 @@
         <v>4.0280375</v>
       </c>
       <c r="G9" t="n">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="H9" t="n">
         <v>494</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>178214</v>
+        <v>178409</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:21</t>
+          <t>2026-07-21 18:05:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>4.01</v>
       </c>
       <c r="G10" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H10" t="n">
         <v>233</v>
@@ -1179,7 +1179,7 @@
         <v>16</v>
       </c>
       <c r="R10" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:21</t>
+          <t>2026-07-21 18:05:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.683371</v>
+        <v>4.682059</v>
       </c>
       <c r="G11" t="n">
-        <v>14872</v>
+        <v>14877</v>
       </c>
       <c r="H11" t="n">
         <v>699</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="O11" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="P11" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q11" t="n">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="R11" t="n">
-        <v>12985</v>
+        <v>12984</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:21</t>
+          <t>2026-07-21 18:05:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>4687</v>
       </c>
       <c r="H12" t="n">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:22</t>
+          <t>2026-07-21 18:05:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:22</t>
+          <t>2026-07-21 18:05:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.805809</v>
+        <v>4.800995</v>
       </c>
       <c r="G14" t="n">
-        <v>13258</v>
+        <v>13267</v>
       </c>
       <c r="H14" t="n">
-        <v>4973</v>
+        <v>4972</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1244534</v>
+        <v>1246443</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="O14" t="n">
         <v>76</v>
       </c>
       <c r="P14" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="Q14" t="n">
         <v>186</v>
       </c>
       <c r="R14" t="n">
-        <v>12420</v>
+        <v>12408</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:22</t>
+          <t>2026-07-21 18:05:54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3401163</v>
+        <v>3.3517442</v>
       </c>
       <c r="G15" t="n">
-        <v>3891</v>
+        <v>3892</v>
       </c>
       <c r="H15" t="n">
         <v>1570</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1447</v>
+        <v>1436</v>
       </c>
       <c r="O15" t="n">
         <v>113</v>
@@ -1545,7 +1545,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2103</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-20 18:47:22</t>
+          <t>2026-07-21 18:05:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.712322</v>
+        <v>4.711525</v>
       </c>
       <c r="G16" t="n">
         <v>46670</v>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2173</v>
+        <v>2183</v>
       </c>
       <c r="O16" t="n">
         <v>335</v>
       </c>
       <c r="P16" t="n">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="Q16" t="n">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="R16" t="n">
-        <v>41157</v>
+        <v>41149</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:51</t>
+          <t>2026-07-22 17:59:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.06</v>
+        <v>4.0495048</v>
       </c>
       <c r="G2" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>38555</v>
+        <v>38670</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,13 +579,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O2" t="n">
         <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="n">
         <v>7</v>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:51</t>
+          <t>2026-07-22 17:59:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4655423</v>
+        <v>4.469163</v>
       </c>
       <c r="G3" t="n">
-        <v>30627</v>
+        <v>30636</v>
       </c>
       <c r="H3" t="n">
         <v>9065</v>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3536</v>
+        <v>3508</v>
       </c>
       <c r="O3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q3" t="n">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="R3" t="n">
-        <v>25843</v>
+        <v>25878</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:51</t>
+          <t>2026-07-22 17:59:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6242738</v>
+        <v>3.6225805</v>
       </c>
       <c r="G4" t="n">
-        <v>24994</v>
+        <v>24996</v>
       </c>
       <c r="H4" t="n">
         <v>5590</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7227</v>
+        <v>7239</v>
       </c>
       <c r="O4" t="n">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="P4" t="n">
         <v>886</v>
       </c>
       <c r="Q4" t="n">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="R4" t="n">
-        <v>14827</v>
+        <v>14820</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:52</t>
+          <t>2026-07-22 17:59:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5386915</v>
+        <v>4.5357447</v>
       </c>
       <c r="G5" t="n">
-        <v>26219</v>
+        <v>26228</v>
       </c>
       <c r="H5" t="n">
-        <v>9767</v>
+        <v>9770</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1972</v>
+        <v>1997</v>
       </c>
       <c r="O5" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P5" t="n">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="Q5" t="n">
-        <v>1703</v>
+        <v>1696</v>
       </c>
       <c r="R5" t="n">
-        <v>21432</v>
+        <v>21428</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:52</t>
+          <t>2026-07-22 17:59:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>110184</v>
+        <v>110261</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:52</t>
+          <t>2026-07-22 17:59:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.709804</v>
+        <v>4.7109375</v>
       </c>
       <c r="G7" t="n">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="H7" t="n">
         <v>1152</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O7" t="n">
         <v>10</v>
@@ -957,7 +957,7 @@
         <v>59</v>
       </c>
       <c r="R7" t="n">
-        <v>2808</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:52</t>
+          <t>2026-07-22 17:59:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -990,7 +990,7 @@
         <v>4.183601</v>
       </c>
       <c r="G8" t="n">
-        <v>6068</v>
+        <v>6067</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>442752</v>
+        <v>443881</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="O8" t="n">
         <v>129</v>
@@ -1031,7 +1031,7 @@
         <v>280</v>
       </c>
       <c r="R8" t="n">
-        <v>4499</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:52</t>
+          <t>2026-07-22 17:59:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:53</t>
+          <t>2026-07-22 17:59:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1141,7 +1141,7 @@
         <v>561</v>
       </c>
       <c r="H10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>90120</v>
+        <v>90309</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:53</t>
+          <t>2026-07-22 17:59:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.682059</v>
+        <v>4.682335</v>
       </c>
       <c r="G11" t="n">
-        <v>14877</v>
+        <v>14887</v>
       </c>
       <c r="H11" t="n">
         <v>699</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>253379</v>
+        <v>256725</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="O11" t="n">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="P11" t="n">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="Q11" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="R11" t="n">
-        <v>12984</v>
+        <v>12990</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:53</t>
+          <t>2026-07-22 17:59:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7818182</v>
+        <v>2.7922077</v>
       </c>
       <c r="G12" t="n">
         <v>4687</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>352163</v>
+        <v>352473</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2373</v>
+        <v>2361</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1323,7 +1323,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1813</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:53</t>
+          <t>2026-07-22 17:59:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21957</v>
+        <v>21963</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:53</t>
+          <t>2026-07-22 17:59:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.800995</v>
+        <v>4.8021436</v>
       </c>
       <c r="G14" t="n">
-        <v>13267</v>
+        <v>13273</v>
       </c>
       <c r="H14" t="n">
-        <v>4972</v>
+        <v>4976</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="O14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q14" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R14" t="n">
-        <v>12408</v>
+        <v>12418</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:54</t>
+          <t>2026-07-22 17:59:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3517442</v>
+        <v>3.363372</v>
       </c>
       <c r="G15" t="n">
-        <v>3892</v>
+        <v>3894</v>
       </c>
       <c r="H15" t="n">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>396615</v>
+        <v>397215</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1436</v>
+        <v>1425</v>
       </c>
       <c r="O15" t="n">
         <v>113</v>
@@ -1545,7 +1545,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2115</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-21 18:05:54</t>
+          <t>2026-07-22 17:59:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.711525</v>
+        <v>4.7116594</v>
       </c>
       <c r="G16" t="n">
-        <v>46670</v>
+        <v>46673</v>
       </c>
       <c r="H16" t="n">
         <v>2941</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>564923</v>
+        <v>565916</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="O16" t="n">
         <v>335</v>
@@ -1616,10 +1616,10 @@
         <v>716</v>
       </c>
       <c r="Q16" t="n">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="R16" t="n">
-        <v>41149</v>
+        <v>41154</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:25</t>
+          <t>2026-07-23 18:04:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.0495048</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
         <v>174</v>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="O2" t="n">
         <v>7</v>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:26</t>
+          <t>2026-07-23 18:04:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.469163</v>
+        <v>4.4699636</v>
       </c>
       <c r="G3" t="n">
-        <v>30636</v>
+        <v>30644</v>
       </c>
       <c r="H3" t="n">
-        <v>9065</v>
+        <v>9066</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2381896</v>
+        <v>2384186</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3508</v>
+        <v>3501</v>
       </c>
       <c r="O3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q3" t="n">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="R3" t="n">
-        <v>25878</v>
+        <v>25883</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:26</t>
+          <t>2026-07-23 18:04:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6225805</v>
+        <v>3.6216915</v>
       </c>
       <c r="G4" t="n">
-        <v>24996</v>
+        <v>24997</v>
       </c>
       <c r="H4" t="n">
         <v>5590</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2591018</v>
+        <v>2593315</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7239</v>
+        <v>7244</v>
       </c>
       <c r="O4" t="n">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="P4" t="n">
         <v>886</v>
       </c>
       <c r="Q4" t="n">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="R4" t="n">
-        <v>14820</v>
+        <v>14813</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:26</t>
+          <t>2026-07-23 18:04:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5357447</v>
+        <v>4.534527</v>
       </c>
       <c r="G5" t="n">
-        <v>26228</v>
+        <v>26239</v>
       </c>
       <c r="H5" t="n">
-        <v>9770</v>
+        <v>9776</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1997</v>
+        <v>1990</v>
       </c>
       <c r="O5" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>825</v>
+        <v>849</v>
       </c>
       <c r="Q5" t="n">
-        <v>1696</v>
+        <v>1710</v>
       </c>
       <c r="R5" t="n">
-        <v>21428</v>
+        <v>21406</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:26</t>
+          <t>2026-07-23 18:04:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:26</t>
+          <t>2026-07-23 18:04:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>436038</v>
+        <v>437016</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:27</t>
+          <t>2026-07-23 18:04:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.183601</v>
+        <v>4.179396</v>
       </c>
       <c r="G8" t="n">
-        <v>6067</v>
+        <v>6069</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="O8" t="n">
         <v>129</v>
       </c>
       <c r="P8" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q8" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R8" t="n">
-        <v>4498</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:27</t>
+          <t>2026-07-23 18:04:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:27</t>
+          <t>2026-07-23 18:04:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>4.01</v>
       </c>
       <c r="G10" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H10" t="n">
         <v>234</v>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:27</t>
+          <t>2026-07-23 18:04:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.682335</v>
+        <v>4.6832957</v>
       </c>
       <c r="G11" t="n">
-        <v>14887</v>
+        <v>14894</v>
       </c>
       <c r="H11" t="n">
         <v>699</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>256725</v>
+        <v>261348</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="O11" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P11" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q11" t="n">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="R11" t="n">
-        <v>12990</v>
+        <v>13002</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:28</t>
+          <t>2026-07-23 18:04:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7922077</v>
+        <v>2.7875648</v>
       </c>
       <c r="G12" t="n">
-        <v>4687</v>
+        <v>4688</v>
       </c>
       <c r="H12" t="n">
         <v>1937</v>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2361</v>
+        <v>2367</v>
       </c>
       <c r="O12" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P12" t="n">
         <v>181</v>
       </c>
       <c r="Q12" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R12" t="n">
-        <v>1825</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:28</t>
+          <t>2026-07-23 18:04:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.795699</v>
+        <v>2.7765958</v>
       </c>
       <c r="G13" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H13" t="n">
         <v>39</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O13" t="n">
         <v>5</v>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:28</t>
+          <t>2026-07-23 18:04:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.8021436</v>
+        <v>4.7975206</v>
       </c>
       <c r="G14" t="n">
-        <v>13273</v>
+        <v>13284</v>
       </c>
       <c r="H14" t="n">
-        <v>4976</v>
+        <v>4978</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="O14" t="n">
         <v>75</v>
@@ -1468,10 +1468,10 @@
         <v>75</v>
       </c>
       <c r="Q14" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="R14" t="n">
-        <v>12418</v>
+        <v>12405</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:28</t>
+          <t>2026-07-23 18:04:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.363372</v>
       </c>
       <c r="G15" t="n">
-        <v>3894</v>
+        <v>3895</v>
       </c>
       <c r="H15" t="n">
         <v>1571</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="O15" t="n">
         <v>113</v>
@@ -1545,7 +1545,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2128</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-22 17:59:28</t>
+          <t>2026-07-23 18:04:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7116594</v>
+        <v>4.711726</v>
       </c>
       <c r="G16" t="n">
-        <v>46673</v>
+        <v>46674</v>
       </c>
       <c r="H16" t="n">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,11 +1589,11 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>565916</v>
+        <v>566942</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.3</t>
+          <t>3.1.4</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Jun 11, 2026</t>
+          <t>Jul 23, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -1619,7 +1619,7 @@
         <v>2280</v>
       </c>
       <c r="R16" t="n">
-        <v>41154</v>
+        <v>41157</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:54</t>
+          <t>2026-07-24 18:09:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>38670</v>
+        <v>38769</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:54</t>
+          <t>2026-07-24 18:09:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4699636</v>
+        <v>4.46371</v>
       </c>
       <c r="G3" t="n">
-        <v>30644</v>
+        <v>30653</v>
       </c>
       <c r="H3" t="n">
-        <v>9066</v>
+        <v>9071</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3501</v>
+        <v>3550</v>
       </c>
       <c r="O3" t="n">
         <v>324</v>
@@ -665,7 +665,7 @@
         <v>605</v>
       </c>
       <c r="R3" t="n">
-        <v>25883</v>
+        <v>25842</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:55</t>
+          <t>2026-07-24 18:09:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6216915</v>
+        <v>3.6219354</v>
       </c>
       <c r="G4" t="n">
-        <v>24997</v>
+        <v>24999</v>
       </c>
       <c r="H4" t="n">
-        <v>5590</v>
+        <v>5592</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 21, 2026</t>
+          <t>Jun 20, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7244</v>
+        <v>7240</v>
       </c>
       <c r="O4" t="n">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="P4" t="n">
         <v>886</v>
       </c>
       <c r="Q4" t="n">
-        <v>1226</v>
+        <v>1240</v>
       </c>
       <c r="R4" t="n">
-        <v>14813</v>
+        <v>14805</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:55</t>
+          <t>2026-07-24 18:09:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.534527</v>
+        <v>4.536263</v>
       </c>
       <c r="G5" t="n">
-        <v>26239</v>
+        <v>26253</v>
       </c>
       <c r="H5" t="n">
-        <v>9776</v>
+        <v>9778</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1990</v>
+        <v>1981</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="Q5" t="n">
-        <v>1710</v>
+        <v>1701</v>
       </c>
       <c r="R5" t="n">
-        <v>21406</v>
+        <v>21436</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:55</t>
+          <t>2026-07-24 18:09:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>110261</v>
+        <v>110383</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:55</t>
+          <t>2026-07-24 18:09:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:55</t>
+          <t>2026-07-24 18:09:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.179396</v>
+        <v>4.177936</v>
       </c>
       <c r="G8" t="n">
-        <v>6069</v>
+        <v>6067</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="O8" t="n">
         <v>129</v>
@@ -1028,10 +1028,10 @@
         <v>171</v>
       </c>
       <c r="Q8" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="R8" t="n">
-        <v>4494</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:55</t>
+          <t>2026-07-24 18:09:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>178409</v>
+        <v>178628</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:56</t>
+          <t>2026-07-24 18:09:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>90309</v>
+        <v>90534</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:56</t>
+          <t>2026-07-24 18:09:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6832957</v>
+        <v>4.681061</v>
       </c>
       <c r="G11" t="n">
-        <v>14894</v>
+        <v>14900</v>
       </c>
       <c r="H11" t="n">
         <v>699</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="O11" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P11" t="n">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="Q11" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="R11" t="n">
-        <v>13002</v>
+        <v>12991</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:56</t>
+          <t>2026-07-24 18:09:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7875648</v>
+        <v>2.7818182</v>
       </c>
       <c r="G12" t="n">
-        <v>4688</v>
+        <v>4687</v>
       </c>
       <c r="H12" t="n">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2367</v>
+        <v>2373</v>
       </c>
       <c r="O12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P12" t="n">
         <v>181</v>
       </c>
       <c r="Q12" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1821</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:56</t>
+          <t>2026-07-24 18:09:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21963</v>
+        <v>21971</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:56</t>
+          <t>2026-07-24 18:09:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7975206</v>
+        <v>4.7890434</v>
       </c>
       <c r="G14" t="n">
-        <v>13284</v>
+        <v>13295</v>
       </c>
       <c r="H14" t="n">
         <v>4978</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1246443</v>
+        <v>1248493</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>526</v>
+        <v>554</v>
       </c>
       <c r="O14" t="n">
         <v>75</v>
@@ -1468,10 +1468,10 @@
         <v>75</v>
       </c>
       <c r="Q14" t="n">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="R14" t="n">
-        <v>12405</v>
+        <v>12381</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:57</t>
+          <t>2026-07-24 18:09:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>397215</v>
+        <v>397891</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-23 18:04:57</t>
+          <t>2026-07-24 18:09:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.711726</v>
+        <v>4.710863</v>
       </c>
       <c r="G16" t="n">
         <v>46674</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2182</v>
+        <v>2192</v>
       </c>
       <c r="O16" t="n">
         <v>335</v>
@@ -1616,10 +1616,10 @@
         <v>716</v>
       </c>
       <c r="Q16" t="n">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="R16" t="n">
-        <v>41157</v>
+        <v>41147</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:06</t>
+          <t>2026-07-25 17:46:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,7 +553,7 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:06</t>
+          <t>2026-07-25 17:46:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -624,10 +624,10 @@
         <v>4.46371</v>
       </c>
       <c r="G3" t="n">
-        <v>30653</v>
+        <v>30662</v>
       </c>
       <c r="H3" t="n">
-        <v>9071</v>
+        <v>9072</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3550</v>
+        <v>3551</v>
       </c>
       <c r="O3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q3" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="R3" t="n">
-        <v>25842</v>
+        <v>25850</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:06</t>
+          <t>2026-07-25 17:46:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6219354</v>
+        <v>3.6133852</v>
       </c>
       <c r="G4" t="n">
-        <v>24999</v>
+        <v>25004</v>
       </c>
       <c r="H4" t="n">
-        <v>5592</v>
+        <v>5593</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 20, 2026</t>
+          <t>Jun 21, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7240</v>
+        <v>7293</v>
       </c>
       <c r="O4" t="n">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="P4" t="n">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="Q4" t="n">
-        <v>1240</v>
+        <v>1218</v>
       </c>
       <c r="R4" t="n">
-        <v>14805</v>
+        <v>14767</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:07</t>
+          <t>2026-07-25 17:46:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.536263</v>
+        <v>4.5378404</v>
       </c>
       <c r="G5" t="n">
-        <v>26253</v>
+        <v>26260</v>
       </c>
       <c r="H5" t="n">
-        <v>9778</v>
+        <v>9780</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>662842</v>
+        <v>663666</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1981</v>
+        <v>1975</v>
       </c>
       <c r="O5" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P5" t="n">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="Q5" t="n">
-        <v>1701</v>
+        <v>1696</v>
       </c>
       <c r="R5" t="n">
-        <v>21436</v>
+        <v>21458</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:07</t>
+          <t>2026-07-25 17:46:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.64</v>
       </c>
       <c r="G6" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H6" t="n">
         <v>163</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:07</t>
+          <t>2026-07-25 17:46:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:07</t>
+          <t>2026-07-25 17:46:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>443881</v>
+        <v>445160</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:08</t>
+          <t>2026-07-25 17:46:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:08</t>
+          <t>2026-07-25 17:46:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:08</t>
+          <t>2026-07-25 17:46:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.681061</v>
+        <v>4.676515</v>
       </c>
       <c r="G11" t="n">
-        <v>14900</v>
+        <v>14906</v>
       </c>
       <c r="H11" t="n">
         <v>699</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="O11" t="n">
         <v>112</v>
@@ -1250,10 +1250,10 @@
         <v>282</v>
       </c>
       <c r="Q11" t="n">
-        <v>733</v>
+        <v>756</v>
       </c>
       <c r="R11" t="n">
-        <v>12991</v>
+        <v>12963</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:08</t>
+          <t>2026-07-25 17:46:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>352473</v>
+        <v>352755</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:08</t>
+          <t>2026-07-25 17:46:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:09</t>
+          <t>2026-07-25 17:46:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7890434</v>
+        <v>4.783211</v>
       </c>
       <c r="G14" t="n">
-        <v>13295</v>
+        <v>13301</v>
       </c>
       <c r="H14" t="n">
-        <v>4978</v>
+        <v>4979</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>554</v>
+        <v>574</v>
       </c>
       <c r="O14" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P14" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q14" t="n">
         <v>205</v>
       </c>
       <c r="R14" t="n">
-        <v>12381</v>
+        <v>12368</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:09</t>
+          <t>2026-07-25 17:46:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-24 18:09:09</t>
+          <t>2026-07-25 17:46:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1578,10 +1578,10 @@
         <v>4.710863</v>
       </c>
       <c r="G16" t="n">
-        <v>46674</v>
+        <v>46673</v>
       </c>
       <c r="H16" t="n">
-        <v>2942</v>
+        <v>2944</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Jul 23, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -1619,7 +1619,7 @@
         <v>2279</v>
       </c>
       <c r="R16" t="n">
-        <v>41147</v>
+        <v>41146</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:08</t>
+          <t>2026-07-26 17:51:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="G2" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H2" t="n">
         <v>176</v>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="O2" t="n">
         <v>7</v>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:08</t>
+          <t>2026-07-26 17:51:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.46371</v>
+        <v>4.465884</v>
       </c>
       <c r="G3" t="n">
-        <v>30662</v>
+        <v>30667</v>
       </c>
       <c r="H3" t="n">
-        <v>9072</v>
+        <v>9077</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2384186</v>
+        <v>2386775</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3551</v>
+        <v>3543</v>
       </c>
       <c r="O3" t="n">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="P3" t="n">
         <v>325</v>
@@ -665,7 +665,7 @@
         <v>606</v>
       </c>
       <c r="R3" t="n">
-        <v>25850</v>
+        <v>25873</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:08</t>
+          <t>2026-07-26 17:51:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6133852</v>
+        <v>3.6142857</v>
       </c>
       <c r="G4" t="n">
         <v>25004</v>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7293</v>
+        <v>7289</v>
       </c>
       <c r="O4" t="n">
         <v>827</v>
@@ -736,10 +736,10 @@
         <v>892</v>
       </c>
       <c r="Q4" t="n">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="R4" t="n">
-        <v>14767</v>
+        <v>14774</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:09</t>
+          <t>2026-07-26 17:51:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5378404</v>
+        <v>4.535608</v>
       </c>
       <c r="G5" t="n">
-        <v>26260</v>
+        <v>26263</v>
       </c>
       <c r="H5" t="n">
-        <v>9780</v>
+        <v>9789</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,11 +783,11 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>663666</v>
+        <v>664849</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>391.0</t>
+          <t>395.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -797,23 +797,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Jul 1, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1975</v>
+        <v>1982</v>
       </c>
       <c r="O5" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="P5" t="n">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="Q5" t="n">
-        <v>1696</v>
+        <v>1690</v>
       </c>
       <c r="R5" t="n">
-        <v>21458</v>
+        <v>21447</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:09</t>
+          <t>2026-07-26 17:51:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.64</v>
       </c>
       <c r="G6" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H6" t="n">
         <v>163</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>110383</v>
+        <v>110384</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:09</t>
+          <t>2026-07-26 17:51:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:10</t>
+          <t>2026-07-26 17:51:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>445160</v>
+        <v>445162</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:10</t>
+          <t>2026-07-26 17:51:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:10</t>
+          <t>2026-07-26 17:51:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1141,7 +1141,7 @@
         <v>562</v>
       </c>
       <c r="H10" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>16</v>
       </c>
       <c r="R10" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:10</t>
+          <t>2026-07-26 17:51:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.676515</v>
+        <v>4.675472</v>
       </c>
       <c r="G11" t="n">
-        <v>14906</v>
+        <v>14915</v>
       </c>
       <c r="H11" t="n">
         <v>699</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>261348</v>
+        <v>266118</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="O11" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P11" t="n">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="Q11" t="n">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="R11" t="n">
-        <v>12963</v>
+        <v>12955</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:11</t>
+          <t>2026-07-26 17:51:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>4687</v>
       </c>
       <c r="H12" t="n">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>352755</v>
+        <v>353258</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:11</t>
+          <t>2026-07-26 17:51:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:11</t>
+          <t>2026-07-26 17:51:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.783211</v>
+        <v>4.780309</v>
       </c>
       <c r="G14" t="n">
-        <v>13301</v>
+        <v>13303</v>
       </c>
       <c r="H14" t="n">
-        <v>4979</v>
+        <v>4985</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1248493</v>
+        <v>1251287</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="O14" t="n">
         <v>74</v>
@@ -1468,10 +1468,10 @@
         <v>74</v>
       </c>
       <c r="Q14" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="R14" t="n">
-        <v>12368</v>
+        <v>12360</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:12</t>
+          <t>2026-07-26 17:51:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,10 +1504,10 @@
         <v>3.363372</v>
       </c>
       <c r="G15" t="n">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="H15" t="n">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="O15" t="n">
         <v>113</v>
@@ -1545,7 +1545,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2127</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-25 17:46:12</t>
+          <t>2026-07-26 17:51:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.710863</v>
+        <v>4.7099023</v>
       </c>
       <c r="G16" t="n">
-        <v>46673</v>
+        <v>46676</v>
       </c>
       <c r="H16" t="n">
         <v>2944</v>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2192</v>
+        <v>2202</v>
       </c>
       <c r="O16" t="n">
         <v>335</v>
       </c>
       <c r="P16" t="n">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="Q16" t="n">
-        <v>2279</v>
+        <v>2289</v>
       </c>
       <c r="R16" t="n">
-        <v>41146</v>
+        <v>41131</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:07</t>
+          <t>2026-07-27 18:17:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:07</t>
+          <t>2026-07-27 18:17:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.465884</v>
+        <v>4.4617915</v>
       </c>
       <c r="G3" t="n">
-        <v>30667</v>
+        <v>30673</v>
       </c>
       <c r="H3" t="n">
-        <v>9077</v>
+        <v>9080</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3543</v>
+        <v>3577</v>
       </c>
       <c r="O3" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q3" t="n">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="R3" t="n">
-        <v>25873</v>
+        <v>25850</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:07</t>
+          <t>2026-07-27 18:17:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.6142857</v>
       </c>
       <c r="G4" t="n">
-        <v>25004</v>
+        <v>25003</v>
       </c>
       <c r="H4" t="n">
         <v>5593</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2593315</v>
+        <v>2596076</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1216</v>
       </c>
       <c r="R4" t="n">
-        <v>14774</v>
+        <v>14773</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:08</t>
+          <t>2026-07-27 18:17:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.535608</v>
+        <v>4.5355773</v>
       </c>
       <c r="G5" t="n">
-        <v>26263</v>
+        <v>26282</v>
       </c>
       <c r="H5" t="n">
-        <v>9789</v>
+        <v>9793</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="O5" t="n">
         <v>290</v>
       </c>
       <c r="P5" t="n">
-        <v>850</v>
+        <v>827</v>
       </c>
       <c r="Q5" t="n">
-        <v>1690</v>
+        <v>1701</v>
       </c>
       <c r="R5" t="n">
-        <v>21447</v>
+        <v>21466</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:08</t>
+          <t>2026-07-27 18:17:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:08</t>
+          <t>2026-07-27 18:17:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -916,10 +916,10 @@
         <v>4.7109375</v>
       </c>
       <c r="G7" t="n">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="H7" t="n">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>59</v>
       </c>
       <c r="R7" t="n">
-        <v>2809</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:09</t>
+          <t>2026-07-27 18:17:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.177936</v>
+        <v>4.172598</v>
       </c>
       <c r="G8" t="n">
-        <v>6067</v>
+        <v>6068</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>445162</v>
+        <v>446318</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>993</v>
       </c>
       <c r="O8" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="P8" t="n">
         <v>171</v>
@@ -1031,7 +1031,7 @@
         <v>280</v>
       </c>
       <c r="R8" t="n">
-        <v>4490</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:09</t>
+          <t>2026-07-27 18:17:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:09</t>
+          <t>2026-07-27 18:17:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.01</v>
+        <v>3.990196</v>
       </c>
       <c r="G10" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H10" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>90534</v>
+        <v>90869</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>16</v>
       </c>
       <c r="R10" t="n">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:10</t>
+          <t>2026-07-27 18:17:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.675472</v>
+        <v>4.6787605</v>
       </c>
       <c r="G11" t="n">
-        <v>14915</v>
+        <v>14922</v>
       </c>
       <c r="H11" t="n">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="O11" t="n">
         <v>111</v>
       </c>
       <c r="P11" t="n">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="Q11" t="n">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="R11" t="n">
-        <v>12955</v>
+        <v>12969</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:10</t>
+          <t>2026-07-27 18:17:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7818182</v>
+        <v>2.7864583</v>
       </c>
       <c r="G12" t="n">
-        <v>4687</v>
+        <v>4690</v>
       </c>
       <c r="H12" t="n">
         <v>1937</v>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2373</v>
+        <v>2369</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
       </c>
       <c r="P12" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q12" t="n">
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1813</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:10</t>
+          <t>2026-07-27 18:17:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21971</v>
+        <v>21997</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:10</t>
+          <t>2026-07-27 18:17:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.780309</v>
+        <v>4.771958</v>
       </c>
       <c r="G14" t="n">
-        <v>13303</v>
+        <v>13316</v>
       </c>
       <c r="H14" t="n">
         <v>4985</v>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>584</v>
+        <v>611</v>
       </c>
       <c r="O14" t="n">
         <v>74</v>
@@ -1468,10 +1468,10 @@
         <v>74</v>
       </c>
       <c r="Q14" t="n">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="R14" t="n">
-        <v>12360</v>
+        <v>12339</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:11</t>
+          <t>2026-07-27 18:17:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.363372</v>
       </c>
       <c r="G15" t="n">
-        <v>3894</v>
+        <v>3896</v>
       </c>
       <c r="H15" t="n">
         <v>1573</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="O15" t="n">
         <v>113</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-26 17:51:11</t>
+          <t>2026-07-27 18:17:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7099023</v>
+        <v>4.7106977</v>
       </c>
       <c r="G16" t="n">
-        <v>46676</v>
+        <v>46674</v>
       </c>
       <c r="H16" t="n">
         <v>2944</v>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2202</v>
+        <v>2192</v>
       </c>
       <c r="O16" t="n">
         <v>335</v>
       </c>
       <c r="P16" t="n">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="Q16" t="n">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="R16" t="n">
-        <v>41131</v>
+        <v>41137</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:19</t>
+          <t>2026-07-28 18:07:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>3.96</v>
       </c>
       <c r="G2" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H2" t="n">
         <v>176</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>38769</v>
+        <v>38923</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:20</t>
+          <t>2026-07-28 18:07:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4617915</v>
+        <v>4.461877</v>
       </c>
       <c r="G3" t="n">
-        <v>30673</v>
+        <v>30685</v>
       </c>
       <c r="H3" t="n">
-        <v>9080</v>
+        <v>9085</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Jul 12, 2026</t>
+          <t>Jul 27, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q3" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="R3" t="n">
-        <v>25850</v>
+        <v>25859</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:20</t>
+          <t>2026-07-28 18:07:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6142857</v>
+        <v>3.6159844</v>
       </c>
       <c r="G4" t="n">
         <v>25003</v>
@@ -723,11 +723,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 21, 2026</t>
+          <t>Jun 20, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7289</v>
+        <v>7277</v>
       </c>
       <c r="O4" t="n">
         <v>827</v>
@@ -736,10 +736,10 @@
         <v>892</v>
       </c>
       <c r="Q4" t="n">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="R4" t="n">
-        <v>14773</v>
+        <v>14783</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:20</t>
+          <t>2026-07-28 18:07:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5355773</v>
+        <v>4.538363</v>
       </c>
       <c r="G5" t="n">
-        <v>26282</v>
+        <v>26291</v>
       </c>
       <c r="H5" t="n">
-        <v>9793</v>
+        <v>9801</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1992</v>
+        <v>1971</v>
       </c>
       <c r="O5" t="n">
         <v>290</v>
       </c>
       <c r="P5" t="n">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="Q5" t="n">
-        <v>1701</v>
+        <v>1714</v>
       </c>
       <c r="R5" t="n">
-        <v>21466</v>
+        <v>21482</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:21</t>
+          <t>2026-07-28 18:07:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>110384</v>
+        <v>110536</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:21</t>
+          <t>2026-07-28 18:07:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7109375</v>
+        <v>4.7120624</v>
       </c>
       <c r="G7" t="n">
         <v>3100</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>437016</v>
+        <v>438279</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>59</v>
       </c>
       <c r="R7" t="n">
-        <v>2808</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:21</t>
+          <t>2026-07-28 18:07:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -990,7 +990,7 @@
         <v>4.172598</v>
       </c>
       <c r="G8" t="n">
-        <v>6068</v>
+        <v>6069</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:22</t>
+          <t>2026-07-28 18:07:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>178628</v>
+        <v>178972</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:22</t>
+          <t>2026-07-28 18:07:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.990196</v>
+        <v>4.05</v>
       </c>
       <c r="G10" t="n">
         <v>563</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>401</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:22</t>
+          <t>2026-07-28 18:07:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1212,7 +1212,7 @@
         <v>4.6787605</v>
       </c>
       <c r="G11" t="n">
-        <v>14922</v>
+        <v>14935</v>
       </c>
       <c r="H11" t="n">
         <v>700</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O11" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P11" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="Q11" t="n">
-        <v>777</v>
+        <v>801</v>
       </c>
       <c r="R11" t="n">
-        <v>12969</v>
+        <v>12970</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:23</t>
+          <t>2026-07-28 18:07:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>4690</v>
       </c>
       <c r="H12" t="n">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:23</t>
+          <t>2026-07-28 18:07:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:23</t>
+          <t>2026-07-28 18:07:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.771958</v>
+        <v>4.772691</v>
       </c>
       <c r="G14" t="n">
-        <v>13316</v>
+        <v>13321</v>
       </c>
       <c r="H14" t="n">
-        <v>4985</v>
+        <v>4987</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="O14" t="n">
         <v>74</v>
@@ -1468,10 +1468,10 @@
         <v>74</v>
       </c>
       <c r="Q14" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="R14" t="n">
-        <v>12339</v>
+        <v>12346</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:23</t>
+          <t>2026-07-28 18:07:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,10 +1504,10 @@
         <v>3.363372</v>
       </c>
       <c r="G15" t="n">
-        <v>3896</v>
+        <v>3895</v>
       </c>
       <c r="H15" t="n">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>397891</v>
+        <v>398795</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1545,7 +1545,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2128</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-27 18:17:24</t>
+          <t>2026-07-28 18:07:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7106977</v>
+        <v>4.710832</v>
       </c>
       <c r="G16" t="n">
-        <v>46674</v>
+        <v>46676</v>
       </c>
       <c r="H16" t="n">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>566942</v>
+        <v>568422</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="O16" t="n">
         <v>335</v>
       </c>
       <c r="P16" t="n">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="Q16" t="n">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="R16" t="n">
-        <v>41137</v>
+        <v>41142</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:08</t>
+          <t>2026-07-29 18:00:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:08</t>
+          <t>2026-07-29 18:00:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.461877</v>
+        <v>4.4634237</v>
       </c>
       <c r="G3" t="n">
-        <v>30685</v>
+        <v>30696</v>
       </c>
       <c r="H3" t="n">
-        <v>9085</v>
+        <v>9091</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2386775</v>
+        <v>2388182</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3576</v>
+        <v>3569</v>
       </c>
       <c r="O3" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q3" t="n">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="R3" t="n">
-        <v>25859</v>
+        <v>25890</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:09</t>
+          <t>2026-07-29 18:00:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6159844</v>
+        <v>3.6149352</v>
       </c>
       <c r="G4" t="n">
-        <v>25003</v>
+        <v>25005</v>
       </c>
       <c r="H4" t="n">
         <v>5593</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7277</v>
+        <v>7274</v>
       </c>
       <c r="O4" t="n">
-        <v>827</v>
+        <v>844</v>
       </c>
       <c r="P4" t="n">
         <v>892</v>
       </c>
       <c r="Q4" t="n">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="R4" t="n">
-        <v>14783</v>
+        <v>14774</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:09</t>
+          <t>2026-07-29 18:00:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.538363</v>
+        <v>4.5387893</v>
       </c>
       <c r="G5" t="n">
-        <v>26291</v>
+        <v>26308</v>
       </c>
       <c r="H5" t="n">
-        <v>9801</v>
+        <v>9803</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,11 +783,11 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>664849</v>
+        <v>665265</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>395.0</t>
+          <t>397.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -797,23 +797,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 27, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1971</v>
+        <v>1962</v>
       </c>
       <c r="O5" t="n">
         <v>290</v>
       </c>
       <c r="P5" t="n">
-        <v>829</v>
+        <v>840</v>
       </c>
       <c r="Q5" t="n">
-        <v>1714</v>
+        <v>1726</v>
       </c>
       <c r="R5" t="n">
-        <v>21482</v>
+        <v>21485</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:09</t>
+          <t>2026-07-29 18:00:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -849,7 +849,7 @@
         <v>465</v>
       </c>
       <c r="H6" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -857,11 +857,11 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>110536</v>
+        <v>110578</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Varies with device</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -869,7 +869,11 @@
           <t>Mar 13, 2017</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Jul 24, 2026</t>
+        </is>
+      </c>
       <c r="N6" t="n">
         <v>129</v>
       </c>
@@ -894,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:09</t>
+          <t>2026-07-29 18:00:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7120624</v>
+        <v>4.6976743</v>
       </c>
       <c r="G7" t="n">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="H7" t="n">
         <v>1151</v>
@@ -945,7 +949,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="O7" t="n">
         <v>10</v>
@@ -957,7 +961,7 @@
         <v>59</v>
       </c>
       <c r="R7" t="n">
-        <v>2809</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:10</t>
+          <t>2026-07-29 18:00:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.172598</v>
+        <v>4.175532</v>
       </c>
       <c r="G8" t="n">
-        <v>6069</v>
+        <v>6071</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1019,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="O8" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P8" t="n">
         <v>171</v>
       </c>
       <c r="Q8" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R8" t="n">
-        <v>4480</v>
+        <v>4488</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:10</t>
+          <t>2026-07-29 18:00:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,7 +1068,7 @@
         <v>4.0280375</v>
       </c>
       <c r="G9" t="n">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H9" t="n">
         <v>494</v>
@@ -1105,7 +1109,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:11</t>
+          <t>2026-07-29 18:00:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:11</t>
+          <t>2026-07-29 18:00:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6787605</v>
+        <v>4.6792455</v>
       </c>
       <c r="G11" t="n">
-        <v>14935</v>
+        <v>14944</v>
       </c>
       <c r="H11" t="n">
         <v>700</v>
@@ -1223,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>266118</v>
+        <v>269086</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1245,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="O11" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P11" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q11" t="n">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="R11" t="n">
-        <v>12970</v>
+        <v>12980</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:12</t>
+          <t>2026-07-29 18:00:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1287,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7864583</v>
+        <v>2.7708333</v>
       </c>
       <c r="G12" t="n">
-        <v>4690</v>
+        <v>4692</v>
       </c>
       <c r="H12" t="n">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,19 +1315,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2369</v>
+        <v>2382</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
       </c>
       <c r="P12" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="Q12" t="n">
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1819</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:13</t>
+          <t>2026-07-29 18:00:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:13</t>
+          <t>2026-07-29 18:00:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.772691</v>
+        <v>4.7670135</v>
       </c>
       <c r="G14" t="n">
-        <v>13321</v>
+        <v>13325</v>
       </c>
       <c r="H14" t="n">
-        <v>4987</v>
+        <v>4988</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1251287</v>
+        <v>1252498</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="O14" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P14" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q14" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R14" t="n">
-        <v>12346</v>
+        <v>12332</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:13</t>
+          <t>2026-07-29 18:00:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,13 +1505,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.363372</v>
+        <v>3.3565218</v>
       </c>
       <c r="G15" t="n">
-        <v>3895</v>
+        <v>3897</v>
       </c>
       <c r="H15" t="n">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1533,19 +1537,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1426</v>
+        <v>1434</v>
       </c>
       <c r="O15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q15" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R15" t="n">
-        <v>2127</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-28 18:07:13</t>
+          <t>2026-07-29 18:00:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1579,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.710832</v>
+        <v>4.70997</v>
       </c>
       <c r="G16" t="n">
-        <v>46676</v>
+        <v>46677</v>
       </c>
       <c r="H16" t="n">
         <v>2945</v>
@@ -1607,7 +1611,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2191</v>
+        <v>2201</v>
       </c>
       <c r="O16" t="n">
         <v>335</v>
@@ -1616,10 +1620,10 @@
         <v>715</v>
       </c>
       <c r="Q16" t="n">
-        <v>2289</v>
+        <v>2287</v>
       </c>
       <c r="R16" t="n">
-        <v>41142</v>
+        <v>41133</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:56</t>
+          <t>2026-07-30 18:08:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>38923</v>
+        <v>39044</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:56</t>
+          <t>2026-07-30 18:08:01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4634237</v>
+        <v>4.4604974</v>
       </c>
       <c r="G3" t="n">
-        <v>30696</v>
+        <v>30702</v>
       </c>
       <c r="H3" t="n">
-        <v>9091</v>
+        <v>9093</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2388182</v>
+        <v>2389073</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3569</v>
+        <v>3592</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
@@ -665,7 +665,7 @@
         <v>594</v>
       </c>
       <c r="R3" t="n">
-        <v>25890</v>
+        <v>25873</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:56</t>
+          <t>2026-07-30 18:08:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6149352</v>
+        <v>3.616083</v>
       </c>
       <c r="G4" t="n">
-        <v>25005</v>
+        <v>25006</v>
       </c>
       <c r="H4" t="n">
         <v>5593</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7274</v>
+        <v>7263</v>
       </c>
       <c r="O4" t="n">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="P4" t="n">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="Q4" t="n">
-        <v>1216</v>
+        <v>1230</v>
       </c>
       <c r="R4" t="n">
-        <v>14774</v>
+        <v>14773</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:56</t>
+          <t>2026-07-30 18:08:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5387893</v>
+        <v>4.538953</v>
       </c>
       <c r="G5" t="n">
-        <v>26308</v>
+        <v>26321</v>
       </c>
       <c r="H5" t="n">
-        <v>9803</v>
+        <v>9805</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="O5" t="n">
         <v>290</v>
       </c>
       <c r="P5" t="n">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q5" t="n">
-        <v>1726</v>
+        <v>1735</v>
       </c>
       <c r="R5" t="n">
-        <v>21485</v>
+        <v>21490</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:57</t>
+          <t>2026-07-30 18:08:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H6" t="n">
         <v>164</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>110578</v>
+        <v>110633</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -887,7 +887,7 @@
         <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:57</t>
+          <t>2026-07-30 18:08:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:57</t>
+          <t>2026-07-30 18:08:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:57</t>
+          <t>2026-07-30 18:08:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:57</t>
+          <t>2026-07-30 18:08:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1142,7 +1142,7 @@
         <v>4.05</v>
       </c>
       <c r="G10" t="n">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H10" t="n">
         <v>236</v>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:58</t>
+          <t>2026-07-30 18:08:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6792455</v>
+        <v>4.67997</v>
       </c>
       <c r="G11" t="n">
-        <v>14944</v>
+        <v>14958</v>
       </c>
       <c r="H11" t="n">
         <v>700</v>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="O11" t="n">
         <v>111</v>
@@ -1254,10 +1254,10 @@
         <v>269</v>
       </c>
       <c r="Q11" t="n">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="R11" t="n">
-        <v>12980</v>
+        <v>12998</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:58</t>
+          <t>2026-07-30 18:08:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7708333</v>
+        <v>2.7604167</v>
       </c>
       <c r="G12" t="n">
-        <v>4692</v>
+        <v>4695</v>
       </c>
       <c r="H12" t="n">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>353258</v>
+        <v>353549</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2382</v>
+        <v>2396</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1795</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:58</t>
+          <t>2026-07-30 18:08:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21997</v>
+        <v>22010</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:58</t>
+          <t>2026-07-30 18:08:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7670135</v>
+        <v>4.7686806</v>
       </c>
       <c r="G14" t="n">
-        <v>13325</v>
+        <v>13334</v>
       </c>
       <c r="H14" t="n">
-        <v>4988</v>
+        <v>4991</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="O14" t="n">
         <v>73</v>
@@ -1472,10 +1472,10 @@
         <v>73</v>
       </c>
       <c r="Q14" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R14" t="n">
-        <v>12332</v>
+        <v>12347</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:58</t>
+          <t>2026-07-30 18:08:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3565218</v>
+        <v>3.352601</v>
       </c>
       <c r="G15" t="n">
-        <v>3897</v>
+        <v>3898</v>
       </c>
       <c r="H15" t="n">
         <v>1575</v>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="O15" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="P15" t="n">
         <v>100</v>
@@ -1549,7 +1549,7 @@
         <v>123</v>
       </c>
       <c r="R15" t="n">
-        <v>2123</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-29 18:00:59</t>
+          <t>2026-07-30 18:08:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1585,7 +1585,7 @@
         <v>46677</v>
       </c>
       <c r="H16" t="n">
-        <v>2945</v>
+        <v>2946</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>568422</v>
+        <v>569707</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 30, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:01</t>
+          <t>2026-07-31 18:14:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:01</t>
+          <t>2026-07-31 18:14:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4604974</v>
+        <v>4.4601607</v>
       </c>
       <c r="G3" t="n">
-        <v>30702</v>
+        <v>30715</v>
       </c>
       <c r="H3" t="n">
-        <v>9093</v>
+        <v>9097</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3592</v>
+        <v>3602</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
       </c>
       <c r="P3" t="n">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="Q3" t="n">
         <v>594</v>
       </c>
       <c r="R3" t="n">
-        <v>25873</v>
+        <v>25887</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:01</t>
+          <t>2026-07-31 18:14:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.616083</v>
+        <v>3.615285</v>
       </c>
       <c r="G4" t="n">
-        <v>25006</v>
+        <v>25011</v>
       </c>
       <c r="H4" t="n">
         <v>5593</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2596076</v>
+        <v>2598059</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7263</v>
+        <v>7272</v>
       </c>
       <c r="O4" t="n">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="P4" t="n">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="Q4" t="n">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="R4" t="n">
-        <v>14773</v>
+        <v>14772</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:01</t>
+          <t>2026-07-31 18:14:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.538953</v>
+        <v>4.5379367</v>
       </c>
       <c r="G5" t="n">
-        <v>26321</v>
+        <v>26331</v>
       </c>
       <c r="H5" t="n">
-        <v>9805</v>
+        <v>9810</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>665265</v>
+        <v>665740</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="O5" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P5" t="n">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="Q5" t="n">
-        <v>1735</v>
+        <v>1750</v>
       </c>
       <c r="R5" t="n">
-        <v>21490</v>
+        <v>21481</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:02</t>
+          <t>2026-07-31 18:14:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="G6" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H6" t="n">
         <v>164</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -887,7 +887,7 @@
         <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:02</t>
+          <t>2026-07-31 18:14:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>438279</v>
+        <v>439401</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:02</t>
+          <t>2026-07-31 18:14:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>4.175532</v>
       </c>
       <c r="G8" t="n">
-        <v>6071</v>
+        <v>6070</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>446318</v>
+        <v>447443</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>279</v>
       </c>
       <c r="R8" t="n">
-        <v>4488</v>
+        <v>4487</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:02</t>
+          <t>2026-07-31 18:14:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>178972</v>
+        <v>179200</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:03</t>
+          <t>2026-07-31 18:14:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1142,7 +1142,7 @@
         <v>4.05</v>
       </c>
       <c r="G10" t="n">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H10" t="n">
         <v>236</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>90869</v>
+        <v>91096</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:03</t>
+          <t>2026-07-31 18:14:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.67997</v>
+        <v>4.6781955</v>
       </c>
       <c r="G11" t="n">
-        <v>14958</v>
+        <v>14971</v>
       </c>
       <c r="H11" t="n">
         <v>700</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>269086</v>
+        <v>270551</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="O11" t="n">
         <v>111</v>
@@ -1254,10 +1254,10 @@
         <v>269</v>
       </c>
       <c r="Q11" t="n">
-        <v>798</v>
+        <v>787</v>
       </c>
       <c r="R11" t="n">
-        <v>12998</v>
+        <v>13012</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:03</t>
+          <t>2026-07-31 18:14:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7604167</v>
+        <v>2.755844</v>
       </c>
       <c r="G12" t="n">
-        <v>4695</v>
+        <v>4696</v>
       </c>
       <c r="H12" t="n">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2396</v>
+        <v>2402</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1784</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:03</t>
+          <t>2026-07-31 18:14:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:03</t>
+          <t>2026-07-31 18:14:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7686806</v>
+        <v>4.769534</v>
       </c>
       <c r="G14" t="n">
-        <v>13334</v>
+        <v>13345</v>
       </c>
       <c r="H14" t="n">
-        <v>4991</v>
+        <v>4994</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1252498</v>
+        <v>1253452</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="O14" t="n">
         <v>73</v>
@@ -1472,10 +1472,10 @@
         <v>73</v>
       </c>
       <c r="Q14" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="R14" t="n">
-        <v>12347</v>
+        <v>12354</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:03</t>
+          <t>2026-07-31 18:14:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.352601</v>
+        <v>3.3662791</v>
       </c>
       <c r="G15" t="n">
-        <v>3898</v>
+        <v>3900</v>
       </c>
       <c r="H15" t="n">
         <v>1575</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>398795</v>
+        <v>399447</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1429</v>
+        <v>1416</v>
       </c>
       <c r="O15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2117</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-30 18:08:04</t>
+          <t>2026-07-31 18:14:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.70997</v>
+        <v>4.70964</v>
       </c>
       <c r="G16" t="n">
-        <v>46677</v>
+        <v>46679</v>
       </c>
       <c r="H16" t="n">
         <v>2946</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>569707</v>
+        <v>569723</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="O16" t="n">
         <v>335</v>
       </c>
       <c r="P16" t="n">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="Q16" t="n">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="R16" t="n">
-        <v>41133</v>
+        <v>41126</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:43</t>
+          <t>2026-08-01 17:47:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>3.96</v>
       </c>
       <c r="G2" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H2" t="n">
         <v>176</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>39044</v>
+        <v>39045</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:43</t>
+          <t>2026-08-01 17:47:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4601607</v>
+        <v>4.458227</v>
       </c>
       <c r="G3" t="n">
-        <v>30715</v>
+        <v>30720</v>
       </c>
       <c r="H3" t="n">
-        <v>9097</v>
+        <v>9103</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2389073</v>
+        <v>2389104</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3602</v>
+        <v>3619</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
@@ -662,10 +662,10 @@
         <v>313</v>
       </c>
       <c r="Q3" t="n">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="R3" t="n">
-        <v>25887</v>
+        <v>25877</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:43</t>
+          <t>2026-08-01 17:47:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.615285</v>
+        <v>3.6161811</v>
       </c>
       <c r="G4" t="n">
-        <v>25011</v>
+        <v>25013</v>
       </c>
       <c r="H4" t="n">
-        <v>5593</v>
+        <v>5594</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2598059</v>
+        <v>2598086</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -723,11 +723,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 20, 2026</t>
+          <t>Jun 21, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7272</v>
+        <v>7267</v>
       </c>
       <c r="O4" t="n">
         <v>840</v>
@@ -736,10 +736,10 @@
         <v>889</v>
       </c>
       <c r="Q4" t="n">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="R4" t="n">
-        <v>14772</v>
+        <v>14780</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:44</t>
+          <t>2026-08-01 17:47:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5379367</v>
+        <v>4.5372815</v>
       </c>
       <c r="G5" t="n">
-        <v>26331</v>
+        <v>26342</v>
       </c>
       <c r="H5" t="n">
-        <v>9810</v>
+        <v>9816</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -804,16 +804,16 @@
         <v>1963</v>
       </c>
       <c r="O5" t="n">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="P5" t="n">
         <v>841</v>
       </c>
       <c r="Q5" t="n">
-        <v>1750</v>
+        <v>1739</v>
       </c>
       <c r="R5" t="n">
-        <v>21481</v>
+        <v>21492</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:44</t>
+          <t>2026-08-01 17:47:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>110633</v>
+        <v>110634</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:44</t>
+          <t>2026-08-01 17:47:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.6976743</v>
+        <v>4.6949806</v>
       </c>
       <c r="G7" t="n">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="H7" t="n">
         <v>1151</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>439401</v>
+        <v>439408</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -958,10 +958,10 @@
         <v>35</v>
       </c>
       <c r="Q7" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="R7" t="n">
-        <v>2799</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:44</t>
+          <t>2026-08-01 17:48:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>4.175532</v>
       </c>
       <c r="G8" t="n">
-        <v>6070</v>
+        <v>6071</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>447443</v>
+        <v>447449</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>279</v>
       </c>
       <c r="R8" t="n">
-        <v>4487</v>
+        <v>4488</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:44</t>
+          <t>2026-08-01 17:48:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1068,7 +1068,7 @@
         <v>4.0280375</v>
       </c>
       <c r="G9" t="n">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H9" t="n">
         <v>494</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>179200</v>
+        <v>179210</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,11 +1093,11 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O9" t="n">
         <v>34</v>
@@ -1109,7 +1109,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:45</t>
+          <t>2026-08-01 17:48:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1142,7 +1142,7 @@
         <v>4.05</v>
       </c>
       <c r="G10" t="n">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H10" t="n">
         <v>236</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>91096</v>
+        <v>91099</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:45</t>
+          <t>2026-08-01 17:48:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6781955</v>
+        <v>4.6789474</v>
       </c>
       <c r="G11" t="n">
-        <v>14971</v>
+        <v>14978</v>
       </c>
       <c r="H11" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>270551</v>
+        <v>270553</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="O11" t="n">
         <v>111</v>
       </c>
       <c r="P11" t="n">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="Q11" t="n">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="R11" t="n">
-        <v>13012</v>
+        <v>13006</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:45</t>
+          <t>2026-08-01 17:48:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.755844</v>
+        <v>2.761039</v>
       </c>
       <c r="G12" t="n">
-        <v>4696</v>
+        <v>4697</v>
       </c>
       <c r="H12" t="n">
         <v>1942</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>353549</v>
+        <v>353552</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1315,19 +1315,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2402</v>
+        <v>2390</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
       </c>
       <c r="P12" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="Q12" t="n">
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:45</t>
+          <t>2026-08-01 17:48:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:45</t>
+          <t>2026-08-01 17:48:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.769534</v>
+        <v>4.766929</v>
       </c>
       <c r="G14" t="n">
-        <v>13345</v>
+        <v>13349</v>
       </c>
       <c r="H14" t="n">
-        <v>4994</v>
+        <v>4995</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="O14" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P14" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q14" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R14" t="n">
-        <v>12354</v>
+        <v>12349</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:45</t>
+          <t>2026-08-01 17:48:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1508,7 +1508,7 @@
         <v>3.3662791</v>
       </c>
       <c r="G15" t="n">
-        <v>3900</v>
+        <v>3903</v>
       </c>
       <c r="H15" t="n">
         <v>1575</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>399447</v>
+        <v>399449</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,11 +1533,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1549,7 +1549,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2130</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-31 18:14:46</t>
+          <t>2026-08-01 17:48:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 17:47:58</t>
+          <t>2026-08-02 17:48:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>39045</v>
+        <v>39178</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-01 17:47:59</t>
+          <t>2026-08-02 17:48:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.458227</v>
+        <v>4.451955</v>
       </c>
       <c r="G3" t="n">
-        <v>30720</v>
+        <v>30731</v>
       </c>
       <c r="H3" t="n">
-        <v>9103</v>
+        <v>9106</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2389104</v>
+        <v>2391889</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3619</v>
+        <v>3671</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
@@ -662,10 +662,10 @@
         <v>313</v>
       </c>
       <c r="Q3" t="n">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="R3" t="n">
-        <v>25877</v>
+        <v>25846</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01 17:47:59</t>
+          <t>2026-08-02 17:48:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6161811</v>
+        <v>3.6197548</v>
       </c>
       <c r="G4" t="n">
-        <v>25013</v>
+        <v>25018</v>
       </c>
       <c r="H4" t="n">
         <v>5594</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2598086</v>
+        <v>2601258</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7267</v>
+        <v>7250</v>
       </c>
       <c r="O4" t="n">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P4" t="n">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="Q4" t="n">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="R4" t="n">
-        <v>14780</v>
+        <v>14809</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-01 17:47:59</t>
+          <t>2026-08-02 17:49:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5372815</v>
+        <v>4.535684</v>
       </c>
       <c r="G5" t="n">
-        <v>26342</v>
+        <v>26347</v>
       </c>
       <c r="H5" t="n">
-        <v>9816</v>
+        <v>9821</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1963</v>
+        <v>1969</v>
       </c>
       <c r="O5" t="n">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="P5" t="n">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="Q5" t="n">
-        <v>1739</v>
+        <v>1734</v>
       </c>
       <c r="R5" t="n">
-        <v>21492</v>
+        <v>21488</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-01 17:47:59</t>
+          <t>2026-08-02 17:49:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>110634</v>
+        <v>110740</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-01 17:47:59</t>
+          <t>2026-08-02 17:49:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>439408</v>
+        <v>440858</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:00</t>
+          <t>2026-08-02 17:49:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.175532</v>
+        <v>4.1784453</v>
       </c>
       <c r="G8" t="n">
-        <v>6071</v>
+        <v>6073</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>447449</v>
+        <v>448255</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="O8" t="n">
         <v>139</v>
       </c>
       <c r="P8" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q8" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R8" t="n">
-        <v>4488</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:00</t>
+          <t>2026-08-02 17:49:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>179210</v>
+        <v>179412</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:00</t>
+          <t>2026-08-02 17:49:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>91099</v>
+        <v>91485</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:01</t>
+          <t>2026-08-02 17:49:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6789474</v>
+        <v>4.678464</v>
       </c>
       <c r="G11" t="n">
-        <v>14978</v>
+        <v>14986</v>
       </c>
       <c r="H11" t="n">
         <v>701</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>270553</v>
+        <v>272093</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="O11" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P11" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q11" t="n">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="R11" t="n">
-        <v>13006</v>
+        <v>13010</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:01</t>
+          <t>2026-08-02 17:49:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1290,10 +1290,10 @@
         <v>2.761039</v>
       </c>
       <c r="G12" t="n">
-        <v>4697</v>
+        <v>4699</v>
       </c>
       <c r="H12" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>353552</v>
+        <v>354116</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1781</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:02</t>
+          <t>2026-08-02 17:49:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22010</v>
+        <v>22021</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:02</t>
+          <t>2026-08-02 17:49:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.766929</v>
+        <v>4.762353</v>
       </c>
       <c r="G14" t="n">
-        <v>13349</v>
+        <v>13354</v>
       </c>
       <c r="H14" t="n">
-        <v>4995</v>
+        <v>4997</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1253452</v>
+        <v>1255368</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="O14" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="P14" t="n">
         <v>72</v>
       </c>
       <c r="Q14" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="R14" t="n">
-        <v>12349</v>
+        <v>12337</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:02</t>
+          <t>2026-08-02 17:49:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1511,7 +1511,7 @@
         <v>3903</v>
       </c>
       <c r="H15" t="n">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>399449</v>
+        <v>400500</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-01 17:48:02</t>
+          <t>2026-08-02 17:49:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1582,10 +1582,10 @@
         <v>4.70964</v>
       </c>
       <c r="G16" t="n">
-        <v>46679</v>
+        <v>46677</v>
       </c>
       <c r="H16" t="n">
-        <v>2946</v>
+        <v>2951</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>569723</v>
+        <v>570795</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>2286</v>
       </c>
       <c r="R16" t="n">
-        <v>41126</v>
+        <v>41125</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02 17:48:58</t>
+          <t>2026-08-03 18:30:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>39178</v>
+        <v>39228</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-02 17:48:58</t>
+          <t>2026-08-03 18:30:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.451955</v>
+        <v>4.451589</v>
       </c>
       <c r="G3" t="n">
-        <v>30731</v>
+        <v>30738</v>
       </c>
       <c r="H3" t="n">
-        <v>9106</v>
+        <v>9104</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2391889</v>
+        <v>2391930</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3671</v>
+        <v>3672</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
@@ -662,10 +662,10 @@
         <v>313</v>
       </c>
       <c r="Q3" t="n">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="R3" t="n">
-        <v>25846</v>
+        <v>25840</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-02 17:48:59</t>
+          <t>2026-08-03 18:30:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,10 +698,10 @@
         <v>3.6197548</v>
       </c>
       <c r="G4" t="n">
-        <v>25018</v>
+        <v>25017</v>
       </c>
       <c r="H4" t="n">
-        <v>5594</v>
+        <v>5593</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2601258</v>
+        <v>2601281</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -723,11 +723,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 21, 2026</t>
+          <t>Jun 20, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7250</v>
+        <v>7251</v>
       </c>
       <c r="O4" t="n">
         <v>839</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:00</t>
+          <t>2026-08-03 18:30:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.535684</v>
+        <v>4.536998</v>
       </c>
       <c r="G5" t="n">
-        <v>26347</v>
+        <v>26356</v>
       </c>
       <c r="H5" t="n">
-        <v>9821</v>
+        <v>9824</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>665740</v>
+        <v>667240</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1969</v>
+        <v>1961</v>
       </c>
       <c r="O5" t="n">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="P5" t="n">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="Q5" t="n">
-        <v>1734</v>
+        <v>1749</v>
       </c>
       <c r="R5" t="n">
-        <v>21488</v>
+        <v>21496</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:00</t>
+          <t>2026-08-03 18:30:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>110740</v>
+        <v>110790</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:00</t>
+          <t>2026-08-03 18:30:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -920,7 +920,7 @@
         <v>4.6949806</v>
       </c>
       <c r="G7" t="n">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="H7" t="n">
         <v>1151</v>
@@ -961,7 +961,7 @@
         <v>70</v>
       </c>
       <c r="R7" t="n">
-        <v>2789</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:00</t>
+          <t>2026-08-03 18:30:33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1784453</v>
+        <v>4.1626616</v>
       </c>
       <c r="G8" t="n">
-        <v>6073</v>
+        <v>6074</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>986</v>
+        <v>1010</v>
       </c>
       <c r="O8" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="P8" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="R8" t="n">
-        <v>4494</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:00</t>
+          <t>2026-08-03 18:30:33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>179412</v>
+        <v>179520</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:00</t>
+          <t>2026-08-03 18:30:33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>91485</v>
+        <v>91486</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:00</t>
+          <t>2026-08-03 18:30:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.678464</v>
+        <v>4.6779532</v>
       </c>
       <c r="G11" t="n">
-        <v>14986</v>
+        <v>14990</v>
       </c>
       <c r="H11" t="n">
         <v>701</v>
@@ -1227,11 +1227,11 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>272093</v>
+        <v>272110</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1241,23 +1241,23 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Aug 2, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="O11" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P11" t="n">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Q11" t="n">
-        <v>801</v>
+        <v>811</v>
       </c>
       <c r="R11" t="n">
-        <v>13010</v>
+        <v>13004</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:01</t>
+          <t>2026-08-03 18:30:34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1290,10 +1290,10 @@
         <v>2.761039</v>
       </c>
       <c r="G12" t="n">
-        <v>4699</v>
+        <v>4701</v>
       </c>
       <c r="H12" t="n">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>354116</v>
+        <v>354120</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1780</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:01</t>
+          <t>2026-08-03 18:30:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22021</v>
+        <v>22030</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:01</t>
+          <t>2026-08-03 18:30:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.762353</v>
+        <v>4.7636504</v>
       </c>
       <c r="G14" t="n">
-        <v>13354</v>
+        <v>13359</v>
       </c>
       <c r="H14" t="n">
-        <v>4997</v>
+        <v>4998</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1255368</v>
+        <v>1256430</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="O14" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P14" t="n">
         <v>72</v>
       </c>
       <c r="Q14" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R14" t="n">
-        <v>12337</v>
+        <v>12347</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:01</t>
+          <t>2026-08-03 18:30:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1508,7 +1508,7 @@
         <v>3.3662791</v>
       </c>
       <c r="G15" t="n">
-        <v>3903</v>
+        <v>3905</v>
       </c>
       <c r="H15" t="n">
         <v>1576</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>400500</v>
+        <v>400506</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1549,7 +1549,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2132</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-02 17:49:02</t>
+          <t>2026-08-03 18:30:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.70964</v>
+        <v>4.7099094</v>
       </c>
       <c r="G16" t="n">
-        <v>46677</v>
+        <v>46680</v>
       </c>
       <c r="H16" t="n">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>570795</v>
+        <v>571426</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="O16" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P16" t="n">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="Q16" t="n">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="R16" t="n">
-        <v>41125</v>
+        <v>41133</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:31</t>
+          <t>2026-08-04 18:20:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:32</t>
+          <t>2026-08-04 18:20:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.451589</v>
+        <v>4.452651</v>
       </c>
       <c r="G3" t="n">
-        <v>30738</v>
+        <v>30740</v>
       </c>
       <c r="H3" t="n">
-        <v>9104</v>
+        <v>9113</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2391930</v>
+        <v>2391946</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3672</v>
+        <v>3663</v>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q3" t="n">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="R3" t="n">
-        <v>25840</v>
+        <v>25850</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:32</t>
+          <t>2026-08-04 18:20:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6197548</v>
+        <v>3.620645</v>
       </c>
       <c r="G4" t="n">
-        <v>25017</v>
+        <v>25018</v>
       </c>
       <c r="H4" t="n">
-        <v>5593</v>
+        <v>5595</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 20, 2026</t>
+          <t>Jun 21, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7251</v>
+        <v>7246</v>
       </c>
       <c r="O4" t="n">
         <v>839</v>
       </c>
       <c r="P4" t="n">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="Q4" t="n">
         <v>1226</v>
       </c>
       <c r="R4" t="n">
-        <v>14809</v>
+        <v>14815</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:32</t>
+          <t>2026-08-04 18:20:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.536998</v>
+        <v>4.527636</v>
       </c>
       <c r="G5" t="n">
-        <v>26356</v>
+        <v>26374</v>
       </c>
       <c r="H5" t="n">
-        <v>9824</v>
+        <v>9826</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1961</v>
+        <v>2007</v>
       </c>
       <c r="O5" t="n">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="P5" t="n">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="Q5" t="n">
-        <v>1749</v>
+        <v>1771</v>
       </c>
       <c r="R5" t="n">
-        <v>21496</v>
+        <v>21428</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:32</t>
+          <t>2026-08-04 18:20:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:33</t>
+          <t>2026-08-04 18:20:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.6949806</v>
+        <v>4.6318183</v>
       </c>
       <c r="G7" t="n">
-        <v>3101</v>
+        <v>3103</v>
       </c>
       <c r="H7" t="n">
         <v>1151</v>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P7" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q7" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="R7" t="n">
-        <v>2788</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:33</t>
+          <t>2026-08-04 18:20:33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>4.1626616</v>
       </c>
       <c r="G8" t="n">
-        <v>6074</v>
+        <v>6075</v>
       </c>
       <c r="H8" t="n">
         <v>2255</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>448255</v>
+        <v>448655</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>246</v>
       </c>
       <c r="R8" t="n">
-        <v>4490</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:33</t>
+          <t>2026-08-04 18:20:33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:33</t>
+          <t>2026-08-04 18:20:33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:34</t>
+          <t>2026-08-04 18:20:33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6779532</v>
+        <v>4.677711</v>
       </c>
       <c r="G11" t="n">
-        <v>14990</v>
+        <v>14996</v>
       </c>
       <c r="H11" t="n">
         <v>701</v>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O11" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P11" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q11" t="n">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="R11" t="n">
-        <v>13004</v>
+        <v>13007</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:34</t>
+          <t>2026-08-04 18:20:34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1293,7 +1293,7 @@
         <v>4701</v>
       </c>
       <c r="H12" t="n">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:34</t>
+          <t>2026-08-04 18:20:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1363,7 +1363,7 @@
         <v>112</v>
       </c>
       <c r="H13" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:34</t>
+          <t>2026-08-04 18:20:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7636504</v>
+        <v>4.756569</v>
       </c>
       <c r="G14" t="n">
-        <v>13359</v>
+        <v>13373</v>
       </c>
       <c r="H14" t="n">
-        <v>4998</v>
+        <v>4997</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>634</v>
+        <v>661</v>
       </c>
       <c r="O14" t="n">
         <v>82</v>
       </c>
       <c r="P14" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q14" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="R14" t="n">
-        <v>12347</v>
+        <v>12338</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:34</t>
+          <t>2026-08-04 18:20:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-03 18:30:35</t>
+          <t>2026-08-04 18:20:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7099094</v>
+        <v>4.7091837</v>
       </c>
       <c r="G16" t="n">
-        <v>46680</v>
+        <v>46683</v>
       </c>
       <c r="H16" t="n">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>571426</v>
+        <v>571434</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,11 +1607,11 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Jul 30, 2026</t>
+          <t>Aug 4, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2198</v>
+        <v>2207</v>
       </c>
       <c r="O16" t="n">
         <v>334</v>
@@ -1620,10 +1620,10 @@
         <v>725</v>
       </c>
       <c r="Q16" t="n">
-        <v>2285</v>
+        <v>2283</v>
       </c>
       <c r="R16" t="n">
-        <v>41133</v>
+        <v>41128</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:30</t>
+          <t>2026-08-05 18:13:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>3.96</v>
       </c>
       <c r="G2" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2" t="n">
         <v>176</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>39228</v>
+        <v>39230</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:32</t>
+          <t>2026-08-05 18:13:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.452651</v>
+        <v>4.448816</v>
       </c>
       <c r="G3" t="n">
-        <v>30740</v>
+        <v>30749</v>
       </c>
       <c r="H3" t="n">
-        <v>9113</v>
+        <v>9119</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3663</v>
+        <v>3695</v>
       </c>
       <c r="O3" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P3" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q3" t="n">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="R3" t="n">
-        <v>25850</v>
+        <v>25830</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:32</t>
+          <t>2026-08-05 18:13:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.620645</v>
+        <v>3.6217782</v>
       </c>
       <c r="G4" t="n">
-        <v>25018</v>
+        <v>25020</v>
       </c>
       <c r="H4" t="n">
-        <v>5595</v>
+        <v>5596</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2601281</v>
+        <v>2602164</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7246</v>
+        <v>7237</v>
       </c>
       <c r="O4" t="n">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="P4" t="n">
         <v>886</v>
       </c>
       <c r="Q4" t="n">
-        <v>1226</v>
+        <v>1240</v>
       </c>
       <c r="R4" t="n">
-        <v>14815</v>
+        <v>14814</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:32</t>
+          <t>2026-08-05 18:13:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.527636</v>
+        <v>4.529038</v>
       </c>
       <c r="G5" t="n">
-        <v>26374</v>
+        <v>26379</v>
       </c>
       <c r="H5" t="n">
-        <v>9826</v>
+        <v>9831</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>667240</v>
+        <v>667243</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="O5" t="n">
         <v>324</v>
       </c>
       <c r="P5" t="n">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="Q5" t="n">
-        <v>1771</v>
+        <v>1765</v>
       </c>
       <c r="R5" t="n">
-        <v>21428</v>
+        <v>21447</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:32</t>
+          <t>2026-08-05 18:13:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>110790</v>
+        <v>110837</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:33</t>
+          <t>2026-08-05 18:13:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.6318183</v>
+        <v>4.630137</v>
       </c>
       <c r="G7" t="n">
         <v>3103</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>440858</v>
+        <v>440865</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>84</v>
       </c>
       <c r="R7" t="n">
-        <v>2721</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:33</t>
+          <t>2026-08-05 18:13:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1626616</v>
+        <v>4.1642065</v>
       </c>
       <c r="G8" t="n">
-        <v>6075</v>
+        <v>6076</v>
       </c>
       <c r="H8" t="n">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="O8" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P8" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="R8" t="n">
-        <v>4491</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:33</t>
+          <t>2026-08-05 18:13:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>179520</v>
+        <v>179526</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:33</t>
+          <t>2026-08-05 18:13:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1145,7 +1145,7 @@
         <v>562</v>
       </c>
       <c r="H10" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>91486</v>
+        <v>91491</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:33</t>
+          <t>2026-08-05 18:13:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.677711</v>
+        <v>4.677201</v>
       </c>
       <c r="G11" t="n">
-        <v>14996</v>
+        <v>14991</v>
       </c>
       <c r="H11" t="n">
         <v>701</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>272110</v>
+        <v>272121</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="O11" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P11" t="n">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Q11" t="n">
-        <v>812</v>
+        <v>822</v>
       </c>
       <c r="R11" t="n">
-        <v>13007</v>
+        <v>12993</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:34</t>
+          <t>2026-08-05 18:13:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.761039</v>
+        <v>2.7416022</v>
       </c>
       <c r="G12" t="n">
-        <v>4701</v>
+        <v>4705</v>
       </c>
       <c r="H12" t="n">
         <v>1946</v>
@@ -1315,19 +1315,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2392</v>
+        <v>2419</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
       </c>
       <c r="P12" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q12" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R12" t="n">
-        <v>1782</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:34</t>
+          <t>2026-08-05 18:13:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7765958</v>
+        <v>2.7578948</v>
       </c>
       <c r="G13" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H13" t="n">
         <v>40</v>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O13" t="n">
         <v>5</v>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:34</t>
+          <t>2026-08-05 18:13:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.756569</v>
+        <v>4.7467103</v>
       </c>
       <c r="G14" t="n">
-        <v>13373</v>
+        <v>13383</v>
       </c>
       <c r="H14" t="n">
-        <v>4997</v>
+        <v>4999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1256430</v>
+        <v>1256459</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="O14" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="P14" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q14" t="n">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="R14" t="n">
-        <v>12338</v>
+        <v>12325</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:34</t>
+          <t>2026-08-05 18:13:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3662791</v>
+        <v>3.3710146</v>
       </c>
       <c r="G15" t="n">
-        <v>3905</v>
+        <v>3906</v>
       </c>
       <c r="H15" t="n">
         <v>1576</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>400506</v>
+        <v>400513</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1549,7 +1549,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2133</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-04 18:20:34</t>
+          <t>2026-08-05 18:13:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7091837</v>
+        <v>4.7087197</v>
       </c>
       <c r="G16" t="n">
-        <v>46683</v>
+        <v>46682</v>
       </c>
       <c r="H16" t="n">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1617,13 +1617,13 @@
         <v>334</v>
       </c>
       <c r="P16" t="n">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="Q16" t="n">
         <v>2283</v>
       </c>
       <c r="R16" t="n">
-        <v>41128</v>
+        <v>41117</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:53</t>
+          <t>2026-08-07 17:37:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>39230</v>
+        <v>39283</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:54</t>
+          <t>2026-08-07 17:37:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.448816</v>
+        <v>4.448339</v>
       </c>
       <c r="G3" t="n">
-        <v>30749</v>
+        <v>30760</v>
       </c>
       <c r="H3" t="n">
-        <v>9119</v>
+        <v>9120</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2391946</v>
+        <v>2395178</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.44.4</t>
+          <t>4.44.5</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3695</v>
+        <v>3716</v>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="P3" t="n">
         <v>313</v>
       </c>
       <c r="Q3" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="R3" t="n">
-        <v>25830</v>
+        <v>25840</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:54</t>
+          <t>2026-08-07 17:37:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6217782</v>
+        <v>3.6252415</v>
       </c>
       <c r="G4" t="n">
         <v>25020</v>
       </c>
       <c r="H4" t="n">
-        <v>5596</v>
+        <v>5597</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2602164</v>
+        <v>2602169</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7237</v>
+        <v>7216</v>
       </c>
       <c r="O4" t="n">
         <v>837</v>
       </c>
       <c r="P4" t="n">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="Q4" t="n">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="R4" t="n">
-        <v>14814</v>
+        <v>14837</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:54</t>
+          <t>2026-08-07 17:37:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.529038</v>
+        <v>4.5309587</v>
       </c>
       <c r="G5" t="n">
-        <v>26379</v>
+        <v>26404</v>
       </c>
       <c r="H5" t="n">
-        <v>9831</v>
+        <v>9833</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>667243</v>
+        <v>667628</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2001</v>
+        <v>1992</v>
       </c>
       <c r="O5" t="n">
         <v>324</v>
       </c>
       <c r="P5" t="n">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="Q5" t="n">
-        <v>1765</v>
+        <v>1779</v>
       </c>
       <c r="R5" t="n">
-        <v>21447</v>
+        <v>21476</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:55</t>
+          <t>2026-08-07 17:37:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Aug 5, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:55</t>
+          <t>2026-08-07 17:37:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -923,7 +923,7 @@
         <v>3103</v>
       </c>
       <c r="H7" t="n">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>440865</v>
+        <v>441377</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>84</v>
       </c>
       <c r="R7" t="n">
-        <v>2720</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:56</t>
+          <t>2026-08-07 17:37:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1642065</v>
+        <v>4.1559634</v>
       </c>
       <c r="G8" t="n">
-        <v>6076</v>
+        <v>6079</v>
       </c>
       <c r="H8" t="n">
         <v>2257</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>448655</v>
+        <v>449049</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="O8" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="P8" t="n">
         <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="R8" t="n">
-        <v>4494</v>
+        <v>4482</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:57</t>
+          <t>2026-08-07 17:37:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.0280375</v>
+        <v>3.9906542</v>
       </c>
       <c r="G9" t="n">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H9" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>179526</v>
+        <v>179640</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="O9" t="n">
         <v>34</v>
@@ -1109,7 +1109,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>872</v>
+        <v>861</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:57</t>
+          <t>2026-08-07 17:37:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="G10" t="n">
         <v>562</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>91491</v>
+        <v>91596</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:57</t>
+          <t>2026-08-07 17:37:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.677201</v>
+        <v>4.6764483</v>
       </c>
       <c r="G11" t="n">
         <v>14991</v>
       </c>
       <c r="H11" t="n">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>272121</v>
+        <v>272214</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         <v>280</v>
       </c>
       <c r="Q11" t="n">
-        <v>822</v>
+        <v>833</v>
       </c>
       <c r="R11" t="n">
-        <v>12993</v>
+        <v>12982</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:58</t>
+          <t>2026-08-07 17:37:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1293,7 +1293,7 @@
         <v>4705</v>
       </c>
       <c r="H12" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>354120</v>
+        <v>354429</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:58</t>
+          <t>2026-08-07 17:37:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22030</v>
+        <v>22038</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:58</t>
+          <t>2026-08-07 17:37:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7467103</v>
+        <v>4.730081</v>
       </c>
       <c r="G14" t="n">
-        <v>13383</v>
+        <v>13397</v>
       </c>
       <c r="H14" t="n">
-        <v>4999</v>
+        <v>5004</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1256459</v>
+        <v>1257426</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>693</v>
+        <v>750</v>
       </c>
       <c r="O14" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="P14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q14" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="R14" t="n">
-        <v>12325</v>
+        <v>12285</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:58</t>
+          <t>2026-08-07 17:37:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1508,7 +1508,7 @@
         <v>3.3710146</v>
       </c>
       <c r="G15" t="n">
-        <v>3906</v>
+        <v>3908</v>
       </c>
       <c r="H15" t="n">
         <v>1576</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>400513</v>
+        <v>400831</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2139</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-05 18:13:58</t>
+          <t>2026-08-07 17:37:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7087197</v>
+        <v>4.7089224</v>
       </c>
       <c r="G16" t="n">
-        <v>46682</v>
+        <v>46683</v>
       </c>
       <c r="H16" t="n">
         <v>2952</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>571434</v>
+        <v>571866</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,11 +1607,11 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Aug 4, 2026</t>
+          <t>Aug 5, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="O16" t="n">
         <v>334</v>
@@ -1620,10 +1620,10 @@
         <v>735</v>
       </c>
       <c r="Q16" t="n">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="R16" t="n">
-        <v>41117</v>
+        <v>41121</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:55</t>
+          <t>2026-08-08 17:19:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>39283</v>
+        <v>39456</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:55</t>
+          <t>2026-08-08 17:19:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.448339</v>
+        <v>4.449397</v>
       </c>
       <c r="G3" t="n">
-        <v>30760</v>
+        <v>30764</v>
       </c>
       <c r="H3" t="n">
-        <v>9120</v>
+        <v>9123</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2395178</v>
+        <v>2396124</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3716</v>
+        <v>3708</v>
       </c>
       <c r="O3" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q3" t="n">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="R3" t="n">
-        <v>25840</v>
+        <v>25851</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:55</t>
+          <t>2026-08-08 17:19:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6252415</v>
+        <v>3.6262043</v>
       </c>
       <c r="G4" t="n">
-        <v>25020</v>
+        <v>25025</v>
       </c>
       <c r="H4" t="n">
         <v>5597</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2602169</v>
+        <v>2605075</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 21, 2026</t>
+          <t>Jun 20, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
         <v>7216</v>
       </c>
       <c r="O4" t="n">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="P4" t="n">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="Q4" t="n">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="R4" t="n">
-        <v>14837</v>
+        <v>14850</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:55</t>
+          <t>2026-08-08 17:19:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5309587</v>
+        <v>4.530284</v>
       </c>
       <c r="G5" t="n">
-        <v>26404</v>
+        <v>26409</v>
       </c>
       <c r="H5" t="n">
-        <v>9833</v>
+        <v>9835</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>667628</v>
+        <v>668863</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="O5" t="n">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="P5" t="n">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="Q5" t="n">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="R5" t="n">
-        <v>21476</v>
+        <v>21475</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:55</t>
+          <t>2026-08-08 17:19:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>110837</v>
+        <v>111016</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:56</t>
+          <t>2026-08-08 17:19:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.630137</v>
+        <v>4.6181817</v>
       </c>
       <c r="G7" t="n">
-        <v>3103</v>
+        <v>3104</v>
       </c>
       <c r="H7" t="n">
         <v>1150</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>441377</v>
+        <v>443080</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>225</v>
       </c>
       <c r="O7" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="P7" t="n">
         <v>55</v>
@@ -961,7 +961,7 @@
         <v>84</v>
       </c>
       <c r="R7" t="n">
-        <v>2719</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:56</t>
+          <t>2026-08-08 17:19:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>449049</v>
+        <v>450537</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:56</t>
+          <t>2026-08-08 17:19:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1071,7 +1071,7 @@
         <v>1230</v>
       </c>
       <c r="H9" t="n">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>179640</v>
+        <v>179979</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:56</t>
+          <t>2026-08-08 17:19:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>91596</v>
+        <v>91890</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:56</t>
+          <t>2026-08-08 17:19:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1216,7 +1216,7 @@
         <v>4.6764483</v>
       </c>
       <c r="G11" t="n">
-        <v>14991</v>
+        <v>14986</v>
       </c>
       <c r="H11" t="n">
         <v>702</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>272214</v>
+        <v>272567</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1251,13 +1251,13 @@
         <v>111</v>
       </c>
       <c r="P11" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q11" t="n">
         <v>833</v>
       </c>
       <c r="R11" t="n">
-        <v>12982</v>
+        <v>12978</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:56</t>
+          <t>2026-08-08 17:19:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7416022</v>
+        <v>2.7402596</v>
       </c>
       <c r="G12" t="n">
-        <v>4705</v>
+        <v>4706</v>
       </c>
       <c r="H12" t="n">
         <v>1947</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>354429</v>
+        <v>355033</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1315,19 +1315,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
       </c>
       <c r="P12" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q12" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1761</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:57</t>
+          <t>2026-08-08 17:19:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22038</v>
+        <v>22061</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:57</t>
+          <t>2026-08-08 17:19:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.730081</v>
+        <v>4.730738</v>
       </c>
       <c r="G14" t="n">
-        <v>13397</v>
+        <v>13399</v>
       </c>
       <c r="H14" t="n">
         <v>5004</v>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1257426</v>
+        <v>1260424</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="O14" t="n">
         <v>86</v>
@@ -1472,10 +1472,10 @@
         <v>75</v>
       </c>
       <c r="Q14" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R14" t="n">
-        <v>12285</v>
+        <v>12289</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:57</t>
+          <t>2026-08-08 17:19:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>400831</v>
+        <v>401853</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-07 17:37:58</t>
+          <t>2026-08-08 17:19:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7089224</v>
+        <v>4.708063</v>
       </c>
       <c r="G16" t="n">
-        <v>46683</v>
+        <v>46684</v>
       </c>
       <c r="H16" t="n">
-        <v>2952</v>
+        <v>2954</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>571866</v>
+        <v>573508</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2206</v>
+        <v>2216</v>
       </c>
       <c r="O16" t="n">
         <v>334</v>
@@ -1620,10 +1620,10 @@
         <v>735</v>
       </c>
       <c r="Q16" t="n">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="R16" t="n">
-        <v>41121</v>
+        <v>41112</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:02</t>
+          <t>2026-08-09 17:19:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:02</t>
+          <t>2026-08-09 17:19:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.449397</v>
+        <v>4.447772</v>
       </c>
       <c r="G3" t="n">
-        <v>30764</v>
+        <v>30772</v>
       </c>
       <c r="H3" t="n">
-        <v>9123</v>
+        <v>9129</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2396124</v>
+        <v>2398755</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3708</v>
+        <v>3719</v>
       </c>
       <c r="O3" t="n">
         <v>292</v>
@@ -662,10 +662,10 @@
         <v>314</v>
       </c>
       <c r="Q3" t="n">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="R3" t="n">
-        <v>25851</v>
+        <v>25837</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:02</t>
+          <t>2026-08-09 17:19:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6262043</v>
+        <v>3.627086</v>
       </c>
       <c r="G4" t="n">
-        <v>25025</v>
+        <v>25028</v>
       </c>
       <c r="H4" t="n">
         <v>5597</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2605075</v>
+        <v>2607628</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -723,11 +723,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 20, 2026</t>
+          <t>Jun 21, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7216</v>
+        <v>7211</v>
       </c>
       <c r="O4" t="n">
         <v>834</v>
@@ -736,10 +736,10 @@
         <v>882</v>
       </c>
       <c r="Q4" t="n">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="R4" t="n">
-        <v>14850</v>
+        <v>14858</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:02</t>
+          <t>2026-08-09 17:19:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.530284</v>
+        <v>4.5290623</v>
       </c>
       <c r="G5" t="n">
-        <v>26409</v>
+        <v>26419</v>
       </c>
       <c r="H5" t="n">
-        <v>9835</v>
+        <v>9837</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>668863</v>
+        <v>669990</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1990</v>
+        <v>1994</v>
       </c>
       <c r="O5" t="n">
         <v>335</v>
       </c>
       <c r="P5" t="n">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="Q5" t="n">
-        <v>1778</v>
+        <v>1793</v>
       </c>
       <c r="R5" t="n">
-        <v>21475</v>
+        <v>21464</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:03</t>
+          <t>2026-08-09 17:19:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111016</v>
+        <v>111168</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:03</t>
+          <t>2026-08-09 17:19:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -923,7 +923,7 @@
         <v>3104</v>
       </c>
       <c r="H7" t="n">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:03</t>
+          <t>2026-08-09 17:19:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1559634</v>
+        <v>4.1575093</v>
       </c>
       <c r="G8" t="n">
-        <v>6079</v>
+        <v>6080</v>
       </c>
       <c r="H8" t="n">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>450537</v>
+        <v>451854</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="O8" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="P8" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q8" t="n">
         <v>244</v>
       </c>
       <c r="R8" t="n">
-        <v>4482</v>
+        <v>4487</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:03</t>
+          <t>2026-08-09 17:19:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:03</t>
+          <t>2026-08-09 17:19:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1142,7 +1142,7 @@
         <v>4.01</v>
       </c>
       <c r="G10" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H10" t="n">
         <v>237</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>91890</v>
+        <v>92214</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:04</t>
+          <t>2026-08-09 17:19:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6764483</v>
+        <v>4.6766915</v>
       </c>
       <c r="G11" t="n">
-        <v>14986</v>
+        <v>14993</v>
       </c>
       <c r="H11" t="n">
         <v>702</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>272567</v>
+        <v>272922</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         <v>281</v>
       </c>
       <c r="Q11" t="n">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="R11" t="n">
-        <v>12978</v>
+        <v>12986</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:04</t>
+          <t>2026-08-09 17:19:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>355033</v>
+        <v>355434</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:04</t>
+          <t>2026-08-09 17:19:52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22061</v>
+        <v>22115</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:04</t>
+          <t>2026-08-09 17:19:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.730738</v>
+        <v>4.7279353</v>
       </c>
       <c r="G14" t="n">
-        <v>13399</v>
+        <v>13401</v>
       </c>
       <c r="H14" t="n">
         <v>5004</v>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1260424</v>
+        <v>1262943</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="O14" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P14" t="n">
         <v>75</v>
@@ -1475,7 +1475,7 @@
         <v>194</v>
       </c>
       <c r="R14" t="n">
-        <v>12289</v>
+        <v>12283</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:05</t>
+          <t>2026-08-09 17:19:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1511,7 +1511,7 @@
         <v>3908</v>
       </c>
       <c r="H15" t="n">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-08 17:19:05</t>
+          <t>2026-08-09 17:19:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.708063</v>
+        <v>4.7074075</v>
       </c>
       <c r="G16" t="n">
-        <v>46684</v>
+        <v>46688</v>
       </c>
       <c r="H16" t="n">
         <v>2954</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>573508</v>
+        <v>574803</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2216</v>
+        <v>2225</v>
       </c>
       <c r="O16" t="n">
         <v>334</v>
       </c>
       <c r="P16" t="n">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="Q16" t="n">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="R16" t="n">
-        <v>41112</v>
+        <v>41111</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:49</t>
+          <t>2026-08-10 17:41:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>39456</v>
+        <v>39652</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:49</t>
+          <t>2026-08-10 17:41:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.447772</v>
+        <v>4.447723</v>
       </c>
       <c r="G3" t="n">
-        <v>30772</v>
+        <v>30781</v>
       </c>
       <c r="H3" t="n">
-        <v>9129</v>
+        <v>9133</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3719</v>
+        <v>3722</v>
       </c>
       <c r="O3" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P3" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q3" t="n">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="R3" t="n">
-        <v>25837</v>
+        <v>25845</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:49</t>
+          <t>2026-08-10 17:41:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.627086</v>
+        <v>3.6273253</v>
       </c>
       <c r="G4" t="n">
         <v>25028</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7211</v>
+        <v>7207</v>
       </c>
       <c r="O4" t="n">
         <v>834</v>
       </c>
       <c r="P4" t="n">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="Q4" t="n">
-        <v>1235</v>
+        <v>1252</v>
       </c>
       <c r="R4" t="n">
-        <v>14858</v>
+        <v>14848</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:50</t>
+          <t>2026-08-10 17:41:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5290623</v>
+        <v>4.528662</v>
       </c>
       <c r="G5" t="n">
-        <v>26419</v>
+        <v>26425</v>
       </c>
       <c r="H5" t="n">
-        <v>9837</v>
+        <v>9839</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="O5" t="n">
         <v>335</v>
@@ -810,7 +810,7 @@
         <v>829</v>
       </c>
       <c r="Q5" t="n">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="R5" t="n">
         <v>21464</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:50</t>
+          <t>2026-08-10 17:41:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:50</t>
+          <t>2026-08-10 17:41:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.6181817</v>
+        <v>4.6199093</v>
       </c>
       <c r="G7" t="n">
-        <v>3104</v>
+        <v>3106</v>
       </c>
       <c r="H7" t="n">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>443080</v>
+        <v>445146</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O7" t="n">
         <v>27</v>
@@ -961,7 +961,7 @@
         <v>84</v>
       </c>
       <c r="R7" t="n">
-        <v>2708</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:51</t>
+          <t>2026-08-10 17:41:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -997,7 +997,7 @@
         <v>6080</v>
       </c>
       <c r="H8" t="n">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>451854</v>
+        <v>452247</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:51</t>
+          <t>2026-08-10 17:41:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.9906542</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H9" t="n">
         <v>494</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>179979</v>
+        <v>180316</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O9" t="n">
         <v>34</v>
@@ -1109,7 +1109,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>861</v>
+        <v>866</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:51</t>
+          <t>2026-08-10 17:41:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1142,7 +1142,7 @@
         <v>4.01</v>
       </c>
       <c r="G10" t="n">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H10" t="n">
         <v>237</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:51</t>
+          <t>2026-08-10 17:41:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6766915</v>
+        <v>4.677419</v>
       </c>
       <c r="G11" t="n">
-        <v>14993</v>
+        <v>14998</v>
       </c>
       <c r="H11" t="n">
         <v>702</v>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="O11" t="n">
         <v>111</v>
       </c>
       <c r="P11" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q11" t="n">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="R11" t="n">
-        <v>12986</v>
+        <v>12995</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:52</t>
+          <t>2026-08-10 17:41:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1290,10 +1290,10 @@
         <v>2.7402596</v>
       </c>
       <c r="G12" t="n">
-        <v>4706</v>
+        <v>4705</v>
       </c>
       <c r="H12" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:52</t>
+          <t>2026-08-10 17:41:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:52</t>
+          <t>2026-08-10 17:41:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7279353</v>
+        <v>4.7309847</v>
       </c>
       <c r="G14" t="n">
-        <v>13401</v>
+        <v>13415</v>
       </c>
       <c r="H14" t="n">
         <v>5004</v>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1262943</v>
+        <v>1263423</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="O14" t="n">
         <v>85</v>
       </c>
       <c r="P14" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q14" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="R14" t="n">
-        <v>12283</v>
+        <v>12308</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:53</t>
+          <t>2026-08-10 17:41:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3710146</v>
+        <v>3.364162</v>
       </c>
       <c r="G15" t="n">
-        <v>3908</v>
+        <v>3909</v>
       </c>
       <c r="H15" t="n">
         <v>1577</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>401853</v>
+        <v>402802</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1415</v>
+        <v>1423</v>
       </c>
       <c r="O15" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q15" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R15" t="n">
-        <v>2140</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-09 17:19:53</t>
+          <t>2026-08-10 17:41:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7074075</v>
+        <v>4.708198</v>
       </c>
       <c r="G16" t="n">
-        <v>46688</v>
+        <v>46682</v>
       </c>
       <c r="H16" t="n">
-        <v>2954</v>
+        <v>2960</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,11 +1593,11 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>574803</v>
+        <v>575115</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.4</t>
+          <t>3.1.5</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Aug 5, 2026</t>
+          <t>Aug 10, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2225</v>
+        <v>2215</v>
       </c>
       <c r="O16" t="n">
         <v>334</v>
@@ -1623,7 +1623,7 @@
         <v>2280</v>
       </c>
       <c r="R16" t="n">
-        <v>41111</v>
+        <v>41114</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:26</t>
+          <t>2026-08-11 17:45:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:26</t>
+          <t>2026-08-11 17:45:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.447723</v>
+        <v>4.446025</v>
       </c>
       <c r="G3" t="n">
-        <v>30781</v>
+        <v>30790</v>
       </c>
       <c r="H3" t="n">
-        <v>9133</v>
+        <v>9137</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2398755</v>
+        <v>2399450</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3722</v>
+        <v>3738</v>
       </c>
       <c r="O3" t="n">
         <v>291</v>
       </c>
       <c r="P3" t="n">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="R3" t="n">
-        <v>25845</v>
+        <v>25837</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:26</t>
+          <t>2026-08-11 17:45:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6273253</v>
+        <v>3.628205</v>
       </c>
       <c r="G4" t="n">
-        <v>25028</v>
+        <v>25029</v>
       </c>
       <c r="H4" t="n">
         <v>5597</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2607628</v>
+        <v>2608137</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7207</v>
+        <v>7202</v>
       </c>
       <c r="O4" t="n">
         <v>834</v>
@@ -736,10 +736,10 @@
         <v>881</v>
       </c>
       <c r="Q4" t="n">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="R4" t="n">
-        <v>14848</v>
+        <v>14855</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:26</t>
+          <t>2026-08-11 17:45:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.528662</v>
+        <v>4.530258</v>
       </c>
       <c r="G5" t="n">
-        <v>26425</v>
+        <v>26434</v>
       </c>
       <c r="H5" t="n">
-        <v>9839</v>
+        <v>9843</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>669990</v>
+        <v>670189</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1996</v>
+        <v>1990</v>
       </c>
       <c r="O5" t="n">
         <v>335</v>
       </c>
       <c r="P5" t="n">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="Q5" t="n">
-        <v>1794</v>
+        <v>1788</v>
       </c>
       <c r="R5" t="n">
-        <v>21464</v>
+        <v>21488</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:27</t>
+          <t>2026-08-11 17:45:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111168</v>
+        <v>111194</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:27</t>
+          <t>2026-08-11 17:45:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.6199093</v>
+        <v>4.598214</v>
       </c>
       <c r="G7" t="n">
-        <v>3106</v>
+        <v>3109</v>
       </c>
       <c r="H7" t="n">
         <v>1152</v>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="O7" t="n">
         <v>27</v>
       </c>
       <c r="P7" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="Q7" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R7" t="n">
-        <v>2712</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:27</t>
+          <t>2026-08-11 17:45:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>4.1575093</v>
       </c>
       <c r="G8" t="n">
-        <v>6080</v>
+        <v>6079</v>
       </c>
       <c r="H8" t="n">
         <v>2257</v>
@@ -1035,7 +1035,7 @@
         <v>244</v>
       </c>
       <c r="R8" t="n">
-        <v>4487</v>
+        <v>4486</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:27</t>
+          <t>2026-08-11 17:45:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:27</t>
+          <t>2026-08-11 17:45:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1142,7 +1142,7 @@
         <v>4.01</v>
       </c>
       <c r="G10" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H10" t="n">
         <v>237</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>92214</v>
+        <v>92315</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:27</t>
+          <t>2026-08-11 17:45:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.677419</v>
+        <v>4.677661</v>
       </c>
       <c r="G11" t="n">
-        <v>14998</v>
+        <v>14999</v>
       </c>
       <c r="H11" t="n">
         <v>702</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>272922</v>
+        <v>272996</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>831</v>
       </c>
       <c r="R11" t="n">
-        <v>12995</v>
+        <v>12997</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:27</t>
+          <t>2026-08-11 17:45:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7402596</v>
+        <v>2.715026</v>
       </c>
       <c r="G12" t="n">
-        <v>4705</v>
+        <v>4709</v>
       </c>
       <c r="H12" t="n">
         <v>1948</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>355434</v>
+        <v>355534</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2419</v>
+        <v>2451</v>
       </c>
       <c r="O12" t="n">
         <v>109</v>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1759</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:28</t>
+          <t>2026-08-11 17:45:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22115</v>
+        <v>22116</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:28</t>
+          <t>2026-08-11 17:45:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7309847</v>
+        <v>4.732484</v>
       </c>
       <c r="G14" t="n">
-        <v>13415</v>
+        <v>13423</v>
       </c>
       <c r="H14" t="n">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="O14" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P14" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q14" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R14" t="n">
-        <v>12308</v>
+        <v>12321</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:28</t>
+          <t>2026-08-11 17:45:50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>402802</v>
+        <v>402975</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-10 17:41:28</t>
+          <t>2026-08-11 17:45:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.708198</v>
+        <v>4.7083035</v>
       </c>
       <c r="G16" t="n">
-        <v>46682</v>
+        <v>46688</v>
       </c>
       <c r="H16" t="n">
-        <v>2960</v>
+        <v>2964</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2215</v>
+        <v>2209</v>
       </c>
       <c r="O16" t="n">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="P16" t="n">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="Q16" t="n">
-        <v>2280</v>
+        <v>2298</v>
       </c>
       <c r="R16" t="n">
-        <v>41114</v>
+        <v>41111</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:48</t>
+          <t>2026-08-12 17:47:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:48</t>
+          <t>2026-08-12 17:47:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.446025</v>
+        <v>4.4447274</v>
       </c>
       <c r="G3" t="n">
-        <v>30790</v>
+        <v>30799</v>
       </c>
       <c r="H3" t="n">
-        <v>9137</v>
+        <v>9142</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2399450</v>
+        <v>2399456</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3738</v>
+        <v>3751</v>
       </c>
       <c r="O3" t="n">
         <v>291</v>
@@ -662,7 +662,7 @@
         <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="R3" t="n">
         <v>25837</v>
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:48</t>
+          <t>2026-08-12 17:47:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.628205</v>
+        <v>3.6265213</v>
       </c>
       <c r="G4" t="n">
-        <v>25029</v>
+        <v>25030</v>
       </c>
       <c r="H4" t="n">
         <v>5597</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2608137</v>
+        <v>2608683</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -723,14 +723,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 21, 2026</t>
+          <t>Jun 20, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7202</v>
+        <v>7215</v>
       </c>
       <c r="O4" t="n">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="P4" t="n">
         <v>881</v>
@@ -739,7 +739,7 @@
         <v>1250</v>
       </c>
       <c r="R4" t="n">
-        <v>14855</v>
+        <v>14846</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:48</t>
+          <t>2026-08-12 17:47:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.530258</v>
+        <v>4.5305085</v>
       </c>
       <c r="G5" t="n">
-        <v>26434</v>
+        <v>26445</v>
       </c>
       <c r="H5" t="n">
-        <v>9843</v>
+        <v>9844</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>670189</v>
+        <v>670191</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1990</v>
+        <v>1994</v>
       </c>
       <c r="O5" t="n">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="P5" t="n">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="Q5" t="n">
-        <v>1788</v>
+        <v>1803</v>
       </c>
       <c r="R5" t="n">
-        <v>21488</v>
+        <v>21491</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:48</t>
+          <t>2026-08-12 17:47:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111194</v>
+        <v>111195</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:48</t>
+          <t>2026-08-12 17:47:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>445146</v>
+        <v>445151</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:49</t>
+          <t>2026-08-12 17:47:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1575093</v>
+        <v>4.1590495</v>
       </c>
       <c r="G8" t="n">
-        <v>6079</v>
+        <v>6080</v>
       </c>
       <c r="H8" t="n">
         <v>2257</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>452247</v>
+        <v>452250</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="O8" t="n">
         <v>154</v>
@@ -1032,10 +1032,10 @@
         <v>177</v>
       </c>
       <c r="Q8" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R8" t="n">
-        <v>4486</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:49</t>
+          <t>2026-08-12 17:47:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1071,7 +1071,7 @@
         <v>1231</v>
       </c>
       <c r="H9" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>180316</v>
+        <v>180319</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:49</t>
+          <t>2026-08-12 17:47:33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:49</t>
+          <t>2026-08-12 17:47:33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:49</t>
+          <t>2026-08-12 17:47:33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1290,7 +1290,7 @@
         <v>2.715026</v>
       </c>
       <c r="G12" t="n">
-        <v>4709</v>
+        <v>4710</v>
       </c>
       <c r="H12" t="n">
         <v>1948</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>355534</v>
+        <v>355615</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:49</t>
+          <t>2026-08-12 17:47:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:49</t>
+          <t>2026-08-12 17:47:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.732484</v>
+        <v>4.731861</v>
       </c>
       <c r="G14" t="n">
-        <v>13423</v>
+        <v>13434</v>
       </c>
       <c r="H14" t="n">
-        <v>5003</v>
+        <v>5005</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1263423</v>
+        <v>1263427</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="O14" t="n">
         <v>84</v>
@@ -1472,10 +1472,10 @@
         <v>73</v>
       </c>
       <c r="Q14" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R14" t="n">
-        <v>12321</v>
+        <v>12331</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:50</t>
+          <t>2026-08-12 17:47:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1511,7 +1511,7 @@
         <v>3909</v>
       </c>
       <c r="H15" t="n">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>402975</v>
+        <v>402977</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-11 17:45:50</t>
+          <t>2026-08-12 17:47:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7083035</v>
+        <v>4.705548</v>
       </c>
       <c r="G16" t="n">
-        <v>46688</v>
+        <v>46701</v>
       </c>
       <c r="H16" t="n">
-        <v>2964</v>
+        <v>2968</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>575115</v>
+        <v>575116</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2209</v>
+        <v>2235</v>
       </c>
       <c r="O16" t="n">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="P16" t="n">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="Q16" t="n">
-        <v>2298</v>
+        <v>2302</v>
       </c>
       <c r="R16" t="n">
-        <v>41111</v>
+        <v>41086</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:31</t>
+          <t>2026-08-13 17:46:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>3.96</v>
       </c>
       <c r="G2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H2" t="n">
         <v>176</v>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:31</t>
+          <t>2026-08-13 17:46:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4447274</v>
+        <v>4.443918</v>
       </c>
       <c r="G3" t="n">
-        <v>30799</v>
+        <v>30809</v>
       </c>
       <c r="H3" t="n">
-        <v>9142</v>
+        <v>9145</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3751</v>
+        <v>3758</v>
       </c>
       <c r="O3" t="n">
         <v>291</v>
@@ -662,10 +662,10 @@
         <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="R3" t="n">
-        <v>25837</v>
+        <v>25838</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:31</t>
+          <t>2026-08-13 17:46:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6265213</v>
+        <v>3.627476</v>
       </c>
       <c r="G4" t="n">
-        <v>25030</v>
+        <v>25035</v>
       </c>
       <c r="H4" t="n">
         <v>5597</v>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 20, 2026</t>
+          <t>Jun 21, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7215</v>
+        <v>7213</v>
       </c>
       <c r="O4" t="n">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="P4" t="n">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="Q4" t="n">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="R4" t="n">
-        <v>14846</v>
+        <v>14860</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:32</t>
+          <t>2026-08-13 17:46:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5305085</v>
+        <v>4.531131</v>
       </c>
       <c r="G5" t="n">
-        <v>26445</v>
+        <v>26453</v>
       </c>
       <c r="H5" t="n">
-        <v>9844</v>
+        <v>9849</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
         <v>828</v>
       </c>
       <c r="Q5" t="n">
-        <v>1803</v>
+        <v>1792</v>
       </c>
       <c r="R5" t="n">
-        <v>21491</v>
+        <v>21510</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:32</t>
+          <t>2026-08-13 17:46:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111195</v>
+        <v>111213</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:32</t>
+          <t>2026-08-13 17:46:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.598214</v>
+        <v>4.5840707</v>
       </c>
       <c r="G7" t="n">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="H7" t="n">
         <v>1152</v>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="O7" t="n">
         <v>27</v>
       </c>
       <c r="P7" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q7" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R7" t="n">
-        <v>2692</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:32</t>
+          <t>2026-08-13 17:46:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:32</t>
+          <t>2026-08-13 17:46:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3.9629629</v>
       </c>
       <c r="G9" t="n">
         <v>1231</v>
@@ -1093,11 +1093,11 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="O9" t="n">
         <v>34</v>
@@ -1109,7 +1109,7 @@
         <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>866</v>
+        <v>854</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:33</t>
+          <t>2026-08-13 17:46:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:33</t>
+          <t>2026-08-13 17:46:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.677661</v>
+        <v>4.677419</v>
       </c>
       <c r="G11" t="n">
         <v>14999</v>
@@ -1257,7 +1257,7 @@
         <v>831</v>
       </c>
       <c r="R11" t="n">
-        <v>12997</v>
+        <v>12995</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:33</t>
+          <t>2026-08-13 17:46:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:33</t>
+          <t>2026-08-13 17:46:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22116</v>
+        <v>22121</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Feb 25, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:33</t>
+          <t>2026-08-13 17:46:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.731861</v>
+        <v>4.725</v>
       </c>
       <c r="G14" t="n">
-        <v>13434</v>
+        <v>13447</v>
       </c>
       <c r="H14" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>751</v>
+        <v>776</v>
       </c>
       <c r="O14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P14" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q14" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="R14" t="n">
-        <v>12331</v>
+        <v>12322</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:34</t>
+          <t>2026-08-13 17:46:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.364162</v>
+        <v>3.3710146</v>
       </c>
       <c r="G15" t="n">
-        <v>3909</v>
+        <v>3910</v>
       </c>
       <c r="H15" t="n">
         <v>1578</v>
@@ -1533,23 +1533,23 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1423</v>
+        <v>1416</v>
       </c>
       <c r="O15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2134</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-12 17:47:34</t>
+          <t>2026-08-13 17:46:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.705548</v>
+        <v>4.7030993</v>
       </c>
       <c r="G16" t="n">
-        <v>46701</v>
+        <v>46708</v>
       </c>
       <c r="H16" t="n">
         <v>2968</v>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2235</v>
+        <v>2264</v>
       </c>
       <c r="O16" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="P16" t="n">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="Q16" t="n">
-        <v>2302</v>
+        <v>2308</v>
       </c>
       <c r="R16" t="n">
-        <v>41086</v>
+        <v>41060</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:40</t>
+          <t>2026-08-14 17:42:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,10 +550,10 @@
         <v>3.96</v>
       </c>
       <c r="G2" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H2" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>39652</v>
+        <v>39729</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:40</t>
+          <t>2026-08-14 17:42:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.443918</v>
+        <v>4.44663</v>
       </c>
       <c r="G3" t="n">
-        <v>30809</v>
+        <v>30820</v>
       </c>
       <c r="H3" t="n">
-        <v>9145</v>
+        <v>9146</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2399456</v>
+        <v>2401809</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3758</v>
+        <v>3749</v>
       </c>
       <c r="O3" t="n">
         <v>291</v>
       </c>
       <c r="P3" t="n">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="Q3" t="n">
         <v>616</v>
       </c>
       <c r="R3" t="n">
-        <v>25838</v>
+        <v>25879</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:41</t>
+          <t>2026-08-14 17:42:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2608683</v>
+        <v>2609424</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 21, 2026</t>
+          <t>Jun 20, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:41</t>
+          <t>2026-08-14 17:42:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.531131</v>
+        <v>4.5323467</v>
       </c>
       <c r="G5" t="n">
-        <v>26453</v>
+        <v>26464</v>
       </c>
       <c r="H5" t="n">
-        <v>9849</v>
+        <v>9848</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>670191</v>
+        <v>670667</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1994</v>
+        <v>1979</v>
       </c>
       <c r="O5" t="n">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="P5" t="n">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="Q5" t="n">
-        <v>1792</v>
+        <v>1789</v>
       </c>
       <c r="R5" t="n">
-        <v>21510</v>
+        <v>21528</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:41</t>
+          <t>2026-08-14 17:42:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:41</t>
+          <t>2026-08-14 17:42:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>445151</v>
+        <v>445540</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:41</t>
+          <t>2026-08-14 17:42:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>452250</v>
+        <v>452633</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:41</t>
+          <t>2026-08-14 17:42:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>180319</v>
+        <v>180379</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:42</t>
+          <t>2026-08-14 17:42:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1142,7 +1142,7 @@
         <v>4.01</v>
       </c>
       <c r="G10" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H10" t="n">
         <v>237</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>92315</v>
+        <v>92413</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R10" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:42</t>
+          <t>2026-08-14 17:42:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>272996</v>
+        <v>273080</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:42</t>
+          <t>2026-08-14 17:42:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1290,10 +1290,10 @@
         <v>2.715026</v>
       </c>
       <c r="G12" t="n">
-        <v>4710</v>
+        <v>4709</v>
       </c>
       <c r="H12" t="n">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>355615</v>
+        <v>355737</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:42</t>
+          <t>2026-08-14 17:42:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22121</v>
+        <v>22124</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:42</t>
+          <t>2026-08-14 17:42:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.725</v>
+        <v>4.7153907</v>
       </c>
       <c r="G14" t="n">
-        <v>13447</v>
+        <v>13459</v>
       </c>
       <c r="H14" t="n">
-        <v>5010</v>
+        <v>5011</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1263427</v>
+        <v>1264012</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>776</v>
+        <v>800</v>
       </c>
       <c r="O14" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="P14" t="n">
         <v>72</v>
       </c>
       <c r="Q14" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="R14" t="n">
-        <v>12322</v>
+        <v>12292</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:42</t>
+          <t>2026-08-14 17:42:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>402977</v>
+        <v>403465</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:43</t>
+          <t>2026-08-14 17:42:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7030993</v>
+        <v>4.702575</v>
       </c>
       <c r="G16" t="n">
-        <v>46708</v>
+        <v>46715</v>
       </c>
       <c r="H16" t="n">
-        <v>2968</v>
+        <v>2970</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>575116</v>
+        <v>575448</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2264</v>
+        <v>2273</v>
       </c>
       <c r="O16" t="n">
         <v>352</v>
@@ -1620,10 +1620,10 @@
         <v>717</v>
       </c>
       <c r="Q16" t="n">
-        <v>2308</v>
+        <v>2305</v>
       </c>
       <c r="R16" t="n">
-        <v>41060</v>
+        <v>41064</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:44</t>
+          <t>2026-08-15 17:10:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>3.96</v>
       </c>
       <c r="G2" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2" t="n">
         <v>177</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>39729</v>
+        <v>39768</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:44</t>
+          <t>2026-08-15 17:10:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.44663</v>
+        <v>4.447799</v>
       </c>
       <c r="G3" t="n">
-        <v>30820</v>
+        <v>30822</v>
       </c>
       <c r="H3" t="n">
         <v>9146</v>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3749</v>
+        <v>3732</v>
       </c>
       <c r="O3" t="n">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="P3" t="n">
         <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="R3" t="n">
-        <v>25879</v>
+        <v>25888</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:45</t>
+          <t>2026-08-15 17:10:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.627476</v>
+        <v>3.628279</v>
       </c>
       <c r="G4" t="n">
-        <v>25035</v>
+        <v>25031</v>
       </c>
       <c r="H4" t="n">
-        <v>5597</v>
+        <v>5596</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2609424</v>
+        <v>2610262</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 20, 2026</t>
+          <t>Jun 21, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7213</v>
+        <v>7205</v>
       </c>
       <c r="O4" t="n">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="P4" t="n">
         <v>879</v>
       </c>
       <c r="Q4" t="n">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="R4" t="n">
-        <v>14860</v>
+        <v>14861</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:45</t>
+          <t>2026-08-15 17:10:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5323467</v>
+        <v>4.532939</v>
       </c>
       <c r="G5" t="n">
-        <v>26464</v>
+        <v>26468</v>
       </c>
       <c r="H5" t="n">
-        <v>9848</v>
+        <v>9850</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>670667</v>
+        <v>670993</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="O5" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P5" t="n">
         <v>827</v>
       </c>
       <c r="Q5" t="n">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="R5" t="n">
-        <v>21528</v>
+        <v>21538</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:45</t>
+          <t>2026-08-15 17:10:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.64</v>
       </c>
       <c r="G6" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H6" t="n">
         <v>164</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111213</v>
+        <v>111280</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:45</t>
+          <t>2026-08-15 17:10:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>445540</v>
+        <v>446511</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:46</t>
+          <t>2026-08-15 17:10:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>4.1590495</v>
       </c>
       <c r="G8" t="n">
-        <v>6080</v>
+        <v>6081</v>
       </c>
       <c r="H8" t="n">
         <v>2257</v>
@@ -1035,7 +1035,7 @@
         <v>243</v>
       </c>
       <c r="R8" t="n">
-        <v>4489</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:46</t>
+          <t>2026-08-15 17:10:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:46</t>
+          <t>2026-08-15 17:10:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:46</t>
+          <t>2026-08-15 17:10:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1216,7 +1216,7 @@
         <v>4.677419</v>
       </c>
       <c r="G11" t="n">
-        <v>14999</v>
+        <v>14998</v>
       </c>
       <c r="H11" t="n">
         <v>702</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>273080</v>
+        <v>273255</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1251,13 +1251,13 @@
         <v>111</v>
       </c>
       <c r="P11" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q11" t="n">
         <v>831</v>
       </c>
       <c r="R11" t="n">
-        <v>12995</v>
+        <v>12994</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:46</t>
+          <t>2026-08-15 17:10:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1293,7 +1293,7 @@
         <v>4709</v>
       </c>
       <c r="H12" t="n">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>355737</v>
+        <v>355864</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:47</t>
+          <t>2026-08-15 17:10:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,11 +1371,11 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22124</v>
+        <v>22144</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.0.1.13</t>
+          <t>1.0.1.15</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:47</t>
+          <t>2026-08-15 17:10:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7153907</v>
+        <v>4.7094283</v>
       </c>
       <c r="G14" t="n">
-        <v>13459</v>
+        <v>13462</v>
       </c>
       <c r="H14" t="n">
-        <v>5011</v>
+        <v>5013</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>800</v>
+        <v>820</v>
       </c>
       <c r="O14" t="n">
         <v>93</v>
@@ -1475,7 +1475,7 @@
         <v>196</v>
       </c>
       <c r="R14" t="n">
-        <v>12292</v>
+        <v>12275</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:47</t>
+          <t>2026-08-15 17:10:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1511,7 +1511,7 @@
         <v>3910</v>
       </c>
       <c r="H15" t="n">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>403465</v>
+        <v>403769</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-14 17:42:47</t>
+          <t>2026-08-15 17:10:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.702575</v>
+        <v>4.7018166</v>
       </c>
       <c r="G16" t="n">
-        <v>46715</v>
+        <v>46721</v>
       </c>
       <c r="H16" t="n">
-        <v>2970</v>
+        <v>2971</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2273</v>
+        <v>2269</v>
       </c>
       <c r="O16" t="n">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="P16" t="n">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="Q16" t="n">
-        <v>2305</v>
+        <v>2303</v>
       </c>
       <c r="R16" t="n">
-        <v>41064</v>
+        <v>41055</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:38</t>
+          <t>2026-08-16 17:09:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="G2" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2" t="n">
         <v>177</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>39768</v>
+        <v>39907</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
         <v>92</v>
       </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:38</t>
+          <t>2026-08-16 17:09:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.447799</v>
+        <v>4.446793</v>
       </c>
       <c r="G3" t="n">
-        <v>30822</v>
+        <v>30827</v>
       </c>
       <c r="H3" t="n">
-        <v>9146</v>
+        <v>9150</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2401809</v>
+        <v>2404270</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3732</v>
+        <v>3740</v>
       </c>
       <c r="O3" t="n">
         <v>302</v>
@@ -662,10 +662,10 @@
         <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="R3" t="n">
-        <v>25888</v>
+        <v>25882</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:38</t>
+          <t>2026-08-16 17:09:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.628279</v>
+        <v>3.6265984</v>
       </c>
       <c r="G4" t="n">
-        <v>25031</v>
+        <v>25032</v>
       </c>
       <c r="H4" t="n">
         <v>5596</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2610262</v>
+        <v>2611754</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 21, 2026</t>
+          <t>Jun 20, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7205</v>
+        <v>7218</v>
       </c>
       <c r="O4" t="n">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="P4" t="n">
         <v>879</v>
       </c>
       <c r="Q4" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="R4" t="n">
-        <v>14861</v>
+        <v>14852</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:38</t>
+          <t>2026-08-16 17:09:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.532939</v>
+        <v>4.5332484</v>
       </c>
       <c r="G5" t="n">
-        <v>26468</v>
+        <v>26476</v>
       </c>
       <c r="H5" t="n">
-        <v>9850</v>
+        <v>9855</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>670993</v>
+        <v>671904</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1977</v>
+        <v>1984</v>
       </c>
       <c r="O5" t="n">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="P5" t="n">
-        <v>827</v>
+        <v>818</v>
       </c>
       <c r="Q5" t="n">
-        <v>1787</v>
+        <v>1804</v>
       </c>
       <c r="R5" t="n">
-        <v>21538</v>
+        <v>21541</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:39</t>
+          <t>2026-08-16 17:09:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111280</v>
+        <v>111350</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:39</t>
+          <t>2026-08-16 17:09:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.5840707</v>
+        <v>4.568282</v>
       </c>
       <c r="G7" t="n">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="H7" t="n">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -931,11 +931,11 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>446511</v>
+        <v>447896</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>5.1.2</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -945,11 +945,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>May 27, 2026</t>
+          <t>Aug 10, 2026</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="O7" t="n">
         <v>27</v>
@@ -961,7 +961,7 @@
         <v>81</v>
       </c>
       <c r="R7" t="n">
-        <v>2682</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:39</t>
+          <t>2026-08-16 17:09:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1590495</v>
+        <v>4.1621127</v>
       </c>
       <c r="G8" t="n">
-        <v>6081</v>
+        <v>6083</v>
       </c>
       <c r="H8" t="n">
         <v>2257</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>452633</v>
+        <v>454368</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="O8" t="n">
         <v>154</v>
       </c>
       <c r="P8" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q8" t="n">
         <v>243</v>
       </c>
       <c r="R8" t="n">
-        <v>4490</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:39</t>
+          <t>2026-08-16 17:09:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>180379</v>
+        <v>180700</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:39</t>
+          <t>2026-08-16 17:09:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>92413</v>
+        <v>92999</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:40</t>
+          <t>2026-08-16 17:09:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1216,7 +1216,7 @@
         <v>4.677419</v>
       </c>
       <c r="G11" t="n">
-        <v>14998</v>
+        <v>14999</v>
       </c>
       <c r="H11" t="n">
         <v>702</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>273255</v>
+        <v>273442</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>831</v>
       </c>
       <c r="R11" t="n">
-        <v>12994</v>
+        <v>12995</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:40</t>
+          <t>2026-08-16 17:09:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>355864</v>
+        <v>356067</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:40</t>
+          <t>2026-08-16 17:09:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22144</v>
+        <v>22152</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:40</t>
+          <t>2026-08-16 17:09:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7094283</v>
+        <v>4.70416</v>
       </c>
       <c r="G14" t="n">
-        <v>13462</v>
+        <v>13466</v>
       </c>
       <c r="H14" t="n">
         <v>5013</v>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1264012</v>
+        <v>1266891</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>820</v>
+        <v>839</v>
       </c>
       <c r="O14" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P14" t="n">
         <v>72</v>
@@ -1475,7 +1475,7 @@
         <v>196</v>
       </c>
       <c r="R14" t="n">
-        <v>12275</v>
+        <v>12262</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:40</t>
+          <t>2026-08-16 17:09:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3710146</v>
+        <v>3.364162</v>
       </c>
       <c r="G15" t="n">
-        <v>3910</v>
+        <v>3911</v>
       </c>
       <c r="H15" t="n">
         <v>1579</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>403769</v>
+        <v>404606</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1416</v>
+        <v>1423</v>
       </c>
       <c r="O15" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q15" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R15" t="n">
-        <v>2141</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-15 17:10:40</t>
+          <t>2026-08-16 17:09:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7018166</v>
+        <v>4.700778</v>
       </c>
       <c r="G16" t="n">
-        <v>46721</v>
+        <v>46723</v>
       </c>
       <c r="H16" t="n">
-        <v>2971</v>
+        <v>2973</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>575448</v>
+        <v>578795</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="O16" t="n">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="P16" t="n">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="Q16" t="n">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="R16" t="n">
-        <v>41055</v>
+        <v>41037</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:40</t>
+          <t>2026-08-17 17:15:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:40</t>
+          <t>2026-08-17 17:15:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.446793</v>
+        <v>4.4433103</v>
       </c>
       <c r="G3" t="n">
-        <v>30827</v>
+        <v>30833</v>
       </c>
       <c r="H3" t="n">
-        <v>9150</v>
+        <v>9158</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3740</v>
+        <v>3765</v>
       </c>
       <c r="O3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q3" t="n">
-        <v>616</v>
+        <v>629</v>
       </c>
       <c r="R3" t="n">
-        <v>25882</v>
+        <v>25852</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:41</t>
+          <t>2026-08-17 17:15:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6265984</v>
+        <v>3.6257198</v>
       </c>
       <c r="G4" t="n">
-        <v>25032</v>
+        <v>25031</v>
       </c>
       <c r="H4" t="n">
-        <v>5596</v>
+        <v>5595</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,11 +709,11 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2611754</v>
+        <v>2612954</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.22.1.1</t>
+          <t>2.22.1.3</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Jun 20, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7218</v>
+        <v>7222</v>
       </c>
       <c r="O4" t="n">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="P4" t="n">
         <v>879</v>
       </c>
       <c r="Q4" t="n">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="R4" t="n">
-        <v>14852</v>
+        <v>14844</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:41</t>
+          <t>2026-08-17 17:15:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5332484</v>
+        <v>4.5329113</v>
       </c>
       <c r="G5" t="n">
-        <v>26476</v>
+        <v>26485</v>
       </c>
       <c r="H5" t="n">
-        <v>9855</v>
+        <v>9858</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1984</v>
+        <v>1988</v>
       </c>
       <c r="O5" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P5" t="n">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="Q5" t="n">
-        <v>1804</v>
+        <v>1810</v>
       </c>
       <c r="R5" t="n">
-        <v>21541</v>
+        <v>21544</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:41</t>
+          <t>2026-08-17 17:15:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:41</t>
+          <t>2026-08-17 17:15:23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.568282</v>
+        <v>4.4479637</v>
       </c>
       <c r="G7" t="n">
-        <v>3109</v>
+        <v>3123</v>
       </c>
       <c r="H7" t="n">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>259</v>
+        <v>338</v>
       </c>
       <c r="O7" t="n">
         <v>27</v>
       </c>
       <c r="P7" t="n">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="Q7" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R7" t="n">
-        <v>2670</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:42</t>
+          <t>2026-08-17 17:15:23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1621127</v>
+        <v>4.163636</v>
       </c>
       <c r="G8" t="n">
-        <v>6083</v>
+        <v>6084</v>
       </c>
       <c r="H8" t="n">
         <v>2257</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>454368</v>
+        <v>455116</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="O8" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P8" t="n">
         <v>176</v>
       </c>
       <c r="Q8" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="R8" t="n">
-        <v>4497</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:42</t>
+          <t>2026-08-17 17:15:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:42</t>
+          <t>2026-08-17 17:15:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1145,7 +1145,7 @@
         <v>566</v>
       </c>
       <c r="H10" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:42</t>
+          <t>2026-08-17 17:15:24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:43</t>
+          <t>2026-08-17 17:15:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.715026</v>
+        <v>2.738342</v>
       </c>
       <c r="G12" t="n">
-        <v>4709</v>
+        <v>4712</v>
       </c>
       <c r="H12" t="n">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2451</v>
+        <v>2416</v>
       </c>
       <c r="O12" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="P12" t="n">
         <v>206</v>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1731</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:43</t>
+          <t>2026-08-17 17:15:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1363,7 +1363,7 @@
         <v>113</v>
       </c>
       <c r="H13" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:43</t>
+          <t>2026-08-17 17:15:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.70416</v>
+        <v>4.703137</v>
       </c>
       <c r="G14" t="n">
-        <v>13466</v>
+        <v>13475</v>
       </c>
       <c r="H14" t="n">
         <v>5013</v>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="O14" t="n">
         <v>92</v>
       </c>
       <c r="P14" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q14" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R14" t="n">
-        <v>12262</v>
+        <v>12268</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:43</t>
+          <t>2026-08-17 17:15:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.364162</v>
+        <v>3.3652174</v>
       </c>
       <c r="G15" t="n">
-        <v>3911</v>
+        <v>3910</v>
       </c>
       <c r="H15" t="n">
         <v>1579</v>
@@ -1533,23 +1533,23 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1423</v>
+        <v>1416</v>
       </c>
       <c r="O15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="Q15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2135</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-16 17:09:44</t>
+          <t>2026-08-17 17:15:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.700778</v>
+        <v>4.6996465</v>
       </c>
       <c r="G16" t="n">
-        <v>46723</v>
+        <v>46724</v>
       </c>
       <c r="H16" t="n">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>578795</v>
+        <v>579182</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,11 +1607,11 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Aug 10, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2268</v>
+        <v>2277</v>
       </c>
       <c r="O16" t="n">
         <v>373</v>
@@ -1620,10 +1620,10 @@
         <v>737</v>
       </c>
       <c r="Q16" t="n">
-        <v>2302</v>
+        <v>2322</v>
       </c>
       <c r="R16" t="n">
-        <v>41037</v>
+        <v>41011</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:22</t>
+          <t>2026-08-18 17:24:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.99</v>
+        <v>4.03</v>
       </c>
       <c r="G2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2" t="n">
         <v>177</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>39907</v>
+        <v>39938</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:22</t>
+          <t>2026-08-18 17:24:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4433103</v>
+        <v>4.4456997</v>
       </c>
       <c r="G3" t="n">
-        <v>30833</v>
+        <v>30846</v>
       </c>
       <c r="H3" t="n">
         <v>9158</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2404270</v>
+        <v>2406532</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3765</v>
+        <v>3754</v>
       </c>
       <c r="O3" t="n">
         <v>303</v>
       </c>
       <c r="P3" t="n">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="Q3" t="n">
         <v>629</v>
       </c>
       <c r="R3" t="n">
-        <v>25852</v>
+        <v>25888</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:22</t>
+          <t>2026-08-18 17:24:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6257198</v>
+        <v>3.6265213</v>
       </c>
       <c r="G4" t="n">
         <v>25031</v>
       </c>
       <c r="H4" t="n">
-        <v>5595</v>
+        <v>5594</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7222</v>
+        <v>7214</v>
       </c>
       <c r="O4" t="n">
         <v>832</v>
       </c>
       <c r="P4" t="n">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="Q4" t="n">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="R4" t="n">
-        <v>14844</v>
+        <v>14847</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:23</t>
+          <t>2026-08-18 17:24:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5329113</v>
+        <v>4.530526</v>
       </c>
       <c r="G5" t="n">
-        <v>26485</v>
+        <v>26491</v>
       </c>
       <c r="H5" t="n">
-        <v>9858</v>
+        <v>9862</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>671904</v>
+        <v>672082</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1988</v>
+        <v>1995</v>
       </c>
       <c r="O5" t="n">
         <v>323</v>
       </c>
       <c r="P5" t="n">
-        <v>814</v>
+        <v>836</v>
       </c>
       <c r="Q5" t="n">
-        <v>1810</v>
+        <v>1806</v>
       </c>
       <c r="R5" t="n">
-        <v>21544</v>
+        <v>21527</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:23</t>
+          <t>2026-08-18 17:24:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111350</v>
+        <v>111405</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:23</t>
+          <t>2026-08-18 17:24:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.4479637</v>
+        <v>4.4215245</v>
       </c>
       <c r="G7" t="n">
-        <v>3123</v>
+        <v>3125</v>
       </c>
       <c r="H7" t="n">
         <v>1158</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>447896</v>
+        <v>448394</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="O7" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="P7" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q7" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R7" t="n">
-        <v>2571</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:23</t>
+          <t>2026-08-18 17:24:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.163636</v>
+        <v>4.1651545</v>
       </c>
       <c r="G8" t="n">
-        <v>6084</v>
+        <v>6085</v>
       </c>
       <c r="H8" t="n">
         <v>2257</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>455116</v>
+        <v>455489</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="O8" t="n">
         <v>153</v>
@@ -1035,7 +1035,7 @@
         <v>242</v>
       </c>
       <c r="R8" t="n">
-        <v>4501</v>
+        <v>4505</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:24</t>
+          <t>2026-08-18 17:24:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>180700</v>
+        <v>180817</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:24</t>
+          <t>2026-08-18 17:24:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1142,10 +1142,10 @@
         <v>4.01</v>
       </c>
       <c r="G10" t="n">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H10" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>92999</v>
+        <v>93091</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:24</t>
+          <t>2026-08-18 17:24:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.677419</v>
+        <v>4.6769347</v>
       </c>
       <c r="G11" t="n">
-        <v>14999</v>
+        <v>14998</v>
       </c>
       <c r="H11" t="n">
         <v>702</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>273442</v>
+        <v>273580</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="O11" t="n">
         <v>111</v>
@@ -1254,10 +1254,10 @@
         <v>281</v>
       </c>
       <c r="Q11" t="n">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="R11" t="n">
-        <v>12995</v>
+        <v>12991</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:24</t>
+          <t>2026-08-18 17:24:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1293,7 +1293,7 @@
         <v>4712</v>
       </c>
       <c r="H12" t="n">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>356067</v>
+        <v>356251</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:25</t>
+          <t>2026-08-18 17:24:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7578948</v>
+        <v>2.7395833</v>
       </c>
       <c r="G13" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H13" t="n">
         <v>41</v>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22152</v>
+        <v>22159</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O13" t="n">
         <v>5</v>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:25</t>
+          <t>2026-08-18 17:24:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.703137</v>
+        <v>4.6979403</v>
       </c>
       <c r="G14" t="n">
-        <v>13475</v>
+        <v>13482</v>
       </c>
       <c r="H14" t="n">
-        <v>5013</v>
+        <v>5014</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1266891</v>
+        <v>1268094</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>845</v>
+        <v>862</v>
       </c>
       <c r="O14" t="n">
         <v>92</v>
@@ -1472,10 +1472,10 @@
         <v>71</v>
       </c>
       <c r="Q14" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R14" t="n">
-        <v>12268</v>
+        <v>12257</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:25</t>
+          <t>2026-08-18 17:24:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1508,10 +1508,10 @@
         <v>3.3652174</v>
       </c>
       <c r="G15" t="n">
-        <v>3910</v>
+        <v>3912</v>
       </c>
       <c r="H15" t="n">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>404606</v>
+        <v>404784</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2129</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-17 17:15:25</t>
+          <t>2026-08-18 17:24:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6996465</v>
+        <v>4.7006593</v>
       </c>
       <c r="G16" t="n">
         <v>46724</v>
       </c>
       <c r="H16" t="n">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2277</v>
+        <v>2266</v>
       </c>
       <c r="O16" t="n">
         <v>373</v>
       </c>
       <c r="P16" t="n">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="Q16" t="n">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="R16" t="n">
-        <v>41011</v>
+        <v>41023</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:14</t>
+          <t>2026-08-19 17:15:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,7 +553,7 @@
         <v>409</v>
       </c>
       <c r="H2" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>39938</v>
+        <v>40006</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:14</t>
+          <t>2026-08-19 17:15:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4456997</v>
+        <v>4.446266</v>
       </c>
       <c r="G3" t="n">
-        <v>30846</v>
+        <v>30851</v>
       </c>
       <c r="H3" t="n">
-        <v>9158</v>
+        <v>9161</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -649,11 +649,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Jul 27, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3754</v>
+        <v>3752</v>
       </c>
       <c r="O3" t="n">
         <v>303</v>
@@ -662,10 +662,10 @@
         <v>269</v>
       </c>
       <c r="Q3" t="n">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="R3" t="n">
-        <v>25888</v>
+        <v>25905</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:14</t>
+          <t>2026-08-19 17:15:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,10 +698,10 @@
         <v>3.6265213</v>
       </c>
       <c r="G4" t="n">
-        <v>25031</v>
+        <v>25034</v>
       </c>
       <c r="H4" t="n">
-        <v>5594</v>
+        <v>5595</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2612954</v>
+        <v>2614250</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7214</v>
+        <v>7215</v>
       </c>
       <c r="O4" t="n">
         <v>832</v>
@@ -739,7 +739,7 @@
         <v>1250</v>
       </c>
       <c r="R4" t="n">
-        <v>14847</v>
+        <v>14849</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:15</t>
+          <t>2026-08-19 17:15:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.530526</v>
+        <v>4.5276723</v>
       </c>
       <c r="G5" t="n">
-        <v>26491</v>
+        <v>26500</v>
       </c>
       <c r="H5" t="n">
-        <v>9862</v>
+        <v>9863</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>672082</v>
+        <v>672572</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1995</v>
+        <v>2014</v>
       </c>
       <c r="O5" t="n">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="P5" t="n">
-        <v>836</v>
+        <v>850</v>
       </c>
       <c r="Q5" t="n">
-        <v>1806</v>
+        <v>1813</v>
       </c>
       <c r="R5" t="n">
-        <v>21527</v>
+        <v>21505</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:15</t>
+          <t>2026-08-19 17:15:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111405</v>
+        <v>111473</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:15</t>
+          <t>2026-08-19 17:15:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.4215245</v>
+        <v>4.41629</v>
       </c>
       <c r="G7" t="n">
-        <v>3125</v>
+        <v>3130</v>
       </c>
       <c r="H7" t="n">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>448394</v>
+        <v>449389</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="O7" t="n">
         <v>41</v>
       </c>
       <c r="P7" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q7" t="n">
         <v>83</v>
       </c>
       <c r="R7" t="n">
-        <v>2549</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:15</t>
+          <t>2026-08-19 17:15:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>455489</v>
+        <v>455917</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:16</t>
+          <t>2026-08-19 17:15:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>180817</v>
+        <v>180943</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:16</t>
+          <t>2026-08-19 17:15:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.01</v>
+        <v>3.980198</v>
       </c>
       <c r="G10" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="H10" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>93091</v>
+        <v>93270</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:16</t>
+          <t>2026-08-19 17:15:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6769347</v>
+        <v>4.677419</v>
       </c>
       <c r="G11" t="n">
-        <v>14998</v>
+        <v>15001</v>
       </c>
       <c r="H11" t="n">
         <v>702</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>273580</v>
+        <v>273715</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="O11" t="n">
         <v>111</v>
@@ -1254,10 +1254,10 @@
         <v>281</v>
       </c>
       <c r="Q11" t="n">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="R11" t="n">
-        <v>12991</v>
+        <v>12997</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:16</t>
+          <t>2026-08-19 17:15:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.738342</v>
+        <v>2.753886</v>
       </c>
       <c r="G12" t="n">
-        <v>4712</v>
+        <v>4715</v>
       </c>
       <c r="H12" t="n">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>356251</v>
+        <v>356450</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1315,19 +1315,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2416</v>
+        <v>2393</v>
       </c>
       <c r="O12" t="n">
         <v>121</v>
       </c>
       <c r="P12" t="n">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="Q12" t="n">
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1757</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:16</t>
+          <t>2026-08-19 17:15:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22159</v>
+        <v>22168</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:17</t>
+          <t>2026-08-19 17:15:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6979403</v>
+        <v>4.694423</v>
       </c>
       <c r="G14" t="n">
-        <v>13482</v>
+        <v>13479</v>
       </c>
       <c r="H14" t="n">
-        <v>5014</v>
+        <v>5016</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1268094</v>
+        <v>1269442</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="O14" t="n">
         <v>92</v>
@@ -1475,7 +1475,7 @@
         <v>194</v>
       </c>
       <c r="R14" t="n">
-        <v>12257</v>
+        <v>12243</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:17</t>
+          <t>2026-08-19 17:15:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3652174</v>
+        <v>3.368116</v>
       </c>
       <c r="G15" t="n">
-        <v>3912</v>
+        <v>3913</v>
       </c>
       <c r="H15" t="n">
         <v>1580</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>404784</v>
+        <v>405294</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,14 +1533,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1416</v>
+        <v>1406</v>
       </c>
       <c r="O15" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="P15" t="n">
         <v>113</v>
@@ -1549,7 +1549,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2130</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-18 17:24:17</t>
+          <t>2026-08-19 17:15:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7006593</v>
+        <v>4.7000704</v>
       </c>
       <c r="G16" t="n">
-        <v>46724</v>
+        <v>46728</v>
       </c>
       <c r="H16" t="n">
         <v>2975</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>579182</v>
+        <v>580089</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2266</v>
+        <v>2275</v>
       </c>
       <c r="O16" t="n">
         <v>373</v>
@@ -1620,10 +1620,10 @@
         <v>736</v>
       </c>
       <c r="Q16" t="n">
-        <v>2320</v>
+        <v>2318</v>
       </c>
       <c r="R16" t="n">
-        <v>41023</v>
+        <v>41022</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:26</t>
+          <t>2026-08-20 17:17:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.03</v>
+        <v>4.019802</v>
       </c>
       <c r="G2" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2" t="n">
         <v>178</v>
@@ -579,19 +579,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q2" t="n">
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:26</t>
+          <t>2026-08-20 17:17:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.446266</v>
+        <v>4.445818</v>
       </c>
       <c r="G3" t="n">
-        <v>30851</v>
+        <v>30856</v>
       </c>
       <c r="H3" t="n">
-        <v>9161</v>
+        <v>9166</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2406532</v>
+        <v>2407526</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3752</v>
+        <v>3758</v>
       </c>
       <c r="O3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P3" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q3" t="n">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="R3" t="n">
-        <v>25905</v>
+        <v>25907</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:26</t>
+          <t>2026-08-20 17:17:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6265213</v>
+        <v>3.629156</v>
       </c>
       <c r="G4" t="n">
-        <v>25034</v>
+        <v>25038</v>
       </c>
       <c r="H4" t="n">
-        <v>5595</v>
+        <v>5596</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2614250</v>
+        <v>2614285</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7215</v>
+        <v>7202</v>
       </c>
       <c r="O4" t="n">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="P4" t="n">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="Q4" t="n">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="R4" t="n">
-        <v>14849</v>
+        <v>14871</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:26</t>
+          <t>2026-08-20 17:17:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5276723</v>
+        <v>4.52725</v>
       </c>
       <c r="G5" t="n">
-        <v>26500</v>
+        <v>26510</v>
       </c>
       <c r="H5" t="n">
-        <v>9863</v>
+        <v>9873</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="O5" t="n">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="P5" t="n">
-        <v>850</v>
+        <v>839</v>
       </c>
       <c r="Q5" t="n">
         <v>1813</v>
       </c>
       <c r="R5" t="n">
-        <v>21505</v>
+        <v>21514</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:27</t>
+          <t>2026-08-20 17:17:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,11 +857,11 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111473</v>
+        <v>111505</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Aug 5, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:27</t>
+          <t>2026-08-20 17:17:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.41629</v>
+        <v>4.3901343</v>
       </c>
       <c r="G7" t="n">
-        <v>3130</v>
+        <v>3133</v>
       </c>
       <c r="H7" t="n">
         <v>1160</v>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="O7" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="P7" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q7" t="n">
         <v>83</v>
       </c>
       <c r="R7" t="n">
-        <v>2548</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:27</t>
+          <t>2026-08-20 17:17:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1651545</v>
+        <v>4.170909</v>
       </c>
       <c r="G8" t="n">
-        <v>6085</v>
+        <v>6084</v>
       </c>
       <c r="H8" t="n">
         <v>2257</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1004</v>
+        <v>994</v>
       </c>
       <c r="O8" t="n">
         <v>153</v>
@@ -1035,7 +1035,7 @@
         <v>242</v>
       </c>
       <c r="R8" t="n">
-        <v>4505</v>
+        <v>4512</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:27</t>
+          <t>2026-08-20 17:17:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:28</t>
+          <t>2026-08-20 17:17:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.980198</v>
+        <v>3.9509804</v>
       </c>
       <c r="G10" t="n">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="H10" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:28</t>
+          <t>2026-08-20 17:17:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1216,7 +1216,7 @@
         <v>4.677419</v>
       </c>
       <c r="G11" t="n">
-        <v>15001</v>
+        <v>15000</v>
       </c>
       <c r="H11" t="n">
         <v>702</v>
@@ -1257,7 +1257,7 @@
         <v>831</v>
       </c>
       <c r="R11" t="n">
-        <v>12997</v>
+        <v>12996</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:28</t>
+          <t>2026-08-20 17:17:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.753886</v>
+        <v>2.7493541</v>
       </c>
       <c r="G12" t="n">
-        <v>4715</v>
+        <v>4716</v>
       </c>
       <c r="H12" t="n">
         <v>1950</v>
@@ -1315,19 +1315,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2393</v>
+        <v>2399</v>
       </c>
       <c r="O12" t="n">
         <v>121</v>
       </c>
       <c r="P12" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q12" t="n">
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1770</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:28</t>
+          <t>2026-08-20 17:17:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:28</t>
+          <t>2026-08-20 17:17:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.694423</v>
+        <v>4.693242</v>
       </c>
       <c r="G14" t="n">
-        <v>13479</v>
+        <v>13487</v>
       </c>
       <c r="H14" t="n">
-        <v>5016</v>
+        <v>5017</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="O14" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P14" t="n">
         <v>71</v>
       </c>
       <c r="Q14" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R14" t="n">
-        <v>12243</v>
+        <v>12246</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:29</t>
+          <t>2026-08-20 17:17:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.368116</v>
+        <v>3.3594203</v>
       </c>
       <c r="G15" t="n">
-        <v>3913</v>
+        <v>3915</v>
       </c>
       <c r="H15" t="n">
         <v>1580</v>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1406</v>
+        <v>1417</v>
       </c>
       <c r="O15" t="n">
         <v>135</v>
@@ -1546,10 +1546,10 @@
         <v>113</v>
       </c>
       <c r="Q15" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="R15" t="n">
-        <v>2131</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-19 17:15:29</t>
+          <t>2026-08-20 17:17:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1593,11 +1593,11 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>580089</v>
+        <v>580686</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.5</t>
+          <t>3.1.6</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:37</t>
+          <t>2026-08-21 17:17:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40006</v>
+        <v>40048</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:37</t>
+          <t>2026-08-21 17:17:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.445818</v>
+        <v>4.4431114</v>
       </c>
       <c r="G3" t="n">
-        <v>30856</v>
+        <v>30870</v>
       </c>
       <c r="H3" t="n">
-        <v>9166</v>
+        <v>9167</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3758</v>
+        <v>3780</v>
       </c>
       <c r="O3" t="n">
         <v>302</v>
@@ -665,7 +665,7 @@
         <v>616</v>
       </c>
       <c r="R3" t="n">
-        <v>25907</v>
+        <v>25898</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:37</t>
+          <t>2026-08-21 17:17:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.629156</v>
+        <v>3.6094866</v>
       </c>
       <c r="G4" t="n">
-        <v>25038</v>
+        <v>25042</v>
       </c>
       <c r="H4" t="n">
-        <v>5596</v>
+        <v>5597</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2614285</v>
+        <v>2615194</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7202</v>
+        <v>7305</v>
       </c>
       <c r="O4" t="n">
-        <v>831</v>
+        <v>845</v>
       </c>
       <c r="P4" t="n">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="Q4" t="n">
-        <v>1247</v>
+        <v>1268</v>
       </c>
       <c r="R4" t="n">
-        <v>14871</v>
+        <v>14725</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:37</t>
+          <t>2026-08-21 17:17:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.52725</v>
+        <v>4.5275326</v>
       </c>
       <c r="G5" t="n">
-        <v>26510</v>
+        <v>26533</v>
       </c>
       <c r="H5" t="n">
-        <v>9873</v>
+        <v>9882</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>672572</v>
+        <v>672583</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="O5" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P5" t="n">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="Q5" t="n">
-        <v>1813</v>
+        <v>1816</v>
       </c>
       <c r="R5" t="n">
-        <v>21514</v>
+        <v>21535</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:38</t>
+          <t>2026-08-21 17:17:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.64</v>
       </c>
       <c r="G6" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H6" t="n">
         <v>164</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:38</t>
+          <t>2026-08-21 17:17:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -920,10 +920,10 @@
         <v>4.3901343</v>
       </c>
       <c r="G7" t="n">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="H7" t="n">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>449389</v>
+        <v>450334</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:38</t>
+          <t>2026-08-21 17:17:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>455917</v>
+        <v>455930</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:38</t>
+          <t>2026-08-21 17:17:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>180943</v>
+        <v>181036</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:38</t>
+          <t>2026-08-21 17:17:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.9509804</v>
+        <v>3.9223301</v>
       </c>
       <c r="G10" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H10" t="n">
         <v>241</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>93270</v>
+        <v>93385</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:39</t>
+          <t>2026-08-21 17:17:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>273715</v>
+        <v>273798</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:39</t>
+          <t>2026-08-21 17:17:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1290,10 +1290,10 @@
         <v>2.7493541</v>
       </c>
       <c r="G12" t="n">
-        <v>4716</v>
+        <v>4717</v>
       </c>
       <c r="H12" t="n">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>356450</v>
+        <v>356584</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="O12" t="n">
         <v>121</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:39</t>
+          <t>2026-08-21 17:17:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22168</v>
+        <v>22171</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:39</t>
+          <t>2026-08-21 17:17:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.693242</v>
+        <v>4.671289</v>
       </c>
       <c r="G14" t="n">
-        <v>13487</v>
+        <v>13499</v>
       </c>
       <c r="H14" t="n">
-        <v>5017</v>
+        <v>5020</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1269442</v>
+        <v>1270305</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>880</v>
+        <v>946</v>
       </c>
       <c r="O14" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="P14" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q14" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="R14" t="n">
-        <v>12246</v>
+        <v>12177</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:39</t>
+          <t>2026-08-21 17:17:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>405294</v>
+        <v>405647</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-20 17:17:40</t>
+          <t>2026-08-21 17:17:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7000704</v>
+        <v>4.700141</v>
       </c>
       <c r="G16" t="n">
-        <v>46728</v>
+        <v>46729</v>
       </c>
       <c r="H16" t="n">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="O16" t="n">
         <v>373</v>
@@ -1623,7 +1623,7 @@
         <v>2318</v>
       </c>
       <c r="R16" t="n">
-        <v>41022</v>
+        <v>41024</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:24</t>
+          <t>2026-08-22 17:10:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40048</v>
+        <v>40091</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:24</t>
+          <t>2026-08-22 17:10:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4431114</v>
+        <v>4.439724</v>
       </c>
       <c r="G3" t="n">
-        <v>30870</v>
+        <v>30881</v>
       </c>
       <c r="H3" t="n">
         <v>9167</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2407526</v>
+        <v>2408430</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3780</v>
+        <v>3800</v>
       </c>
       <c r="O3" t="n">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="P3" t="n">
         <v>268</v>
       </c>
       <c r="Q3" t="n">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="R3" t="n">
-        <v>25898</v>
+        <v>25879</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:25</t>
+          <t>2026-08-22 17:10:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6094866</v>
+        <v>3.6103897</v>
       </c>
       <c r="G4" t="n">
-        <v>25042</v>
+        <v>25043</v>
       </c>
       <c r="H4" t="n">
         <v>5597</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2615194</v>
+        <v>2615922</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7305</v>
+        <v>7300</v>
       </c>
       <c r="O4" t="n">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="P4" t="n">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="Q4" t="n">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="R4" t="n">
-        <v>14725</v>
+        <v>14732</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:25</t>
+          <t>2026-08-22 17:10:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5275326</v>
+        <v>4.5338125</v>
       </c>
       <c r="G5" t="n">
-        <v>26533</v>
+        <v>26542</v>
       </c>
       <c r="H5" t="n">
-        <v>9882</v>
+        <v>9883</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>672583</v>
+        <v>673304</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2017</v>
+        <v>1985</v>
       </c>
       <c r="O5" t="n">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="P5" t="n">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="Q5" t="n">
-        <v>1816</v>
+        <v>1828</v>
       </c>
       <c r="R5" t="n">
-        <v>21535</v>
+        <v>21582</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:25</t>
+          <t>2026-08-22 17:10:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111505</v>
+        <v>111548</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:25</t>
+          <t>2026-08-22 17:10:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3901343</v>
+        <v>4.3761063</v>
       </c>
       <c r="G7" t="n">
-        <v>3132</v>
+        <v>3135</v>
       </c>
       <c r="H7" t="n">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>450334</v>
+        <v>450977</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="O7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P7" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q7" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="R7" t="n">
-        <v>2527</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:26</t>
+          <t>2026-08-22 17:10:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.170909</v>
+        <v>4.172414</v>
       </c>
       <c r="G8" t="n">
-        <v>6084</v>
+        <v>6085</v>
       </c>
       <c r="H8" t="n">
         <v>2257</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>455930</v>
+        <v>456747</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="O8" t="n">
         <v>153</v>
@@ -1035,7 +1035,7 @@
         <v>242</v>
       </c>
       <c r="R8" t="n">
-        <v>4512</v>
+        <v>4515</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:26</t>
+          <t>2026-08-22 17:10:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.9629629</v>
+        <v>3.972477</v>
       </c>
       <c r="G9" t="n">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H9" t="n">
         <v>495</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>181036</v>
+        <v>181125</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>854</v>
+        <v>858</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:26</t>
+          <t>2026-08-22 17:10:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>93385</v>
+        <v>93485</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:26</t>
+          <t>2026-08-22 17:10:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>273798</v>
+        <v>273868</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:27</t>
+          <t>2026-08-22 17:10:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1293,7 +1293,7 @@
         <v>4717</v>
       </c>
       <c r="H12" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>356584</v>
+        <v>356690</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:27</t>
+          <t>2026-08-22 17:10:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22171</v>
+        <v>22175</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:27</t>
+          <t>2026-08-22 17:10:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.671289</v>
+        <v>4.6653094</v>
       </c>
       <c r="G14" t="n">
-        <v>13499</v>
+        <v>13502</v>
       </c>
       <c r="H14" t="n">
-        <v>5020</v>
+        <v>5022</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1270305</v>
+        <v>1271085</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>946</v>
+        <v>967</v>
       </c>
       <c r="O14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q14" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="R14" t="n">
-        <v>12177</v>
+        <v>12159</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:27</t>
+          <t>2026-08-22 17:10:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1511,7 +1511,7 @@
         <v>3915</v>
       </c>
       <c r="H15" t="n">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>405647</v>
+        <v>405966</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 17:17:28</t>
+          <t>2026-08-22 17:10:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.700141</v>
+        <v>4.7002115</v>
       </c>
       <c r="G16" t="n">
-        <v>46729</v>
+        <v>46730</v>
       </c>
       <c r="H16" t="n">
         <v>2976</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>580686</v>
+        <v>581192</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1614,16 +1614,16 @@
         <v>2274</v>
       </c>
       <c r="O16" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P16" t="n">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="Q16" t="n">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="R16" t="n">
-        <v>41024</v>
+        <v>41026</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:15</t>
+          <t>2026-08-23 17:10:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40091</v>
+        <v>40129</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:15</t>
+          <t>2026-08-23 17:10:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.439724</v>
+        <v>4.440334</v>
       </c>
       <c r="G3" t="n">
-        <v>30881</v>
+        <v>30885</v>
       </c>
       <c r="H3" t="n">
-        <v>9167</v>
+        <v>9172</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2408430</v>
+        <v>2409262</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3800</v>
+        <v>3797</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
@@ -665,7 +665,7 @@
         <v>615</v>
       </c>
       <c r="R3" t="n">
-        <v>25879</v>
+        <v>25888</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:15</t>
+          <t>2026-08-23 17:10:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6103897</v>
+        <v>3.612192</v>
       </c>
       <c r="G4" t="n">
-        <v>25043</v>
+        <v>25046</v>
       </c>
       <c r="H4" t="n">
-        <v>5597</v>
+        <v>5598</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2615922</v>
+        <v>2616661</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7300</v>
+        <v>7292</v>
       </c>
       <c r="O4" t="n">
         <v>844</v>
@@ -736,10 +736,10 @@
         <v>893</v>
       </c>
       <c r="Q4" t="n">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="R4" t="n">
-        <v>14732</v>
+        <v>14747</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:16</t>
+          <t>2026-08-23 17:10:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5338125</v>
+        <v>4.5340095</v>
       </c>
       <c r="G5" t="n">
-        <v>26542</v>
+        <v>26543</v>
       </c>
       <c r="H5" t="n">
-        <v>9883</v>
+        <v>9887</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>673304</v>
+        <v>673684</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="O5" t="n">
         <v>313</v>
@@ -810,10 +810,10 @@
         <v>829</v>
       </c>
       <c r="Q5" t="n">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="R5" t="n">
-        <v>21582</v>
+        <v>21585</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:16</t>
+          <t>2026-08-23 17:10:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.64</v>
       </c>
       <c r="G6" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H6" t="n">
         <v>164</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111548</v>
+        <v>111591</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:16</t>
+          <t>2026-08-23 17:10:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3761063</v>
+        <v>4.364035</v>
       </c>
       <c r="G7" t="n">
-        <v>3135</v>
+        <v>3137</v>
       </c>
       <c r="H7" t="n">
         <v>1160</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>450977</v>
+        <v>451707</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="O7" t="n">
         <v>54</v>
@@ -961,7 +961,7 @@
         <v>96</v>
       </c>
       <c r="R7" t="n">
-        <v>2510</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:16</t>
+          <t>2026-08-23 17:10:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.172414</v>
+        <v>4.169399</v>
       </c>
       <c r="G8" t="n">
-        <v>6085</v>
+        <v>6083</v>
       </c>
       <c r="H8" t="n">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>456747</v>
+        <v>457093</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="O8" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P8" t="n">
         <v>176</v>
       </c>
       <c r="Q8" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R8" t="n">
-        <v>4515</v>
+        <v>4509</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:16</t>
+          <t>2026-08-23 17:10:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>181125</v>
+        <v>181211</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:16</t>
+          <t>2026-08-23 17:10:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>93485</v>
+        <v>93591</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:17</t>
+          <t>2026-08-23 17:10:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>273868</v>
+        <v>273938</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:17</t>
+          <t>2026-08-23 17:10:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7493541</v>
+        <v>2.7441862</v>
       </c>
       <c r="G12" t="n">
         <v>4717</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>356690</v>
+        <v>356829</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1315,13 +1315,13 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2400</v>
+        <v>2412</v>
       </c>
       <c r="O12" t="n">
         <v>121</v>
       </c>
       <c r="P12" t="n">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="Q12" t="n">
         <v>206</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:17</t>
+          <t>2026-08-23 17:10:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22175</v>
+        <v>22185</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:17</t>
+          <t>2026-08-23 17:10:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6653094</v>
+        <v>4.6661253</v>
       </c>
       <c r="G14" t="n">
-        <v>13502</v>
+        <v>13506</v>
       </c>
       <c r="H14" t="n">
-        <v>5022</v>
+        <v>5024</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1271085</v>
+        <v>1271941</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="O14" t="n">
         <v>97</v>
@@ -1475,7 +1475,7 @@
         <v>196</v>
       </c>
       <c r="R14" t="n">
-        <v>12159</v>
+        <v>12166</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:17</t>
+          <t>2026-08-23 17:10:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3594203</v>
+        <v>3.368876</v>
       </c>
       <c r="G15" t="n">
-        <v>3915</v>
+        <v>3917</v>
       </c>
       <c r="H15" t="n">
         <v>1582</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>405966</v>
+        <v>406301</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,23 +1533,23 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1417</v>
+        <v>1410</v>
       </c>
       <c r="O15" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P15" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q15" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R15" t="n">
-        <v>2132</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-22 17:10:17</t>
+          <t>2026-08-23 17:10:23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7002115</v>
+        <v>4.700282</v>
       </c>
       <c r="G16" t="n">
-        <v>46730</v>
+        <v>46729</v>
       </c>
       <c r="H16" t="n">
-        <v>2976</v>
+        <v>2978</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>581192</v>
+        <v>581680</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="O16" t="n">
         <v>372</v>
@@ -1623,7 +1623,7 @@
         <v>2317</v>
       </c>
       <c r="R16" t="n">
-        <v>41026</v>
+        <v>41027</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:20</t>
+          <t>2026-08-24 17:20:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40129</v>
+        <v>40194</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:20</t>
+          <t>2026-08-24 17:20:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.440334</v>
+        <v>4.437341</v>
       </c>
       <c r="G3" t="n">
-        <v>30885</v>
+        <v>30893</v>
       </c>
       <c r="H3" t="n">
-        <v>9172</v>
+        <v>9173</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2409262</v>
+        <v>2410189</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3797</v>
+        <v>3825</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
       </c>
       <c r="P3" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="Q3" t="n">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="R3" t="n">
-        <v>25888</v>
+        <v>25876</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:21</t>
+          <t>2026-08-24 17:20:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.612192</v>
+        <v>3.611757</v>
       </c>
       <c r="G4" t="n">
-        <v>25046</v>
+        <v>25053</v>
       </c>
       <c r="H4" t="n">
-        <v>5598</v>
+        <v>5600</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2616661</v>
+        <v>2617329</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7292</v>
+        <v>7298</v>
       </c>
       <c r="O4" t="n">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="P4" t="n">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="Q4" t="n">
-        <v>1265</v>
+        <v>1278</v>
       </c>
       <c r="R4" t="n">
-        <v>14747</v>
+        <v>14742</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:21</t>
+          <t>2026-08-24 17:20:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5340095</v>
+        <v>4.5343156</v>
       </c>
       <c r="G5" t="n">
-        <v>26543</v>
+        <v>26550</v>
       </c>
       <c r="H5" t="n">
-        <v>9887</v>
+        <v>9892</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>673684</v>
+        <v>674116</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1984</v>
+        <v>1989</v>
       </c>
       <c r="O5" t="n">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="P5" t="n">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="Q5" t="n">
-        <v>1827</v>
+        <v>1810</v>
       </c>
       <c r="R5" t="n">
-        <v>21585</v>
+        <v>21608</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:21</t>
+          <t>2026-08-24 17:20:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111591</v>
+        <v>111645</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:21</t>
+          <t>2026-08-24 17:20:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>451707</v>
+        <v>452433</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:22</t>
+          <t>2026-08-24 17:20:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.169399</v>
+        <v>4.1623616</v>
       </c>
       <c r="G8" t="n">
-        <v>6083</v>
+        <v>6086</v>
       </c>
       <c r="H8" t="n">
         <v>2258</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>457093</v>
+        <v>457245</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="O8" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="P8" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="Q8" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="R8" t="n">
-        <v>4509</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:22</t>
+          <t>2026-08-24 17:20:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1071,7 +1071,7 @@
         <v>1232</v>
       </c>
       <c r="H9" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>181211</v>
+        <v>181314</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:22</t>
+          <t>2026-08-24 17:20:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>93591</v>
+        <v>93721</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:22</t>
+          <t>2026-08-24 17:20:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>273938</v>
+        <v>274021</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:22</t>
+          <t>2026-08-24 17:20:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7441862</v>
+        <v>2.7467701</v>
       </c>
       <c r="G12" t="n">
         <v>4717</v>
       </c>
       <c r="H12" t="n">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>356829</v>
+        <v>357063</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2412</v>
+        <v>2400</v>
       </c>
       <c r="O12" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="P12" t="n">
         <v>206</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:23</t>
+          <t>2026-08-24 17:20:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22185</v>
+        <v>22194</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:23</t>
+          <t>2026-08-24 17:20:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6661253</v>
+        <v>4.6645107</v>
       </c>
       <c r="G14" t="n">
-        <v>13506</v>
+        <v>13512</v>
       </c>
       <c r="H14" t="n">
         <v>5024</v>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1271941</v>
+        <v>1272985</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="O14" t="n">
         <v>97</v>
@@ -1472,10 +1472,10 @@
         <v>75</v>
       </c>
       <c r="Q14" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R14" t="n">
-        <v>12166</v>
+        <v>12168</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:23</t>
+          <t>2026-08-24 17:20:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.368876</v>
+        <v>3.384393</v>
       </c>
       <c r="G15" t="n">
         <v>3917</v>
       </c>
       <c r="H15" t="n">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>406301</v>
+        <v>406676</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,23 +1533,23 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1410</v>
+        <v>1403</v>
       </c>
       <c r="O15" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="P15" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q15" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R15" t="n">
-        <v>2144</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-23 17:10:23</t>
+          <t>2026-08-24 17:20:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.700282</v>
+        <v>4.7001176</v>
       </c>
       <c r="G16" t="n">
-        <v>46729</v>
+        <v>46728</v>
       </c>
       <c r="H16" t="n">
-        <v>2978</v>
+        <v>2981</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>581680</v>
+        <v>582355</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
         <v>735</v>
       </c>
       <c r="Q16" t="n">
-        <v>2317</v>
+        <v>2327</v>
       </c>
       <c r="R16" t="n">
-        <v>41027</v>
+        <v>41016</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:08</t>
+          <t>2026-08-25 17:20:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40194</v>
+        <v>40197</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:08</t>
+          <t>2026-08-25 17:20:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.437341</v>
+        <v>4.4341817</v>
       </c>
       <c r="G3" t="n">
-        <v>30893</v>
+        <v>30901</v>
       </c>
       <c r="H3" t="n">
-        <v>9173</v>
+        <v>9171</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2410189</v>
+        <v>2410751</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.44.5</t>
+          <t>4.45.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3825</v>
+        <v>3842</v>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P3" t="n">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="Q3" t="n">
-        <v>616</v>
+        <v>629</v>
       </c>
       <c r="R3" t="n">
-        <v>25876</v>
+        <v>25843</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:08</t>
+          <t>2026-08-25 17:20:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.611757</v>
+        <v>3.6063554</v>
       </c>
       <c r="G4" t="n">
-        <v>25053</v>
+        <v>25056</v>
       </c>
       <c r="H4" t="n">
-        <v>5600</v>
+        <v>5601</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7298</v>
+        <v>7327</v>
       </c>
       <c r="O4" t="n">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="P4" t="n">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="Q4" t="n">
-        <v>1278</v>
+        <v>1283</v>
       </c>
       <c r="R4" t="n">
-        <v>14742</v>
+        <v>14704</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:08</t>
+          <t>2026-08-25 17:20:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5343156</v>
+        <v>4.5343447</v>
       </c>
       <c r="G5" t="n">
-        <v>26550</v>
+        <v>26560</v>
       </c>
       <c r="H5" t="n">
-        <v>9892</v>
+        <v>9895</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="O5" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P5" t="n">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="Q5" t="n">
-        <v>1810</v>
+        <v>1801</v>
       </c>
       <c r="R5" t="n">
-        <v>21608</v>
+        <v>21623</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:08</t>
+          <t>2026-08-25 17:20:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:09</t>
+          <t>2026-08-25 17:20:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -920,7 +920,7 @@
         <v>4.364035</v>
       </c>
       <c r="G7" t="n">
-        <v>3137</v>
+        <v>3138</v>
       </c>
       <c r="H7" t="n">
         <v>1160</v>
@@ -961,7 +961,7 @@
         <v>96</v>
       </c>
       <c r="R7" t="n">
-        <v>2503</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:09</t>
+          <t>2026-08-25 17:20:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>4.1623616</v>
       </c>
       <c r="G8" t="n">
-        <v>6086</v>
+        <v>6087</v>
       </c>
       <c r="H8" t="n">
         <v>2258</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="O8" t="n">
         <v>157</v>
@@ -1035,7 +1035,7 @@
         <v>246</v>
       </c>
       <c r="R8" t="n">
-        <v>4490</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:09</t>
+          <t>2026-08-25 17:20:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.972477</v>
+        <v>3.9818182</v>
       </c>
       <c r="G9" t="n">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H9" t="n">
         <v>496</v>
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O9" t="n">
         <v>33</v>
       </c>
       <c r="P9" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q9" t="n">
         <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>858</v>
+        <v>862</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:10</t>
+          <t>2026-08-25 17:20:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>93721</v>
+        <v>93723</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:10</t>
+          <t>2026-08-25 17:20:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.677419</v>
+        <v>4.6769347</v>
       </c>
       <c r="G11" t="n">
-        <v>15000</v>
+        <v>14994</v>
       </c>
       <c r="H11" t="n">
         <v>702</v>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="O11" t="n">
         <v>111</v>
@@ -1254,10 +1254,10 @@
         <v>281</v>
       </c>
       <c r="Q11" t="n">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="R11" t="n">
-        <v>12996</v>
+        <v>12988</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:10</t>
+          <t>2026-08-25 17:20:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7467701</v>
+        <v>2.7571058</v>
       </c>
       <c r="G12" t="n">
-        <v>4717</v>
+        <v>4720</v>
       </c>
       <c r="H12" t="n">
         <v>1954</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2400</v>
+        <v>2389</v>
       </c>
       <c r="O12" t="n">
         <v>133</v>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1766</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:10</t>
+          <t>2026-08-25 17:20:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:11</t>
+          <t>2026-08-25 17:20:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6645107</v>
+        <v>4.661031</v>
       </c>
       <c r="G14" t="n">
-        <v>13512</v>
+        <v>13516</v>
       </c>
       <c r="H14" t="n">
-        <v>5024</v>
+        <v>5026</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1272985</v>
+        <v>1273004</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="O14" t="n">
         <v>97</v>
       </c>
       <c r="P14" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="Q14" t="n">
         <v>195</v>
       </c>
       <c r="R14" t="n">
-        <v>12168</v>
+        <v>12154</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:11</t>
+          <t>2026-08-25 17:20:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.384393</v>
+        <v>3.3930635</v>
       </c>
       <c r="G15" t="n">
-        <v>3917</v>
+        <v>3920</v>
       </c>
       <c r="H15" t="n">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>406676</v>
+        <v>406680</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1403</v>
+        <v>1393</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1546,10 +1546,10 @@
         <v>113</v>
       </c>
       <c r="Q15" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2161</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 17:20:11</t>
+          <t>2026-08-25 17:20:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7001176</v>
+        <v>4.6985207</v>
       </c>
       <c r="G16" t="n">
-        <v>46728</v>
+        <v>46730</v>
       </c>
       <c r="H16" t="n">
-        <v>2981</v>
+        <v>2985</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2273</v>
+        <v>2293</v>
       </c>
       <c r="O16" t="n">
         <v>372</v>
@@ -1620,10 +1620,10 @@
         <v>735</v>
       </c>
       <c r="Q16" t="n">
-        <v>2327</v>
+        <v>2325</v>
       </c>
       <c r="R16" t="n">
-        <v>41016</v>
+        <v>41001</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:54</t>
+          <t>2026-08-26 18:31:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.019802</v>
+        <v>4.05</v>
       </c>
       <c r="G2" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2" t="n">
         <v>178</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40197</v>
+        <v>40306</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,19 +579,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q2" t="n">
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:54</t>
+          <t>2026-08-26 18:31:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4341817</v>
+        <v>4.435051</v>
       </c>
       <c r="G3" t="n">
-        <v>30901</v>
+        <v>30908</v>
       </c>
       <c r="H3" t="n">
-        <v>9171</v>
+        <v>9176</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2410751</v>
+        <v>2412505</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3842</v>
+        <v>3834</v>
       </c>
       <c r="O3" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P3" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q3" t="n">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="R3" t="n">
-        <v>25843</v>
+        <v>25849</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:55</t>
+          <t>2026-08-26 18:31:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6063554</v>
+        <v>3.6058443</v>
       </c>
       <c r="G4" t="n">
-        <v>25056</v>
+        <v>25058</v>
       </c>
       <c r="H4" t="n">
         <v>5601</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2617329</v>
+        <v>2619058</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7327</v>
+        <v>7321</v>
       </c>
       <c r="O4" t="n">
-        <v>844</v>
+        <v>861</v>
       </c>
       <c r="P4" t="n">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="Q4" t="n">
-        <v>1283</v>
+        <v>1268</v>
       </c>
       <c r="R4" t="n">
-        <v>14704</v>
+        <v>14708</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:55</t>
+          <t>2026-08-26 18:31:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5343447</v>
+        <v>4.5369043</v>
       </c>
       <c r="G5" t="n">
-        <v>26560</v>
+        <v>26571</v>
       </c>
       <c r="H5" t="n">
         <v>9895</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>674116</v>
+        <v>674893</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1991</v>
+        <v>1960</v>
       </c>
       <c r="O5" t="n">
         <v>313</v>
       </c>
       <c r="P5" t="n">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="Q5" t="n">
-        <v>1801</v>
+        <v>1837</v>
       </c>
       <c r="R5" t="n">
-        <v>21623</v>
+        <v>21617</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:55</t>
+          <t>2026-08-26 18:31:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111645</v>
+        <v>111718</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:55</t>
+          <t>2026-08-26 18:31:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.364035</v>
+        <v>4.3608694</v>
       </c>
       <c r="G7" t="n">
-        <v>3138</v>
+        <v>3140</v>
       </c>
       <c r="H7" t="n">
         <v>1160</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>452433</v>
+        <v>453524</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="O7" t="n">
         <v>54</v>
       </c>
       <c r="P7" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="Q7" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="R7" t="n">
-        <v>2504</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:55</t>
+          <t>2026-08-26 18:31:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1623616</v>
+        <v>4.163904</v>
       </c>
       <c r="G8" t="n">
-        <v>6087</v>
+        <v>6088</v>
       </c>
       <c r="H8" t="n">
         <v>2258</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>457245</v>
+        <v>457667</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="O8" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P8" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q8" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="R8" t="n">
-        <v>4491</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:56</t>
+          <t>2026-08-26 18:31:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>181314</v>
+        <v>181534</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:56</t>
+          <t>2026-08-26 18:31:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1142,7 +1142,7 @@
         <v>3.9223301</v>
       </c>
       <c r="G10" t="n">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H10" t="n">
         <v>241</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>93723</v>
+        <v>94207</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:56</t>
+          <t>2026-08-26 18:31:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6769347</v>
+        <v>4.6764483</v>
       </c>
       <c r="G11" t="n">
-        <v>14994</v>
+        <v>14990</v>
       </c>
       <c r="H11" t="n">
         <v>702</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>274021</v>
+        <v>274237</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="O11" t="n">
         <v>111</v>
@@ -1254,10 +1254,10 @@
         <v>281</v>
       </c>
       <c r="Q11" t="n">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="R11" t="n">
-        <v>12988</v>
+        <v>12981</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:56</t>
+          <t>2026-08-26 18:32:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>357063</v>
+        <v>357466</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:57</t>
+          <t>2026-08-26 18:32:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22194</v>
+        <v>22205</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:57</t>
+          <t>2026-08-26 18:32:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.661031</v>
+        <v>4.6586347</v>
       </c>
       <c r="G14" t="n">
-        <v>13516</v>
+        <v>13519</v>
       </c>
       <c r="H14" t="n">
-        <v>5026</v>
+        <v>5027</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1273004</v>
+        <v>1274283</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>979</v>
+        <v>988</v>
       </c>
       <c r="O14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P14" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q14" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R14" t="n">
-        <v>12154</v>
+        <v>12150</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:57</t>
+          <t>2026-08-26 18:32:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3930635</v>
+        <v>3.384393</v>
       </c>
       <c r="G15" t="n">
-        <v>3920</v>
+        <v>3921</v>
       </c>
       <c r="H15" t="n">
         <v>1584</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>406680</v>
+        <v>407083</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,14 +1533,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
         <v>1393</v>
       </c>
       <c r="O15" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="P15" t="n">
         <v>113</v>
@@ -1549,7 +1549,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2163</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 17:20:57</t>
+          <t>2026-08-26 18:32:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6985207</v>
+        <v>4.6962028</v>
       </c>
       <c r="G16" t="n">
-        <v>46730</v>
+        <v>46734</v>
       </c>
       <c r="H16" t="n">
-        <v>2985</v>
+        <v>2987</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>582355</v>
+        <v>583147</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2293</v>
+        <v>2310</v>
       </c>
       <c r="O16" t="n">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="P16" t="n">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="Q16" t="n">
-        <v>2325</v>
+        <v>2332</v>
       </c>
       <c r="R16" t="n">
-        <v>41001</v>
+        <v>40971</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 18:31:57</t>
+          <t>2026-08-28 01:12:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 18:31:57</t>
+          <t>2026-08-28 01:12:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.435051</v>
+        <v>4.434215</v>
       </c>
       <c r="G3" t="n">
-        <v>30908</v>
+        <v>30921</v>
       </c>
       <c r="H3" t="n">
-        <v>9176</v>
+        <v>9180</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3834</v>
+        <v>3843</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
@@ -665,7 +665,7 @@
         <v>638</v>
       </c>
       <c r="R3" t="n">
-        <v>25849</v>
+        <v>25854</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 18:31:58</t>
+          <t>2026-08-28 01:12:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6058443</v>
+        <v>3.6067488</v>
       </c>
       <c r="G4" t="n">
-        <v>25058</v>
+        <v>25063</v>
       </c>
       <c r="H4" t="n">
-        <v>5601</v>
+        <v>5603</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7321</v>
+        <v>7317</v>
       </c>
       <c r="O4" t="n">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="P4" t="n">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="Q4" t="n">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="R4" t="n">
-        <v>14708</v>
+        <v>14718</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 18:31:58</t>
+          <t>2026-08-28 01:12:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5369043</v>
+        <v>4.5363903</v>
       </c>
       <c r="G5" t="n">
-        <v>26571</v>
+        <v>26577</v>
       </c>
       <c r="H5" t="n">
-        <v>9895</v>
+        <v>9900</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1960</v>
+        <v>1967</v>
       </c>
       <c r="O5" t="n">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="P5" t="n">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="Q5" t="n">
-        <v>1837</v>
+        <v>1832</v>
       </c>
       <c r="R5" t="n">
-        <v>21617</v>
+        <v>21623</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 18:31:58</t>
+          <t>2026-08-28 01:12:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111718</v>
+        <v>111772</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 18:31:58</t>
+          <t>2026-08-28 01:12:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3608694</v>
+        <v>4.3636365</v>
       </c>
       <c r="G7" t="n">
         <v>3140</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>453524</v>
+        <v>454137</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O7" t="n">
         <v>54</v>
@@ -961,7 +961,7 @@
         <v>94</v>
       </c>
       <c r="R7" t="n">
-        <v>2498</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 18:31:59</t>
+          <t>2026-08-28 01:12:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 18:31:59</t>
+          <t>2026-08-28 01:12:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 18:31:59</t>
+          <t>2026-08-28 01:12:54</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 18:31:59</t>
+          <t>2026-08-28 01:12:54</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6764483</v>
+        <v>4.6779532</v>
       </c>
       <c r="G11" t="n">
-        <v>14990</v>
+        <v>14997</v>
       </c>
       <c r="H11" t="n">
         <v>702</v>
@@ -1251,13 +1251,13 @@
         <v>111</v>
       </c>
       <c r="P11" t="n">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="Q11" t="n">
         <v>834</v>
       </c>
       <c r="R11" t="n">
-        <v>12981</v>
+        <v>12999</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:00</t>
+          <t>2026-08-28 01:12:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7571058</v>
+        <v>2.761658</v>
       </c>
       <c r="G12" t="n">
-        <v>4720</v>
+        <v>4719</v>
       </c>
       <c r="H12" t="n">
-        <v>1954</v>
+        <v>1957</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2389</v>
+        <v>2383</v>
       </c>
       <c r="O12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P12" t="n">
         <v>206</v>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1780</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:00</t>
+          <t>2026-08-28 01:12:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22205</v>
+        <v>22214</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:00</t>
+          <t>2026-08-28 01:12:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6586347</v>
+        <v>4.656525</v>
       </c>
       <c r="G14" t="n">
-        <v>13519</v>
+        <v>13524</v>
       </c>
       <c r="H14" t="n">
         <v>5027</v>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1274283</v>
+        <v>1275208</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="O14" t="n">
         <v>96</v>
@@ -1475,7 +1475,7 @@
         <v>194</v>
       </c>
       <c r="R14" t="n">
-        <v>12150</v>
+        <v>12148</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:00</t>
+          <t>2026-08-28 01:12:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.384393</v>
+        <v>3.389049</v>
       </c>
       <c r="G15" t="n">
-        <v>3921</v>
+        <v>3922</v>
       </c>
       <c r="H15" t="n">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>407083</v>
+        <v>407407</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,23 +1533,23 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="O15" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P15" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q15" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R15" t="n">
-        <v>2152</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 18:32:00</t>
+          <t>2026-08-28 01:12:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6962028</v>
+        <v>4.694737</v>
       </c>
       <c r="G16" t="n">
-        <v>46734</v>
+        <v>46742</v>
       </c>
       <c r="H16" t="n">
         <v>2987</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>583147</v>
+        <v>583716</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,23 +1607,23 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 27, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2310</v>
+        <v>2317</v>
       </c>
       <c r="O16" t="n">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="P16" t="n">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="Q16" t="n">
-        <v>2332</v>
+        <v>2328</v>
       </c>
       <c r="R16" t="n">
-        <v>40971</v>
+        <v>40957</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:50</t>
+          <t>2026-08-29 00:46:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:51</t>
+          <t>2026-08-29 00:46:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.434215</v>
+        <v>4.430076</v>
       </c>
       <c r="G3" t="n">
-        <v>30921</v>
+        <v>30924</v>
       </c>
       <c r="H3" t="n">
         <v>9180</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3843</v>
+        <v>3875</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
@@ -662,10 +662,10 @@
         <v>268</v>
       </c>
       <c r="Q3" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25854</v>
+        <v>25824</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:51</t>
+          <t>2026-08-29 00:47:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6067488</v>
+        <v>3.6076524</v>
       </c>
       <c r="G4" t="n">
-        <v>25063</v>
+        <v>25070</v>
       </c>
       <c r="H4" t="n">
         <v>5603</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7317</v>
+        <v>7316</v>
       </c>
       <c r="O4" t="n">
         <v>860</v>
       </c>
       <c r="P4" t="n">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="Q4" t="n">
         <v>1267</v>
       </c>
       <c r="R4" t="n">
-        <v>14718</v>
+        <v>14729</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:52</t>
+          <t>2026-08-29 00:47:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5363903</v>
+        <v>4.5406656</v>
       </c>
       <c r="G5" t="n">
-        <v>26577</v>
+        <v>26590</v>
       </c>
       <c r="H5" t="n">
-        <v>9900</v>
+        <v>9903</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1967</v>
+        <v>1949</v>
       </c>
       <c r="O5" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P5" t="n">
-        <v>838</v>
+        <v>816</v>
       </c>
       <c r="Q5" t="n">
-        <v>1832</v>
+        <v>1837</v>
       </c>
       <c r="R5" t="n">
-        <v>21623</v>
+        <v>21670</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:52</t>
+          <t>2026-08-29 00:47:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111772</v>
+        <v>111861</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:52</t>
+          <t>2026-08-29 00:47:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -920,7 +920,7 @@
         <v>4.3636365</v>
       </c>
       <c r="G7" t="n">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="H7" t="n">
         <v>1160</v>
@@ -961,7 +961,7 @@
         <v>94</v>
       </c>
       <c r="R7" t="n">
-        <v>2499</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:53</t>
+          <t>2026-08-29 00:47:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:53</t>
+          <t>2026-08-29 00:47:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:54</t>
+          <t>2026-08-29 00:47:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:54</t>
+          <t>2026-08-29 00:47:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6779532</v>
+        <v>4.6791606</v>
       </c>
       <c r="G11" t="n">
-        <v>14997</v>
+        <v>15002</v>
       </c>
       <c r="H11" t="n">
         <v>702</v>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="O11" t="n">
         <v>111</v>
@@ -1254,10 +1254,10 @@
         <v>269</v>
       </c>
       <c r="Q11" t="n">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="R11" t="n">
-        <v>12999</v>
+        <v>13011</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:55</t>
+          <t>2026-08-29 00:47:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.761658</v>
+        <v>2.7571058</v>
       </c>
       <c r="G12" t="n">
-        <v>4719</v>
+        <v>4722</v>
       </c>
       <c r="H12" t="n">
         <v>1957</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2383</v>
+        <v>2390</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1784</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:55</t>
+          <t>2026-08-29 00:47:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:56</t>
+          <t>2026-08-29 00:47:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.656525</v>
+        <v>4.657348</v>
       </c>
       <c r="G14" t="n">
-        <v>13524</v>
+        <v>13527</v>
       </c>
       <c r="H14" t="n">
         <v>5027</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="O14" t="n">
         <v>96</v>
@@ -1472,10 +1472,10 @@
         <v>85</v>
       </c>
       <c r="Q14" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R14" t="n">
-        <v>12148</v>
+        <v>12154</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:56</t>
+          <t>2026-08-29 00:47:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.389049</v>
+        <v>3.3901734</v>
       </c>
       <c r="G15" t="n">
-        <v>3922</v>
+        <v>3924</v>
       </c>
       <c r="H15" t="n">
         <v>1586</v>
@@ -1533,23 +1533,23 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="O15" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P15" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="Q15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2157</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 01:12:56</t>
+          <t>2026-08-29 00:47:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.694737</v>
+        <v>4.693873</v>
       </c>
       <c r="G16" t="n">
         <v>46742</v>
       </c>
       <c r="H16" t="n">
-        <v>2987</v>
+        <v>2988</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2317</v>
+        <v>2327</v>
       </c>
       <c r="O16" t="n">
         <v>392</v>
@@ -1620,10 +1620,10 @@
         <v>742</v>
       </c>
       <c r="Q16" t="n">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="R16" t="n">
-        <v>40957</v>
+        <v>40947</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-29 00:46:59</t>
+          <t>2026-08-29 19:33:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-29 00:46:59</t>
+          <t>2026-08-29 19:33:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.430076</v>
+        <v>4.429038</v>
       </c>
       <c r="G3" t="n">
         <v>30924</v>
       </c>
       <c r="H3" t="n">
-        <v>9180</v>
+        <v>9181</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3875</v>
+        <v>3883</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
@@ -665,7 +665,7 @@
         <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25824</v>
+        <v>25816</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:00</t>
+          <t>2026-08-29 19:33:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6076524</v>
+        <v>3.6086957</v>
       </c>
       <c r="G4" t="n">
-        <v>25070</v>
+        <v>25076</v>
       </c>
       <c r="H4" t="n">
-        <v>5603</v>
+        <v>5604</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7316</v>
+        <v>7304</v>
       </c>
       <c r="O4" t="n">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="P4" t="n">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="Q4" t="n">
-        <v>1267</v>
+        <v>1285</v>
       </c>
       <c r="R4" t="n">
-        <v>14729</v>
+        <v>14725</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:00</t>
+          <t>2026-08-29 19:33:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5406656</v>
+        <v>4.5397224</v>
       </c>
       <c r="G5" t="n">
-        <v>26590</v>
+        <v>26595</v>
       </c>
       <c r="H5" t="n">
-        <v>9903</v>
+        <v>9904</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1949</v>
+        <v>1944</v>
       </c>
       <c r="O5" t="n">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="P5" t="n">
-        <v>816</v>
+        <v>838</v>
       </c>
       <c r="Q5" t="n">
-        <v>1837</v>
+        <v>1843</v>
       </c>
       <c r="R5" t="n">
-        <v>21670</v>
+        <v>21652</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:00</t>
+          <t>2026-08-29 19:33:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:00</t>
+          <t>2026-08-29 19:33:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3636365</v>
+        <v>4.3348417</v>
       </c>
       <c r="G7" t="n">
-        <v>3139</v>
+        <v>3140</v>
       </c>
       <c r="H7" t="n">
         <v>1160</v>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="O7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P7" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="Q7" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="R7" t="n">
-        <v>2500</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:01</t>
+          <t>2026-08-29 19:33:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.163904</v>
+        <v>4.158088</v>
       </c>
       <c r="G8" t="n">
-        <v>6088</v>
+        <v>6089</v>
       </c>
       <c r="H8" t="n">
         <v>2258</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>996</v>
+        <v>1006</v>
       </c>
       <c r="O8" t="n">
         <v>156</v>
@@ -1035,7 +1035,7 @@
         <v>245</v>
       </c>
       <c r="R8" t="n">
-        <v>4494</v>
+        <v>4488</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:01</t>
+          <t>2026-08-29 19:33:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:01</t>
+          <t>2026-08-29 19:33:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:01</t>
+          <t>2026-08-29 19:33:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:02</t>
+          <t>2026-08-29 19:33:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:02</t>
+          <t>2026-08-29 19:33:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:02</t>
+          <t>2026-08-29 19:33:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.657348</v>
+        <v>4.6552277</v>
       </c>
       <c r="G14" t="n">
-        <v>13527</v>
+        <v>13528</v>
       </c>
       <c r="H14" t="n">
-        <v>5027</v>
+        <v>5028</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="O14" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="P14" t="n">
         <v>85</v>
@@ -1475,7 +1475,7 @@
         <v>193</v>
       </c>
       <c r="R14" t="n">
-        <v>12154</v>
+        <v>12145</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:02</t>
+          <t>2026-08-29 19:33:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-29 00:47:02</t>
+          <t>2026-08-29 19:33:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.693873</v>
+        <v>4.694016</v>
       </c>
       <c r="G16" t="n">
         <v>46742</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="O16" t="n">
         <v>392</v>
@@ -1620,10 +1620,10 @@
         <v>742</v>
       </c>
       <c r="Q16" t="n">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="R16" t="n">
-        <v>40947</v>
+        <v>40950</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:29</t>
+          <t>2026-08-30 19:32:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40306</v>
+        <v>40401</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:29</t>
+          <t>2026-08-30 19:32:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.429038</v>
+        <v>4.4254546</v>
       </c>
       <c r="G3" t="n">
-        <v>30924</v>
+        <v>30929</v>
       </c>
       <c r="H3" t="n">
-        <v>9181</v>
+        <v>9182</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2412505</v>
+        <v>2415272</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 25, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3883</v>
+        <v>3913</v>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P3" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q3" t="n">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="R3" t="n">
-        <v>25816</v>
+        <v>25800</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:29</t>
+          <t>2026-08-30 19:32:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,10 +698,10 @@
         <v>3.6086957</v>
       </c>
       <c r="G4" t="n">
-        <v>25076</v>
+        <v>25077</v>
       </c>
       <c r="H4" t="n">
-        <v>5604</v>
+        <v>5603</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2619058</v>
+        <v>2621324</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7304</v>
+        <v>7305</v>
       </c>
       <c r="O4" t="n">
         <v>862</v>
@@ -739,7 +739,7 @@
         <v>1285</v>
       </c>
       <c r="R4" t="n">
-        <v>14725</v>
+        <v>14726</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:29</t>
+          <t>2026-08-30 19:32:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5397224</v>
+        <v>4.5381694</v>
       </c>
       <c r="G5" t="n">
-        <v>26595</v>
+        <v>26600</v>
       </c>
       <c r="H5" t="n">
-        <v>9904</v>
+        <v>9910</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>674893</v>
+        <v>675580</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1944</v>
+        <v>1962</v>
       </c>
       <c r="O5" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P5" t="n">
-        <v>838</v>
+        <v>829</v>
       </c>
       <c r="Q5" t="n">
-        <v>1843</v>
+        <v>1828</v>
       </c>
       <c r="R5" t="n">
-        <v>21652</v>
+        <v>21663</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:30</t>
+          <t>2026-08-30 19:32:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111861</v>
+        <v>111894</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:30</t>
+          <t>2026-08-30 19:32:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>454137</v>
+        <v>455264</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:30</t>
+          <t>2026-08-30 19:32:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -994,10 +994,10 @@
         <v>4.158088</v>
       </c>
       <c r="G8" t="n">
-        <v>6089</v>
+        <v>6087</v>
       </c>
       <c r="H8" t="n">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1005,11 +1005,11 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>457667</v>
+        <v>458201</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.1.27</t>
+          <t>2.1.28</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1019,11 +1019,11 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Aug 26, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="O8" t="n">
         <v>156</v>
@@ -1035,7 +1035,7 @@
         <v>245</v>
       </c>
       <c r="R8" t="n">
-        <v>4488</v>
+        <v>4486</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:30</t>
+          <t>2026-08-30 19:32:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1068,10 +1068,10 @@
         <v>3.9818182</v>
       </c>
       <c r="G9" t="n">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H9" t="n">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,11 +1079,11 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>181534</v>
+        <v>181804</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.7.15GMS</t>
+          <t>1.8.0GMS</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Aug 27, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1109,7 +1109,7 @@
         <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:30</t>
+          <t>2026-08-30 19:32:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>94207</v>
+        <v>94433</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:31</t>
+          <t>2026-08-30 19:32:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>274237</v>
+        <v>274410</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:31</t>
+          <t>2026-08-30 19:32:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1290,7 +1290,7 @@
         <v>2.7571058</v>
       </c>
       <c r="G12" t="n">
-        <v>4722</v>
+        <v>4723</v>
       </c>
       <c r="H12" t="n">
         <v>1957</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>357466</v>
+        <v>357741</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:31</t>
+          <t>2026-08-30 19:32:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22214</v>
+        <v>22238</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:31</t>
+          <t>2026-08-30 19:32:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6552277</v>
+        <v>4.65259</v>
       </c>
       <c r="G14" t="n">
-        <v>13528</v>
+        <v>13529</v>
       </c>
       <c r="H14" t="n">
         <v>5028</v>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1275208</v>
+        <v>1276892</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>992</v>
+        <v>1002</v>
       </c>
       <c r="O14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P14" t="n">
         <v>85</v>
@@ -1475,7 +1475,7 @@
         <v>193</v>
       </c>
       <c r="R14" t="n">
-        <v>12145</v>
+        <v>12138</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:31</t>
+          <t>2026-08-30 19:32:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1508,7 +1508,7 @@
         <v>3.3901734</v>
       </c>
       <c r="G15" t="n">
-        <v>3924</v>
+        <v>3925</v>
       </c>
       <c r="H15" t="n">
         <v>1586</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>407407</v>
+        <v>408024</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,11 +1533,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="O15" t="n">
         <v>135</v>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-29 19:33:32</t>
+          <t>2026-08-30 19:32:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.694016</v>
+        <v>4.694717</v>
       </c>
       <c r="G16" t="n">
         <v>46742</v>
       </c>
       <c r="H16" t="n">
-        <v>2988</v>
+        <v>2990</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>583716</v>
+        <v>584952</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>2326</v>
       </c>
       <c r="O16" t="n">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="P16" t="n">
         <v>742</v>
@@ -1623,7 +1623,7 @@
         <v>2326</v>
       </c>
       <c r="R16" t="n">
-        <v>40950</v>
+        <v>40961</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:30</t>
+          <t>2026-08-31 21:41:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40401</v>
+        <v>40513</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:30</t>
+          <t>2026-08-31 21:41:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4254546</v>
+        <v>4.428779</v>
       </c>
       <c r="G3" t="n">
-        <v>30929</v>
+        <v>30935</v>
       </c>
       <c r="H3" t="n">
-        <v>9182</v>
+        <v>9185</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2415272</v>
+        <v>2416165</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3913</v>
+        <v>3888</v>
       </c>
       <c r="O3" t="n">
         <v>314</v>
@@ -665,7 +665,7 @@
         <v>629</v>
       </c>
       <c r="R3" t="n">
-        <v>25800</v>
+        <v>25830</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:30</t>
+          <t>2026-08-31 21:41:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6086957</v>
+        <v>3.609456</v>
       </c>
       <c r="G4" t="n">
-        <v>25077</v>
+        <v>25085</v>
       </c>
       <c r="H4" t="n">
-        <v>5603</v>
+        <v>5606</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2621324</v>
+        <v>2622092</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7305</v>
+        <v>7293</v>
       </c>
       <c r="O4" t="n">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="P4" t="n">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="Q4" t="n">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="R4" t="n">
-        <v>14726</v>
+        <v>14735</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:30</t>
+          <t>2026-08-31 21:41:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5381694</v>
+        <v>4.538753</v>
       </c>
       <c r="G5" t="n">
-        <v>26600</v>
+        <v>26617</v>
       </c>
       <c r="H5" t="n">
-        <v>9910</v>
+        <v>9915</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>675580</v>
+        <v>676436</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="O5" t="n">
         <v>313</v>
@@ -810,10 +810,10 @@
         <v>829</v>
       </c>
       <c r="Q5" t="n">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="R5" t="n">
-        <v>21663</v>
+        <v>21683</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:31</t>
+          <t>2026-08-31 21:41:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111894</v>
+        <v>111931</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:31</t>
+          <t>2026-08-31 21:41:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -920,7 +920,7 @@
         <v>4.3348417</v>
       </c>
       <c r="G7" t="n">
-        <v>3140</v>
+        <v>3142</v>
       </c>
       <c r="H7" t="n">
         <v>1160</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>455264</v>
+        <v>456038</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P7" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q7" t="n">
         <v>98</v>
       </c>
       <c r="R7" t="n">
-        <v>2471</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:31</t>
+          <t>2026-08-31 21:41:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.158088</v>
+        <v>4.159341</v>
       </c>
       <c r="G8" t="n">
-        <v>6087</v>
+        <v>6098</v>
       </c>
       <c r="H8" t="n">
         <v>2260</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>458201</v>
+        <v>458376</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="O8" t="n">
         <v>156</v>
@@ -1032,10 +1032,10 @@
         <v>189</v>
       </c>
       <c r="Q8" t="n">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="R8" t="n">
-        <v>4486</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:31</t>
+          <t>2026-08-31 21:41:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.9818182</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>1232</v>
+        <v>1245</v>
       </c>
       <c r="H9" t="n">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,11 +1079,11 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>181804</v>
+        <v>181898</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.8.0GMS</t>
+          <t>1.8.1GMS</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1093,23 +1093,23 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Aug 27, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="O9" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="P9" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>861</v>
+        <v>867</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:31</t>
+          <t>2026-08-31 21:41:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>94433</v>
+        <v>94797</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:32</t>
+          <t>2026-08-31 21:41:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>274410</v>
+        <v>274632</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:32</t>
+          <t>2026-08-31 21:41:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>357741</v>
+        <v>357994</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:32</t>
+          <t>2026-08-31 21:41:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22238</v>
+        <v>22260</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:32</t>
+          <t>2026-08-31 21:41:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.65259</v>
+        <v>4.6505165</v>
       </c>
       <c r="G14" t="n">
-        <v>13529</v>
+        <v>13533</v>
       </c>
       <c r="H14" t="n">
-        <v>5028</v>
+        <v>5029</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1276892</v>
+        <v>1278666</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="O14" t="n">
         <v>106</v>
@@ -1472,10 +1472,10 @@
         <v>85</v>
       </c>
       <c r="Q14" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R14" t="n">
-        <v>12138</v>
+        <v>12135</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:33</t>
+          <t>2026-08-31 21:41:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>408024</v>
+        <v>408696</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-30 19:32:33</t>
+          <t>2026-08-31 21:41:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.694717</v>
+        <v>4.6939254</v>
       </c>
       <c r="G16" t="n">
-        <v>46742</v>
+        <v>46744</v>
       </c>
       <c r="H16" t="n">
-        <v>2990</v>
+        <v>2992</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>584952</v>
+        <v>586092</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2326</v>
+        <v>2336</v>
       </c>
       <c r="O16" t="n">
         <v>381</v>
       </c>
       <c r="P16" t="n">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="Q16" t="n">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="R16" t="n">
-        <v>40961</v>
+        <v>40954</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:08</t>
+          <t>2026-09-01 19:40:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.05</v>
+        <v>4.059406</v>
       </c>
       <c r="G2" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2" t="n">
         <v>178</v>
@@ -579,19 +579,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q2" t="n">
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:08</t>
+          <t>2026-09-01 19:40:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.428779</v>
+        <v>4.428157</v>
       </c>
       <c r="G3" t="n">
-        <v>30935</v>
+        <v>30940</v>
       </c>
       <c r="H3" t="n">
-        <v>9185</v>
+        <v>9193</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2416165</v>
+        <v>2416856</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3888</v>
+        <v>3895</v>
       </c>
       <c r="O3" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P3" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q3" t="n">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="R3" t="n">
-        <v>25830</v>
+        <v>25831</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:08</t>
+          <t>2026-09-01 19:40:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.609456</v>
+        <v>3.6050584</v>
       </c>
       <c r="G4" t="n">
-        <v>25085</v>
+        <v>25091</v>
       </c>
       <c r="H4" t="n">
         <v>5606</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2622092</v>
+        <v>2622586</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7293</v>
+        <v>7322</v>
       </c>
       <c r="O4" t="n">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="P4" t="n">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="Q4" t="n">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="R4" t="n">
-        <v>14735</v>
+        <v>14709</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:08</t>
+          <t>2026-09-01 19:40:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.538753</v>
+        <v>4.5379105</v>
       </c>
       <c r="G5" t="n">
-        <v>26617</v>
+        <v>26629</v>
       </c>
       <c r="H5" t="n">
-        <v>9915</v>
+        <v>9917</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1961</v>
+        <v>1973</v>
       </c>
       <c r="O5" t="n">
         <v>313</v>
@@ -810,10 +810,10 @@
         <v>829</v>
       </c>
       <c r="Q5" t="n">
-        <v>1826</v>
+        <v>1805</v>
       </c>
       <c r="R5" t="n">
-        <v>21683</v>
+        <v>21704</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:08</t>
+          <t>2026-09-01 19:40:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:08</t>
+          <t>2026-09-01 19:40:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:09</t>
+          <t>2026-09-01 19:40:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>458376</v>
+        <v>458489</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:09</t>
+          <t>2026-09-01 19:40:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3.6666667</v>
       </c>
       <c r="G9" t="n">
-        <v>1245</v>
+        <v>1264</v>
       </c>
       <c r="H9" t="n">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>251</v>
+        <v>329</v>
       </c>
       <c r="O9" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="P9" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="Q9" t="n">
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>867</v>
+        <v>762</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:09</t>
+          <t>2026-09-01 19:40:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1142,7 +1142,7 @@
         <v>3.9223301</v>
       </c>
       <c r="G10" t="n">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H10" t="n">
         <v>241</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:09</t>
+          <t>2026-09-01 19:40:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1227,11 +1227,11 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>274632</v>
+        <v>274700</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.1.1</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Aug 2, 2026</t>
+          <t>Aug 26, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:09</t>
+          <t>2026-09-01 19:40:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:09</t>
+          <t>2026-09-01 19:40:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:10</t>
+          <t>2026-09-01 19:40:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6505165</v>
+        <v>4.6488853</v>
       </c>
       <c r="G14" t="n">
-        <v>13533</v>
+        <v>13529</v>
       </c>
       <c r="H14" t="n">
-        <v>5029</v>
+        <v>5030</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1278666</v>
+        <v>1279697</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="O14" t="n">
         <v>106</v>
@@ -1472,10 +1472,10 @@
         <v>85</v>
       </c>
       <c r="Q14" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="R14" t="n">
-        <v>12135</v>
+        <v>12117</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:10</t>
+          <t>2026-09-01 19:40:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 21:41:10</t>
+          <t>2026-09-01 19:40:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6939254</v>
+        <v>4.6933675</v>
       </c>
       <c r="G16" t="n">
-        <v>46744</v>
+        <v>46745</v>
       </c>
       <c r="H16" t="n">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="O16" t="n">
         <v>381</v>
       </c>
       <c r="P16" t="n">
-        <v>741</v>
+        <v>752</v>
       </c>
       <c r="Q16" t="n">
-        <v>2325</v>
+        <v>2335</v>
       </c>
       <c r="R16" t="n">
-        <v>40954</v>
+        <v>40937</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:41</t>
+          <t>2026-09-02 19:32:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40513</v>
+        <v>40539</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:41</t>
+          <t>2026-09-02 19:32:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.428157</v>
+        <v>4.425154</v>
       </c>
       <c r="G3" t="n">
-        <v>30940</v>
+        <v>30955</v>
       </c>
       <c r="H3" t="n">
-        <v>9193</v>
+        <v>9196</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2416856</v>
+        <v>2418429</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3895</v>
+        <v>3915</v>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="P3" t="n">
         <v>268</v>
       </c>
       <c r="Q3" t="n">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="R3" t="n">
-        <v>25831</v>
+        <v>25827</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:41</t>
+          <t>2026-09-02 19:32:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,10 +698,10 @@
         <v>3.6050584</v>
       </c>
       <c r="G4" t="n">
-        <v>25091</v>
+        <v>25094</v>
       </c>
       <c r="H4" t="n">
-        <v>5606</v>
+        <v>5607</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2622586</v>
+        <v>2623968</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7322</v>
+        <v>7323</v>
       </c>
       <c r="O4" t="n">
         <v>878</v>
       </c>
       <c r="P4" t="n">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="Q4" t="n">
         <v>1285</v>
       </c>
       <c r="R4" t="n">
-        <v>14709</v>
+        <v>14711</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:41</t>
+          <t>2026-09-02 19:32:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5379105</v>
+        <v>4.537783</v>
       </c>
       <c r="G5" t="n">
-        <v>26629</v>
+        <v>26638</v>
       </c>
       <c r="H5" t="n">
-        <v>9917</v>
+        <v>9922</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,11 +783,11 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>676436</v>
+        <v>677233</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>397.0</t>
+          <t>399.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -797,23 +797,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Jul 27, 2026</t>
+          <t>Aug 27, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1973</v>
+        <v>1979</v>
       </c>
       <c r="O5" t="n">
         <v>313</v>
       </c>
       <c r="P5" t="n">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="Q5" t="n">
-        <v>1805</v>
+        <v>1799</v>
       </c>
       <c r="R5" t="n">
-        <v>21704</v>
+        <v>21716</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:41</t>
+          <t>2026-09-02 19:32:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,10 +846,10 @@
         <v>3.64</v>
       </c>
       <c r="G6" t="n">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H6" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -857,11 +857,11 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>111931</v>
+        <v>112033</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -871,11 +871,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 2, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:42</t>
+          <t>2026-09-02 19:32:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3348417</v>
+        <v>4.316742</v>
       </c>
       <c r="G7" t="n">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="H7" t="n">
         <v>1160</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>456038</v>
+        <v>456329</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="O7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P7" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q7" t="n">
         <v>98</v>
       </c>
       <c r="R7" t="n">
-        <v>2473</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:42</t>
+          <t>2026-09-02 19:32:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1005,11 +1005,11 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>458489</v>
+        <v>458759</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.1.28</t>
+          <t>2.1.29</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Aug 26, 2026</t>
+          <t>Sep 1, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:42</t>
+          <t>2026-09-02 19:32:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6666667</v>
+        <v>3.7117116</v>
       </c>
       <c r="G9" t="n">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="H9" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>181898</v>
+        <v>181954</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="O9" t="n">
+        <v>68</v>
+      </c>
+      <c r="P9" t="n">
         <v>56</v>
-      </c>
-      <c r="P9" t="n">
-        <v>79</v>
       </c>
       <c r="Q9" t="n">
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>762</v>
+        <v>787</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:42</t>
+          <t>2026-09-02 19:32:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>94797</v>
+        <v>94873</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:42</t>
+          <t>2026-09-02 19:32:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6791606</v>
+        <v>4.67892</v>
       </c>
       <c r="G11" t="n">
         <v>15002</v>
@@ -1257,7 +1257,7 @@
         <v>831</v>
       </c>
       <c r="R11" t="n">
-        <v>13011</v>
+        <v>13009</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:43</t>
+          <t>2026-09-02 19:32:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1293,7 +1293,7 @@
         <v>4723</v>
       </c>
       <c r="H12" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>357994</v>
+        <v>358043</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:43</t>
+          <t>2026-09-02 19:32:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22260</v>
+        <v>22264</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:43</t>
+          <t>2026-09-02 19:32:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6488853</v>
+        <v>4.6451354</v>
       </c>
       <c r="G14" t="n">
-        <v>13529</v>
+        <v>13527</v>
       </c>
       <c r="H14" t="n">
-        <v>5030</v>
+        <v>5032</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1279697</v>
+        <v>1280597</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1012</v>
+        <v>1024</v>
       </c>
       <c r="O14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P14" t="n">
         <v>85</v>
@@ -1475,7 +1475,7 @@
         <v>204</v>
       </c>
       <c r="R14" t="n">
-        <v>12117</v>
+        <v>12103</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:43</t>
+          <t>2026-09-02 19:32:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3901734</v>
+        <v>3.3948126</v>
       </c>
       <c r="G15" t="n">
-        <v>3925</v>
+        <v>3926</v>
       </c>
       <c r="H15" t="n">
         <v>1586</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>408696</v>
+        <v>408875</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="O15" t="n">
         <v>135</v>
@@ -1549,7 +1549,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2165</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 19:40:43</t>
+          <t>2026-09-02 19:32:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6933675</v>
+        <v>4.693439</v>
       </c>
       <c r="G16" t="n">
-        <v>46745</v>
+        <v>46744</v>
       </c>
       <c r="H16" t="n">
-        <v>2991</v>
+        <v>2994</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>586092</v>
+        <v>586400</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:40</t>
+          <t>2026-09-03 19:29:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40539</v>
+        <v>40602</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:40</t>
+          <t>2026-09-03 19:29:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.425154</v>
+        <v>4.4235377</v>
       </c>
       <c r="G3" t="n">
-        <v>30955</v>
+        <v>30963</v>
       </c>
       <c r="H3" t="n">
         <v>9196</v>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2418429</v>
+        <v>2418447</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.45.0</t>
+          <t>4.45.1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3915</v>
+        <v>3924</v>
       </c>
       <c r="O3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P3" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q3" t="n">
-        <v>616</v>
+        <v>629</v>
       </c>
       <c r="R3" t="n">
-        <v>25827</v>
+        <v>25811</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:41</t>
+          <t>2026-09-03 19:29:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6050584</v>
+        <v>3.6080468</v>
       </c>
       <c r="G4" t="n">
-        <v>25094</v>
+        <v>25093</v>
       </c>
       <c r="H4" t="n">
         <v>5607</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7323</v>
+        <v>7310</v>
       </c>
       <c r="O4" t="n">
         <v>878</v>
       </c>
       <c r="P4" t="n">
-        <v>895</v>
+        <v>878</v>
       </c>
       <c r="Q4" t="n">
         <v>1285</v>
       </c>
       <c r="R4" t="n">
-        <v>14711</v>
+        <v>14736</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:41</t>
+          <t>2026-09-03 19:29:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.537783</v>
+        <v>4.536842</v>
       </c>
       <c r="G5" t="n">
-        <v>26638</v>
+        <v>26643</v>
       </c>
       <c r="H5" t="n">
-        <v>9922</v>
+        <v>9926</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1979</v>
+        <v>1984</v>
       </c>
       <c r="O5" t="n">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>826</v>
+        <v>840</v>
       </c>
       <c r="Q5" t="n">
-        <v>1799</v>
+        <v>1805</v>
       </c>
       <c r="R5" t="n">
-        <v>21716</v>
+        <v>21705</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:41</t>
+          <t>2026-09-03 19:29:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.64</v>
+        <v>3.71</v>
       </c>
       <c r="G6" t="n">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="H6" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -884,10 +884,10 @@
         <v>22</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="R6" t="n">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:41</t>
+          <t>2026-09-03 19:29:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:41</t>
+          <t>2026-09-03 19:29:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -997,7 +997,7 @@
         <v>6098</v>
       </c>
       <c r="H8" t="n">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:41</t>
+          <t>2026-09-03 19:29:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.7117116</v>
+        <v>3.7232144</v>
       </c>
       <c r="G9" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="H9" t="n">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>181954</v>
+        <v>182236</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>787</v>
+        <v>795</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:42</t>
+          <t>2026-09-03 19:29:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1142,7 +1142,7 @@
         <v>3.9223301</v>
       </c>
       <c r="G10" t="n">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H10" t="n">
         <v>241</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>94873</v>
+        <v>95043</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:42</t>
+          <t>2026-09-03 19:29:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1219,7 +1219,7 @@
         <v>15002</v>
       </c>
       <c r="H11" t="n">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>274700</v>
+        <v>274872</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:42</t>
+          <t>2026-09-03 19:29:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7571058</v>
+        <v>2.7525773</v>
       </c>
       <c r="G12" t="n">
-        <v>4723</v>
+        <v>4724</v>
       </c>
       <c r="H12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>358043</v>
+        <v>358227</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2391</v>
+        <v>2397</v>
       </c>
       <c r="O12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P12" t="n">
         <v>206</v>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1781</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:42</t>
+          <t>2026-09-03 19:29:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22264</v>
+        <v>22278</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:42</t>
+          <t>2026-09-03 19:29:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6451354</v>
+        <v>4.6335454</v>
       </c>
       <c r="G14" t="n">
-        <v>13527</v>
+        <v>13530</v>
       </c>
       <c r="H14" t="n">
-        <v>5032</v>
+        <v>5034</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1024</v>
+        <v>1064</v>
       </c>
       <c r="O14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P14" t="n">
         <v>85</v>
       </c>
       <c r="Q14" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R14" t="n">
-        <v>12103</v>
+        <v>12066</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:43</t>
+          <t>2026-09-03 19:29:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>408875</v>
+        <v>409393</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 19:32:43</t>
+          <t>2026-09-03 19:29:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.693439</v>
+        <v>4.6927204</v>
       </c>
       <c r="G16" t="n">
-        <v>46744</v>
+        <v>46746</v>
       </c>
       <c r="H16" t="n">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>586400</v>
+        <v>587217</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2335</v>
+        <v>2344</v>
       </c>
       <c r="O16" t="n">
         <v>381</v>
       </c>
       <c r="P16" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="Q16" t="n">
-        <v>2335</v>
+        <v>2332</v>
       </c>
       <c r="R16" t="n">
-        <v>40937</v>
+        <v>40932</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:49</t>
+          <t>2026-09-04 19:39:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,7 +553,7 @@
         <v>412</v>
       </c>
       <c r="H2" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40602</v>
+        <v>40603</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:49</t>
+          <t>2026-09-04 19:39:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4235377</v>
+        <v>4.422311</v>
       </c>
       <c r="G3" t="n">
-        <v>30963</v>
+        <v>30971</v>
       </c>
       <c r="H3" t="n">
-        <v>9196</v>
+        <v>9198</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3924</v>
+        <v>3936</v>
       </c>
       <c r="O3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P3" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q3" t="n">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="R3" t="n">
-        <v>25811</v>
+        <v>25810</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:49</t>
+          <t>2026-09-04 19:39:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6080468</v>
+        <v>3.609851</v>
       </c>
       <c r="G4" t="n">
-        <v>25093</v>
+        <v>25098</v>
       </c>
       <c r="H4" t="n">
         <v>5607</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2623968</v>
+        <v>2623981</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7310</v>
+        <v>7301</v>
       </c>
       <c r="O4" t="n">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="P4" t="n">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="Q4" t="n">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="R4" t="n">
-        <v>14736</v>
+        <v>14751</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:49</t>
+          <t>2026-09-04 19:39:14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.536842</v>
+        <v>4.5359397</v>
       </c>
       <c r="G5" t="n">
-        <v>26643</v>
+        <v>26646</v>
       </c>
       <c r="H5" t="n">
-        <v>9926</v>
+        <v>9928</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1984</v>
+        <v>1992</v>
       </c>
       <c r="O5" t="n">
         <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q5" t="n">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="R5" t="n">
         <v>21705</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:49</t>
+          <t>2026-09-04 19:39:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="G6" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H6" t="n">
         <v>166</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>112033</v>
+        <v>112034</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -887,7 +887,7 @@
         <v>27</v>
       </c>
       <c r="R6" t="n">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:50</t>
+          <t>2026-09-04 19:39:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>456329</v>
+        <v>456331</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:50</t>
+          <t>2026-09-04 19:39:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.159341</v>
+        <v>4.154412</v>
       </c>
       <c r="G8" t="n">
-        <v>6098</v>
+        <v>6100</v>
       </c>
       <c r="H8" t="n">
         <v>2261</v>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1004</v>
+        <v>1019</v>
       </c>
       <c r="O8" t="n">
         <v>156</v>
       </c>
       <c r="P8" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="R8" t="n">
-        <v>4489</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:50</t>
+          <t>2026-09-04 19:39:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.7232144</v>
+        <v>3.7589285</v>
       </c>
       <c r="G9" t="n">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="H9" t="n">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="O9" t="n">
         <v>68</v>
@@ -1109,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>795</v>
+        <v>808</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:50</t>
+          <t>2026-09-04 19:39:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:51</t>
+          <t>2026-09-04 19:39:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.67892</v>
+        <v>4.6781697</v>
       </c>
       <c r="G11" t="n">
-        <v>15002</v>
+        <v>15003</v>
       </c>
       <c r="H11" t="n">
         <v>703</v>
@@ -1254,10 +1254,10 @@
         <v>269</v>
       </c>
       <c r="Q11" t="n">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="R11" t="n">
-        <v>13009</v>
+        <v>12999</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:51</t>
+          <t>2026-09-04 19:39:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7525773</v>
+        <v>2.7467701</v>
       </c>
       <c r="G12" t="n">
         <v>4724</v>
       </c>
       <c r="H12" t="n">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2397</v>
+        <v>2403</v>
       </c>
       <c r="O12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P12" t="n">
         <v>206</v>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1776</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:51</t>
+          <t>2026-09-04 19:39:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:51</t>
+          <t>2026-09-04 19:39:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6335454</v>
+        <v>4.631746</v>
       </c>
       <c r="G14" t="n">
-        <v>13530</v>
+        <v>13532</v>
       </c>
       <c r="H14" t="n">
-        <v>5034</v>
+        <v>5035</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="O14" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="P14" t="n">
         <v>85</v>
@@ -1475,7 +1475,7 @@
         <v>203</v>
       </c>
       <c r="R14" t="n">
-        <v>12066</v>
+        <v>12059</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:52</t>
+          <t>2026-09-04 19:39:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 19:29:52</t>
+          <t>2026-09-04 19:39:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6927204</v>
+        <v>4.691931</v>
       </c>
       <c r="G16" t="n">
-        <v>46746</v>
+        <v>46749</v>
       </c>
       <c r="H16" t="n">
-        <v>2993</v>
+        <v>2994</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2344</v>
+        <v>2354</v>
       </c>
       <c r="O16" t="n">
         <v>381</v>
@@ -1620,10 +1620,10 @@
         <v>751</v>
       </c>
       <c r="Q16" t="n">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="R16" t="n">
-        <v>40932</v>
+        <v>40926</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:14</t>
+          <t>2026-09-05 18:38:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.059406</v>
+        <v>4.05</v>
       </c>
       <c r="G2" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2" t="n">
         <v>179</v>
@@ -579,13 +579,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q2" t="n">
         <v>7</v>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:14</t>
+          <t>2026-09-05 18:38:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -624,7 +624,7 @@
         <v>4.422311</v>
       </c>
       <c r="G3" t="n">
-        <v>30971</v>
+        <v>30980</v>
       </c>
       <c r="H3" t="n">
         <v>9198</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="O3" t="n">
         <v>324</v>
@@ -665,7 +665,7 @@
         <v>628</v>
       </c>
       <c r="R3" t="n">
-        <v>25810</v>
+        <v>25817</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:14</t>
+          <t>2026-09-05 18:38:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7301</v>
+        <v>7302</v>
       </c>
       <c r="O4" t="n">
         <v>877</v>
@@ -736,10 +736,10 @@
         <v>877</v>
       </c>
       <c r="Q4" t="n">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="R4" t="n">
-        <v>14751</v>
+        <v>14752</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:14</t>
+          <t>2026-09-05 18:38:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5359397</v>
+        <v>4.5354</v>
       </c>
       <c r="G5" t="n">
-        <v>26646</v>
+        <v>26652</v>
       </c>
       <c r="H5" t="n">
-        <v>9928</v>
+        <v>9929</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1992</v>
+        <v>1998</v>
       </c>
       <c r="O5" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P5" t="n">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="Q5" t="n">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="R5" t="n">
-        <v>21705</v>
+        <v>21704</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:15</t>
+          <t>2026-09-05 18:38:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:15</t>
+          <t>2026-09-05 18:38:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -920,7 +920,7 @@
         <v>4.316742</v>
       </c>
       <c r="G7" t="n">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="H7" t="n">
         <v>1160</v>
@@ -961,7 +961,7 @@
         <v>98</v>
       </c>
       <c r="R7" t="n">
-        <v>2458</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:15</t>
+          <t>2026-09-05 18:38:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.154412</v>
+        <v>4.160221</v>
       </c>
       <c r="G8" t="n">
-        <v>6100</v>
+        <v>6099</v>
       </c>
       <c r="H8" t="n">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1019</v>
+        <v>1010</v>
       </c>
       <c r="O8" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P8" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="R8" t="n">
-        <v>4495</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:15</t>
+          <t>2026-09-05 18:38:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.7589285</v>
+        <v>3.7410715</v>
       </c>
       <c r="G9" t="n">
         <v>1276</v>
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="O9" t="n">
         <v>68</v>
       </c>
       <c r="P9" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
         <v>34</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:15</t>
+          <t>2026-09-05 18:38:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:16</t>
+          <t>2026-09-05 18:38:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:16</t>
+          <t>2026-09-05 18:38:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:16</t>
+          <t>2026-09-05 18:38:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:16</t>
+          <t>2026-09-05 18:38:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.631746</v>
+        <v>4.6311607</v>
       </c>
       <c r="G14" t="n">
-        <v>13532</v>
+        <v>13530</v>
       </c>
       <c r="H14" t="n">
-        <v>5035</v>
+        <v>5038</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="O14" t="n">
         <v>117</v>
@@ -1475,7 +1475,7 @@
         <v>203</v>
       </c>
       <c r="R14" t="n">
-        <v>12059</v>
+        <v>12055</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:16</t>
+          <t>2026-09-05 18:38:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-04 19:39:17</t>
+          <t>2026-09-05 18:38:23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1582,10 +1582,10 @@
         <v>4.691931</v>
       </c>
       <c r="G16" t="n">
-        <v>46749</v>
+        <v>46747</v>
       </c>
       <c r="H16" t="n">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
         <v>751</v>
       </c>
       <c r="Q16" t="n">
-        <v>2333</v>
+        <v>2331</v>
       </c>
       <c r="R16" t="n">
-        <v>40926</v>
+        <v>40924</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:19</t>
+          <t>2026-09-06 18:41:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:19</t>
+          <t>2026-09-06 18:41:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.422311</v>
+        <v>4.4259324</v>
       </c>
       <c r="G3" t="n">
-        <v>30980</v>
+        <v>30981</v>
       </c>
       <c r="H3" t="n">
-        <v>9198</v>
+        <v>9200</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3937</v>
+        <v>3915</v>
       </c>
       <c r="O3" t="n">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="P3" t="n">
         <v>268</v>
       </c>
       <c r="Q3" t="n">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25817</v>
+        <v>25840</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:19</t>
+          <t>2026-09-06 18:41:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.609851</v>
+        <v>3.6107514</v>
       </c>
       <c r="G4" t="n">
-        <v>25098</v>
+        <v>25101</v>
       </c>
       <c r="H4" t="n">
-        <v>5607</v>
+        <v>5608</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7302</v>
+        <v>7299</v>
       </c>
       <c r="O4" t="n">
         <v>877</v>
@@ -739,7 +739,7 @@
         <v>1284</v>
       </c>
       <c r="R4" t="n">
-        <v>14752</v>
+        <v>14761</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:20</t>
+          <t>2026-09-06 18:41:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5354</v>
+        <v>4.532604</v>
       </c>
       <c r="G5" t="n">
-        <v>26652</v>
+        <v>26655</v>
       </c>
       <c r="H5" t="n">
-        <v>9929</v>
+        <v>9932</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>677233</v>
+        <v>677238</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1998</v>
+        <v>2017</v>
       </c>
       <c r="O5" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="Q5" t="n">
-        <v>1808</v>
+        <v>1794</v>
       </c>
       <c r="R5" t="n">
-        <v>21704</v>
+        <v>21697</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:20</t>
+          <t>2026-09-06 18:41:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:20</t>
+          <t>2026-09-06 18:41:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.316742</v>
+        <v>4.3348417</v>
       </c>
       <c r="G7" t="n">
-        <v>3140</v>
+        <v>3141</v>
       </c>
       <c r="H7" t="n">
         <v>1160</v>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="O7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P7" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q7" t="n">
         <v>98</v>
       </c>
       <c r="R7" t="n">
-        <v>2457</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:21</t>
+          <t>2026-09-06 18:41:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.160221</v>
+        <v>4.1657457</v>
       </c>
       <c r="G8" t="n">
         <v>6099</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>458759</v>
+        <v>458765</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1010</v>
+        <v>999</v>
       </c>
       <c r="O8" t="n">
         <v>157</v>
@@ -1032,7 +1032,7 @@
         <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="R8" t="n">
         <v>4503</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:21</t>
+          <t>2026-09-06 18:41:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1071,7 +1071,7 @@
         <v>1276</v>
       </c>
       <c r="H9" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>182236</v>
+        <v>182238</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O9" t="n">
         <v>68</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:21</t>
+          <t>2026-09-06 18:41:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1145,7 +1145,7 @@
         <v>567</v>
       </c>
       <c r="H10" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:22</t>
+          <t>2026-09-06 18:41:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1216,7 +1216,7 @@
         <v>4.6781697</v>
       </c>
       <c r="G11" t="n">
-        <v>15003</v>
+        <v>15002</v>
       </c>
       <c r="H11" t="n">
         <v>703</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>274872</v>
+        <v>274873</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>843</v>
       </c>
       <c r="R11" t="n">
-        <v>12999</v>
+        <v>12998</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:22</t>
+          <t>2026-09-06 18:41:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:22</t>
+          <t>2026-09-06 18:41:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:23</t>
+          <t>2026-09-06 18:41:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6311607</v>
+        <v>4.6211524</v>
       </c>
       <c r="G14" t="n">
-        <v>13530</v>
+        <v>13539</v>
       </c>
       <c r="H14" t="n">
-        <v>5038</v>
+        <v>5040</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1280597</v>
+        <v>1280610</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1064</v>
+        <v>1100</v>
       </c>
       <c r="O14" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P14" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q14" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="R14" t="n">
-        <v>12055</v>
+        <v>12031</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:23</t>
+          <t>2026-09-06 18:41:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1511,7 +1511,7 @@
         <v>3926</v>
       </c>
       <c r="H15" t="n">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>409393</v>
+        <v>409397</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-05 18:38:23</t>
+          <t>2026-09-06 18:41:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.691931</v>
+        <v>4.691142</v>
       </c>
       <c r="G16" t="n">
-        <v>46747</v>
+        <v>46749</v>
       </c>
       <c r="H16" t="n">
         <v>2995</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2354</v>
+        <v>2364</v>
       </c>
       <c r="O16" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P16" t="n">
         <v>751</v>
@@ -1623,7 +1623,7 @@
         <v>2331</v>
       </c>
       <c r="R16" t="n">
-        <v>40924</v>
+        <v>40918</v>
       </c>
     </row>
   </sheetData>
